--- a/高橋さん用フォルダ/図解.xlsx
+++ b/高橋さん用フォルダ/図解.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\iret_pm\高橋さん用フォルダ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54073A3-74F7-49E3-8832-04A32ABB88C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10810A50-DF9D-44F4-A6F8-6D03803A0070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11110" yWindow="0" windowWidth="11380" windowHeight="13370" xr2:uid="{048F0377-5F86-481C-B78B-CC2C2E2E164F}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="11380" windowHeight="13370" activeTab="1" xr2:uid="{048F0377-5F86-481C-B78B-CC2C2E2E164F}"/>
   </bookViews>
   <sheets>
-    <sheet name="3.5_6.3図解" sheetId="1" r:id="rId1"/>
-    <sheet name="3.6_5図解" sheetId="2" r:id="rId2"/>
-    <sheet name="3.5_6図解" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="8_図解" sheetId="6" r:id="rId1"/>
+    <sheet name="8_1図解" sheetId="7" r:id="rId2"/>
+    <sheet name="3.5_6.3図解" sheetId="1" r:id="rId3"/>
+    <sheet name="3.6_5図解" sheetId="2" r:id="rId4"/>
+    <sheet name="3.5_6図解" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="3" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'3.5_6図解'!$B$1:$AO$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'3.5_6図解'!$B$1:$AO$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="81">
   <si>
     <t>List</t>
     <phoneticPr fontId="1"/>
@@ -373,17 +375,103 @@
     <t xml:space="preserve">  ソフトウェア要件の分析</t>
     <phoneticPr fontId="6"/>
   </si>
+  <si>
+    <t>キーパートナー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーアクティビティ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>与える価値</t>
+    <rPh sb="0" eb="1">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客との関係</t>
+    <rPh sb="0" eb="2">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客</t>
+    <rPh sb="0" eb="2">
+      <t>コキャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーリソース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チャネル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(Key Partners)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(Key Activities)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(Key Resources)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(Value Provided) </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(CustomerRelationships)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(Channels)</t>
+  </si>
+  <si>
+    <t>(Customers)</t>
+  </si>
+  <si>
+    <t>(Costs)</t>
+  </si>
+  <si>
+    <t>(Revenue)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="185" formatCode="m&quot;月&quot;"/>
-    <numFmt numFmtId="186" formatCode="d"/>
-    <numFmt numFmtId="187" formatCode="0\ &quot;日&quot;"/>
+    <numFmt numFmtId="176" formatCode="m&quot;月&quot;"/>
+    <numFmt numFmtId="177" formatCode="d"/>
+    <numFmt numFmtId="178" formatCode="0\ &quot;日&quot;"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -450,6 +538,14 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -489,7 +585,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="61">
+  <borders count="70">
     <border>
       <left/>
       <right/>
@@ -1279,6 +1375,97 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1288,7 +1475,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1373,192 +1560,240 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="57" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="58" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="59" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="55" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1568,89 +1803,72 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="57" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="4" fillId="5" borderId="57" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="185" fontId="4" fillId="5" borderId="58" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="185" fontId="4" fillId="5" borderId="59" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="60" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="59" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="186" fontId="4" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="61" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="60" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="6" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="6" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="1" applyBorder="1">
+    <xf numFmtId="178" fontId="7" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="4" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="14" fontId="7" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="8" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{A7789D78-5A0D-4F38-85E6-F4F2BEF55F8B}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1" tint="0.499984740745262"/>
-        </top>
-        <bottom style="thin">
-          <color theme="1" tint="0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -1687,6 +1905,1315 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{411B3C02-E178-4E30-802E-0C9B1404649A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="736600" y="1600200"/>
+          <a:ext cx="1219200" cy="1206500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>外部に委託 される活動 や、外部か ら調達され るリソース</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="テキスト ボックス 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2747F722-2534-4376-8462-C9B10A4B2A74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2387600" y="806450"/>
+          <a:ext cx="1219200" cy="1263650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>ビジネスモデ ルが機能する よう組織が取 組まなければ ならない活動</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>196850</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="テキスト ボックス 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8AB601E-1176-4D4C-A5BC-2F3906F31550}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2381250" y="2914650"/>
+          <a:ext cx="1219200" cy="1206500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>ここにあげた要 素を提供するの に必要となる資 源</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="テキスト ボックス 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFB47EC3-A58F-4679-9F9D-AA5121BED721}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4057650" y="914400"/>
+          <a:ext cx="1219200" cy="1206500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>顧客の抱え る問題を解 決し、ニー ズを満たす もの </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C948CF7C-4103-4061-A4AF-3B88AA4263B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5676900" y="838200"/>
+          <a:ext cx="1219200" cy="1206500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>顧客との関係性 を構築、維持、展 開するための 様々な仕組み</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="テキスト ボックス 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D075C3DF-8BF4-44A0-BA39-E067521D7091}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5670550" y="2755900"/>
+          <a:ext cx="1219200" cy="1504950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>顧客の求める価値を 提供していることを告 知する方法、その価 値を届ける様々な ルート </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="テキスト ボックス 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A3197CD-A712-4C83-AA81-EEEE4E891CD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7321550" y="920750"/>
+          <a:ext cx="1219200" cy="1206500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>組織が作り出 す価値を届け る相手：人、 他の組織 </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="テキスト ボックス 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{331D0E3D-2D8A-44F4-A3EE-58424B57A384}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1162050" y="4826000"/>
+          <a:ext cx="2940050" cy="825500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>キーリソースを調達し、 キーアクティビティを行ない、 キーパートナーと働くために支払うコスト</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="テキスト ボックス 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7A84816-A41E-4656-B775-ED8D1BDC9BA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5187950" y="4813300"/>
+          <a:ext cx="2940050" cy="825500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>顧客に、与える価値が届けら れる際、支払われるお金 </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F39639E8-2510-4080-8F85-0011A4B259CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="736600" y="1600200"/>
+          <a:ext cx="1219200" cy="1206500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・学生集客の ための近隣小学校</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・地域行政機関 </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="テキスト ボックス 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{132C0B4C-E14B-4AD2-BBBE-BD4ECDCB7626}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2387600" y="641350"/>
+          <a:ext cx="1219200" cy="1543050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・教材のコンテ ンツ作成 </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・施設・備品・ インストラクターの調達 </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・広報</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>196850</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="テキスト ボックス 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{800370FB-EA53-47BC-B9B9-159E3837DD54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2381250" y="2914650"/>
+          <a:ext cx="1219200" cy="850900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>社内に蓄積された技術、施設、 人材</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="テキスト ボックス 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A70FC8BA-748D-456A-9348-40B2FF555899}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4057650" y="914400"/>
+          <a:ext cx="1219200" cy="1568450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>理科に関心を持ってくれる子供（特に 女子学生）を育てることで、 社会に貢献</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B4087E0-1529-4FD5-9BEE-B92A74AE3876}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5676900" y="838200"/>
+          <a:ext cx="1219200" cy="1206500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>長期的な展望での企業イメージの強化</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="テキスト ボックス 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{456B0FC6-4C0C-441C-B85D-71BC0F04768E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5670550" y="2965450"/>
+          <a:ext cx="1219200" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・広報のチラシ </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・WEB ページ </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・企業の実験室 </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>196850</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="テキスト ボックス 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98C3946D-A770-468B-92EB-B0463BDE0DEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7296150" y="1473200"/>
+          <a:ext cx="1219200" cy="1473200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・小学5，6年生 </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・子供の父兄 </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・子供の学校 の先生 </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="テキスト ボックス 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD047083-15A0-4486-80DD-143C98CE3F83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1162050" y="4826000"/>
+          <a:ext cx="1104900" cy="825500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・備品 </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>・広報費</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="テキスト ボックス 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E9DE57A-D691-41A3-9E57-E250A401FCE1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5187950" y="4946650"/>
+          <a:ext cx="2940050" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP"/>
+            <a:t>企業の広報、社会貢献の定性的効果 </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2647,7 +4174,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3526,6 +5053,680 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{181ABBC1-F8F9-4619-BCE9-34C8D5BD06A4}">
+  <dimension ref="C1:AF25"/>
+  <sheetFormatPr defaultColWidth="4.58203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="34" width="3.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C2" s="120" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="120" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="121" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="121"/>
+      <c r="R2" s="121"/>
+      <c r="S2" s="121"/>
+      <c r="T2" s="121"/>
+      <c r="U2" s="120" t="s">
+        <v>66</v>
+      </c>
+      <c r="V2" s="121"/>
+      <c r="W2" s="121"/>
+      <c r="X2" s="121"/>
+      <c r="Y2" s="121"/>
+      <c r="Z2" s="122"/>
+      <c r="AA2" s="121" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB2" s="121"/>
+      <c r="AC2" s="121"/>
+      <c r="AD2" s="121"/>
+      <c r="AE2" s="121"/>
+      <c r="AF2" s="122"/>
+    </row>
+    <row r="3" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C3" s="123"/>
+      <c r="D3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="123"/>
+      <c r="J3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" s="124"/>
+      <c r="P3" t="s">
+        <v>75</v>
+      </c>
+      <c r="U3" s="123"/>
+      <c r="V3" s="128" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z3" s="124"/>
+      <c r="AB3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF3" s="124"/>
+    </row>
+    <row r="4" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="N4" s="124"/>
+      <c r="U4" s="123"/>
+      <c r="Z4" s="124"/>
+      <c r="AF4" s="124"/>
+    </row>
+    <row r="5" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="N5" s="124"/>
+      <c r="U5" s="123"/>
+      <c r="Z5" s="124"/>
+      <c r="AF5" s="124"/>
+    </row>
+    <row r="6" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C6" s="123"/>
+      <c r="I6" s="123"/>
+      <c r="N6" s="124"/>
+      <c r="U6" s="123"/>
+      <c r="Z6" s="124"/>
+      <c r="AF6" s="124"/>
+    </row>
+    <row r="7" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C7" s="123"/>
+      <c r="I7" s="123"/>
+      <c r="N7" s="124"/>
+      <c r="U7" s="123"/>
+      <c r="Z7" s="124"/>
+      <c r="AF7" s="124"/>
+    </row>
+    <row r="8" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C8" s="123"/>
+      <c r="I8" s="123"/>
+      <c r="N8" s="124"/>
+      <c r="U8" s="123"/>
+      <c r="Z8" s="124"/>
+      <c r="AF8" s="124"/>
+    </row>
+    <row r="9" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C9" s="123"/>
+      <c r="I9" s="123"/>
+      <c r="N9" s="124"/>
+      <c r="U9" s="123"/>
+      <c r="Z9" s="124"/>
+      <c r="AF9" s="124"/>
+    </row>
+    <row r="10" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C10" s="123"/>
+      <c r="I10" s="123"/>
+      <c r="N10" s="124"/>
+      <c r="U10" s="123"/>
+      <c r="Z10" s="124"/>
+      <c r="AF10" s="124"/>
+    </row>
+    <row r="11" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C11" s="123"/>
+      <c r="I11" s="120" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="121"/>
+      <c r="K11" s="121"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="122"/>
+      <c r="U11" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="V11" s="121"/>
+      <c r="W11" s="121"/>
+      <c r="X11" s="121"/>
+      <c r="Y11" s="121"/>
+      <c r="Z11" s="122"/>
+      <c r="AF11" s="124"/>
+    </row>
+    <row r="12" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="J12" t="s">
+        <v>74</v>
+      </c>
+      <c r="N12" s="124"/>
+      <c r="U12" s="123"/>
+      <c r="V12" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z12" s="124"/>
+      <c r="AF12" s="124"/>
+    </row>
+    <row r="13" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C13" s="123"/>
+      <c r="I13" s="123"/>
+      <c r="N13" s="124"/>
+      <c r="U13" s="123"/>
+      <c r="Z13" s="124"/>
+      <c r="AF13" s="124"/>
+    </row>
+    <row r="14" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C14" s="123"/>
+      <c r="I14" s="123"/>
+      <c r="N14" s="124"/>
+      <c r="U14" s="123"/>
+      <c r="Z14" s="124"/>
+      <c r="AF14" s="124"/>
+    </row>
+    <row r="15" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C15" s="123"/>
+      <c r="I15" s="123"/>
+      <c r="N15" s="124"/>
+      <c r="U15" s="123"/>
+      <c r="Z15" s="124"/>
+      <c r="AF15" s="124"/>
+    </row>
+    <row r="16" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C16" s="123"/>
+      <c r="I16" s="123"/>
+      <c r="N16" s="124"/>
+      <c r="U16" s="123"/>
+      <c r="Z16" s="124"/>
+      <c r="AF16" s="124"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C17" s="123"/>
+      <c r="I17" s="123"/>
+      <c r="N17" s="124"/>
+      <c r="U17" s="123"/>
+      <c r="Z17" s="124"/>
+      <c r="AF17" s="124"/>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C18" s="123"/>
+      <c r="I18" s="123"/>
+      <c r="N18" s="124"/>
+      <c r="U18" s="123"/>
+      <c r="Z18" s="124"/>
+      <c r="AF18" s="124"/>
+    </row>
+    <row r="19" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C19" s="123"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="127"/>
+      <c r="U19" s="125"/>
+      <c r="V19" s="126"/>
+      <c r="W19" s="126"/>
+      <c r="X19" s="126"/>
+      <c r="Y19" s="126"/>
+      <c r="Z19" s="127"/>
+      <c r="AF19" s="124"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C20" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="121"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="121"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="121"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="122"/>
+      <c r="R20" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="S20" s="121"/>
+      <c r="T20" s="121"/>
+      <c r="U20" s="121"/>
+      <c r="V20" s="121"/>
+      <c r="W20" s="121"/>
+      <c r="X20" s="121"/>
+      <c r="Y20" s="121"/>
+      <c r="Z20" s="121"/>
+      <c r="AA20" s="121"/>
+      <c r="AB20" s="121"/>
+      <c r="AC20" s="121"/>
+      <c r="AD20" s="121"/>
+      <c r="AE20" s="121"/>
+      <c r="AF20" s="122"/>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C21" s="123"/>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q21" s="124"/>
+      <c r="R21" s="123"/>
+      <c r="S21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF21" s="124"/>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C22" s="123"/>
+      <c r="Q22" s="124"/>
+      <c r="R22" s="123"/>
+      <c r="AF22" s="124"/>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C23" s="123"/>
+      <c r="Q23" s="124"/>
+      <c r="R23" s="123"/>
+      <c r="AF23" s="124"/>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C24" s="123"/>
+      <c r="Q24" s="124"/>
+      <c r="R24" s="123"/>
+      <c r="AF24" s="124"/>
+    </row>
+    <row r="25" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C25" s="125"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="126"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="126"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="126"/>
+      <c r="K25" s="126"/>
+      <c r="L25" s="126"/>
+      <c r="M25" s="126"/>
+      <c r="N25" s="126"/>
+      <c r="O25" s="126"/>
+      <c r="P25" s="126"/>
+      <c r="Q25" s="127"/>
+      <c r="R25" s="125"/>
+      <c r="S25" s="126"/>
+      <c r="T25" s="126"/>
+      <c r="U25" s="126"/>
+      <c r="V25" s="126"/>
+      <c r="W25" s="126"/>
+      <c r="X25" s="126"/>
+      <c r="Y25" s="126"/>
+      <c r="Z25" s="126"/>
+      <c r="AA25" s="126"/>
+      <c r="AB25" s="126"/>
+      <c r="AC25" s="126"/>
+      <c r="AD25" s="126"/>
+      <c r="AE25" s="126"/>
+      <c r="AF25" s="127"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L組織のビジネスモデル</oddHeader>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41E9FEA-3024-44B9-86DB-5F5050837042}">
+  <dimension ref="C1:AF25"/>
+  <sheetFormatPr defaultColWidth="4.58203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="34" width="3.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C2" s="120" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="120" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="121" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="121"/>
+      <c r="R2" s="121"/>
+      <c r="S2" s="121"/>
+      <c r="T2" s="121"/>
+      <c r="U2" s="120" t="s">
+        <v>66</v>
+      </c>
+      <c r="V2" s="121"/>
+      <c r="W2" s="121"/>
+      <c r="X2" s="121"/>
+      <c r="Y2" s="121"/>
+      <c r="Z2" s="122"/>
+      <c r="AA2" s="121" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB2" s="121"/>
+      <c r="AC2" s="121"/>
+      <c r="AD2" s="121"/>
+      <c r="AE2" s="121"/>
+      <c r="AF2" s="122"/>
+    </row>
+    <row r="3" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C3" s="123"/>
+      <c r="D3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="123"/>
+      <c r="J3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" s="124"/>
+      <c r="P3" t="s">
+        <v>75</v>
+      </c>
+      <c r="U3" s="123"/>
+      <c r="V3" s="128" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z3" s="124"/>
+      <c r="AB3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF3" s="124"/>
+    </row>
+    <row r="4" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="N4" s="124"/>
+      <c r="U4" s="123"/>
+      <c r="Z4" s="124"/>
+      <c r="AF4" s="124"/>
+    </row>
+    <row r="5" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="N5" s="124"/>
+      <c r="U5" s="123"/>
+      <c r="Z5" s="124"/>
+      <c r="AF5" s="124"/>
+    </row>
+    <row r="6" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C6" s="123"/>
+      <c r="I6" s="123"/>
+      <c r="N6" s="124"/>
+      <c r="U6" s="123"/>
+      <c r="Z6" s="124"/>
+      <c r="AF6" s="124"/>
+    </row>
+    <row r="7" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C7" s="123"/>
+      <c r="I7" s="123"/>
+      <c r="N7" s="124"/>
+      <c r="U7" s="123"/>
+      <c r="Z7" s="124"/>
+      <c r="AF7" s="124"/>
+    </row>
+    <row r="8" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C8" s="123"/>
+      <c r="I8" s="123"/>
+      <c r="N8" s="124"/>
+      <c r="U8" s="123"/>
+      <c r="Z8" s="124"/>
+      <c r="AF8" s="124"/>
+    </row>
+    <row r="9" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C9" s="123"/>
+      <c r="I9" s="123"/>
+      <c r="N9" s="124"/>
+      <c r="U9" s="123"/>
+      <c r="Z9" s="124"/>
+      <c r="AF9" s="124"/>
+    </row>
+    <row r="10" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C10" s="123"/>
+      <c r="I10" s="123"/>
+      <c r="N10" s="124"/>
+      <c r="U10" s="123"/>
+      <c r="Z10" s="124"/>
+      <c r="AF10" s="124"/>
+    </row>
+    <row r="11" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C11" s="123"/>
+      <c r="I11" s="120" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="121"/>
+      <c r="K11" s="121"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="122"/>
+      <c r="U11" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="V11" s="121"/>
+      <c r="W11" s="121"/>
+      <c r="X11" s="121"/>
+      <c r="Y11" s="121"/>
+      <c r="Z11" s="122"/>
+      <c r="AF11" s="124"/>
+    </row>
+    <row r="12" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="J12" t="s">
+        <v>74</v>
+      </c>
+      <c r="N12" s="124"/>
+      <c r="U12" s="123"/>
+      <c r="V12" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z12" s="124"/>
+      <c r="AF12" s="124"/>
+    </row>
+    <row r="13" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C13" s="123"/>
+      <c r="I13" s="123"/>
+      <c r="N13" s="124"/>
+      <c r="U13" s="123"/>
+      <c r="Z13" s="124"/>
+      <c r="AF13" s="124"/>
+    </row>
+    <row r="14" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C14" s="123"/>
+      <c r="I14" s="123"/>
+      <c r="N14" s="124"/>
+      <c r="U14" s="123"/>
+      <c r="Z14" s="124"/>
+      <c r="AF14" s="124"/>
+    </row>
+    <row r="15" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C15" s="123"/>
+      <c r="I15" s="123"/>
+      <c r="N15" s="124"/>
+      <c r="U15" s="123"/>
+      <c r="Z15" s="124"/>
+      <c r="AF15" s="124"/>
+    </row>
+    <row r="16" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C16" s="123"/>
+      <c r="I16" s="123"/>
+      <c r="N16" s="124"/>
+      <c r="U16" s="123"/>
+      <c r="Z16" s="124"/>
+      <c r="AF16" s="124"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C17" s="123"/>
+      <c r="I17" s="123"/>
+      <c r="N17" s="124"/>
+      <c r="U17" s="123"/>
+      <c r="Z17" s="124"/>
+      <c r="AF17" s="124"/>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C18" s="123"/>
+      <c r="I18" s="123"/>
+      <c r="N18" s="124"/>
+      <c r="U18" s="123"/>
+      <c r="Z18" s="124"/>
+      <c r="AF18" s="124"/>
+    </row>
+    <row r="19" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C19" s="123"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="127"/>
+      <c r="U19" s="125"/>
+      <c r="V19" s="126"/>
+      <c r="W19" s="126"/>
+      <c r="X19" s="126"/>
+      <c r="Y19" s="126"/>
+      <c r="Z19" s="127"/>
+      <c r="AF19" s="124"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C20" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="121"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="121"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="121"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="122"/>
+      <c r="R20" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="S20" s="121"/>
+      <c r="T20" s="121"/>
+      <c r="U20" s="121"/>
+      <c r="V20" s="121"/>
+      <c r="W20" s="121"/>
+      <c r="X20" s="121"/>
+      <c r="Y20" s="121"/>
+      <c r="Z20" s="121"/>
+      <c r="AA20" s="121"/>
+      <c r="AB20" s="121"/>
+      <c r="AC20" s="121"/>
+      <c r="AD20" s="121"/>
+      <c r="AE20" s="121"/>
+      <c r="AF20" s="122"/>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C21" s="123"/>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q21" s="124"/>
+      <c r="R21" s="123"/>
+      <c r="S21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF21" s="124"/>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C22" s="123"/>
+      <c r="Q22" s="124"/>
+      <c r="R22" s="123"/>
+      <c r="AF22" s="124"/>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C23" s="123"/>
+      <c r="Q23" s="124"/>
+      <c r="R23" s="123"/>
+      <c r="AF23" s="124"/>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="C24" s="123"/>
+      <c r="Q24" s="124"/>
+      <c r="R24" s="123"/>
+      <c r="AF24" s="124"/>
+    </row>
+    <row r="25" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C25" s="125"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="126"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="126"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="126"/>
+      <c r="K25" s="126"/>
+      <c r="L25" s="126"/>
+      <c r="M25" s="126"/>
+      <c r="N25" s="126"/>
+      <c r="O25" s="126"/>
+      <c r="P25" s="126"/>
+      <c r="Q25" s="127"/>
+      <c r="R25" s="125"/>
+      <c r="S25" s="126"/>
+      <c r="T25" s="126"/>
+      <c r="U25" s="126"/>
+      <c r="V25" s="126"/>
+      <c r="W25" s="126"/>
+      <c r="X25" s="126"/>
+      <c r="Y25" s="126"/>
+      <c r="Z25" s="126"/>
+      <c r="AA25" s="126"/>
+      <c r="AB25" s="126"/>
+      <c r="AC25" s="126"/>
+      <c r="AD25" s="126"/>
+      <c r="AE25" s="126"/>
+      <c r="AF25" s="127"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L組織のビジネスモデル</oddHeader>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8B7800-CC13-4A16-990F-CCE2A9CAEB39}">
   <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3536,89 +5737,89 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="39" t="s">
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="33"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="33" t="s">
+      <c r="F2" s="84"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="33"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="35"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="82"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="40" t="s">
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31" t="s">
+      <c r="F3" s="86"/>
+      <c r="G3" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="30" t="s">
+      <c r="H3" s="88"/>
+      <c r="I3" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="30"/>
-      <c r="K3" s="32">
+      <c r="J3" s="86"/>
+      <c r="K3" s="28">
         <v>62.3</v>
       </c>
-      <c r="L3" s="31" t="s">
+      <c r="L3" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="36"/>
+      <c r="M3" s="89"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="36"/>
+      <c r="B4" s="97"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="89"/>
     </row>
     <row r="5" spans="1:13" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="38"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="91"/>
+      <c r="M5" s="92"/>
     </row>
     <row r="6" spans="1:13" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="26" t="s">
@@ -3645,14 +5846,14 @@
       <c r="I6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="58" t="s">
+      <c r="J6" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="53" t="s">
+      <c r="K6" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="28"/>
-      <c r="M6" s="29"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="95"/>
     </row>
     <row r="7" spans="1:13" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="10" t="s">
@@ -3673,12 +5874,12 @@
       <c r="H7" s="6"/>
       <c r="I7" s="23"/>
       <c r="J7" s="25"/>
-      <c r="K7" s="54"/>
+      <c r="K7" s="38"/>
       <c r="L7" s="23"/>
       <c r="M7" s="25"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="49"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="15"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -3688,12 +5889,12 @@
       <c r="H8" s="2"/>
       <c r="I8" s="3"/>
       <c r="J8" s="16"/>
-      <c r="K8" s="55"/>
+      <c r="K8" s="39"/>
       <c r="L8" s="3"/>
       <c r="M8" s="16"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="35" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="17" t="s">
@@ -3711,12 +5912,12 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="56"/>
+      <c r="K9" s="40"/>
       <c r="L9" s="4"/>
       <c r="M9" s="14"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="49"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="13"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -3726,12 +5927,12 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="16"/>
-      <c r="K10" s="55"/>
+      <c r="K10" s="39"/>
       <c r="L10" s="3"/>
       <c r="M10" s="16"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="36" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="17" t="s">
@@ -3749,12 +5950,12 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="14"/>
-      <c r="K11" s="56"/>
+      <c r="K11" s="40"/>
       <c r="L11" s="4"/>
       <c r="M11" s="14"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="52"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="13"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -3764,12 +5965,12 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="16"/>
-      <c r="K12" s="55"/>
+      <c r="K12" s="39"/>
       <c r="L12" s="3"/>
       <c r="M12" s="16"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="36" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="17" t="s">
@@ -3787,12 +5988,12 @@
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="14"/>
-      <c r="K13" s="56"/>
+      <c r="K13" s="40"/>
       <c r="L13" s="4"/>
       <c r="M13" s="14"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="52"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="13"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -3802,12 +6003,12 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="16"/>
-      <c r="K14" s="55"/>
+      <c r="K14" s="39"/>
       <c r="L14" s="3"/>
       <c r="M14" s="16"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="36" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
@@ -3825,12 +6026,12 @@
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="14"/>
-      <c r="K15" s="56"/>
+      <c r="K15" s="40"/>
       <c r="L15" s="4"/>
       <c r="M15" s="14"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="52"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="13"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -3840,12 +6041,12 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="16"/>
-      <c r="K16" s="55"/>
+      <c r="K16" s="39"/>
       <c r="L16" s="3"/>
       <c r="M16" s="16"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="17"/>
@@ -3857,12 +6058,12 @@
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="14"/>
-      <c r="K17" s="56"/>
+      <c r="K17" s="40"/>
       <c r="L17" s="4"/>
       <c r="M17" s="14"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="52"/>
+      <c r="A18" s="37"/>
       <c r="B18" s="13"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -3872,12 +6073,12 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="16"/>
-      <c r="K18" s="55"/>
+      <c r="K18" s="39"/>
       <c r="L18" s="3"/>
       <c r="M18" s="16"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="36" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="17"/>
@@ -3889,12 +6090,12 @@
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
       <c r="J19" s="14"/>
-      <c r="K19" s="56"/>
+      <c r="K19" s="40"/>
       <c r="L19" s="4"/>
       <c r="M19" s="14"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="52"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="13"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -3904,12 +6105,12 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="16"/>
-      <c r="K20" s="55"/>
+      <c r="K20" s="39"/>
       <c r="L20" s="3"/>
       <c r="M20" s="16"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="51" t="s">
+      <c r="A21" s="36" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="17"/>
@@ -3921,12 +6122,12 @@
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="14"/>
-      <c r="K21" s="56"/>
+      <c r="K21" s="40"/>
       <c r="L21" s="4"/>
       <c r="M21" s="14"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="52"/>
+      <c r="A22" s="37"/>
       <c r="B22" s="13"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -3936,12 +6137,12 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="16"/>
-      <c r="K22" s="55"/>
+      <c r="K22" s="39"/>
       <c r="L22" s="3"/>
       <c r="M22" s="16"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="51" t="s">
+      <c r="A23" s="36" t="s">
         <v>18</v>
       </c>
       <c r="B23" s="17"/>
@@ -3953,7 +6154,7 @@
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="14"/>
-      <c r="K23" s="56"/>
+      <c r="K23" s="40"/>
       <c r="L23" s="4"/>
       <c r="M23" s="14"/>
     </row>
@@ -3968,7 +6169,7 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="19"/>
-      <c r="K24" s="57"/>
+      <c r="K24" s="41"/>
       <c r="L24" s="6"/>
       <c r="M24" s="19"/>
     </row>
@@ -3976,7 +6177,7 @@
       <c r="A25" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="59"/>
+      <c r="B25" s="43"/>
       <c r="C25" s="8"/>
       <c r="D25" s="7"/>
       <c r="E25" s="8"/>
@@ -3984,14 +6185,14 @@
       <c r="G25" s="8"/>
       <c r="H25" s="7"/>
       <c r="I25" s="8"/>
-      <c r="J25" s="60"/>
+      <c r="J25" s="44"/>
       <c r="K25" s="8"/>
       <c r="L25" s="7"/>
       <c r="M25" s="21"/>
     </row>
     <row r="26" spans="1:13" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A26" s="9"/>
-      <c r="B26" s="61"/>
+      <c r="B26" s="45"/>
       <c r="C26" s="11"/>
       <c r="D26" s="22"/>
       <c r="E26" s="11"/>
@@ -3999,13 +6200,17 @@
       <c r="G26" s="11"/>
       <c r="H26" s="22"/>
       <c r="I26" s="11"/>
-      <c r="J26" s="62"/>
+      <c r="J26" s="46"/>
       <c r="K26" s="11"/>
       <c r="L26" s="22"/>
       <c r="M26" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
@@ -4016,10 +6221,6 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4027,7 +6228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CD410A-1050-466C-A52E-EBD7DBA5F117}">
   <dimension ref="A3:L12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -4040,237 +6241,237 @@
       <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69" t="s">
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="70"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="100"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="71">
+      <c r="B5" s="53">
         <v>0.9</v>
       </c>
-      <c r="C5" s="67">
+      <c r="C5" s="51">
         <v>0.05</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="28">
         <v>0.09</v>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="49">
         <v>0.18</v>
       </c>
-      <c r="F5" s="65">
+      <c r="F5" s="49">
         <v>0.36</v>
       </c>
-      <c r="G5" s="65">
+      <c r="G5" s="49">
         <v>0.72</v>
       </c>
-      <c r="H5" s="65">
+      <c r="H5" s="49">
         <v>0.72</v>
       </c>
-      <c r="I5" s="65">
+      <c r="I5" s="49">
         <v>0.36</v>
       </c>
-      <c r="J5" s="65">
+      <c r="J5" s="49">
         <v>0.18</v>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="28">
         <v>0.09</v>
       </c>
-      <c r="L5" s="72">
+      <c r="L5" s="54">
         <v>0.05</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="71">
+      <c r="B6" s="53">
         <v>0.7</v>
       </c>
-      <c r="C6" s="67">
+      <c r="C6" s="51">
         <v>0.04</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="28">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="28">
         <v>0.14000000000000001</v>
       </c>
-      <c r="F6" s="65">
+      <c r="F6" s="49">
         <v>0.28000000000000003</v>
       </c>
-      <c r="G6" s="65">
+      <c r="G6" s="49">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H6" s="65">
+      <c r="H6" s="49">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="49">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="28">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="28">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L6" s="72">
+      <c r="L6" s="54">
         <v>0.04</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="71">
+      <c r="B7" s="53">
         <v>0.5</v>
       </c>
-      <c r="C7" s="67">
+      <c r="C7" s="51">
         <v>0.03</v>
       </c>
-      <c r="D7" s="67">
+      <c r="D7" s="51">
         <v>0.05</v>
       </c>
-      <c r="E7" s="64">
+      <c r="E7" s="48">
         <v>0.1</v>
       </c>
-      <c r="F7" s="66">
+      <c r="F7" s="50">
         <v>0.2</v>
       </c>
-      <c r="G7" s="66">
+      <c r="G7" s="50">
         <v>0.4</v>
       </c>
-      <c r="H7" s="66">
+      <c r="H7" s="50">
         <v>0.4</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="50">
         <v>0.2</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="48">
         <v>0.1</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="51">
         <v>0.05</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="54">
         <v>0.03</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="71">
+      <c r="B8" s="53">
         <v>0.3</v>
       </c>
-      <c r="C8" s="67">
+      <c r="C8" s="51">
         <v>0.02</v>
       </c>
-      <c r="D8" s="67">
+      <c r="D8" s="51">
         <v>0.03</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="28">
         <v>0.06</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="28">
         <v>0.12</v>
       </c>
-      <c r="G8" s="65">
+      <c r="G8" s="49">
         <v>0.24</v>
       </c>
-      <c r="H8" s="65">
+      <c r="H8" s="49">
         <v>0.24</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="28">
         <v>0.12</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="28">
         <v>0.06</v>
       </c>
-      <c r="K8" s="67">
+      <c r="K8" s="51">
         <v>0.03</v>
       </c>
-      <c r="L8" s="72">
+      <c r="L8" s="54">
         <v>0.02</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="71">
+      <c r="B9" s="53">
         <v>0.1</v>
       </c>
-      <c r="C9" s="67">
+      <c r="C9" s="51">
         <v>0.01</v>
       </c>
-      <c r="D9" s="67">
+      <c r="D9" s="51">
         <v>0.01</v>
       </c>
-      <c r="E9" s="67">
+      <c r="E9" s="51">
         <v>0.02</v>
       </c>
-      <c r="F9" s="67">
+      <c r="F9" s="51">
         <v>0.04</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="28">
         <v>0.08</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="28">
         <v>0.08</v>
       </c>
-      <c r="I9" s="67">
+      <c r="I9" s="51">
         <v>0.04</v>
       </c>
-      <c r="J9" s="67">
+      <c r="J9" s="51">
         <v>0.02</v>
       </c>
-      <c r="K9" s="67">
+      <c r="K9" s="51">
         <v>0.01</v>
       </c>
-      <c r="L9" s="72">
+      <c r="L9" s="54">
         <v>0.01</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B10" s="73"/>
-      <c r="C10" s="74">
+      <c r="B10" s="55"/>
+      <c r="C10" s="29">
         <v>0.05</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="56">
         <v>0.1</v>
       </c>
-      <c r="E10" s="75">
+      <c r="E10" s="56">
         <v>0.2</v>
       </c>
-      <c r="F10" s="75">
+      <c r="F10" s="56">
         <v>0.4</v>
       </c>
-      <c r="G10" s="75">
+      <c r="G10" s="56">
         <v>0.8</v>
       </c>
-      <c r="H10" s="75">
+      <c r="H10" s="56">
         <v>0.8</v>
       </c>
-      <c r="I10" s="75">
+      <c r="I10" s="56">
         <v>0.4</v>
       </c>
-      <c r="J10" s="75">
+      <c r="J10" s="56">
         <v>0.2</v>
       </c>
-      <c r="K10" s="75">
+      <c r="K10" s="56">
         <v>0.1</v>
       </c>
-      <c r="L10" s="76">
+      <c r="L10" s="30">
         <v>0.05</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="63"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="63"/>
+      <c r="B12" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4283,7 +6484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F8E1BD2-153E-4295-80BD-AA7707B95F92}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4291,3044 +6492,3062 @@
   <dimension ref="B1:CS29"/>
   <sheetFormatPr defaultColWidth="2.83203125" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="1.83203125" style="86" customWidth="1"/>
-    <col min="2" max="2" width="36.4140625" style="112" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.75" style="86" customWidth="1"/>
-    <col min="5" max="5" width="11.4140625" style="86" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="86" customWidth="1"/>
-    <col min="7" max="36" width="3.75" style="84" customWidth="1"/>
-    <col min="37" max="37" width="2.9140625" style="84" bestFit="1" customWidth="1"/>
-    <col min="38" max="45" width="2.9140625" style="86" bestFit="1" customWidth="1"/>
-    <col min="46" max="66" width="3.5" style="86" bestFit="1" customWidth="1"/>
-    <col min="67" max="75" width="2.9140625" style="86" bestFit="1" customWidth="1"/>
-    <col min="76" max="88" width="3.5" style="86" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="2.83203125" style="86" customWidth="1"/>
-    <col min="90" max="16384" width="2.83203125" style="86"/>
+    <col min="1" max="1" width="1.83203125" style="65" customWidth="1"/>
+    <col min="2" max="2" width="36.4140625" style="80" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.75" style="65" customWidth="1"/>
+    <col min="5" max="5" width="11.4140625" style="65" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="65" customWidth="1"/>
+    <col min="7" max="36" width="3.75" style="63" customWidth="1"/>
+    <col min="37" max="37" width="2.9140625" style="63" bestFit="1" customWidth="1"/>
+    <col min="38" max="45" width="2.9140625" style="65" bestFit="1" customWidth="1"/>
+    <col min="46" max="66" width="3.5" style="65" bestFit="1" customWidth="1"/>
+    <col min="67" max="75" width="2.9140625" style="65" bestFit="1" customWidth="1"/>
+    <col min="76" max="88" width="3.5" style="65" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="2.83203125" style="65" customWidth="1"/>
+    <col min="90" max="16384" width="2.83203125" style="65"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:97" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="84" t="s">
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="85">
+      <c r="F1" s="64">
         <v>46236</v>
       </c>
     </row>
     <row r="2" spans="2:97" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="88" t="s">
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="89">
+      <c r="F2" s="67">
         <v>46332</v>
       </c>
     </row>
     <row r="3" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="84"/>
+      <c r="B3" s="63"/>
     </row>
     <row r="4" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="90" t="s">
+      <c r="B4" s="106" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="90" t="s">
+      <c r="C4" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="91" t="s">
+      <c r="D4" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="90" t="s">
+      <c r="E4" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="92" t="s">
+      <c r="F4" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="93">
+      <c r="G4" s="101">
         <f>G5</f>
         <v>46236</v>
       </c>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="95"/>
-      <c r="N4" s="93">
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="101">
         <f t="shared" ref="N4" si="0">N5</f>
         <v>46243</v>
       </c>
-      <c r="O4" s="94"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="94"/>
-      <c r="T4" s="95"/>
-      <c r="U4" s="93">
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
+      <c r="U4" s="101">
         <f t="shared" ref="U4" si="1">U5</f>
         <v>46250</v>
       </c>
-      <c r="V4" s="94"/>
-      <c r="W4" s="94"/>
-      <c r="X4" s="94"/>
-      <c r="Y4" s="94"/>
-      <c r="Z4" s="94"/>
-      <c r="AA4" s="95"/>
-      <c r="AB4" s="93">
+      <c r="V4" s="102"/>
+      <c r="W4" s="102"/>
+      <c r="X4" s="102"/>
+      <c r="Y4" s="102"/>
+      <c r="Z4" s="102"/>
+      <c r="AA4" s="103"/>
+      <c r="AB4" s="101">
         <f t="shared" ref="AB4" si="2">AB5</f>
         <v>46257</v>
       </c>
-      <c r="AC4" s="94"/>
-      <c r="AD4" s="94"/>
-      <c r="AE4" s="94"/>
-      <c r="AF4" s="94"/>
-      <c r="AG4" s="94"/>
-      <c r="AH4" s="94"/>
-      <c r="AI4" s="93">
+      <c r="AC4" s="102"/>
+      <c r="AD4" s="102"/>
+      <c r="AE4" s="102"/>
+      <c r="AF4" s="102"/>
+      <c r="AG4" s="102"/>
+      <c r="AH4" s="102"/>
+      <c r="AI4" s="101">
         <f t="shared" ref="AI4" si="3">AI5</f>
         <v>46264</v>
       </c>
-      <c r="AJ4" s="94"/>
-      <c r="AK4" s="94"/>
-      <c r="AL4" s="94"/>
-      <c r="AM4" s="94"/>
-      <c r="AN4" s="94"/>
-      <c r="AO4" s="94"/>
-      <c r="AP4" s="93">
+      <c r="AJ4" s="102"/>
+      <c r="AK4" s="102"/>
+      <c r="AL4" s="102"/>
+      <c r="AM4" s="102"/>
+      <c r="AN4" s="102"/>
+      <c r="AO4" s="102"/>
+      <c r="AP4" s="101">
         <f t="shared" ref="AP4" si="4">AP5</f>
         <v>46271</v>
       </c>
-      <c r="AQ4" s="94"/>
-      <c r="AR4" s="94"/>
-      <c r="AS4" s="94"/>
-      <c r="AT4" s="94"/>
-      <c r="AU4" s="94"/>
-      <c r="AV4" s="94"/>
-      <c r="AW4" s="93">
+      <c r="AQ4" s="102"/>
+      <c r="AR4" s="102"/>
+      <c r="AS4" s="102"/>
+      <c r="AT4" s="102"/>
+      <c r="AU4" s="102"/>
+      <c r="AV4" s="102"/>
+      <c r="AW4" s="101">
         <f t="shared" ref="AW4" si="5">AW5</f>
         <v>46278</v>
       </c>
-      <c r="AX4" s="94"/>
-      <c r="AY4" s="94"/>
-      <c r="AZ4" s="94"/>
-      <c r="BA4" s="94"/>
-      <c r="BB4" s="94"/>
-      <c r="BC4" s="94"/>
-      <c r="BD4" s="93">
+      <c r="AX4" s="102"/>
+      <c r="AY4" s="102"/>
+      <c r="AZ4" s="102"/>
+      <c r="BA4" s="102"/>
+      <c r="BB4" s="102"/>
+      <c r="BC4" s="102"/>
+      <c r="BD4" s="101">
         <f t="shared" ref="BD4" si="6">BD5</f>
         <v>46285</v>
       </c>
-      <c r="BE4" s="94"/>
-      <c r="BF4" s="94"/>
-      <c r="BG4" s="94"/>
-      <c r="BH4" s="94"/>
-      <c r="BI4" s="94"/>
-      <c r="BJ4" s="94"/>
-      <c r="BK4" s="93">
+      <c r="BE4" s="102"/>
+      <c r="BF4" s="102"/>
+      <c r="BG4" s="102"/>
+      <c r="BH4" s="102"/>
+      <c r="BI4" s="102"/>
+      <c r="BJ4" s="102"/>
+      <c r="BK4" s="101">
         <f t="shared" ref="BK4" si="7">BK5</f>
         <v>46292</v>
       </c>
-      <c r="BL4" s="94"/>
-      <c r="BM4" s="94"/>
-      <c r="BN4" s="94"/>
-      <c r="BO4" s="94"/>
-      <c r="BP4" s="94"/>
-      <c r="BQ4" s="94"/>
-      <c r="BR4" s="93">
+      <c r="BL4" s="102"/>
+      <c r="BM4" s="102"/>
+      <c r="BN4" s="102"/>
+      <c r="BO4" s="102"/>
+      <c r="BP4" s="102"/>
+      <c r="BQ4" s="102"/>
+      <c r="BR4" s="101">
         <f t="shared" ref="BR4" si="8">BR5</f>
         <v>46299</v>
       </c>
-      <c r="BS4" s="94"/>
-      <c r="BT4" s="94"/>
-      <c r="BU4" s="94"/>
-      <c r="BV4" s="94"/>
-      <c r="BW4" s="94"/>
-      <c r="BX4" s="94"/>
-      <c r="BY4" s="93">
+      <c r="BS4" s="102"/>
+      <c r="BT4" s="102"/>
+      <c r="BU4" s="102"/>
+      <c r="BV4" s="102"/>
+      <c r="BW4" s="102"/>
+      <c r="BX4" s="102"/>
+      <c r="BY4" s="101">
         <f t="shared" ref="BY4" si="9">BY5</f>
         <v>46306</v>
       </c>
-      <c r="BZ4" s="94"/>
-      <c r="CA4" s="94"/>
-      <c r="CB4" s="94"/>
-      <c r="CC4" s="94"/>
-      <c r="CD4" s="94"/>
-      <c r="CE4" s="94"/>
-      <c r="CF4" s="93">
+      <c r="BZ4" s="102"/>
+      <c r="CA4" s="102"/>
+      <c r="CB4" s="102"/>
+      <c r="CC4" s="102"/>
+      <c r="CD4" s="102"/>
+      <c r="CE4" s="102"/>
+      <c r="CF4" s="101">
         <f t="shared" ref="CF4" si="10">CF5</f>
         <v>46313</v>
       </c>
-      <c r="CG4" s="94"/>
-      <c r="CH4" s="94"/>
-      <c r="CI4" s="94"/>
-      <c r="CJ4" s="94"/>
-      <c r="CK4" s="94"/>
-      <c r="CL4" s="94"/>
-      <c r="CM4" s="93">
+      <c r="CG4" s="102"/>
+      <c r="CH4" s="102"/>
+      <c r="CI4" s="102"/>
+      <c r="CJ4" s="102"/>
+      <c r="CK4" s="102"/>
+      <c r="CL4" s="102"/>
+      <c r="CM4" s="101">
         <f t="shared" ref="CM4" si="11">CM5</f>
         <v>46320</v>
       </c>
-      <c r="CN4" s="94"/>
-      <c r="CO4" s="94"/>
-      <c r="CP4" s="94"/>
-      <c r="CQ4" s="94"/>
-      <c r="CR4" s="94"/>
-      <c r="CS4" s="94"/>
+      <c r="CN4" s="102"/>
+      <c r="CO4" s="102"/>
+      <c r="CP4" s="102"/>
+      <c r="CQ4" s="102"/>
+      <c r="CR4" s="102"/>
+      <c r="CS4" s="102"/>
     </row>
     <row r="5" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="90"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="97">
+      <c r="B5" s="106"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="68">
         <f>F1</f>
         <v>46236</v>
       </c>
-      <c r="H5" s="97">
+      <c r="H5" s="68">
         <f>G5+1</f>
         <v>46237</v>
       </c>
-      <c r="I5" s="97">
+      <c r="I5" s="68">
         <f t="shared" ref="I5:BT5" si="12">H5+1</f>
         <v>46238</v>
       </c>
-      <c r="J5" s="97">
+      <c r="J5" s="68">
         <f t="shared" si="12"/>
         <v>46239</v>
       </c>
-      <c r="K5" s="97">
+      <c r="K5" s="68">
         <f t="shared" si="12"/>
         <v>46240</v>
       </c>
-      <c r="L5" s="97">
+      <c r="L5" s="68">
         <f t="shared" si="12"/>
         <v>46241</v>
       </c>
-      <c r="M5" s="97">
+      <c r="M5" s="68">
         <f t="shared" si="12"/>
         <v>46242</v>
       </c>
-      <c r="N5" s="97">
+      <c r="N5" s="68">
         <f t="shared" si="12"/>
         <v>46243</v>
       </c>
-      <c r="O5" s="97">
+      <c r="O5" s="68">
         <f t="shared" si="12"/>
         <v>46244</v>
       </c>
-      <c r="P5" s="97">
+      <c r="P5" s="68">
         <f t="shared" si="12"/>
         <v>46245</v>
       </c>
-      <c r="Q5" s="97">
+      <c r="Q5" s="68">
         <f t="shared" si="12"/>
         <v>46246</v>
       </c>
-      <c r="R5" s="97">
+      <c r="R5" s="68">
         <f t="shared" si="12"/>
         <v>46247</v>
       </c>
-      <c r="S5" s="97">
+      <c r="S5" s="68">
         <f t="shared" si="12"/>
         <v>46248</v>
       </c>
-      <c r="T5" s="97">
+      <c r="T5" s="68">
         <f t="shared" si="12"/>
         <v>46249</v>
       </c>
-      <c r="U5" s="97">
+      <c r="U5" s="68">
         <f t="shared" si="12"/>
         <v>46250</v>
       </c>
-      <c r="V5" s="97">
+      <c r="V5" s="68">
         <f t="shared" si="12"/>
         <v>46251</v>
       </c>
-      <c r="W5" s="97">
+      <c r="W5" s="68">
         <f t="shared" si="12"/>
         <v>46252</v>
       </c>
-      <c r="X5" s="97">
+      <c r="X5" s="68">
         <f t="shared" si="12"/>
         <v>46253</v>
       </c>
-      <c r="Y5" s="97">
+      <c r="Y5" s="68">
         <f t="shared" si="12"/>
         <v>46254</v>
       </c>
-      <c r="Z5" s="97">
+      <c r="Z5" s="68">
         <f t="shared" si="12"/>
         <v>46255</v>
       </c>
-      <c r="AA5" s="97">
+      <c r="AA5" s="68">
         <f t="shared" si="12"/>
         <v>46256</v>
       </c>
-      <c r="AB5" s="97">
+      <c r="AB5" s="68">
         <f t="shared" si="12"/>
         <v>46257</v>
       </c>
-      <c r="AC5" s="97">
+      <c r="AC5" s="68">
         <f t="shared" si="12"/>
         <v>46258</v>
       </c>
-      <c r="AD5" s="97">
+      <c r="AD5" s="68">
         <f t="shared" si="12"/>
         <v>46259</v>
       </c>
-      <c r="AE5" s="97">
+      <c r="AE5" s="68">
         <f t="shared" si="12"/>
         <v>46260</v>
       </c>
-      <c r="AF5" s="97">
+      <c r="AF5" s="68">
         <f t="shared" si="12"/>
         <v>46261</v>
       </c>
-      <c r="AG5" s="97">
+      <c r="AG5" s="68">
         <f t="shared" si="12"/>
         <v>46262</v>
       </c>
-      <c r="AH5" s="97">
+      <c r="AH5" s="68">
         <f t="shared" si="12"/>
         <v>46263</v>
       </c>
-      <c r="AI5" s="97">
+      <c r="AI5" s="68">
         <f t="shared" si="12"/>
         <v>46264</v>
       </c>
-      <c r="AJ5" s="97">
+      <c r="AJ5" s="68">
         <f t="shared" si="12"/>
         <v>46265</v>
       </c>
-      <c r="AK5" s="97">
+      <c r="AK5" s="68">
         <f t="shared" si="12"/>
         <v>46266</v>
       </c>
-      <c r="AL5" s="97">
+      <c r="AL5" s="68">
         <f t="shared" si="12"/>
         <v>46267</v>
       </c>
-      <c r="AM5" s="97">
+      <c r="AM5" s="68">
         <f t="shared" si="12"/>
         <v>46268</v>
       </c>
-      <c r="AN5" s="97">
+      <c r="AN5" s="68">
         <f t="shared" si="12"/>
         <v>46269</v>
       </c>
-      <c r="AO5" s="97">
+      <c r="AO5" s="68">
         <f t="shared" si="12"/>
         <v>46270</v>
       </c>
-      <c r="AP5" s="97">
+      <c r="AP5" s="68">
         <f t="shared" si="12"/>
         <v>46271</v>
       </c>
-      <c r="AQ5" s="97">
+      <c r="AQ5" s="68">
         <f t="shared" si="12"/>
         <v>46272</v>
       </c>
-      <c r="AR5" s="97">
+      <c r="AR5" s="68">
         <f t="shared" si="12"/>
         <v>46273</v>
       </c>
-      <c r="AS5" s="97">
+      <c r="AS5" s="68">
         <f t="shared" si="12"/>
         <v>46274</v>
       </c>
-      <c r="AT5" s="97">
+      <c r="AT5" s="68">
         <f t="shared" si="12"/>
         <v>46275</v>
       </c>
-      <c r="AU5" s="97">
+      <c r="AU5" s="68">
         <f t="shared" si="12"/>
         <v>46276</v>
       </c>
-      <c r="AV5" s="97">
+      <c r="AV5" s="68">
         <f t="shared" si="12"/>
         <v>46277</v>
       </c>
-      <c r="AW5" s="97">
+      <c r="AW5" s="68">
         <f t="shared" si="12"/>
         <v>46278</v>
       </c>
-      <c r="AX5" s="97">
+      <c r="AX5" s="68">
         <f t="shared" si="12"/>
         <v>46279</v>
       </c>
-      <c r="AY5" s="97">
+      <c r="AY5" s="68">
         <f t="shared" si="12"/>
         <v>46280</v>
       </c>
-      <c r="AZ5" s="97">
+      <c r="AZ5" s="68">
         <f t="shared" si="12"/>
         <v>46281</v>
       </c>
-      <c r="BA5" s="97">
+      <c r="BA5" s="68">
         <f t="shared" si="12"/>
         <v>46282</v>
       </c>
-      <c r="BB5" s="97">
+      <c r="BB5" s="68">
         <f t="shared" si="12"/>
         <v>46283</v>
       </c>
-      <c r="BC5" s="97">
+      <c r="BC5" s="68">
         <f t="shared" si="12"/>
         <v>46284</v>
       </c>
-      <c r="BD5" s="97">
+      <c r="BD5" s="68">
         <f t="shared" si="12"/>
         <v>46285</v>
       </c>
-      <c r="BE5" s="97">
+      <c r="BE5" s="68">
         <f t="shared" si="12"/>
         <v>46286</v>
       </c>
-      <c r="BF5" s="97">
+      <c r="BF5" s="68">
         <f t="shared" si="12"/>
         <v>46287</v>
       </c>
-      <c r="BG5" s="97">
+      <c r="BG5" s="68">
         <f t="shared" si="12"/>
         <v>46288</v>
       </c>
-      <c r="BH5" s="97">
+      <c r="BH5" s="68">
         <f t="shared" si="12"/>
         <v>46289</v>
       </c>
-      <c r="BI5" s="97">
+      <c r="BI5" s="68">
         <f t="shared" si="12"/>
         <v>46290</v>
       </c>
-      <c r="BJ5" s="97">
+      <c r="BJ5" s="68">
         <f t="shared" si="12"/>
         <v>46291</v>
       </c>
-      <c r="BK5" s="97">
+      <c r="BK5" s="68">
         <f t="shared" si="12"/>
         <v>46292</v>
       </c>
-      <c r="BL5" s="97">
+      <c r="BL5" s="68">
         <f t="shared" si="12"/>
         <v>46293</v>
       </c>
-      <c r="BM5" s="97">
+      <c r="BM5" s="68">
         <f t="shared" si="12"/>
         <v>46294</v>
       </c>
-      <c r="BN5" s="97">
+      <c r="BN5" s="68">
         <f t="shared" si="12"/>
         <v>46295</v>
       </c>
-      <c r="BO5" s="97">
+      <c r="BO5" s="68">
         <f t="shared" si="12"/>
         <v>46296</v>
       </c>
-      <c r="BP5" s="97">
+      <c r="BP5" s="68">
         <f t="shared" si="12"/>
         <v>46297</v>
       </c>
-      <c r="BQ5" s="97">
+      <c r="BQ5" s="68">
         <f t="shared" si="12"/>
         <v>46298</v>
       </c>
-      <c r="BR5" s="97">
+      <c r="BR5" s="68">
         <f t="shared" si="12"/>
         <v>46299</v>
       </c>
-      <c r="BS5" s="97">
+      <c r="BS5" s="68">
         <f t="shared" si="12"/>
         <v>46300</v>
       </c>
-      <c r="BT5" s="97">
+      <c r="BT5" s="68">
         <f t="shared" si="12"/>
         <v>46301</v>
       </c>
-      <c r="BU5" s="97">
+      <c r="BU5" s="68">
         <f t="shared" ref="BU5:CS5" si="13">BT5+1</f>
         <v>46302</v>
       </c>
-      <c r="BV5" s="97">
+      <c r="BV5" s="68">
         <f t="shared" si="13"/>
         <v>46303</v>
       </c>
-      <c r="BW5" s="97">
+      <c r="BW5" s="68">
         <f t="shared" si="13"/>
         <v>46304</v>
       </c>
-      <c r="BX5" s="97">
+      <c r="BX5" s="68">
         <f t="shared" si="13"/>
         <v>46305</v>
       </c>
-      <c r="BY5" s="97">
+      <c r="BY5" s="68">
         <f t="shared" si="13"/>
         <v>46306</v>
       </c>
-      <c r="BZ5" s="97">
+      <c r="BZ5" s="68">
         <f t="shared" si="13"/>
         <v>46307</v>
       </c>
-      <c r="CA5" s="97">
+      <c r="CA5" s="68">
         <f t="shared" si="13"/>
         <v>46308</v>
       </c>
-      <c r="CB5" s="97">
+      <c r="CB5" s="68">
         <f t="shared" si="13"/>
         <v>46309</v>
       </c>
-      <c r="CC5" s="97">
+      <c r="CC5" s="68">
         <f t="shared" si="13"/>
         <v>46310</v>
       </c>
-      <c r="CD5" s="97">
+      <c r="CD5" s="68">
         <f t="shared" si="13"/>
         <v>46311</v>
       </c>
-      <c r="CE5" s="97">
+      <c r="CE5" s="68">
         <f t="shared" si="13"/>
         <v>46312</v>
       </c>
-      <c r="CF5" s="97">
+      <c r="CF5" s="68">
         <f t="shared" si="13"/>
         <v>46313</v>
       </c>
-      <c r="CG5" s="97">
+      <c r="CG5" s="68">
         <f t="shared" si="13"/>
         <v>46314</v>
       </c>
-      <c r="CH5" s="97">
+      <c r="CH5" s="68">
         <f t="shared" si="13"/>
         <v>46315</v>
       </c>
-      <c r="CI5" s="97">
+      <c r="CI5" s="68">
         <f t="shared" si="13"/>
         <v>46316</v>
       </c>
-      <c r="CJ5" s="97">
+      <c r="CJ5" s="68">
         <f t="shared" si="13"/>
         <v>46317</v>
       </c>
-      <c r="CK5" s="97">
+      <c r="CK5" s="68">
         <f t="shared" si="13"/>
         <v>46318</v>
       </c>
-      <c r="CL5" s="97">
+      <c r="CL5" s="68">
         <f t="shared" si="13"/>
         <v>46319</v>
       </c>
-      <c r="CM5" s="97">
+      <c r="CM5" s="68">
         <f t="shared" si="13"/>
         <v>46320</v>
       </c>
-      <c r="CN5" s="97">
+      <c r="CN5" s="68">
         <f t="shared" si="13"/>
         <v>46321</v>
       </c>
-      <c r="CO5" s="97">
+      <c r="CO5" s="68">
         <f t="shared" si="13"/>
         <v>46322</v>
       </c>
-      <c r="CP5" s="97">
+      <c r="CP5" s="68">
         <f t="shared" si="13"/>
         <v>46323</v>
       </c>
-      <c r="CQ5" s="97">
+      <c r="CQ5" s="68">
         <f t="shared" si="13"/>
         <v>46324</v>
       </c>
-      <c r="CR5" s="97">
+      <c r="CR5" s="68">
         <f t="shared" si="13"/>
         <v>46325</v>
       </c>
-      <c r="CS5" s="97">
+      <c r="CS5" s="68">
         <f t="shared" si="13"/>
         <v>46326</v>
       </c>
     </row>
     <row r="6" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="98" t="s">
+      <c r="B6" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="100">
+      <c r="C6" s="114"/>
+      <c r="D6" s="115">
+        <f>SUM(D7:D12)</f>
+        <v>3.5</v>
+      </c>
+      <c r="E6" s="116">
         <v>46236</v>
       </c>
-      <c r="F6" s="101">
+      <c r="F6" s="116">
         <v>46240</v>
       </c>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="102"/>
-      <c r="O6" s="102"/>
-      <c r="P6" s="102"/>
-      <c r="Q6" s="102"/>
-      <c r="R6" s="102"/>
-      <c r="S6" s="102"/>
-      <c r="T6" s="102"/>
-      <c r="U6" s="102"/>
-      <c r="V6" s="102"/>
-      <c r="W6" s="102"/>
-      <c r="X6" s="102"/>
-      <c r="Y6" s="102"/>
-      <c r="Z6" s="102"/>
-      <c r="AA6" s="102"/>
-      <c r="AB6" s="102"/>
-      <c r="AC6" s="102"/>
-      <c r="AD6" s="102"/>
-      <c r="AE6" s="102"/>
-      <c r="AF6" s="102"/>
-      <c r="AG6" s="102"/>
-      <c r="AH6" s="102"/>
-      <c r="AI6" s="102"/>
-      <c r="AJ6" s="102"/>
-      <c r="AK6" s="102"/>
-      <c r="AL6" s="102"/>
-      <c r="AM6" s="102"/>
-      <c r="AN6" s="102"/>
-      <c r="AO6" s="102"/>
-      <c r="AP6" s="102"/>
-      <c r="AQ6" s="102"/>
-      <c r="AR6" s="102"/>
-      <c r="AS6" s="102"/>
-      <c r="AT6" s="102"/>
-      <c r="AU6" s="102"/>
-      <c r="AV6" s="102"/>
-      <c r="AW6" s="102"/>
-      <c r="AX6" s="102"/>
-      <c r="AY6" s="102"/>
-      <c r="AZ6" s="102"/>
-      <c r="BA6" s="102"/>
-      <c r="BB6" s="102"/>
-      <c r="BC6" s="102"/>
-      <c r="BD6" s="102"/>
-      <c r="BE6" s="102"/>
-      <c r="BF6" s="102"/>
-      <c r="BG6" s="102"/>
-      <c r="BH6" s="102"/>
-      <c r="BI6" s="102"/>
-      <c r="BJ6" s="102"/>
-      <c r="BK6" s="102"/>
-      <c r="BL6" s="102"/>
-      <c r="BM6" s="102"/>
-      <c r="BN6" s="102"/>
-      <c r="BO6" s="102"/>
-      <c r="BP6" s="102"/>
-      <c r="BQ6" s="102"/>
-      <c r="BR6" s="102"/>
-      <c r="BS6" s="102"/>
-      <c r="BT6" s="102"/>
-      <c r="BU6" s="102"/>
-      <c r="BV6" s="102"/>
-      <c r="BW6" s="102"/>
-      <c r="BX6" s="102"/>
-      <c r="BY6" s="102"/>
-      <c r="BZ6" s="102"/>
-      <c r="CA6" s="102"/>
-      <c r="CB6" s="102"/>
-      <c r="CC6" s="102"/>
-      <c r="CD6" s="102"/>
-      <c r="CE6" s="102"/>
-      <c r="CF6" s="102"/>
-      <c r="CG6" s="102"/>
-      <c r="CH6" s="102"/>
-      <c r="CI6" s="102"/>
-      <c r="CJ6" s="102"/>
-      <c r="CK6" s="102"/>
-      <c r="CL6" s="102"/>
-      <c r="CM6" s="102"/>
-      <c r="CN6" s="102"/>
-      <c r="CO6" s="102"/>
-      <c r="CP6" s="102"/>
-      <c r="CQ6" s="102"/>
-      <c r="CR6" s="102"/>
-      <c r="CS6" s="102"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="70"/>
+      <c r="X6" s="70"/>
+      <c r="Y6" s="70"/>
+      <c r="Z6" s="70"/>
+      <c r="AA6" s="70"/>
+      <c r="AB6" s="70"/>
+      <c r="AC6" s="70"/>
+      <c r="AD6" s="70"/>
+      <c r="AE6" s="70"/>
+      <c r="AF6" s="70"/>
+      <c r="AG6" s="70"/>
+      <c r="AH6" s="70"/>
+      <c r="AI6" s="70"/>
+      <c r="AJ6" s="70"/>
+      <c r="AK6" s="70"/>
+      <c r="AL6" s="70"/>
+      <c r="AM6" s="70"/>
+      <c r="AN6" s="70"/>
+      <c r="AO6" s="70"/>
+      <c r="AP6" s="70"/>
+      <c r="AQ6" s="70"/>
+      <c r="AR6" s="70"/>
+      <c r="AS6" s="70"/>
+      <c r="AT6" s="70"/>
+      <c r="AU6" s="70"/>
+      <c r="AV6" s="70"/>
+      <c r="AW6" s="70"/>
+      <c r="AX6" s="70"/>
+      <c r="AY6" s="70"/>
+      <c r="AZ6" s="70"/>
+      <c r="BA6" s="70"/>
+      <c r="BB6" s="70"/>
+      <c r="BC6" s="70"/>
+      <c r="BD6" s="70"/>
+      <c r="BE6" s="70"/>
+      <c r="BF6" s="70"/>
+      <c r="BG6" s="70"/>
+      <c r="BH6" s="70"/>
+      <c r="BI6" s="70"/>
+      <c r="BJ6" s="70"/>
+      <c r="BK6" s="70"/>
+      <c r="BL6" s="70"/>
+      <c r="BM6" s="70"/>
+      <c r="BN6" s="70"/>
+      <c r="BO6" s="70"/>
+      <c r="BP6" s="70"/>
+      <c r="BQ6" s="70"/>
+      <c r="BR6" s="70"/>
+      <c r="BS6" s="70"/>
+      <c r="BT6" s="70"/>
+      <c r="BU6" s="70"/>
+      <c r="BV6" s="70"/>
+      <c r="BW6" s="70"/>
+      <c r="BX6" s="70"/>
+      <c r="BY6" s="70"/>
+      <c r="BZ6" s="70"/>
+      <c r="CA6" s="70"/>
+      <c r="CB6" s="70"/>
+      <c r="CC6" s="70"/>
+      <c r="CD6" s="70"/>
+      <c r="CE6" s="70"/>
+      <c r="CF6" s="70"/>
+      <c r="CG6" s="70"/>
+      <c r="CH6" s="70"/>
+      <c r="CI6" s="70"/>
+      <c r="CJ6" s="70"/>
+      <c r="CK6" s="70"/>
+      <c r="CL6" s="70"/>
+      <c r="CM6" s="70"/>
+      <c r="CN6" s="70"/>
+      <c r="CO6" s="70"/>
+      <c r="CP6" s="70"/>
+      <c r="CQ6" s="70"/>
+      <c r="CR6" s="70"/>
+      <c r="CS6" s="70"/>
     </row>
     <row r="7" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="105">
+      <c r="C7" s="111"/>
+      <c r="D7" s="112">
         <v>0.5</v>
       </c>
-      <c r="E7" s="106">
+      <c r="E7" s="113">
         <v>46236</v>
       </c>
-      <c r="F7" s="106">
+      <c r="F7" s="113">
         <v>46236</v>
       </c>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="102"/>
-      <c r="R7" s="102"/>
-      <c r="S7" s="102"/>
-      <c r="T7" s="102"/>
-      <c r="U7" s="102"/>
-      <c r="V7" s="102"/>
-      <c r="W7" s="102"/>
-      <c r="X7" s="102"/>
-      <c r="Y7" s="102"/>
-      <c r="Z7" s="102"/>
-      <c r="AA7" s="102"/>
-      <c r="AB7" s="102"/>
-      <c r="AC7" s="102"/>
-      <c r="AD7" s="102"/>
-      <c r="AE7" s="102"/>
-      <c r="AF7" s="102"/>
-      <c r="AG7" s="102"/>
-      <c r="AH7" s="102"/>
-      <c r="AI7" s="102"/>
-      <c r="AJ7" s="102"/>
-      <c r="AK7" s="102"/>
-      <c r="AL7" s="102"/>
-      <c r="AM7" s="102"/>
-      <c r="AN7" s="102"/>
-      <c r="AO7" s="102"/>
-      <c r="AP7" s="102"/>
-      <c r="AQ7" s="102"/>
-      <c r="AR7" s="102"/>
-      <c r="AS7" s="102"/>
-      <c r="AT7" s="102"/>
-      <c r="AU7" s="102"/>
-      <c r="AV7" s="102"/>
-      <c r="AW7" s="102"/>
-      <c r="AX7" s="102"/>
-      <c r="AY7" s="102"/>
-      <c r="AZ7" s="102"/>
-      <c r="BA7" s="102"/>
-      <c r="BB7" s="102"/>
-      <c r="BC7" s="102"/>
-      <c r="BD7" s="102"/>
-      <c r="BE7" s="102"/>
-      <c r="BF7" s="102"/>
-      <c r="BG7" s="102"/>
-      <c r="BH7" s="102"/>
-      <c r="BI7" s="102"/>
-      <c r="BJ7" s="102"/>
-      <c r="BK7" s="102"/>
-      <c r="BL7" s="102"/>
-      <c r="BM7" s="102"/>
-      <c r="BN7" s="102"/>
-      <c r="BO7" s="102"/>
-      <c r="BP7" s="102"/>
-      <c r="BQ7" s="102"/>
-      <c r="BR7" s="102"/>
-      <c r="BS7" s="102"/>
-      <c r="BT7" s="102"/>
-      <c r="BU7" s="102"/>
-      <c r="BV7" s="102"/>
-      <c r="BW7" s="102"/>
-      <c r="BX7" s="102"/>
-      <c r="BY7" s="102"/>
-      <c r="BZ7" s="102"/>
-      <c r="CA7" s="102"/>
-      <c r="CB7" s="102"/>
-      <c r="CC7" s="102"/>
-      <c r="CD7" s="102"/>
-      <c r="CE7" s="102"/>
-      <c r="CF7" s="102"/>
-      <c r="CG7" s="102"/>
-      <c r="CH7" s="102"/>
-      <c r="CI7" s="102"/>
-      <c r="CJ7" s="102"/>
-      <c r="CK7" s="102"/>
-      <c r="CL7" s="102"/>
-      <c r="CM7" s="102"/>
-      <c r="CN7" s="102"/>
-      <c r="CO7" s="102"/>
-      <c r="CP7" s="102"/>
-      <c r="CQ7" s="102"/>
-      <c r="CR7" s="102"/>
-      <c r="CS7" s="102"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="70"/>
+      <c r="T7" s="70"/>
+      <c r="U7" s="70"/>
+      <c r="V7" s="70"/>
+      <c r="W7" s="70"/>
+      <c r="X7" s="70"/>
+      <c r="Y7" s="70"/>
+      <c r="Z7" s="70"/>
+      <c r="AA7" s="70"/>
+      <c r="AB7" s="70"/>
+      <c r="AC7" s="70"/>
+      <c r="AD7" s="70"/>
+      <c r="AE7" s="70"/>
+      <c r="AF7" s="70"/>
+      <c r="AG7" s="70"/>
+      <c r="AH7" s="70"/>
+      <c r="AI7" s="70"/>
+      <c r="AJ7" s="70"/>
+      <c r="AK7" s="70"/>
+      <c r="AL7" s="70"/>
+      <c r="AM7" s="70"/>
+      <c r="AN7" s="70"/>
+      <c r="AO7" s="70"/>
+      <c r="AP7" s="70"/>
+      <c r="AQ7" s="70"/>
+      <c r="AR7" s="70"/>
+      <c r="AS7" s="70"/>
+      <c r="AT7" s="70"/>
+      <c r="AU7" s="70"/>
+      <c r="AV7" s="70"/>
+      <c r="AW7" s="70"/>
+      <c r="AX7" s="70"/>
+      <c r="AY7" s="70"/>
+      <c r="AZ7" s="70"/>
+      <c r="BA7" s="70"/>
+      <c r="BB7" s="70"/>
+      <c r="BC7" s="70"/>
+      <c r="BD7" s="70"/>
+      <c r="BE7" s="70"/>
+      <c r="BF7" s="70"/>
+      <c r="BG7" s="70"/>
+      <c r="BH7" s="70"/>
+      <c r="BI7" s="70"/>
+      <c r="BJ7" s="70"/>
+      <c r="BK7" s="70"/>
+      <c r="BL7" s="70"/>
+      <c r="BM7" s="70"/>
+      <c r="BN7" s="70"/>
+      <c r="BO7" s="70"/>
+      <c r="BP7" s="70"/>
+      <c r="BQ7" s="70"/>
+      <c r="BR7" s="70"/>
+      <c r="BS7" s="70"/>
+      <c r="BT7" s="70"/>
+      <c r="BU7" s="70"/>
+      <c r="BV7" s="70"/>
+      <c r="BW7" s="70"/>
+      <c r="BX7" s="70"/>
+      <c r="BY7" s="70"/>
+      <c r="BZ7" s="70"/>
+      <c r="CA7" s="70"/>
+      <c r="CB7" s="70"/>
+      <c r="CC7" s="70"/>
+      <c r="CD7" s="70"/>
+      <c r="CE7" s="70"/>
+      <c r="CF7" s="70"/>
+      <c r="CG7" s="70"/>
+      <c r="CH7" s="70"/>
+      <c r="CI7" s="70"/>
+      <c r="CJ7" s="70"/>
+      <c r="CK7" s="70"/>
+      <c r="CL7" s="70"/>
+      <c r="CM7" s="70"/>
+      <c r="CN7" s="70"/>
+      <c r="CO7" s="70"/>
+      <c r="CP7" s="70"/>
+      <c r="CQ7" s="70"/>
+      <c r="CR7" s="70"/>
+      <c r="CS7" s="70"/>
     </row>
     <row r="8" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="103" t="s">
+      <c r="B8" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="105">
+      <c r="C8" s="72"/>
+      <c r="D8" s="73">
         <v>1</v>
       </c>
-      <c r="E8" s="106">
+      <c r="E8" s="74">
         <v>46237</v>
       </c>
-      <c r="F8" s="106">
+      <c r="F8" s="74">
         <v>46237</v>
       </c>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="102"/>
-      <c r="N8" s="102"/>
-      <c r="O8" s="102"/>
-      <c r="P8" s="102"/>
-      <c r="Q8" s="102"/>
-      <c r="R8" s="102"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="102"/>
-      <c r="U8" s="102"/>
-      <c r="V8" s="102"/>
-      <c r="W8" s="102"/>
-      <c r="X8" s="102"/>
-      <c r="Y8" s="102"/>
-      <c r="Z8" s="102"/>
-      <c r="AA8" s="102"/>
-      <c r="AB8" s="102"/>
-      <c r="AC8" s="102"/>
-      <c r="AD8" s="102"/>
-      <c r="AE8" s="102"/>
-      <c r="AF8" s="102"/>
-      <c r="AG8" s="102"/>
-      <c r="AH8" s="102"/>
-      <c r="AI8" s="102"/>
-      <c r="AJ8" s="102"/>
-      <c r="AK8" s="102"/>
-      <c r="AL8" s="102"/>
-      <c r="AM8" s="102"/>
-      <c r="AN8" s="102"/>
-      <c r="AO8" s="102"/>
-      <c r="AP8" s="102"/>
-      <c r="AQ8" s="102"/>
-      <c r="AR8" s="102"/>
-      <c r="AS8" s="102"/>
-      <c r="AT8" s="102"/>
-      <c r="AU8" s="102"/>
-      <c r="AV8" s="102"/>
-      <c r="AW8" s="102"/>
-      <c r="AX8" s="102"/>
-      <c r="AY8" s="102"/>
-      <c r="AZ8" s="102"/>
-      <c r="BA8" s="102"/>
-      <c r="BB8" s="102"/>
-      <c r="BC8" s="102"/>
-      <c r="BD8" s="102"/>
-      <c r="BE8" s="102"/>
-      <c r="BF8" s="102"/>
-      <c r="BG8" s="102"/>
-      <c r="BH8" s="102"/>
-      <c r="BI8" s="102"/>
-      <c r="BJ8" s="102"/>
-      <c r="BK8" s="102"/>
-      <c r="BL8" s="102"/>
-      <c r="BM8" s="102"/>
-      <c r="BN8" s="102"/>
-      <c r="BO8" s="102"/>
-      <c r="BP8" s="102"/>
-      <c r="BQ8" s="102"/>
-      <c r="BR8" s="102"/>
-      <c r="BS8" s="102"/>
-      <c r="BT8" s="102"/>
-      <c r="BU8" s="102"/>
-      <c r="BV8" s="102"/>
-      <c r="BW8" s="102"/>
-      <c r="BX8" s="102"/>
-      <c r="BY8" s="102"/>
-      <c r="BZ8" s="102"/>
-      <c r="CA8" s="102"/>
-      <c r="CB8" s="102"/>
-      <c r="CC8" s="102"/>
-      <c r="CD8" s="102"/>
-      <c r="CE8" s="102"/>
-      <c r="CF8" s="102"/>
-      <c r="CG8" s="102"/>
-      <c r="CH8" s="102"/>
-      <c r="CI8" s="102"/>
-      <c r="CJ8" s="102"/>
-      <c r="CK8" s="102"/>
-      <c r="CL8" s="102"/>
-      <c r="CM8" s="102"/>
-      <c r="CN8" s="102"/>
-      <c r="CO8" s="102"/>
-      <c r="CP8" s="102"/>
-      <c r="CQ8" s="102"/>
-      <c r="CR8" s="102"/>
-      <c r="CS8" s="102"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="70"/>
+      <c r="Q8" s="70"/>
+      <c r="R8" s="70"/>
+      <c r="S8" s="70"/>
+      <c r="T8" s="70"/>
+      <c r="U8" s="70"/>
+      <c r="V8" s="70"/>
+      <c r="W8" s="70"/>
+      <c r="X8" s="70"/>
+      <c r="Y8" s="70"/>
+      <c r="Z8" s="70"/>
+      <c r="AA8" s="70"/>
+      <c r="AB8" s="70"/>
+      <c r="AC8" s="70"/>
+      <c r="AD8" s="70"/>
+      <c r="AE8" s="70"/>
+      <c r="AF8" s="70"/>
+      <c r="AG8" s="70"/>
+      <c r="AH8" s="70"/>
+      <c r="AI8" s="70"/>
+      <c r="AJ8" s="70"/>
+      <c r="AK8" s="70"/>
+      <c r="AL8" s="70"/>
+      <c r="AM8" s="70"/>
+      <c r="AN8" s="70"/>
+      <c r="AO8" s="70"/>
+      <c r="AP8" s="70"/>
+      <c r="AQ8" s="70"/>
+      <c r="AR8" s="70"/>
+      <c r="AS8" s="70"/>
+      <c r="AT8" s="70"/>
+      <c r="AU8" s="70"/>
+      <c r="AV8" s="70"/>
+      <c r="AW8" s="70"/>
+      <c r="AX8" s="70"/>
+      <c r="AY8" s="70"/>
+      <c r="AZ8" s="70"/>
+      <c r="BA8" s="70"/>
+      <c r="BB8" s="70"/>
+      <c r="BC8" s="70"/>
+      <c r="BD8" s="70"/>
+      <c r="BE8" s="70"/>
+      <c r="BF8" s="70"/>
+      <c r="BG8" s="70"/>
+      <c r="BH8" s="70"/>
+      <c r="BI8" s="70"/>
+      <c r="BJ8" s="70"/>
+      <c r="BK8" s="70"/>
+      <c r="BL8" s="70"/>
+      <c r="BM8" s="70"/>
+      <c r="BN8" s="70"/>
+      <c r="BO8" s="70"/>
+      <c r="BP8" s="70"/>
+      <c r="BQ8" s="70"/>
+      <c r="BR8" s="70"/>
+      <c r="BS8" s="70"/>
+      <c r="BT8" s="70"/>
+      <c r="BU8" s="70"/>
+      <c r="BV8" s="70"/>
+      <c r="BW8" s="70"/>
+      <c r="BX8" s="70"/>
+      <c r="BY8" s="70"/>
+      <c r="BZ8" s="70"/>
+      <c r="CA8" s="70"/>
+      <c r="CB8" s="70"/>
+      <c r="CC8" s="70"/>
+      <c r="CD8" s="70"/>
+      <c r="CE8" s="70"/>
+      <c r="CF8" s="70"/>
+      <c r="CG8" s="70"/>
+      <c r="CH8" s="70"/>
+      <c r="CI8" s="70"/>
+      <c r="CJ8" s="70"/>
+      <c r="CK8" s="70"/>
+      <c r="CL8" s="70"/>
+      <c r="CM8" s="70"/>
+      <c r="CN8" s="70"/>
+      <c r="CO8" s="70"/>
+      <c r="CP8" s="70"/>
+      <c r="CQ8" s="70"/>
+      <c r="CR8" s="70"/>
+      <c r="CS8" s="70"/>
     </row>
     <row r="9" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="104"/>
-      <c r="D9" s="105">
+      <c r="C9" s="72"/>
+      <c r="D9" s="73">
         <v>1</v>
       </c>
-      <c r="E9" s="106">
+      <c r="E9" s="74">
         <v>46238</v>
       </c>
-      <c r="F9" s="106">
+      <c r="F9" s="74">
         <v>46238</v>
       </c>
-      <c r="G9" s="102"/>
-      <c r="H9" s="102"/>
-      <c r="I9" s="102"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="102"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="102"/>
-      <c r="P9" s="102"/>
-      <c r="Q9" s="102"/>
-      <c r="R9" s="102"/>
-      <c r="S9" s="102"/>
-      <c r="T9" s="102"/>
-      <c r="U9" s="102"/>
-      <c r="V9" s="102"/>
-      <c r="W9" s="102"/>
-      <c r="X9" s="102"/>
-      <c r="Y9" s="102"/>
-      <c r="Z9" s="102"/>
-      <c r="AA9" s="102"/>
-      <c r="AB9" s="102"/>
-      <c r="AC9" s="102"/>
-      <c r="AD9" s="102"/>
-      <c r="AE9" s="102"/>
-      <c r="AF9" s="102"/>
-      <c r="AG9" s="102"/>
-      <c r="AH9" s="102"/>
-      <c r="AI9" s="102"/>
-      <c r="AJ9" s="102"/>
-      <c r="AK9" s="102"/>
-      <c r="AL9" s="102"/>
-      <c r="AM9" s="102"/>
-      <c r="AN9" s="102"/>
-      <c r="AO9" s="102"/>
-      <c r="AP9" s="102"/>
-      <c r="AQ9" s="102"/>
-      <c r="AR9" s="102"/>
-      <c r="AS9" s="102"/>
-      <c r="AT9" s="102"/>
-      <c r="AU9" s="102"/>
-      <c r="AV9" s="102"/>
-      <c r="AW9" s="102"/>
-      <c r="AX9" s="102"/>
-      <c r="AY9" s="102"/>
-      <c r="AZ9" s="102"/>
-      <c r="BA9" s="102"/>
-      <c r="BB9" s="102"/>
-      <c r="BC9" s="102"/>
-      <c r="BD9" s="102"/>
-      <c r="BE9" s="102"/>
-      <c r="BF9" s="102"/>
-      <c r="BG9" s="102"/>
-      <c r="BH9" s="102"/>
-      <c r="BI9" s="102"/>
-      <c r="BJ9" s="102"/>
-      <c r="BK9" s="102"/>
-      <c r="BL9" s="102"/>
-      <c r="BM9" s="102"/>
-      <c r="BN9" s="102"/>
-      <c r="BO9" s="102"/>
-      <c r="BP9" s="102"/>
-      <c r="BQ9" s="102"/>
-      <c r="BR9" s="102"/>
-      <c r="BS9" s="102"/>
-      <c r="BT9" s="102"/>
-      <c r="BU9" s="102"/>
-      <c r="BV9" s="102"/>
-      <c r="BW9" s="102"/>
-      <c r="BX9" s="102"/>
-      <c r="BY9" s="102"/>
-      <c r="BZ9" s="102"/>
-      <c r="CA9" s="102"/>
-      <c r="CB9" s="102"/>
-      <c r="CC9" s="102"/>
-      <c r="CD9" s="102"/>
-      <c r="CE9" s="102"/>
-      <c r="CF9" s="102"/>
-      <c r="CG9" s="102"/>
-      <c r="CH9" s="102"/>
-      <c r="CI9" s="102"/>
-      <c r="CJ9" s="102"/>
-      <c r="CK9" s="102"/>
-      <c r="CL9" s="102"/>
-      <c r="CM9" s="102"/>
-      <c r="CN9" s="102"/>
-      <c r="CO9" s="102"/>
-      <c r="CP9" s="102"/>
-      <c r="CQ9" s="102"/>
-      <c r="CR9" s="102"/>
-      <c r="CS9" s="102"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="70"/>
+      <c r="Q9" s="70"/>
+      <c r="R9" s="70"/>
+      <c r="S9" s="70"/>
+      <c r="T9" s="70"/>
+      <c r="U9" s="70"/>
+      <c r="V9" s="70"/>
+      <c r="W9" s="70"/>
+      <c r="X9" s="70"/>
+      <c r="Y9" s="70"/>
+      <c r="Z9" s="70"/>
+      <c r="AA9" s="70"/>
+      <c r="AB9" s="70"/>
+      <c r="AC9" s="70"/>
+      <c r="AD9" s="70"/>
+      <c r="AE9" s="70"/>
+      <c r="AF9" s="70"/>
+      <c r="AG9" s="70"/>
+      <c r="AH9" s="70"/>
+      <c r="AI9" s="70"/>
+      <c r="AJ9" s="70"/>
+      <c r="AK9" s="70"/>
+      <c r="AL9" s="70"/>
+      <c r="AM9" s="70"/>
+      <c r="AN9" s="70"/>
+      <c r="AO9" s="70"/>
+      <c r="AP9" s="70"/>
+      <c r="AQ9" s="70"/>
+      <c r="AR9" s="70"/>
+      <c r="AS9" s="70"/>
+      <c r="AT9" s="70"/>
+      <c r="AU9" s="70"/>
+      <c r="AV9" s="70"/>
+      <c r="AW9" s="70"/>
+      <c r="AX9" s="70"/>
+      <c r="AY9" s="70"/>
+      <c r="AZ9" s="70"/>
+      <c r="BA9" s="70"/>
+      <c r="BB9" s="70"/>
+      <c r="BC9" s="70"/>
+      <c r="BD9" s="70"/>
+      <c r="BE9" s="70"/>
+      <c r="BF9" s="70"/>
+      <c r="BG9" s="70"/>
+      <c r="BH9" s="70"/>
+      <c r="BI9" s="70"/>
+      <c r="BJ9" s="70"/>
+      <c r="BK9" s="70"/>
+      <c r="BL9" s="70"/>
+      <c r="BM9" s="70"/>
+      <c r="BN9" s="70"/>
+      <c r="BO9" s="70"/>
+      <c r="BP9" s="70"/>
+      <c r="BQ9" s="70"/>
+      <c r="BR9" s="70"/>
+      <c r="BS9" s="70"/>
+      <c r="BT9" s="70"/>
+      <c r="BU9" s="70"/>
+      <c r="BV9" s="70"/>
+      <c r="BW9" s="70"/>
+      <c r="BX9" s="70"/>
+      <c r="BY9" s="70"/>
+      <c r="BZ9" s="70"/>
+      <c r="CA9" s="70"/>
+      <c r="CB9" s="70"/>
+      <c r="CC9" s="70"/>
+      <c r="CD9" s="70"/>
+      <c r="CE9" s="70"/>
+      <c r="CF9" s="70"/>
+      <c r="CG9" s="70"/>
+      <c r="CH9" s="70"/>
+      <c r="CI9" s="70"/>
+      <c r="CJ9" s="70"/>
+      <c r="CK9" s="70"/>
+      <c r="CL9" s="70"/>
+      <c r="CM9" s="70"/>
+      <c r="CN9" s="70"/>
+      <c r="CO9" s="70"/>
+      <c r="CP9" s="70"/>
+      <c r="CQ9" s="70"/>
+      <c r="CR9" s="70"/>
+      <c r="CS9" s="70"/>
     </row>
     <row r="10" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="103" t="s">
+      <c r="B10" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="104"/>
-      <c r="D10" s="105">
+      <c r="C10" s="72"/>
+      <c r="D10" s="73">
         <v>1</v>
       </c>
-      <c r="E10" s="106">
+      <c r="E10" s="74">
         <v>46239</v>
       </c>
-      <c r="F10" s="106">
+      <c r="F10" s="74">
         <v>46239</v>
       </c>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="102"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="102"/>
-      <c r="N10" s="102"/>
-      <c r="O10" s="102"/>
-      <c r="P10" s="102"/>
-      <c r="Q10" s="102"/>
-      <c r="R10" s="102"/>
-      <c r="S10" s="102"/>
-      <c r="T10" s="102"/>
-      <c r="U10" s="102"/>
-      <c r="V10" s="102"/>
-      <c r="W10" s="102"/>
-      <c r="X10" s="102"/>
-      <c r="Y10" s="102"/>
-      <c r="Z10" s="102"/>
-      <c r="AA10" s="102"/>
-      <c r="AB10" s="102"/>
-      <c r="AC10" s="102"/>
-      <c r="AD10" s="102"/>
-      <c r="AE10" s="102"/>
-      <c r="AF10" s="102"/>
-      <c r="AG10" s="102"/>
-      <c r="AH10" s="102"/>
-      <c r="AI10" s="102"/>
-      <c r="AJ10" s="102"/>
-      <c r="AK10" s="102"/>
-      <c r="AL10" s="102"/>
-      <c r="AM10" s="102"/>
-      <c r="AN10" s="102"/>
-      <c r="AO10" s="102"/>
-      <c r="AP10" s="102"/>
-      <c r="AQ10" s="102"/>
-      <c r="AR10" s="102"/>
-      <c r="AS10" s="102"/>
-      <c r="AT10" s="102"/>
-      <c r="AU10" s="102"/>
-      <c r="AV10" s="102"/>
-      <c r="AW10" s="102"/>
-      <c r="AX10" s="102"/>
-      <c r="AY10" s="102"/>
-      <c r="AZ10" s="102"/>
-      <c r="BA10" s="102"/>
-      <c r="BB10" s="102"/>
-      <c r="BC10" s="102"/>
-      <c r="BD10" s="102"/>
-      <c r="BE10" s="102"/>
-      <c r="BF10" s="102"/>
-      <c r="BG10" s="102"/>
-      <c r="BH10" s="102"/>
-      <c r="BI10" s="102"/>
-      <c r="BJ10" s="102"/>
-      <c r="BK10" s="102"/>
-      <c r="BL10" s="102"/>
-      <c r="BM10" s="102"/>
-      <c r="BN10" s="102"/>
-      <c r="BO10" s="102"/>
-      <c r="BP10" s="102"/>
-      <c r="BQ10" s="102"/>
-      <c r="BR10" s="102"/>
-      <c r="BS10" s="102"/>
-      <c r="BT10" s="102"/>
-      <c r="BU10" s="102"/>
-      <c r="BV10" s="102"/>
-      <c r="BW10" s="102"/>
-      <c r="BX10" s="102"/>
-      <c r="BY10" s="102"/>
-      <c r="BZ10" s="102"/>
-      <c r="CA10" s="102"/>
-      <c r="CB10" s="102"/>
-      <c r="CC10" s="102"/>
-      <c r="CD10" s="102"/>
-      <c r="CE10" s="102"/>
-      <c r="CF10" s="102"/>
-      <c r="CG10" s="102"/>
-      <c r="CH10" s="102"/>
-      <c r="CI10" s="102"/>
-      <c r="CJ10" s="102"/>
-      <c r="CK10" s="102"/>
-      <c r="CL10" s="102"/>
-      <c r="CM10" s="102"/>
-      <c r="CN10" s="102"/>
-      <c r="CO10" s="102"/>
-      <c r="CP10" s="102"/>
-      <c r="CQ10" s="102"/>
-      <c r="CR10" s="102"/>
-      <c r="CS10" s="102"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="70"/>
+      <c r="Q10" s="70"/>
+      <c r="R10" s="70"/>
+      <c r="S10" s="70"/>
+      <c r="T10" s="70"/>
+      <c r="U10" s="70"/>
+      <c r="V10" s="70"/>
+      <c r="W10" s="70"/>
+      <c r="X10" s="70"/>
+      <c r="Y10" s="70"/>
+      <c r="Z10" s="70"/>
+      <c r="AA10" s="70"/>
+      <c r="AB10" s="70"/>
+      <c r="AC10" s="70"/>
+      <c r="AD10" s="70"/>
+      <c r="AE10" s="70"/>
+      <c r="AF10" s="70"/>
+      <c r="AG10" s="70"/>
+      <c r="AH10" s="70"/>
+      <c r="AI10" s="70"/>
+      <c r="AJ10" s="70"/>
+      <c r="AK10" s="70"/>
+      <c r="AL10" s="70"/>
+      <c r="AM10" s="70"/>
+      <c r="AN10" s="70"/>
+      <c r="AO10" s="70"/>
+      <c r="AP10" s="70"/>
+      <c r="AQ10" s="70"/>
+      <c r="AR10" s="70"/>
+      <c r="AS10" s="70"/>
+      <c r="AT10" s="70"/>
+      <c r="AU10" s="70"/>
+      <c r="AV10" s="70"/>
+      <c r="AW10" s="70"/>
+      <c r="AX10" s="70"/>
+      <c r="AY10" s="70"/>
+      <c r="AZ10" s="70"/>
+      <c r="BA10" s="70"/>
+      <c r="BB10" s="70"/>
+      <c r="BC10" s="70"/>
+      <c r="BD10" s="70"/>
+      <c r="BE10" s="70"/>
+      <c r="BF10" s="70"/>
+      <c r="BG10" s="70"/>
+      <c r="BH10" s="70"/>
+      <c r="BI10" s="70"/>
+      <c r="BJ10" s="70"/>
+      <c r="BK10" s="70"/>
+      <c r="BL10" s="70"/>
+      <c r="BM10" s="70"/>
+      <c r="BN10" s="70"/>
+      <c r="BO10" s="70"/>
+      <c r="BP10" s="70"/>
+      <c r="BQ10" s="70"/>
+      <c r="BR10" s="70"/>
+      <c r="BS10" s="70"/>
+      <c r="BT10" s="70"/>
+      <c r="BU10" s="70"/>
+      <c r="BV10" s="70"/>
+      <c r="BW10" s="70"/>
+      <c r="BX10" s="70"/>
+      <c r="BY10" s="70"/>
+      <c r="BZ10" s="70"/>
+      <c r="CA10" s="70"/>
+      <c r="CB10" s="70"/>
+      <c r="CC10" s="70"/>
+      <c r="CD10" s="70"/>
+      <c r="CE10" s="70"/>
+      <c r="CF10" s="70"/>
+      <c r="CG10" s="70"/>
+      <c r="CH10" s="70"/>
+      <c r="CI10" s="70"/>
+      <c r="CJ10" s="70"/>
+      <c r="CK10" s="70"/>
+      <c r="CL10" s="70"/>
+      <c r="CM10" s="70"/>
+      <c r="CN10" s="70"/>
+      <c r="CO10" s="70"/>
+      <c r="CP10" s="70"/>
+      <c r="CQ10" s="70"/>
+      <c r="CR10" s="70"/>
+      <c r="CS10" s="70"/>
     </row>
     <row r="11" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="103" t="s">
+      <c r="B11" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="104"/>
-      <c r="D11" s="105">
+      <c r="C11" s="72"/>
+      <c r="D11" s="73">
         <v>0</v>
       </c>
-      <c r="E11" s="106">
+      <c r="E11" s="74">
         <v>46240</v>
       </c>
-      <c r="F11" s="106">
+      <c r="F11" s="74">
         <v>46240</v>
       </c>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
-      <c r="I11" s="102"/>
-      <c r="J11" s="102"/>
-      <c r="K11" s="102"/>
-      <c r="L11" s="102"/>
-      <c r="M11" s="102"/>
-      <c r="N11" s="102"/>
-      <c r="O11" s="102"/>
-      <c r="P11" s="102"/>
-      <c r="Q11" s="102"/>
-      <c r="R11" s="102"/>
-      <c r="S11" s="102"/>
-      <c r="T11" s="102"/>
-      <c r="U11" s="102"/>
-      <c r="V11" s="102"/>
-      <c r="W11" s="102"/>
-      <c r="X11" s="102"/>
-      <c r="Y11" s="102"/>
-      <c r="Z11" s="102"/>
-      <c r="AA11" s="102"/>
-      <c r="AB11" s="102"/>
-      <c r="AC11" s="102"/>
-      <c r="AD11" s="102"/>
-      <c r="AE11" s="102"/>
-      <c r="AF11" s="102"/>
-      <c r="AG11" s="102"/>
-      <c r="AH11" s="102"/>
-      <c r="AI11" s="102"/>
-      <c r="AJ11" s="102"/>
-      <c r="AK11" s="102"/>
-      <c r="AL11" s="102"/>
-      <c r="AM11" s="102"/>
-      <c r="AN11" s="102"/>
-      <c r="AO11" s="102"/>
-      <c r="AP11" s="102"/>
-      <c r="AQ11" s="102"/>
-      <c r="AR11" s="102"/>
-      <c r="AS11" s="102"/>
-      <c r="AT11" s="102"/>
-      <c r="AU11" s="102"/>
-      <c r="AV11" s="102"/>
-      <c r="AW11" s="102"/>
-      <c r="AX11" s="102"/>
-      <c r="AY11" s="102"/>
-      <c r="AZ11" s="102"/>
-      <c r="BA11" s="102"/>
-      <c r="BB11" s="102"/>
-      <c r="BC11" s="102"/>
-      <c r="BD11" s="102"/>
-      <c r="BE11" s="102"/>
-      <c r="BF11" s="102"/>
-      <c r="BG11" s="102"/>
-      <c r="BH11" s="102"/>
-      <c r="BI11" s="102"/>
-      <c r="BJ11" s="102"/>
-      <c r="BK11" s="102"/>
-      <c r="BL11" s="102"/>
-      <c r="BM11" s="102"/>
-      <c r="BN11" s="102"/>
-      <c r="BO11" s="102"/>
-      <c r="BP11" s="102"/>
-      <c r="BQ11" s="102"/>
-      <c r="BR11" s="102"/>
-      <c r="BS11" s="102"/>
-      <c r="BT11" s="102"/>
-      <c r="BU11" s="102"/>
-      <c r="BV11" s="102"/>
-      <c r="BW11" s="102"/>
-      <c r="BX11" s="102"/>
-      <c r="BY11" s="102"/>
-      <c r="BZ11" s="102"/>
-      <c r="CA11" s="102"/>
-      <c r="CB11" s="102"/>
-      <c r="CC11" s="102"/>
-      <c r="CD11" s="102"/>
-      <c r="CE11" s="102"/>
-      <c r="CF11" s="102"/>
-      <c r="CG11" s="102"/>
-      <c r="CH11" s="102"/>
-      <c r="CI11" s="102"/>
-      <c r="CJ11" s="102"/>
-      <c r="CK11" s="102"/>
-      <c r="CL11" s="102"/>
-      <c r="CM11" s="102"/>
-      <c r="CN11" s="102"/>
-      <c r="CO11" s="102"/>
-      <c r="CP11" s="102"/>
-      <c r="CQ11" s="102"/>
-      <c r="CR11" s="102"/>
-      <c r="CS11" s="102"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="70"/>
+      <c r="N11" s="70"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="70"/>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="70"/>
+      <c r="T11" s="70"/>
+      <c r="U11" s="70"/>
+      <c r="V11" s="70"/>
+      <c r="W11" s="70"/>
+      <c r="X11" s="70"/>
+      <c r="Y11" s="70"/>
+      <c r="Z11" s="70"/>
+      <c r="AA11" s="70"/>
+      <c r="AB11" s="70"/>
+      <c r="AC11" s="70"/>
+      <c r="AD11" s="70"/>
+      <c r="AE11" s="70"/>
+      <c r="AF11" s="70"/>
+      <c r="AG11" s="70"/>
+      <c r="AH11" s="70"/>
+      <c r="AI11" s="70"/>
+      <c r="AJ11" s="70"/>
+      <c r="AK11" s="70"/>
+      <c r="AL11" s="70"/>
+      <c r="AM11" s="70"/>
+      <c r="AN11" s="70"/>
+      <c r="AO11" s="70"/>
+      <c r="AP11" s="70"/>
+      <c r="AQ11" s="70"/>
+      <c r="AR11" s="70"/>
+      <c r="AS11" s="70"/>
+      <c r="AT11" s="70"/>
+      <c r="AU11" s="70"/>
+      <c r="AV11" s="70"/>
+      <c r="AW11" s="70"/>
+      <c r="AX11" s="70"/>
+      <c r="AY11" s="70"/>
+      <c r="AZ11" s="70"/>
+      <c r="BA11" s="70"/>
+      <c r="BB11" s="70"/>
+      <c r="BC11" s="70"/>
+      <c r="BD11" s="70"/>
+      <c r="BE11" s="70"/>
+      <c r="BF11" s="70"/>
+      <c r="BG11" s="70"/>
+      <c r="BH11" s="70"/>
+      <c r="BI11" s="70"/>
+      <c r="BJ11" s="70"/>
+      <c r="BK11" s="70"/>
+      <c r="BL11" s="70"/>
+      <c r="BM11" s="70"/>
+      <c r="BN11" s="70"/>
+      <c r="BO11" s="70"/>
+      <c r="BP11" s="70"/>
+      <c r="BQ11" s="70"/>
+      <c r="BR11" s="70"/>
+      <c r="BS11" s="70"/>
+      <c r="BT11" s="70"/>
+      <c r="BU11" s="70"/>
+      <c r="BV11" s="70"/>
+      <c r="BW11" s="70"/>
+      <c r="BX11" s="70"/>
+      <c r="BY11" s="70"/>
+      <c r="BZ11" s="70"/>
+      <c r="CA11" s="70"/>
+      <c r="CB11" s="70"/>
+      <c r="CC11" s="70"/>
+      <c r="CD11" s="70"/>
+      <c r="CE11" s="70"/>
+      <c r="CF11" s="70"/>
+      <c r="CG11" s="70"/>
+      <c r="CH11" s="70"/>
+      <c r="CI11" s="70"/>
+      <c r="CJ11" s="70"/>
+      <c r="CK11" s="70"/>
+      <c r="CL11" s="70"/>
+      <c r="CM11" s="70"/>
+      <c r="CN11" s="70"/>
+      <c r="CO11" s="70"/>
+      <c r="CP11" s="70"/>
+      <c r="CQ11" s="70"/>
+      <c r="CR11" s="70"/>
+      <c r="CS11" s="70"/>
     </row>
     <row r="12" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="103"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="102"/>
-      <c r="K12" s="102"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="102"/>
-      <c r="N12" s="102"/>
-      <c r="O12" s="102"/>
-      <c r="P12" s="102"/>
-      <c r="Q12" s="102"/>
-      <c r="R12" s="102"/>
-      <c r="S12" s="102"/>
-      <c r="T12" s="102"/>
-      <c r="U12" s="102"/>
-      <c r="V12" s="102"/>
-      <c r="W12" s="102"/>
-      <c r="X12" s="102"/>
-      <c r="Y12" s="102"/>
-      <c r="Z12" s="102"/>
-      <c r="AA12" s="102"/>
-      <c r="AB12" s="102"/>
-      <c r="AC12" s="102"/>
-      <c r="AD12" s="102"/>
-      <c r="AE12" s="102"/>
-      <c r="AF12" s="102"/>
-      <c r="AG12" s="102"/>
-      <c r="AH12" s="102"/>
-      <c r="AI12" s="102"/>
-      <c r="AJ12" s="102"/>
-      <c r="AK12" s="102"/>
-      <c r="AL12" s="102"/>
-      <c r="AM12" s="102"/>
-      <c r="AN12" s="102"/>
-      <c r="AO12" s="102"/>
-      <c r="AP12" s="102"/>
-      <c r="AQ12" s="102"/>
-      <c r="AR12" s="102"/>
-      <c r="AS12" s="102"/>
-      <c r="AT12" s="102"/>
-      <c r="AU12" s="102"/>
-      <c r="AV12" s="102"/>
-      <c r="AW12" s="102"/>
-      <c r="AX12" s="102"/>
-      <c r="AY12" s="102"/>
-      <c r="AZ12" s="102"/>
-      <c r="BA12" s="102"/>
-      <c r="BB12" s="102"/>
-      <c r="BC12" s="102"/>
-      <c r="BD12" s="102"/>
-      <c r="BE12" s="102"/>
-      <c r="BF12" s="102"/>
-      <c r="BG12" s="102"/>
-      <c r="BH12" s="102"/>
-      <c r="BI12" s="102"/>
-      <c r="BJ12" s="102"/>
-      <c r="BK12" s="102"/>
-      <c r="BL12" s="102"/>
-      <c r="BM12" s="102"/>
-      <c r="BN12" s="102"/>
-      <c r="BO12" s="102"/>
-      <c r="BP12" s="102"/>
-      <c r="BQ12" s="102"/>
-      <c r="BR12" s="102"/>
-      <c r="BS12" s="102"/>
-      <c r="BT12" s="102"/>
-      <c r="BU12" s="102"/>
-      <c r="BV12" s="102"/>
-      <c r="BW12" s="102"/>
-      <c r="BX12" s="102"/>
-      <c r="BY12" s="102"/>
-      <c r="BZ12" s="102"/>
-      <c r="CA12" s="102"/>
-      <c r="CB12" s="102"/>
-      <c r="CC12" s="102"/>
-      <c r="CD12" s="102"/>
-      <c r="CE12" s="102"/>
-      <c r="CF12" s="102"/>
-      <c r="CG12" s="102"/>
-      <c r="CH12" s="102"/>
-      <c r="CI12" s="102"/>
-      <c r="CJ12" s="102"/>
-      <c r="CK12" s="102"/>
-      <c r="CL12" s="102"/>
-      <c r="CM12" s="102"/>
-      <c r="CN12" s="102"/>
-      <c r="CO12" s="102"/>
-      <c r="CP12" s="102"/>
-      <c r="CQ12" s="102"/>
-      <c r="CR12" s="102"/>
-      <c r="CS12" s="102"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="70"/>
+      <c r="P12" s="70"/>
+      <c r="Q12" s="70"/>
+      <c r="R12" s="70"/>
+      <c r="S12" s="70"/>
+      <c r="T12" s="70"/>
+      <c r="U12" s="70"/>
+      <c r="V12" s="70"/>
+      <c r="W12" s="70"/>
+      <c r="X12" s="70"/>
+      <c r="Y12" s="70"/>
+      <c r="Z12" s="70"/>
+      <c r="AA12" s="70"/>
+      <c r="AB12" s="70"/>
+      <c r="AC12" s="70"/>
+      <c r="AD12" s="70"/>
+      <c r="AE12" s="70"/>
+      <c r="AF12" s="70"/>
+      <c r="AG12" s="70"/>
+      <c r="AH12" s="70"/>
+      <c r="AI12" s="70"/>
+      <c r="AJ12" s="70"/>
+      <c r="AK12" s="70"/>
+      <c r="AL12" s="70"/>
+      <c r="AM12" s="70"/>
+      <c r="AN12" s="70"/>
+      <c r="AO12" s="70"/>
+      <c r="AP12" s="70"/>
+      <c r="AQ12" s="70"/>
+      <c r="AR12" s="70"/>
+      <c r="AS12" s="70"/>
+      <c r="AT12" s="70"/>
+      <c r="AU12" s="70"/>
+      <c r="AV12" s="70"/>
+      <c r="AW12" s="70"/>
+      <c r="AX12" s="70"/>
+      <c r="AY12" s="70"/>
+      <c r="AZ12" s="70"/>
+      <c r="BA12" s="70"/>
+      <c r="BB12" s="70"/>
+      <c r="BC12" s="70"/>
+      <c r="BD12" s="70"/>
+      <c r="BE12" s="70"/>
+      <c r="BF12" s="70"/>
+      <c r="BG12" s="70"/>
+      <c r="BH12" s="70"/>
+      <c r="BI12" s="70"/>
+      <c r="BJ12" s="70"/>
+      <c r="BK12" s="70"/>
+      <c r="BL12" s="70"/>
+      <c r="BM12" s="70"/>
+      <c r="BN12" s="70"/>
+      <c r="BO12" s="70"/>
+      <c r="BP12" s="70"/>
+      <c r="BQ12" s="70"/>
+      <c r="BR12" s="70"/>
+      <c r="BS12" s="70"/>
+      <c r="BT12" s="70"/>
+      <c r="BU12" s="70"/>
+      <c r="BV12" s="70"/>
+      <c r="BW12" s="70"/>
+      <c r="BX12" s="70"/>
+      <c r="BY12" s="70"/>
+      <c r="BZ12" s="70"/>
+      <c r="CA12" s="70"/>
+      <c r="CB12" s="70"/>
+      <c r="CC12" s="70"/>
+      <c r="CD12" s="70"/>
+      <c r="CE12" s="70"/>
+      <c r="CF12" s="70"/>
+      <c r="CG12" s="70"/>
+      <c r="CH12" s="70"/>
+      <c r="CI12" s="70"/>
+      <c r="CJ12" s="70"/>
+      <c r="CK12" s="70"/>
+      <c r="CL12" s="70"/>
+      <c r="CM12" s="70"/>
+      <c r="CN12" s="70"/>
+      <c r="CO12" s="70"/>
+      <c r="CP12" s="70"/>
+      <c r="CQ12" s="70"/>
+      <c r="CR12" s="70"/>
+      <c r="CS12" s="70"/>
     </row>
     <row r="13" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="100">
+      <c r="C13" s="114"/>
+      <c r="D13" s="115">
+        <f>SUM(D14:D22)</f>
+        <v>21</v>
+      </c>
+      <c r="E13" s="116">
         <v>46241</v>
       </c>
-      <c r="F13" s="101">
+      <c r="F13" s="116">
         <v>46260</v>
       </c>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="102"/>
-      <c r="K13" s="102"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="102"/>
-      <c r="N13" s="102"/>
-      <c r="O13" s="102"/>
-      <c r="P13" s="102"/>
-      <c r="Q13" s="102"/>
-      <c r="R13" s="102"/>
-      <c r="S13" s="102"/>
-      <c r="T13" s="102"/>
-      <c r="U13" s="102"/>
-      <c r="V13" s="102"/>
-      <c r="W13" s="102"/>
-      <c r="X13" s="102"/>
-      <c r="Y13" s="102"/>
-      <c r="Z13" s="102"/>
-      <c r="AA13" s="102"/>
-      <c r="AB13" s="102"/>
-      <c r="AC13" s="102"/>
-      <c r="AD13" s="102"/>
-      <c r="AE13" s="102"/>
-      <c r="AF13" s="102"/>
-      <c r="AG13" s="102"/>
-      <c r="AH13" s="102"/>
-      <c r="AI13" s="102"/>
-      <c r="AJ13" s="102"/>
-      <c r="AK13" s="102"/>
-      <c r="AL13" s="102"/>
-      <c r="AM13" s="102"/>
-      <c r="AN13" s="102"/>
-      <c r="AO13" s="102"/>
-      <c r="AP13" s="102"/>
-      <c r="AQ13" s="102"/>
-      <c r="AR13" s="102"/>
-      <c r="AS13" s="102"/>
-      <c r="AT13" s="102"/>
-      <c r="AU13" s="102"/>
-      <c r="AV13" s="102"/>
-      <c r="AW13" s="102"/>
-      <c r="AX13" s="102"/>
-      <c r="AY13" s="102"/>
-      <c r="AZ13" s="102"/>
-      <c r="BA13" s="102"/>
-      <c r="BB13" s="102"/>
-      <c r="BC13" s="102"/>
-      <c r="BD13" s="102"/>
-      <c r="BE13" s="102"/>
-      <c r="BF13" s="102"/>
-      <c r="BG13" s="102"/>
-      <c r="BH13" s="102"/>
-      <c r="BI13" s="102"/>
-      <c r="BJ13" s="102"/>
-      <c r="BK13" s="102"/>
-      <c r="BL13" s="102"/>
-      <c r="BM13" s="102"/>
-      <c r="BN13" s="102"/>
-      <c r="BO13" s="102"/>
-      <c r="BP13" s="102"/>
-      <c r="BQ13" s="102"/>
-      <c r="BR13" s="102"/>
-      <c r="BS13" s="102"/>
-      <c r="BT13" s="102"/>
-      <c r="BU13" s="102"/>
-      <c r="BV13" s="102"/>
-      <c r="BW13" s="102"/>
-      <c r="BX13" s="102"/>
-      <c r="BY13" s="102"/>
-      <c r="BZ13" s="102"/>
-      <c r="CA13" s="102"/>
-      <c r="CB13" s="102"/>
-      <c r="CC13" s="102"/>
-      <c r="CD13" s="102"/>
-      <c r="CE13" s="102"/>
-      <c r="CF13" s="102"/>
-      <c r="CG13" s="102"/>
-      <c r="CH13" s="102"/>
-      <c r="CI13" s="102"/>
-      <c r="CJ13" s="102"/>
-      <c r="CK13" s="102"/>
-      <c r="CL13" s="102"/>
-      <c r="CM13" s="102"/>
-      <c r="CN13" s="102"/>
-      <c r="CO13" s="102"/>
-      <c r="CP13" s="102"/>
-      <c r="CQ13" s="102"/>
-      <c r="CR13" s="102"/>
-      <c r="CS13" s="102"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="70"/>
+      <c r="Q13" s="70"/>
+      <c r="R13" s="70"/>
+      <c r="S13" s="70"/>
+      <c r="T13" s="70"/>
+      <c r="U13" s="70"/>
+      <c r="V13" s="70"/>
+      <c r="W13" s="70"/>
+      <c r="X13" s="70"/>
+      <c r="Y13" s="70"/>
+      <c r="Z13" s="70"/>
+      <c r="AA13" s="70"/>
+      <c r="AB13" s="70"/>
+      <c r="AC13" s="70"/>
+      <c r="AD13" s="70"/>
+      <c r="AE13" s="70"/>
+      <c r="AF13" s="70"/>
+      <c r="AG13" s="70"/>
+      <c r="AH13" s="70"/>
+      <c r="AI13" s="70"/>
+      <c r="AJ13" s="70"/>
+      <c r="AK13" s="70"/>
+      <c r="AL13" s="70"/>
+      <c r="AM13" s="70"/>
+      <c r="AN13" s="70"/>
+      <c r="AO13" s="70"/>
+      <c r="AP13" s="70"/>
+      <c r="AQ13" s="70"/>
+      <c r="AR13" s="70"/>
+      <c r="AS13" s="70"/>
+      <c r="AT13" s="70"/>
+      <c r="AU13" s="70"/>
+      <c r="AV13" s="70"/>
+      <c r="AW13" s="70"/>
+      <c r="AX13" s="70"/>
+      <c r="AY13" s="70"/>
+      <c r="AZ13" s="70"/>
+      <c r="BA13" s="70"/>
+      <c r="BB13" s="70"/>
+      <c r="BC13" s="70"/>
+      <c r="BD13" s="70"/>
+      <c r="BE13" s="70"/>
+      <c r="BF13" s="70"/>
+      <c r="BG13" s="70"/>
+      <c r="BH13" s="70"/>
+      <c r="BI13" s="70"/>
+      <c r="BJ13" s="70"/>
+      <c r="BK13" s="70"/>
+      <c r="BL13" s="70"/>
+      <c r="BM13" s="70"/>
+      <c r="BN13" s="70"/>
+      <c r="BO13" s="70"/>
+      <c r="BP13" s="70"/>
+      <c r="BQ13" s="70"/>
+      <c r="BR13" s="70"/>
+      <c r="BS13" s="70"/>
+      <c r="BT13" s="70"/>
+      <c r="BU13" s="70"/>
+      <c r="BV13" s="70"/>
+      <c r="BW13" s="70"/>
+      <c r="BX13" s="70"/>
+      <c r="BY13" s="70"/>
+      <c r="BZ13" s="70"/>
+      <c r="CA13" s="70"/>
+      <c r="CB13" s="70"/>
+      <c r="CC13" s="70"/>
+      <c r="CD13" s="70"/>
+      <c r="CE13" s="70"/>
+      <c r="CF13" s="70"/>
+      <c r="CG13" s="70"/>
+      <c r="CH13" s="70"/>
+      <c r="CI13" s="70"/>
+      <c r="CJ13" s="70"/>
+      <c r="CK13" s="70"/>
+      <c r="CL13" s="70"/>
+      <c r="CM13" s="70"/>
+      <c r="CN13" s="70"/>
+      <c r="CO13" s="70"/>
+      <c r="CP13" s="70"/>
+      <c r="CQ13" s="70"/>
+      <c r="CR13" s="70"/>
+      <c r="CS13" s="70"/>
     </row>
     <row r="14" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="107" t="s">
+      <c r="B14" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="104"/>
-      <c r="D14" s="105">
+      <c r="C14" s="111"/>
+      <c r="D14" s="112">
         <v>5</v>
       </c>
-      <c r="E14" s="106">
+      <c r="E14" s="113">
         <v>46241</v>
       </c>
-      <c r="F14" s="106">
+      <c r="F14" s="113">
         <v>46245</v>
       </c>
-      <c r="G14" s="102"/>
-      <c r="H14" s="102"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="102"/>
-      <c r="M14" s="102"/>
-      <c r="N14" s="102"/>
-      <c r="O14" s="102"/>
-      <c r="P14" s="102"/>
-      <c r="Q14" s="102"/>
-      <c r="R14" s="102"/>
-      <c r="S14" s="102"/>
-      <c r="T14" s="102"/>
-      <c r="U14" s="102"/>
-      <c r="V14" s="102"/>
-      <c r="W14" s="102"/>
-      <c r="X14" s="102"/>
-      <c r="Y14" s="102"/>
-      <c r="Z14" s="102"/>
-      <c r="AA14" s="102"/>
-      <c r="AB14" s="102"/>
-      <c r="AC14" s="102"/>
-      <c r="AD14" s="102"/>
-      <c r="AE14" s="102"/>
-      <c r="AF14" s="102"/>
-      <c r="AG14" s="102"/>
-      <c r="AH14" s="102"/>
-      <c r="AI14" s="102"/>
-      <c r="AJ14" s="102"/>
-      <c r="AK14" s="102"/>
-      <c r="AL14" s="102"/>
-      <c r="AM14" s="102"/>
-      <c r="AN14" s="102"/>
-      <c r="AO14" s="102"/>
-      <c r="AP14" s="102"/>
-      <c r="AQ14" s="102"/>
-      <c r="AR14" s="102"/>
-      <c r="AS14" s="102"/>
-      <c r="AT14" s="102"/>
-      <c r="AU14" s="102"/>
-      <c r="AV14" s="102"/>
-      <c r="AW14" s="102"/>
-      <c r="AX14" s="102"/>
-      <c r="AY14" s="102"/>
-      <c r="AZ14" s="102"/>
-      <c r="BA14" s="102"/>
-      <c r="BB14" s="102"/>
-      <c r="BC14" s="102"/>
-      <c r="BD14" s="102"/>
-      <c r="BE14" s="102"/>
-      <c r="BF14" s="102"/>
-      <c r="BG14" s="102"/>
-      <c r="BH14" s="102"/>
-      <c r="BI14" s="102"/>
-      <c r="BJ14" s="102"/>
-      <c r="BK14" s="102"/>
-      <c r="BL14" s="102"/>
-      <c r="BM14" s="102"/>
-      <c r="BN14" s="102"/>
-      <c r="BO14" s="102"/>
-      <c r="BP14" s="102"/>
-      <c r="BQ14" s="102"/>
-      <c r="BR14" s="102"/>
-      <c r="BS14" s="102"/>
-      <c r="BT14" s="102"/>
-      <c r="BU14" s="102"/>
-      <c r="BV14" s="102"/>
-      <c r="BW14" s="102"/>
-      <c r="BX14" s="102"/>
-      <c r="BY14" s="102"/>
-      <c r="BZ14" s="102"/>
-      <c r="CA14" s="102"/>
-      <c r="CB14" s="102"/>
-      <c r="CC14" s="102"/>
-      <c r="CD14" s="102"/>
-      <c r="CE14" s="102"/>
-      <c r="CF14" s="102"/>
-      <c r="CG14" s="102"/>
-      <c r="CH14" s="102"/>
-      <c r="CI14" s="102"/>
-      <c r="CJ14" s="102"/>
-      <c r="CK14" s="102"/>
-      <c r="CL14" s="102"/>
-      <c r="CM14" s="102"/>
-      <c r="CN14" s="102"/>
-      <c r="CO14" s="102"/>
-      <c r="CP14" s="102"/>
-      <c r="CQ14" s="102"/>
-      <c r="CR14" s="102"/>
-      <c r="CS14" s="102"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="70"/>
+      <c r="M14" s="70"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="70"/>
+      <c r="Q14" s="70"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="70"/>
+      <c r="T14" s="70"/>
+      <c r="U14" s="70"/>
+      <c r="V14" s="70"/>
+      <c r="W14" s="70"/>
+      <c r="X14" s="70"/>
+      <c r="Y14" s="70"/>
+      <c r="Z14" s="70"/>
+      <c r="AA14" s="70"/>
+      <c r="AB14" s="70"/>
+      <c r="AC14" s="70"/>
+      <c r="AD14" s="70"/>
+      <c r="AE14" s="70"/>
+      <c r="AF14" s="70"/>
+      <c r="AG14" s="70"/>
+      <c r="AH14" s="70"/>
+      <c r="AI14" s="70"/>
+      <c r="AJ14" s="70"/>
+      <c r="AK14" s="70"/>
+      <c r="AL14" s="70"/>
+      <c r="AM14" s="70"/>
+      <c r="AN14" s="70"/>
+      <c r="AO14" s="70"/>
+      <c r="AP14" s="70"/>
+      <c r="AQ14" s="70"/>
+      <c r="AR14" s="70"/>
+      <c r="AS14" s="70"/>
+      <c r="AT14" s="70"/>
+      <c r="AU14" s="70"/>
+      <c r="AV14" s="70"/>
+      <c r="AW14" s="70"/>
+      <c r="AX14" s="70"/>
+      <c r="AY14" s="70"/>
+      <c r="AZ14" s="70"/>
+      <c r="BA14" s="70"/>
+      <c r="BB14" s="70"/>
+      <c r="BC14" s="70"/>
+      <c r="BD14" s="70"/>
+      <c r="BE14" s="70"/>
+      <c r="BF14" s="70"/>
+      <c r="BG14" s="70"/>
+      <c r="BH14" s="70"/>
+      <c r="BI14" s="70"/>
+      <c r="BJ14" s="70"/>
+      <c r="BK14" s="70"/>
+      <c r="BL14" s="70"/>
+      <c r="BM14" s="70"/>
+      <c r="BN14" s="70"/>
+      <c r="BO14" s="70"/>
+      <c r="BP14" s="70"/>
+      <c r="BQ14" s="70"/>
+      <c r="BR14" s="70"/>
+      <c r="BS14" s="70"/>
+      <c r="BT14" s="70"/>
+      <c r="BU14" s="70"/>
+      <c r="BV14" s="70"/>
+      <c r="BW14" s="70"/>
+      <c r="BX14" s="70"/>
+      <c r="BY14" s="70"/>
+      <c r="BZ14" s="70"/>
+      <c r="CA14" s="70"/>
+      <c r="CB14" s="70"/>
+      <c r="CC14" s="70"/>
+      <c r="CD14" s="70"/>
+      <c r="CE14" s="70"/>
+      <c r="CF14" s="70"/>
+      <c r="CG14" s="70"/>
+      <c r="CH14" s="70"/>
+      <c r="CI14" s="70"/>
+      <c r="CJ14" s="70"/>
+      <c r="CK14" s="70"/>
+      <c r="CL14" s="70"/>
+      <c r="CM14" s="70"/>
+      <c r="CN14" s="70"/>
+      <c r="CO14" s="70"/>
+      <c r="CP14" s="70"/>
+      <c r="CQ14" s="70"/>
+      <c r="CR14" s="70"/>
+      <c r="CS14" s="70"/>
     </row>
     <row r="15" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="107" t="s">
+      <c r="B15" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="109"/>
-      <c r="D15" s="110">
+      <c r="C15" s="77"/>
+      <c r="D15" s="78">
         <v>7.5</v>
       </c>
-      <c r="E15" s="111">
+      <c r="E15" s="79">
         <v>46246</v>
       </c>
-      <c r="F15" s="106">
+      <c r="F15" s="74">
         <v>46252</v>
       </c>
-      <c r="G15" s="102"/>
-      <c r="H15" s="102"/>
-      <c r="I15" s="102"/>
-      <c r="J15" s="102"/>
-      <c r="K15" s="102"/>
-      <c r="L15" s="102"/>
-      <c r="M15" s="102"/>
-      <c r="N15" s="102"/>
-      <c r="O15" s="102"/>
-      <c r="P15" s="102"/>
-      <c r="Q15" s="102"/>
-      <c r="R15" s="102"/>
-      <c r="S15" s="102"/>
-      <c r="T15" s="102"/>
-      <c r="U15" s="102"/>
-      <c r="V15" s="102"/>
-      <c r="W15" s="102"/>
-      <c r="X15" s="102"/>
-      <c r="Y15" s="102"/>
-      <c r="Z15" s="102"/>
-      <c r="AA15" s="102"/>
-      <c r="AB15" s="102"/>
-      <c r="AC15" s="102"/>
-      <c r="AD15" s="102"/>
-      <c r="AE15" s="102"/>
-      <c r="AF15" s="102"/>
-      <c r="AG15" s="102"/>
-      <c r="AH15" s="102"/>
-      <c r="AI15" s="102"/>
-      <c r="AJ15" s="102"/>
-      <c r="AK15" s="102"/>
-      <c r="AL15" s="102"/>
-      <c r="AM15" s="102"/>
-      <c r="AN15" s="102"/>
-      <c r="AO15" s="102"/>
-      <c r="AP15" s="102"/>
-      <c r="AQ15" s="102"/>
-      <c r="AR15" s="102"/>
-      <c r="AS15" s="102"/>
-      <c r="AT15" s="102"/>
-      <c r="AU15" s="102"/>
-      <c r="AV15" s="102"/>
-      <c r="AW15" s="102"/>
-      <c r="AX15" s="102"/>
-      <c r="AY15" s="102"/>
-      <c r="AZ15" s="102"/>
-      <c r="BA15" s="102"/>
-      <c r="BB15" s="102"/>
-      <c r="BC15" s="102"/>
-      <c r="BD15" s="102"/>
-      <c r="BE15" s="102"/>
-      <c r="BF15" s="102"/>
-      <c r="BG15" s="102"/>
-      <c r="BH15" s="102"/>
-      <c r="BI15" s="102"/>
-      <c r="BJ15" s="102"/>
-      <c r="BK15" s="102"/>
-      <c r="BL15" s="102"/>
-      <c r="BM15" s="102"/>
-      <c r="BN15" s="102"/>
-      <c r="BO15" s="102"/>
-      <c r="BP15" s="102"/>
-      <c r="BQ15" s="102"/>
-      <c r="BR15" s="102"/>
-      <c r="BS15" s="102"/>
-      <c r="BT15" s="102"/>
-      <c r="BU15" s="102"/>
-      <c r="BV15" s="102"/>
-      <c r="BW15" s="102"/>
-      <c r="BX15" s="102"/>
-      <c r="BY15" s="102"/>
-      <c r="BZ15" s="102"/>
-      <c r="CA15" s="102"/>
-      <c r="CB15" s="102"/>
-      <c r="CC15" s="102"/>
-      <c r="CD15" s="102"/>
-      <c r="CE15" s="102"/>
-      <c r="CF15" s="102"/>
-      <c r="CG15" s="102"/>
-      <c r="CH15" s="102"/>
-      <c r="CI15" s="102"/>
-      <c r="CJ15" s="102"/>
-      <c r="CK15" s="102"/>
-      <c r="CL15" s="102"/>
-      <c r="CM15" s="102"/>
-      <c r="CN15" s="102"/>
-      <c r="CO15" s="102"/>
-      <c r="CP15" s="102"/>
-      <c r="CQ15" s="102"/>
-      <c r="CR15" s="102"/>
-      <c r="CS15" s="102"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="70"/>
+      <c r="S15" s="70"/>
+      <c r="T15" s="70"/>
+      <c r="U15" s="70"/>
+      <c r="V15" s="70"/>
+      <c r="W15" s="70"/>
+      <c r="X15" s="70"/>
+      <c r="Y15" s="70"/>
+      <c r="Z15" s="70"/>
+      <c r="AA15" s="70"/>
+      <c r="AB15" s="70"/>
+      <c r="AC15" s="70"/>
+      <c r="AD15" s="70"/>
+      <c r="AE15" s="70"/>
+      <c r="AF15" s="70"/>
+      <c r="AG15" s="70"/>
+      <c r="AH15" s="70"/>
+      <c r="AI15" s="70"/>
+      <c r="AJ15" s="70"/>
+      <c r="AK15" s="70"/>
+      <c r="AL15" s="70"/>
+      <c r="AM15" s="70"/>
+      <c r="AN15" s="70"/>
+      <c r="AO15" s="70"/>
+      <c r="AP15" s="70"/>
+      <c r="AQ15" s="70"/>
+      <c r="AR15" s="70"/>
+      <c r="AS15" s="70"/>
+      <c r="AT15" s="70"/>
+      <c r="AU15" s="70"/>
+      <c r="AV15" s="70"/>
+      <c r="AW15" s="70"/>
+      <c r="AX15" s="70"/>
+      <c r="AY15" s="70"/>
+      <c r="AZ15" s="70"/>
+      <c r="BA15" s="70"/>
+      <c r="BB15" s="70"/>
+      <c r="BC15" s="70"/>
+      <c r="BD15" s="70"/>
+      <c r="BE15" s="70"/>
+      <c r="BF15" s="70"/>
+      <c r="BG15" s="70"/>
+      <c r="BH15" s="70"/>
+      <c r="BI15" s="70"/>
+      <c r="BJ15" s="70"/>
+      <c r="BK15" s="70"/>
+      <c r="BL15" s="70"/>
+      <c r="BM15" s="70"/>
+      <c r="BN15" s="70"/>
+      <c r="BO15" s="70"/>
+      <c r="BP15" s="70"/>
+      <c r="BQ15" s="70"/>
+      <c r="BR15" s="70"/>
+      <c r="BS15" s="70"/>
+      <c r="BT15" s="70"/>
+      <c r="BU15" s="70"/>
+      <c r="BV15" s="70"/>
+      <c r="BW15" s="70"/>
+      <c r="BX15" s="70"/>
+      <c r="BY15" s="70"/>
+      <c r="BZ15" s="70"/>
+      <c r="CA15" s="70"/>
+      <c r="CB15" s="70"/>
+      <c r="CC15" s="70"/>
+      <c r="CD15" s="70"/>
+      <c r="CE15" s="70"/>
+      <c r="CF15" s="70"/>
+      <c r="CG15" s="70"/>
+      <c r="CH15" s="70"/>
+      <c r="CI15" s="70"/>
+      <c r="CJ15" s="70"/>
+      <c r="CK15" s="70"/>
+      <c r="CL15" s="70"/>
+      <c r="CM15" s="70"/>
+      <c r="CN15" s="70"/>
+      <c r="CO15" s="70"/>
+      <c r="CP15" s="70"/>
+      <c r="CQ15" s="70"/>
+      <c r="CR15" s="70"/>
+      <c r="CS15" s="70"/>
     </row>
     <row r="16" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="107" t="s">
+      <c r="B16" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="109"/>
-      <c r="D16" s="110">
+      <c r="C16" s="77"/>
+      <c r="D16" s="78">
         <v>1</v>
       </c>
-      <c r="E16" s="111">
+      <c r="E16" s="79">
         <v>46253</v>
       </c>
-      <c r="F16" s="106">
+      <c r="F16" s="74">
         <v>46253</v>
       </c>
-      <c r="G16" s="102"/>
-      <c r="H16" s="102"/>
-      <c r="I16" s="102"/>
-      <c r="J16" s="102"/>
-      <c r="K16" s="102"/>
-      <c r="L16" s="102"/>
-      <c r="M16" s="102"/>
-      <c r="N16" s="102"/>
-      <c r="O16" s="102"/>
-      <c r="P16" s="102"/>
-      <c r="Q16" s="102"/>
-      <c r="R16" s="102"/>
-      <c r="S16" s="102"/>
-      <c r="T16" s="102"/>
-      <c r="U16" s="102"/>
-      <c r="V16" s="102"/>
-      <c r="W16" s="102"/>
-      <c r="X16" s="102"/>
-      <c r="Y16" s="102"/>
-      <c r="Z16" s="102"/>
-      <c r="AA16" s="102"/>
-      <c r="AB16" s="102"/>
-      <c r="AC16" s="102"/>
-      <c r="AD16" s="102"/>
-      <c r="AE16" s="102"/>
-      <c r="AF16" s="102"/>
-      <c r="AG16" s="102"/>
-      <c r="AH16" s="102"/>
-      <c r="AI16" s="102"/>
-      <c r="AJ16" s="102"/>
-      <c r="AK16" s="102"/>
-      <c r="AL16" s="102"/>
-      <c r="AM16" s="102"/>
-      <c r="AN16" s="102"/>
-      <c r="AO16" s="102"/>
-      <c r="AP16" s="102"/>
-      <c r="AQ16" s="102"/>
-      <c r="AR16" s="102"/>
-      <c r="AS16" s="102"/>
-      <c r="AT16" s="102"/>
-      <c r="AU16" s="102"/>
-      <c r="AV16" s="102"/>
-      <c r="AW16" s="102"/>
-      <c r="AX16" s="102"/>
-      <c r="AY16" s="102"/>
-      <c r="AZ16" s="102"/>
-      <c r="BA16" s="102"/>
-      <c r="BB16" s="102"/>
-      <c r="BC16" s="102"/>
-      <c r="BD16" s="102"/>
-      <c r="BE16" s="102"/>
-      <c r="BF16" s="102"/>
-      <c r="BG16" s="102"/>
-      <c r="BH16" s="102"/>
-      <c r="BI16" s="102"/>
-      <c r="BJ16" s="102"/>
-      <c r="BK16" s="102"/>
-      <c r="BL16" s="102"/>
-      <c r="BM16" s="102"/>
-      <c r="BN16" s="102"/>
-      <c r="BO16" s="102"/>
-      <c r="BP16" s="102"/>
-      <c r="BQ16" s="102"/>
-      <c r="BR16" s="102"/>
-      <c r="BS16" s="102"/>
-      <c r="BT16" s="102"/>
-      <c r="BU16" s="102"/>
-      <c r="BV16" s="102"/>
-      <c r="BW16" s="102"/>
-      <c r="BX16" s="102"/>
-      <c r="BY16" s="102"/>
-      <c r="BZ16" s="102"/>
-      <c r="CA16" s="102"/>
-      <c r="CB16" s="102"/>
-      <c r="CC16" s="102"/>
-      <c r="CD16" s="102"/>
-      <c r="CE16" s="102"/>
-      <c r="CF16" s="102"/>
-      <c r="CG16" s="102"/>
-      <c r="CH16" s="102"/>
-      <c r="CI16" s="102"/>
-      <c r="CJ16" s="102"/>
-      <c r="CK16" s="102"/>
-      <c r="CL16" s="102"/>
-      <c r="CM16" s="102"/>
-      <c r="CN16" s="102"/>
-      <c r="CO16" s="102"/>
-      <c r="CP16" s="102"/>
-      <c r="CQ16" s="102"/>
-      <c r="CR16" s="102"/>
-      <c r="CS16" s="102"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="70"/>
+      <c r="S16" s="70"/>
+      <c r="T16" s="70"/>
+      <c r="U16" s="70"/>
+      <c r="V16" s="70"/>
+      <c r="W16" s="70"/>
+      <c r="X16" s="70"/>
+      <c r="Y16" s="70"/>
+      <c r="Z16" s="70"/>
+      <c r="AA16" s="70"/>
+      <c r="AB16" s="70"/>
+      <c r="AC16" s="70"/>
+      <c r="AD16" s="70"/>
+      <c r="AE16" s="70"/>
+      <c r="AF16" s="70"/>
+      <c r="AG16" s="70"/>
+      <c r="AH16" s="70"/>
+      <c r="AI16" s="70"/>
+      <c r="AJ16" s="70"/>
+      <c r="AK16" s="70"/>
+      <c r="AL16" s="70"/>
+      <c r="AM16" s="70"/>
+      <c r="AN16" s="70"/>
+      <c r="AO16" s="70"/>
+      <c r="AP16" s="70"/>
+      <c r="AQ16" s="70"/>
+      <c r="AR16" s="70"/>
+      <c r="AS16" s="70"/>
+      <c r="AT16" s="70"/>
+      <c r="AU16" s="70"/>
+      <c r="AV16" s="70"/>
+      <c r="AW16" s="70"/>
+      <c r="AX16" s="70"/>
+      <c r="AY16" s="70"/>
+      <c r="AZ16" s="70"/>
+      <c r="BA16" s="70"/>
+      <c r="BB16" s="70"/>
+      <c r="BC16" s="70"/>
+      <c r="BD16" s="70"/>
+      <c r="BE16" s="70"/>
+      <c r="BF16" s="70"/>
+      <c r="BG16" s="70"/>
+      <c r="BH16" s="70"/>
+      <c r="BI16" s="70"/>
+      <c r="BJ16" s="70"/>
+      <c r="BK16" s="70"/>
+      <c r="BL16" s="70"/>
+      <c r="BM16" s="70"/>
+      <c r="BN16" s="70"/>
+      <c r="BO16" s="70"/>
+      <c r="BP16" s="70"/>
+      <c r="BQ16" s="70"/>
+      <c r="BR16" s="70"/>
+      <c r="BS16" s="70"/>
+      <c r="BT16" s="70"/>
+      <c r="BU16" s="70"/>
+      <c r="BV16" s="70"/>
+      <c r="BW16" s="70"/>
+      <c r="BX16" s="70"/>
+      <c r="BY16" s="70"/>
+      <c r="BZ16" s="70"/>
+      <c r="CA16" s="70"/>
+      <c r="CB16" s="70"/>
+      <c r="CC16" s="70"/>
+      <c r="CD16" s="70"/>
+      <c r="CE16" s="70"/>
+      <c r="CF16" s="70"/>
+      <c r="CG16" s="70"/>
+      <c r="CH16" s="70"/>
+      <c r="CI16" s="70"/>
+      <c r="CJ16" s="70"/>
+      <c r="CK16" s="70"/>
+      <c r="CL16" s="70"/>
+      <c r="CM16" s="70"/>
+      <c r="CN16" s="70"/>
+      <c r="CO16" s="70"/>
+      <c r="CP16" s="70"/>
+      <c r="CQ16" s="70"/>
+      <c r="CR16" s="70"/>
+      <c r="CS16" s="70"/>
     </row>
     <row r="17" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="107" t="s">
+      <c r="B17" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="109"/>
-      <c r="D17" s="110">
+      <c r="C17" s="77"/>
+      <c r="D17" s="78">
         <v>4</v>
       </c>
-      <c r="E17" s="111">
+      <c r="E17" s="79">
         <v>46254</v>
       </c>
-      <c r="F17" s="106">
+      <c r="F17" s="74">
         <v>46257</v>
       </c>
-      <c r="G17" s="102"/>
-      <c r="H17" s="102"/>
-      <c r="I17" s="102"/>
-      <c r="J17" s="102"/>
-      <c r="K17" s="102"/>
-      <c r="L17" s="102"/>
-      <c r="M17" s="102"/>
-      <c r="N17" s="102"/>
-      <c r="O17" s="102"/>
-      <c r="P17" s="102"/>
-      <c r="Q17" s="102"/>
-      <c r="R17" s="102"/>
-      <c r="S17" s="102"/>
-      <c r="T17" s="102"/>
-      <c r="U17" s="102"/>
-      <c r="V17" s="102"/>
-      <c r="W17" s="102"/>
-      <c r="X17" s="102"/>
-      <c r="Y17" s="102"/>
-      <c r="Z17" s="102"/>
-      <c r="AA17" s="102"/>
-      <c r="AB17" s="102"/>
-      <c r="AC17" s="102"/>
-      <c r="AD17" s="102"/>
-      <c r="AE17" s="102"/>
-      <c r="AF17" s="102"/>
-      <c r="AG17" s="102"/>
-      <c r="AH17" s="102"/>
-      <c r="AI17" s="102"/>
-      <c r="AJ17" s="102"/>
-      <c r="AK17" s="102"/>
-      <c r="AL17" s="102"/>
-      <c r="AM17" s="102"/>
-      <c r="AN17" s="102"/>
-      <c r="AO17" s="102"/>
-      <c r="AP17" s="102"/>
-      <c r="AQ17" s="102"/>
-      <c r="AR17" s="102"/>
-      <c r="AS17" s="102"/>
-      <c r="AT17" s="102"/>
-      <c r="AU17" s="102"/>
-      <c r="AV17" s="102"/>
-      <c r="AW17" s="102"/>
-      <c r="AX17" s="102"/>
-      <c r="AY17" s="102"/>
-      <c r="AZ17" s="102"/>
-      <c r="BA17" s="102"/>
-      <c r="BB17" s="102"/>
-      <c r="BC17" s="102"/>
-      <c r="BD17" s="102"/>
-      <c r="BE17" s="102"/>
-      <c r="BF17" s="102"/>
-      <c r="BG17" s="102"/>
-      <c r="BH17" s="102"/>
-      <c r="BI17" s="102"/>
-      <c r="BJ17" s="102"/>
-      <c r="BK17" s="102"/>
-      <c r="BL17" s="102"/>
-      <c r="BM17" s="102"/>
-      <c r="BN17" s="102"/>
-      <c r="BO17" s="102"/>
-      <c r="BP17" s="102"/>
-      <c r="BQ17" s="102"/>
-      <c r="BR17" s="102"/>
-      <c r="BS17" s="102"/>
-      <c r="BT17" s="102"/>
-      <c r="BU17" s="102"/>
-      <c r="BV17" s="102"/>
-      <c r="BW17" s="102"/>
-      <c r="BX17" s="102"/>
-      <c r="BY17" s="102"/>
-      <c r="BZ17" s="102"/>
-      <c r="CA17" s="102"/>
-      <c r="CB17" s="102"/>
-      <c r="CC17" s="102"/>
-      <c r="CD17" s="102"/>
-      <c r="CE17" s="102"/>
-      <c r="CF17" s="102"/>
-      <c r="CG17" s="102"/>
-      <c r="CH17" s="102"/>
-      <c r="CI17" s="102"/>
-      <c r="CJ17" s="102"/>
-      <c r="CK17" s="102"/>
-      <c r="CL17" s="102"/>
-      <c r="CM17" s="102"/>
-      <c r="CN17" s="102"/>
-      <c r="CO17" s="102"/>
-      <c r="CP17" s="102"/>
-      <c r="CQ17" s="102"/>
-      <c r="CR17" s="102"/>
-      <c r="CS17" s="102"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="70"/>
+      <c r="S17" s="70"/>
+      <c r="T17" s="70"/>
+      <c r="U17" s="70"/>
+      <c r="V17" s="70"/>
+      <c r="W17" s="70"/>
+      <c r="X17" s="70"/>
+      <c r="Y17" s="70"/>
+      <c r="Z17" s="70"/>
+      <c r="AA17" s="70"/>
+      <c r="AB17" s="70"/>
+      <c r="AC17" s="70"/>
+      <c r="AD17" s="70"/>
+      <c r="AE17" s="70"/>
+      <c r="AF17" s="70"/>
+      <c r="AG17" s="70"/>
+      <c r="AH17" s="70"/>
+      <c r="AI17" s="70"/>
+      <c r="AJ17" s="70"/>
+      <c r="AK17" s="70"/>
+      <c r="AL17" s="70"/>
+      <c r="AM17" s="70"/>
+      <c r="AN17" s="70"/>
+      <c r="AO17" s="70"/>
+      <c r="AP17" s="70"/>
+      <c r="AQ17" s="70"/>
+      <c r="AR17" s="70"/>
+      <c r="AS17" s="70"/>
+      <c r="AT17" s="70"/>
+      <c r="AU17" s="70"/>
+      <c r="AV17" s="70"/>
+      <c r="AW17" s="70"/>
+      <c r="AX17" s="70"/>
+      <c r="AY17" s="70"/>
+      <c r="AZ17" s="70"/>
+      <c r="BA17" s="70"/>
+      <c r="BB17" s="70"/>
+      <c r="BC17" s="70"/>
+      <c r="BD17" s="70"/>
+      <c r="BE17" s="70"/>
+      <c r="BF17" s="70"/>
+      <c r="BG17" s="70"/>
+      <c r="BH17" s="70"/>
+      <c r="BI17" s="70"/>
+      <c r="BJ17" s="70"/>
+      <c r="BK17" s="70"/>
+      <c r="BL17" s="70"/>
+      <c r="BM17" s="70"/>
+      <c r="BN17" s="70"/>
+      <c r="BO17" s="70"/>
+      <c r="BP17" s="70"/>
+      <c r="BQ17" s="70"/>
+      <c r="BR17" s="70"/>
+      <c r="BS17" s="70"/>
+      <c r="BT17" s="70"/>
+      <c r="BU17" s="70"/>
+      <c r="BV17" s="70"/>
+      <c r="BW17" s="70"/>
+      <c r="BX17" s="70"/>
+      <c r="BY17" s="70"/>
+      <c r="BZ17" s="70"/>
+      <c r="CA17" s="70"/>
+      <c r="CB17" s="70"/>
+      <c r="CC17" s="70"/>
+      <c r="CD17" s="70"/>
+      <c r="CE17" s="70"/>
+      <c r="CF17" s="70"/>
+      <c r="CG17" s="70"/>
+      <c r="CH17" s="70"/>
+      <c r="CI17" s="70"/>
+      <c r="CJ17" s="70"/>
+      <c r="CK17" s="70"/>
+      <c r="CL17" s="70"/>
+      <c r="CM17" s="70"/>
+      <c r="CN17" s="70"/>
+      <c r="CO17" s="70"/>
+      <c r="CP17" s="70"/>
+      <c r="CQ17" s="70"/>
+      <c r="CR17" s="70"/>
+      <c r="CS17" s="70"/>
     </row>
     <row r="18" spans="2:97" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="107" t="s">
+      <c r="B18" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="109"/>
-      <c r="D18" s="110">
+      <c r="C18" s="77"/>
+      <c r="D18" s="78">
         <v>1</v>
       </c>
-      <c r="E18" s="111">
+      <c r="E18" s="79">
         <v>46258</v>
       </c>
-      <c r="F18" s="106">
+      <c r="F18" s="74">
         <v>46258</v>
       </c>
-      <c r="G18" s="102"/>
-      <c r="H18" s="102"/>
-      <c r="I18" s="102"/>
-      <c r="J18" s="102"/>
-      <c r="K18" s="102"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="102"/>
-      <c r="N18" s="102"/>
-      <c r="O18" s="102"/>
-      <c r="P18" s="102"/>
-      <c r="Q18" s="102"/>
-      <c r="R18" s="102"/>
-      <c r="S18" s="102"/>
-      <c r="T18" s="102"/>
-      <c r="U18" s="102"/>
-      <c r="V18" s="102"/>
-      <c r="W18" s="102"/>
-      <c r="X18" s="102"/>
-      <c r="Y18" s="102"/>
-      <c r="Z18" s="102"/>
-      <c r="AA18" s="102"/>
-      <c r="AB18" s="102"/>
-      <c r="AC18" s="102"/>
-      <c r="AD18" s="102"/>
-      <c r="AE18" s="102"/>
-      <c r="AF18" s="102"/>
-      <c r="AG18" s="102"/>
-      <c r="AH18" s="102"/>
-      <c r="AI18" s="102"/>
-      <c r="AJ18" s="102"/>
-      <c r="AK18" s="102"/>
-      <c r="AL18" s="102"/>
-      <c r="AM18" s="102"/>
-      <c r="AN18" s="102"/>
-      <c r="AO18" s="102"/>
-      <c r="AP18" s="102"/>
-      <c r="AQ18" s="102"/>
-      <c r="AR18" s="102"/>
-      <c r="AS18" s="102"/>
-      <c r="AT18" s="102"/>
-      <c r="AU18" s="102"/>
-      <c r="AV18" s="102"/>
-      <c r="AW18" s="102"/>
-      <c r="AX18" s="102"/>
-      <c r="AY18" s="102"/>
-      <c r="AZ18" s="102"/>
-      <c r="BA18" s="102"/>
-      <c r="BB18" s="102"/>
-      <c r="BC18" s="102"/>
-      <c r="BD18" s="102"/>
-      <c r="BE18" s="102"/>
-      <c r="BF18" s="102"/>
-      <c r="BG18" s="102"/>
-      <c r="BH18" s="102"/>
-      <c r="BI18" s="102"/>
-      <c r="BJ18" s="102"/>
-      <c r="BK18" s="102"/>
-      <c r="BL18" s="102"/>
-      <c r="BM18" s="102"/>
-      <c r="BN18" s="102"/>
-      <c r="BO18" s="102"/>
-      <c r="BP18" s="102"/>
-      <c r="BQ18" s="102"/>
-      <c r="BR18" s="102"/>
-      <c r="BS18" s="102"/>
-      <c r="BT18" s="102"/>
-      <c r="BU18" s="102"/>
-      <c r="BV18" s="102"/>
-      <c r="BW18" s="102"/>
-      <c r="BX18" s="102"/>
-      <c r="BY18" s="102"/>
-      <c r="BZ18" s="102"/>
-      <c r="CA18" s="102"/>
-      <c r="CB18" s="102"/>
-      <c r="CC18" s="102"/>
-      <c r="CD18" s="102"/>
-      <c r="CE18" s="102"/>
-      <c r="CF18" s="102"/>
-      <c r="CG18" s="102"/>
-      <c r="CH18" s="102"/>
-      <c r="CI18" s="102"/>
-      <c r="CJ18" s="102"/>
-      <c r="CK18" s="102"/>
-      <c r="CL18" s="102"/>
-      <c r="CM18" s="102"/>
-      <c r="CN18" s="102"/>
-      <c r="CO18" s="102"/>
-      <c r="CP18" s="102"/>
-      <c r="CQ18" s="102"/>
-      <c r="CR18" s="102"/>
-      <c r="CS18" s="102"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="70"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="70"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="70"/>
+      <c r="R18" s="70"/>
+      <c r="S18" s="70"/>
+      <c r="T18" s="70"/>
+      <c r="U18" s="70"/>
+      <c r="V18" s="70"/>
+      <c r="W18" s="70"/>
+      <c r="X18" s="70"/>
+      <c r="Y18" s="70"/>
+      <c r="Z18" s="70"/>
+      <c r="AA18" s="70"/>
+      <c r="AB18" s="70"/>
+      <c r="AC18" s="70"/>
+      <c r="AD18" s="70"/>
+      <c r="AE18" s="70"/>
+      <c r="AF18" s="70"/>
+      <c r="AG18" s="70"/>
+      <c r="AH18" s="70"/>
+      <c r="AI18" s="70"/>
+      <c r="AJ18" s="70"/>
+      <c r="AK18" s="70"/>
+      <c r="AL18" s="70"/>
+      <c r="AM18" s="70"/>
+      <c r="AN18" s="70"/>
+      <c r="AO18" s="70"/>
+      <c r="AP18" s="70"/>
+      <c r="AQ18" s="70"/>
+      <c r="AR18" s="70"/>
+      <c r="AS18" s="70"/>
+      <c r="AT18" s="70"/>
+      <c r="AU18" s="70"/>
+      <c r="AV18" s="70"/>
+      <c r="AW18" s="70"/>
+      <c r="AX18" s="70"/>
+      <c r="AY18" s="70"/>
+      <c r="AZ18" s="70"/>
+      <c r="BA18" s="70"/>
+      <c r="BB18" s="70"/>
+      <c r="BC18" s="70"/>
+      <c r="BD18" s="70"/>
+      <c r="BE18" s="70"/>
+      <c r="BF18" s="70"/>
+      <c r="BG18" s="70"/>
+      <c r="BH18" s="70"/>
+      <c r="BI18" s="70"/>
+      <c r="BJ18" s="70"/>
+      <c r="BK18" s="70"/>
+      <c r="BL18" s="70"/>
+      <c r="BM18" s="70"/>
+      <c r="BN18" s="70"/>
+      <c r="BO18" s="70"/>
+      <c r="BP18" s="70"/>
+      <c r="BQ18" s="70"/>
+      <c r="BR18" s="70"/>
+      <c r="BS18" s="70"/>
+      <c r="BT18" s="70"/>
+      <c r="BU18" s="70"/>
+      <c r="BV18" s="70"/>
+      <c r="BW18" s="70"/>
+      <c r="BX18" s="70"/>
+      <c r="BY18" s="70"/>
+      <c r="BZ18" s="70"/>
+      <c r="CA18" s="70"/>
+      <c r="CB18" s="70"/>
+      <c r="CC18" s="70"/>
+      <c r="CD18" s="70"/>
+      <c r="CE18" s="70"/>
+      <c r="CF18" s="70"/>
+      <c r="CG18" s="70"/>
+      <c r="CH18" s="70"/>
+      <c r="CI18" s="70"/>
+      <c r="CJ18" s="70"/>
+      <c r="CK18" s="70"/>
+      <c r="CL18" s="70"/>
+      <c r="CM18" s="70"/>
+      <c r="CN18" s="70"/>
+      <c r="CO18" s="70"/>
+      <c r="CP18" s="70"/>
+      <c r="CQ18" s="70"/>
+      <c r="CR18" s="70"/>
+      <c r="CS18" s="70"/>
     </row>
     <row r="19" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="107" t="s">
+      <c r="B19" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="109"/>
-      <c r="D19" s="110">
+      <c r="C19" s="77"/>
+      <c r="D19" s="78">
         <v>1</v>
       </c>
-      <c r="E19" s="111">
+      <c r="E19" s="79">
         <v>46259</v>
       </c>
-      <c r="F19" s="106">
+      <c r="F19" s="74">
         <v>46259</v>
       </c>
-      <c r="G19" s="102"/>
-      <c r="H19" s="102"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="102"/>
-      <c r="K19" s="102"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="102"/>
-      <c r="N19" s="102"/>
-      <c r="O19" s="102"/>
-      <c r="P19" s="102"/>
-      <c r="Q19" s="102"/>
-      <c r="R19" s="102"/>
-      <c r="S19" s="102"/>
-      <c r="T19" s="102"/>
-      <c r="U19" s="102"/>
-      <c r="V19" s="102"/>
-      <c r="W19" s="102"/>
-      <c r="X19" s="102"/>
-      <c r="Y19" s="102"/>
-      <c r="Z19" s="102"/>
-      <c r="AA19" s="102"/>
-      <c r="AB19" s="102"/>
-      <c r="AC19" s="102"/>
-      <c r="AD19" s="102"/>
-      <c r="AE19" s="102"/>
-      <c r="AF19" s="102"/>
-      <c r="AG19" s="102"/>
-      <c r="AH19" s="102"/>
-      <c r="AI19" s="102"/>
-      <c r="AJ19" s="102"/>
-      <c r="AK19" s="102"/>
-      <c r="AL19" s="102"/>
-      <c r="AM19" s="102"/>
-      <c r="AN19" s="102"/>
-      <c r="AO19" s="102"/>
-      <c r="AP19" s="102"/>
-      <c r="AQ19" s="102"/>
-      <c r="AR19" s="102"/>
-      <c r="AS19" s="102"/>
-      <c r="AT19" s="102"/>
-      <c r="AU19" s="102"/>
-      <c r="AV19" s="102"/>
-      <c r="AW19" s="102"/>
-      <c r="AX19" s="102"/>
-      <c r="AY19" s="102"/>
-      <c r="AZ19" s="102"/>
-      <c r="BA19" s="102"/>
-      <c r="BB19" s="102"/>
-      <c r="BC19" s="102"/>
-      <c r="BD19" s="102"/>
-      <c r="BE19" s="102"/>
-      <c r="BF19" s="102"/>
-      <c r="BG19" s="102"/>
-      <c r="BH19" s="102"/>
-      <c r="BI19" s="102"/>
-      <c r="BJ19" s="102"/>
-      <c r="BK19" s="102"/>
-      <c r="BL19" s="102"/>
-      <c r="BM19" s="102"/>
-      <c r="BN19" s="102"/>
-      <c r="BO19" s="102"/>
-      <c r="BP19" s="102"/>
-      <c r="BQ19" s="102"/>
-      <c r="BR19" s="102"/>
-      <c r="BS19" s="102"/>
-      <c r="BT19" s="102"/>
-      <c r="BU19" s="102"/>
-      <c r="BV19" s="102"/>
-      <c r="BW19" s="102"/>
-      <c r="BX19" s="102"/>
-      <c r="BY19" s="102"/>
-      <c r="BZ19" s="102"/>
-      <c r="CA19" s="102"/>
-      <c r="CB19" s="102"/>
-      <c r="CC19" s="102"/>
-      <c r="CD19" s="102"/>
-      <c r="CE19" s="102"/>
-      <c r="CF19" s="102"/>
-      <c r="CG19" s="102"/>
-      <c r="CH19" s="102"/>
-      <c r="CI19" s="102"/>
-      <c r="CJ19" s="102"/>
-      <c r="CK19" s="102"/>
-      <c r="CL19" s="102"/>
-      <c r="CM19" s="102"/>
-      <c r="CN19" s="102"/>
-      <c r="CO19" s="102"/>
-      <c r="CP19" s="102"/>
-      <c r="CQ19" s="102"/>
-      <c r="CR19" s="102"/>
-      <c r="CS19" s="102"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="70"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="70"/>
+      <c r="R19" s="70"/>
+      <c r="S19" s="70"/>
+      <c r="T19" s="70"/>
+      <c r="U19" s="70"/>
+      <c r="V19" s="70"/>
+      <c r="W19" s="70"/>
+      <c r="X19" s="70"/>
+      <c r="Y19" s="70"/>
+      <c r="Z19" s="70"/>
+      <c r="AA19" s="70"/>
+      <c r="AB19" s="70"/>
+      <c r="AC19" s="70"/>
+      <c r="AD19" s="70"/>
+      <c r="AE19" s="70"/>
+      <c r="AF19" s="70"/>
+      <c r="AG19" s="70"/>
+      <c r="AH19" s="70"/>
+      <c r="AI19" s="70"/>
+      <c r="AJ19" s="70"/>
+      <c r="AK19" s="70"/>
+      <c r="AL19" s="70"/>
+      <c r="AM19" s="70"/>
+      <c r="AN19" s="70"/>
+      <c r="AO19" s="70"/>
+      <c r="AP19" s="70"/>
+      <c r="AQ19" s="70"/>
+      <c r="AR19" s="70"/>
+      <c r="AS19" s="70"/>
+      <c r="AT19" s="70"/>
+      <c r="AU19" s="70"/>
+      <c r="AV19" s="70"/>
+      <c r="AW19" s="70"/>
+      <c r="AX19" s="70"/>
+      <c r="AY19" s="70"/>
+      <c r="AZ19" s="70"/>
+      <c r="BA19" s="70"/>
+      <c r="BB19" s="70"/>
+      <c r="BC19" s="70"/>
+      <c r="BD19" s="70"/>
+      <c r="BE19" s="70"/>
+      <c r="BF19" s="70"/>
+      <c r="BG19" s="70"/>
+      <c r="BH19" s="70"/>
+      <c r="BI19" s="70"/>
+      <c r="BJ19" s="70"/>
+      <c r="BK19" s="70"/>
+      <c r="BL19" s="70"/>
+      <c r="BM19" s="70"/>
+      <c r="BN19" s="70"/>
+      <c r="BO19" s="70"/>
+      <c r="BP19" s="70"/>
+      <c r="BQ19" s="70"/>
+      <c r="BR19" s="70"/>
+      <c r="BS19" s="70"/>
+      <c r="BT19" s="70"/>
+      <c r="BU19" s="70"/>
+      <c r="BV19" s="70"/>
+      <c r="BW19" s="70"/>
+      <c r="BX19" s="70"/>
+      <c r="BY19" s="70"/>
+      <c r="BZ19" s="70"/>
+      <c r="CA19" s="70"/>
+      <c r="CB19" s="70"/>
+      <c r="CC19" s="70"/>
+      <c r="CD19" s="70"/>
+      <c r="CE19" s="70"/>
+      <c r="CF19" s="70"/>
+      <c r="CG19" s="70"/>
+      <c r="CH19" s="70"/>
+      <c r="CI19" s="70"/>
+      <c r="CJ19" s="70"/>
+      <c r="CK19" s="70"/>
+      <c r="CL19" s="70"/>
+      <c r="CM19" s="70"/>
+      <c r="CN19" s="70"/>
+      <c r="CO19" s="70"/>
+      <c r="CP19" s="70"/>
+      <c r="CQ19" s="70"/>
+      <c r="CR19" s="70"/>
+      <c r="CS19" s="70"/>
     </row>
     <row r="20" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="107" t="s">
+      <c r="B20" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="109"/>
-      <c r="D20" s="110">
+      <c r="C20" s="77"/>
+      <c r="D20" s="78">
         <v>0.5</v>
       </c>
-      <c r="E20" s="111">
+      <c r="E20" s="79">
         <v>46260</v>
       </c>
-      <c r="F20" s="106">
+      <c r="F20" s="74">
         <v>46260</v>
       </c>
-      <c r="G20" s="102"/>
-      <c r="H20" s="102"/>
-      <c r="I20" s="102"/>
-      <c r="J20" s="102"/>
-      <c r="K20" s="102"/>
-      <c r="L20" s="102"/>
-      <c r="M20" s="102"/>
-      <c r="N20" s="102"/>
-      <c r="O20" s="102"/>
-      <c r="P20" s="102"/>
-      <c r="Q20" s="102"/>
-      <c r="R20" s="102"/>
-      <c r="S20" s="102"/>
-      <c r="T20" s="102"/>
-      <c r="U20" s="102"/>
-      <c r="V20" s="102"/>
-      <c r="W20" s="102"/>
-      <c r="X20" s="102"/>
-      <c r="Y20" s="102"/>
-      <c r="Z20" s="102"/>
-      <c r="AA20" s="102"/>
-      <c r="AB20" s="102"/>
-      <c r="AC20" s="102"/>
-      <c r="AD20" s="102"/>
-      <c r="AE20" s="102"/>
-      <c r="AF20" s="102"/>
-      <c r="AG20" s="102"/>
-      <c r="AH20" s="102"/>
-      <c r="AI20" s="102"/>
-      <c r="AJ20" s="102"/>
-      <c r="AK20" s="102"/>
-      <c r="AL20" s="102"/>
-      <c r="AM20" s="102"/>
-      <c r="AN20" s="102"/>
-      <c r="AO20" s="102"/>
-      <c r="AP20" s="102"/>
-      <c r="AQ20" s="102"/>
-      <c r="AR20" s="102"/>
-      <c r="AS20" s="102"/>
-      <c r="AT20" s="102"/>
-      <c r="AU20" s="102"/>
-      <c r="AV20" s="102"/>
-      <c r="AW20" s="102"/>
-      <c r="AX20" s="102"/>
-      <c r="AY20" s="102"/>
-      <c r="AZ20" s="102"/>
-      <c r="BA20" s="102"/>
-      <c r="BB20" s="102"/>
-      <c r="BC20" s="102"/>
-      <c r="BD20" s="102"/>
-      <c r="BE20" s="102"/>
-      <c r="BF20" s="102"/>
-      <c r="BG20" s="102"/>
-      <c r="BH20" s="102"/>
-      <c r="BI20" s="102"/>
-      <c r="BJ20" s="102"/>
-      <c r="BK20" s="102"/>
-      <c r="BL20" s="102"/>
-      <c r="BM20" s="102"/>
-      <c r="BN20" s="102"/>
-      <c r="BO20" s="102"/>
-      <c r="BP20" s="102"/>
-      <c r="BQ20" s="102"/>
-      <c r="BR20" s="102"/>
-      <c r="BS20" s="102"/>
-      <c r="BT20" s="102"/>
-      <c r="BU20" s="102"/>
-      <c r="BV20" s="102"/>
-      <c r="BW20" s="102"/>
-      <c r="BX20" s="102"/>
-      <c r="BY20" s="102"/>
-      <c r="BZ20" s="102"/>
-      <c r="CA20" s="102"/>
-      <c r="CB20" s="102"/>
-      <c r="CC20" s="102"/>
-      <c r="CD20" s="102"/>
-      <c r="CE20" s="102"/>
-      <c r="CF20" s="102"/>
-      <c r="CG20" s="102"/>
-      <c r="CH20" s="102"/>
-      <c r="CI20" s="102"/>
-      <c r="CJ20" s="102"/>
-      <c r="CK20" s="102"/>
-      <c r="CL20" s="102"/>
-      <c r="CM20" s="102"/>
-      <c r="CN20" s="102"/>
-      <c r="CO20" s="102"/>
-      <c r="CP20" s="102"/>
-      <c r="CQ20" s="102"/>
-      <c r="CR20" s="102"/>
-      <c r="CS20" s="102"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="70"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="70"/>
+      <c r="S20" s="70"/>
+      <c r="T20" s="70"/>
+      <c r="U20" s="70"/>
+      <c r="V20" s="70"/>
+      <c r="W20" s="70"/>
+      <c r="X20" s="70"/>
+      <c r="Y20" s="70"/>
+      <c r="Z20" s="70"/>
+      <c r="AA20" s="70"/>
+      <c r="AB20" s="70"/>
+      <c r="AC20" s="70"/>
+      <c r="AD20" s="70"/>
+      <c r="AE20" s="70"/>
+      <c r="AF20" s="70"/>
+      <c r="AG20" s="70"/>
+      <c r="AH20" s="70"/>
+      <c r="AI20" s="70"/>
+      <c r="AJ20" s="70"/>
+      <c r="AK20" s="70"/>
+      <c r="AL20" s="70"/>
+      <c r="AM20" s="70"/>
+      <c r="AN20" s="70"/>
+      <c r="AO20" s="70"/>
+      <c r="AP20" s="70"/>
+      <c r="AQ20" s="70"/>
+      <c r="AR20" s="70"/>
+      <c r="AS20" s="70"/>
+      <c r="AT20" s="70"/>
+      <c r="AU20" s="70"/>
+      <c r="AV20" s="70"/>
+      <c r="AW20" s="70"/>
+      <c r="AX20" s="70"/>
+      <c r="AY20" s="70"/>
+      <c r="AZ20" s="70"/>
+      <c r="BA20" s="70"/>
+      <c r="BB20" s="70"/>
+      <c r="BC20" s="70"/>
+      <c r="BD20" s="70"/>
+      <c r="BE20" s="70"/>
+      <c r="BF20" s="70"/>
+      <c r="BG20" s="70"/>
+      <c r="BH20" s="70"/>
+      <c r="BI20" s="70"/>
+      <c r="BJ20" s="70"/>
+      <c r="BK20" s="70"/>
+      <c r="BL20" s="70"/>
+      <c r="BM20" s="70"/>
+      <c r="BN20" s="70"/>
+      <c r="BO20" s="70"/>
+      <c r="BP20" s="70"/>
+      <c r="BQ20" s="70"/>
+      <c r="BR20" s="70"/>
+      <c r="BS20" s="70"/>
+      <c r="BT20" s="70"/>
+      <c r="BU20" s="70"/>
+      <c r="BV20" s="70"/>
+      <c r="BW20" s="70"/>
+      <c r="BX20" s="70"/>
+      <c r="BY20" s="70"/>
+      <c r="BZ20" s="70"/>
+      <c r="CA20" s="70"/>
+      <c r="CB20" s="70"/>
+      <c r="CC20" s="70"/>
+      <c r="CD20" s="70"/>
+      <c r="CE20" s="70"/>
+      <c r="CF20" s="70"/>
+      <c r="CG20" s="70"/>
+      <c r="CH20" s="70"/>
+      <c r="CI20" s="70"/>
+      <c r="CJ20" s="70"/>
+      <c r="CK20" s="70"/>
+      <c r="CL20" s="70"/>
+      <c r="CM20" s="70"/>
+      <c r="CN20" s="70"/>
+      <c r="CO20" s="70"/>
+      <c r="CP20" s="70"/>
+      <c r="CQ20" s="70"/>
+      <c r="CR20" s="70"/>
+      <c r="CS20" s="70"/>
     </row>
     <row r="21" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="107" t="s">
+      <c r="B21" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="109"/>
-      <c r="D21" s="110">
+      <c r="C21" s="77"/>
+      <c r="D21" s="78">
         <v>1</v>
       </c>
-      <c r="E21" s="111">
+      <c r="E21" s="79">
         <v>46260</v>
       </c>
-      <c r="F21" s="106">
+      <c r="F21" s="74">
         <v>46260</v>
       </c>
-      <c r="G21" s="102"/>
-      <c r="H21" s="102"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="102"/>
-      <c r="K21" s="102"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="102"/>
-      <c r="N21" s="102"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="102"/>
-      <c r="Q21" s="102"/>
-      <c r="R21" s="102"/>
-      <c r="S21" s="102"/>
-      <c r="T21" s="102"/>
-      <c r="U21" s="102"/>
-      <c r="V21" s="102"/>
-      <c r="W21" s="102"/>
-      <c r="X21" s="102"/>
-      <c r="Y21" s="102"/>
-      <c r="Z21" s="102"/>
-      <c r="AA21" s="102"/>
-      <c r="AB21" s="102"/>
-      <c r="AC21" s="102"/>
-      <c r="AD21" s="102"/>
-      <c r="AE21" s="102"/>
-      <c r="AF21" s="102"/>
-      <c r="AG21" s="102"/>
-      <c r="AH21" s="102"/>
-      <c r="AI21" s="102"/>
-      <c r="AJ21" s="102"/>
-      <c r="AK21" s="102"/>
-      <c r="AL21" s="102"/>
-      <c r="AM21" s="102"/>
-      <c r="AN21" s="102"/>
-      <c r="AO21" s="102"/>
-      <c r="AP21" s="102"/>
-      <c r="AQ21" s="102"/>
-      <c r="AR21" s="102"/>
-      <c r="AS21" s="102"/>
-      <c r="AT21" s="102"/>
-      <c r="AU21" s="102"/>
-      <c r="AV21" s="102"/>
-      <c r="AW21" s="102"/>
-      <c r="AX21" s="102"/>
-      <c r="AY21" s="102"/>
-      <c r="AZ21" s="102"/>
-      <c r="BA21" s="102"/>
-      <c r="BB21" s="102"/>
-      <c r="BC21" s="102"/>
-      <c r="BD21" s="102"/>
-      <c r="BE21" s="102"/>
-      <c r="BF21" s="102"/>
-      <c r="BG21" s="102"/>
-      <c r="BH21" s="102"/>
-      <c r="BI21" s="102"/>
-      <c r="BJ21" s="102"/>
-      <c r="BK21" s="102"/>
-      <c r="BL21" s="102"/>
-      <c r="BM21" s="102"/>
-      <c r="BN21" s="102"/>
-      <c r="BO21" s="102"/>
-      <c r="BP21" s="102"/>
-      <c r="BQ21" s="102"/>
-      <c r="BR21" s="102"/>
-      <c r="BS21" s="102"/>
-      <c r="BT21" s="102"/>
-      <c r="BU21" s="102"/>
-      <c r="BV21" s="102"/>
-      <c r="BW21" s="102"/>
-      <c r="BX21" s="102"/>
-      <c r="BY21" s="102"/>
-      <c r="BZ21" s="102"/>
-      <c r="CA21" s="102"/>
-      <c r="CB21" s="102"/>
-      <c r="CC21" s="102"/>
-      <c r="CD21" s="102"/>
-      <c r="CE21" s="102"/>
-      <c r="CF21" s="102"/>
-      <c r="CG21" s="102"/>
-      <c r="CH21" s="102"/>
-      <c r="CI21" s="102"/>
-      <c r="CJ21" s="102"/>
-      <c r="CK21" s="102"/>
-      <c r="CL21" s="102"/>
-      <c r="CM21" s="102"/>
-      <c r="CN21" s="102"/>
-      <c r="CO21" s="102"/>
-      <c r="CP21" s="102"/>
-      <c r="CQ21" s="102"/>
-      <c r="CR21" s="102"/>
-      <c r="CS21" s="102"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="70"/>
+      <c r="R21" s="70"/>
+      <c r="S21" s="70"/>
+      <c r="T21" s="70"/>
+      <c r="U21" s="70"/>
+      <c r="V21" s="70"/>
+      <c r="W21" s="70"/>
+      <c r="X21" s="70"/>
+      <c r="Y21" s="70"/>
+      <c r="Z21" s="70"/>
+      <c r="AA21" s="70"/>
+      <c r="AB21" s="70"/>
+      <c r="AC21" s="70"/>
+      <c r="AD21" s="70"/>
+      <c r="AE21" s="70"/>
+      <c r="AF21" s="70"/>
+      <c r="AG21" s="70"/>
+      <c r="AH21" s="70"/>
+      <c r="AI21" s="70"/>
+      <c r="AJ21" s="70"/>
+      <c r="AK21" s="70"/>
+      <c r="AL21" s="70"/>
+      <c r="AM21" s="70"/>
+      <c r="AN21" s="70"/>
+      <c r="AO21" s="70"/>
+      <c r="AP21" s="70"/>
+      <c r="AQ21" s="70"/>
+      <c r="AR21" s="70"/>
+      <c r="AS21" s="70"/>
+      <c r="AT21" s="70"/>
+      <c r="AU21" s="70"/>
+      <c r="AV21" s="70"/>
+      <c r="AW21" s="70"/>
+      <c r="AX21" s="70"/>
+      <c r="AY21" s="70"/>
+      <c r="AZ21" s="70"/>
+      <c r="BA21" s="70"/>
+      <c r="BB21" s="70"/>
+      <c r="BC21" s="70"/>
+      <c r="BD21" s="70"/>
+      <c r="BE21" s="70"/>
+      <c r="BF21" s="70"/>
+      <c r="BG21" s="70"/>
+      <c r="BH21" s="70"/>
+      <c r="BI21" s="70"/>
+      <c r="BJ21" s="70"/>
+      <c r="BK21" s="70"/>
+      <c r="BL21" s="70"/>
+      <c r="BM21" s="70"/>
+      <c r="BN21" s="70"/>
+      <c r="BO21" s="70"/>
+      <c r="BP21" s="70"/>
+      <c r="BQ21" s="70"/>
+      <c r="BR21" s="70"/>
+      <c r="BS21" s="70"/>
+      <c r="BT21" s="70"/>
+      <c r="BU21" s="70"/>
+      <c r="BV21" s="70"/>
+      <c r="BW21" s="70"/>
+      <c r="BX21" s="70"/>
+      <c r="BY21" s="70"/>
+      <c r="BZ21" s="70"/>
+      <c r="CA21" s="70"/>
+      <c r="CB21" s="70"/>
+      <c r="CC21" s="70"/>
+      <c r="CD21" s="70"/>
+      <c r="CE21" s="70"/>
+      <c r="CF21" s="70"/>
+      <c r="CG21" s="70"/>
+      <c r="CH21" s="70"/>
+      <c r="CI21" s="70"/>
+      <c r="CJ21" s="70"/>
+      <c r="CK21" s="70"/>
+      <c r="CL21" s="70"/>
+      <c r="CM21" s="70"/>
+      <c r="CN21" s="70"/>
+      <c r="CO21" s="70"/>
+      <c r="CP21" s="70"/>
+      <c r="CQ21" s="70"/>
+      <c r="CR21" s="70"/>
+      <c r="CS21" s="70"/>
     </row>
     <row r="22" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="107" t="s">
+      <c r="B22" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="109"/>
-      <c r="D22" s="110">
+      <c r="C22" s="77"/>
+      <c r="D22" s="78">
         <v>0</v>
       </c>
-      <c r="E22" s="111">
+      <c r="E22" s="79">
         <v>46260</v>
       </c>
-      <c r="F22" s="106">
+      <c r="F22" s="74">
         <v>46260</v>
       </c>
-      <c r="G22" s="102"/>
-      <c r="H22" s="102"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="102"/>
-      <c r="K22" s="102"/>
-      <c r="L22" s="102"/>
-      <c r="M22" s="102"/>
-      <c r="N22" s="102"/>
-      <c r="O22" s="102"/>
-      <c r="P22" s="102"/>
-      <c r="Q22" s="102"/>
-      <c r="R22" s="102"/>
-      <c r="S22" s="102"/>
-      <c r="T22" s="102"/>
-      <c r="U22" s="102"/>
-      <c r="V22" s="102"/>
-      <c r="W22" s="102"/>
-      <c r="X22" s="102"/>
-      <c r="Y22" s="102"/>
-      <c r="Z22" s="102"/>
-      <c r="AA22" s="102"/>
-      <c r="AB22" s="102"/>
-      <c r="AC22" s="102"/>
-      <c r="AD22" s="102"/>
-      <c r="AE22" s="102"/>
-      <c r="AF22" s="102"/>
-      <c r="AG22" s="102"/>
-      <c r="AH22" s="102"/>
-      <c r="AI22" s="102"/>
-      <c r="AJ22" s="102"/>
-      <c r="AK22" s="102"/>
-      <c r="AL22" s="102"/>
-      <c r="AM22" s="102"/>
-      <c r="AN22" s="102"/>
-      <c r="AO22" s="102"/>
-      <c r="AP22" s="102"/>
-      <c r="AQ22" s="102"/>
-      <c r="AR22" s="102"/>
-      <c r="AS22" s="102"/>
-      <c r="AT22" s="102"/>
-      <c r="AU22" s="102"/>
-      <c r="AV22" s="102"/>
-      <c r="AW22" s="102"/>
-      <c r="AX22" s="102"/>
-      <c r="AY22" s="102"/>
-      <c r="AZ22" s="102"/>
-      <c r="BA22" s="102"/>
-      <c r="BB22" s="102"/>
-      <c r="BC22" s="102"/>
-      <c r="BD22" s="102"/>
-      <c r="BE22" s="102"/>
-      <c r="BF22" s="102"/>
-      <c r="BG22" s="102"/>
-      <c r="BH22" s="102"/>
-      <c r="BI22" s="102"/>
-      <c r="BJ22" s="102"/>
-      <c r="BK22" s="102"/>
-      <c r="BL22" s="102"/>
-      <c r="BM22" s="102"/>
-      <c r="BN22" s="102"/>
-      <c r="BO22" s="102"/>
-      <c r="BP22" s="102"/>
-      <c r="BQ22" s="102"/>
-      <c r="BR22" s="102"/>
-      <c r="BS22" s="102"/>
-      <c r="BT22" s="102"/>
-      <c r="BU22" s="102"/>
-      <c r="BV22" s="102"/>
-      <c r="BW22" s="102"/>
-      <c r="BX22" s="102"/>
-      <c r="BY22" s="102"/>
-      <c r="BZ22" s="102"/>
-      <c r="CA22" s="102"/>
-      <c r="CB22" s="102"/>
-      <c r="CC22" s="102"/>
-      <c r="CD22" s="102"/>
-      <c r="CE22" s="102"/>
-      <c r="CF22" s="102"/>
-      <c r="CG22" s="102"/>
-      <c r="CH22" s="102"/>
-      <c r="CI22" s="102"/>
-      <c r="CJ22" s="102"/>
-      <c r="CK22" s="102"/>
-      <c r="CL22" s="102"/>
-      <c r="CM22" s="102"/>
-      <c r="CN22" s="102"/>
-      <c r="CO22" s="102"/>
-      <c r="CP22" s="102"/>
-      <c r="CQ22" s="102"/>
-      <c r="CR22" s="102"/>
-      <c r="CS22" s="102"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="70"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="70"/>
+      <c r="T22" s="70"/>
+      <c r="U22" s="70"/>
+      <c r="V22" s="70"/>
+      <c r="W22" s="70"/>
+      <c r="X22" s="70"/>
+      <c r="Y22" s="70"/>
+      <c r="Z22" s="70"/>
+      <c r="AA22" s="70"/>
+      <c r="AB22" s="70"/>
+      <c r="AC22" s="70"/>
+      <c r="AD22" s="70"/>
+      <c r="AE22" s="70"/>
+      <c r="AF22" s="70"/>
+      <c r="AG22" s="70"/>
+      <c r="AH22" s="70"/>
+      <c r="AI22" s="70"/>
+      <c r="AJ22" s="70"/>
+      <c r="AK22" s="70"/>
+      <c r="AL22" s="70"/>
+      <c r="AM22" s="70"/>
+      <c r="AN22" s="70"/>
+      <c r="AO22" s="70"/>
+      <c r="AP22" s="70"/>
+      <c r="AQ22" s="70"/>
+      <c r="AR22" s="70"/>
+      <c r="AS22" s="70"/>
+      <c r="AT22" s="70"/>
+      <c r="AU22" s="70"/>
+      <c r="AV22" s="70"/>
+      <c r="AW22" s="70"/>
+      <c r="AX22" s="70"/>
+      <c r="AY22" s="70"/>
+      <c r="AZ22" s="70"/>
+      <c r="BA22" s="70"/>
+      <c r="BB22" s="70"/>
+      <c r="BC22" s="70"/>
+      <c r="BD22" s="70"/>
+      <c r="BE22" s="70"/>
+      <c r="BF22" s="70"/>
+      <c r="BG22" s="70"/>
+      <c r="BH22" s="70"/>
+      <c r="BI22" s="70"/>
+      <c r="BJ22" s="70"/>
+      <c r="BK22" s="70"/>
+      <c r="BL22" s="70"/>
+      <c r="BM22" s="70"/>
+      <c r="BN22" s="70"/>
+      <c r="BO22" s="70"/>
+      <c r="BP22" s="70"/>
+      <c r="BQ22" s="70"/>
+      <c r="BR22" s="70"/>
+      <c r="BS22" s="70"/>
+      <c r="BT22" s="70"/>
+      <c r="BU22" s="70"/>
+      <c r="BV22" s="70"/>
+      <c r="BW22" s="70"/>
+      <c r="BX22" s="70"/>
+      <c r="BY22" s="70"/>
+      <c r="BZ22" s="70"/>
+      <c r="CA22" s="70"/>
+      <c r="CB22" s="70"/>
+      <c r="CC22" s="70"/>
+      <c r="CD22" s="70"/>
+      <c r="CE22" s="70"/>
+      <c r="CF22" s="70"/>
+      <c r="CG22" s="70"/>
+      <c r="CH22" s="70"/>
+      <c r="CI22" s="70"/>
+      <c r="CJ22" s="70"/>
+      <c r="CK22" s="70"/>
+      <c r="CL22" s="70"/>
+      <c r="CM22" s="70"/>
+      <c r="CN22" s="70"/>
+      <c r="CO22" s="70"/>
+      <c r="CP22" s="70"/>
+      <c r="CQ22" s="70"/>
+      <c r="CR22" s="70"/>
+      <c r="CS22" s="70"/>
     </row>
     <row r="23" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="107"/>
-      <c r="C23" s="109"/>
-      <c r="D23" s="110"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="102"/>
-      <c r="H23" s="102"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="102"/>
-      <c r="K23" s="102"/>
-      <c r="L23" s="102"/>
-      <c r="M23" s="102"/>
-      <c r="N23" s="102"/>
-      <c r="O23" s="102"/>
-      <c r="P23" s="102"/>
-      <c r="Q23" s="102"/>
-      <c r="R23" s="102"/>
-      <c r="S23" s="102"/>
-      <c r="T23" s="102"/>
-      <c r="U23" s="102"/>
-      <c r="V23" s="102"/>
-      <c r="W23" s="102"/>
-      <c r="X23" s="102"/>
-      <c r="Y23" s="102"/>
-      <c r="Z23" s="102"/>
-      <c r="AA23" s="102"/>
-      <c r="AB23" s="102"/>
-      <c r="AC23" s="102"/>
-      <c r="AD23" s="102"/>
-      <c r="AE23" s="102"/>
-      <c r="AF23" s="102"/>
-      <c r="AG23" s="102"/>
-      <c r="AH23" s="102"/>
-      <c r="AI23" s="102"/>
-      <c r="AJ23" s="102"/>
-      <c r="AK23" s="102"/>
-      <c r="AL23" s="102"/>
-      <c r="AM23" s="102"/>
-      <c r="AN23" s="102"/>
-      <c r="AO23" s="102"/>
-      <c r="AP23" s="102"/>
-      <c r="AQ23" s="102"/>
-      <c r="AR23" s="102"/>
-      <c r="AS23" s="102"/>
-      <c r="AT23" s="102"/>
-      <c r="AU23" s="102"/>
-      <c r="AV23" s="102"/>
-      <c r="AW23" s="102"/>
-      <c r="AX23" s="102"/>
-      <c r="AY23" s="102"/>
-      <c r="AZ23" s="102"/>
-      <c r="BA23" s="102"/>
-      <c r="BB23" s="102"/>
-      <c r="BC23" s="102"/>
-      <c r="BD23" s="102"/>
-      <c r="BE23" s="102"/>
-      <c r="BF23" s="102"/>
-      <c r="BG23" s="102"/>
-      <c r="BH23" s="102"/>
-      <c r="BI23" s="102"/>
-      <c r="BJ23" s="102"/>
-      <c r="BK23" s="102"/>
-      <c r="BL23" s="102"/>
-      <c r="BM23" s="102"/>
-      <c r="BN23" s="102"/>
-      <c r="BO23" s="102"/>
-      <c r="BP23" s="102"/>
-      <c r="BQ23" s="102"/>
-      <c r="BR23" s="102"/>
-      <c r="BS23" s="102"/>
-      <c r="BT23" s="102"/>
-      <c r="BU23" s="102"/>
-      <c r="BV23" s="102"/>
-      <c r="BW23" s="102"/>
-      <c r="BX23" s="102"/>
-      <c r="BY23" s="102"/>
-      <c r="BZ23" s="102"/>
-      <c r="CA23" s="102"/>
-      <c r="CB23" s="102"/>
-      <c r="CC23" s="102"/>
-      <c r="CD23" s="102"/>
-      <c r="CE23" s="102"/>
-      <c r="CF23" s="102"/>
-      <c r="CG23" s="102"/>
-      <c r="CH23" s="102"/>
-      <c r="CI23" s="102"/>
-      <c r="CJ23" s="102"/>
-      <c r="CK23" s="102"/>
-      <c r="CL23" s="102"/>
-      <c r="CM23" s="102"/>
-      <c r="CN23" s="102"/>
-      <c r="CO23" s="102"/>
-      <c r="CP23" s="102"/>
-      <c r="CQ23" s="102"/>
-      <c r="CR23" s="102"/>
-      <c r="CS23" s="102"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="70"/>
+      <c r="S23" s="70"/>
+      <c r="T23" s="70"/>
+      <c r="U23" s="70"/>
+      <c r="V23" s="70"/>
+      <c r="W23" s="70"/>
+      <c r="X23" s="70"/>
+      <c r="Y23" s="70"/>
+      <c r="Z23" s="70"/>
+      <c r="AA23" s="70"/>
+      <c r="AB23" s="70"/>
+      <c r="AC23" s="70"/>
+      <c r="AD23" s="70"/>
+      <c r="AE23" s="70"/>
+      <c r="AF23" s="70"/>
+      <c r="AG23" s="70"/>
+      <c r="AH23" s="70"/>
+      <c r="AI23" s="70"/>
+      <c r="AJ23" s="70"/>
+      <c r="AK23" s="70"/>
+      <c r="AL23" s="70"/>
+      <c r="AM23" s="70"/>
+      <c r="AN23" s="70"/>
+      <c r="AO23" s="70"/>
+      <c r="AP23" s="70"/>
+      <c r="AQ23" s="70"/>
+      <c r="AR23" s="70"/>
+      <c r="AS23" s="70"/>
+      <c r="AT23" s="70"/>
+      <c r="AU23" s="70"/>
+      <c r="AV23" s="70"/>
+      <c r="AW23" s="70"/>
+      <c r="AX23" s="70"/>
+      <c r="AY23" s="70"/>
+      <c r="AZ23" s="70"/>
+      <c r="BA23" s="70"/>
+      <c r="BB23" s="70"/>
+      <c r="BC23" s="70"/>
+      <c r="BD23" s="70"/>
+      <c r="BE23" s="70"/>
+      <c r="BF23" s="70"/>
+      <c r="BG23" s="70"/>
+      <c r="BH23" s="70"/>
+      <c r="BI23" s="70"/>
+      <c r="BJ23" s="70"/>
+      <c r="BK23" s="70"/>
+      <c r="BL23" s="70"/>
+      <c r="BM23" s="70"/>
+      <c r="BN23" s="70"/>
+      <c r="BO23" s="70"/>
+      <c r="BP23" s="70"/>
+      <c r="BQ23" s="70"/>
+      <c r="BR23" s="70"/>
+      <c r="BS23" s="70"/>
+      <c r="BT23" s="70"/>
+      <c r="BU23" s="70"/>
+      <c r="BV23" s="70"/>
+      <c r="BW23" s="70"/>
+      <c r="BX23" s="70"/>
+      <c r="BY23" s="70"/>
+      <c r="BZ23" s="70"/>
+      <c r="CA23" s="70"/>
+      <c r="CB23" s="70"/>
+      <c r="CC23" s="70"/>
+      <c r="CD23" s="70"/>
+      <c r="CE23" s="70"/>
+      <c r="CF23" s="70"/>
+      <c r="CG23" s="70"/>
+      <c r="CH23" s="70"/>
+      <c r="CI23" s="70"/>
+      <c r="CJ23" s="70"/>
+      <c r="CK23" s="70"/>
+      <c r="CL23" s="70"/>
+      <c r="CM23" s="70"/>
+      <c r="CN23" s="70"/>
+      <c r="CO23" s="70"/>
+      <c r="CP23" s="70"/>
+      <c r="CQ23" s="70"/>
+      <c r="CR23" s="70"/>
+      <c r="CS23" s="70"/>
     </row>
     <row r="24" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="107"/>
-      <c r="C24" s="109"/>
-      <c r="D24" s="110"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="106"/>
-      <c r="G24" s="102"/>
-      <c r="H24" s="102"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="102"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="102"/>
-      <c r="N24" s="102"/>
-      <c r="O24" s="102"/>
-      <c r="P24" s="102"/>
-      <c r="Q24" s="102"/>
-      <c r="R24" s="102"/>
-      <c r="S24" s="102"/>
-      <c r="T24" s="102"/>
-      <c r="U24" s="102"/>
-      <c r="V24" s="102"/>
-      <c r="W24" s="102"/>
-      <c r="X24" s="102"/>
-      <c r="Y24" s="102"/>
-      <c r="Z24" s="102"/>
-      <c r="AA24" s="102"/>
-      <c r="AB24" s="102"/>
-      <c r="AC24" s="102"/>
-      <c r="AD24" s="102"/>
-      <c r="AE24" s="102"/>
-      <c r="AF24" s="102"/>
-      <c r="AG24" s="102"/>
-      <c r="AH24" s="102"/>
-      <c r="AI24" s="102"/>
-      <c r="AJ24" s="102"/>
-      <c r="AK24" s="102"/>
-      <c r="AL24" s="102"/>
-      <c r="AM24" s="102"/>
-      <c r="AN24" s="102"/>
-      <c r="AO24" s="102"/>
-      <c r="AP24" s="102"/>
-      <c r="AQ24" s="102"/>
-      <c r="AR24" s="102"/>
-      <c r="AS24" s="102"/>
-      <c r="AT24" s="102"/>
-      <c r="AU24" s="102"/>
-      <c r="AV24" s="102"/>
-      <c r="AW24" s="102"/>
-      <c r="AX24" s="102"/>
-      <c r="AY24" s="102"/>
-      <c r="AZ24" s="102"/>
-      <c r="BA24" s="102"/>
-      <c r="BB24" s="102"/>
-      <c r="BC24" s="102"/>
-      <c r="BD24" s="102"/>
-      <c r="BE24" s="102"/>
-      <c r="BF24" s="102"/>
-      <c r="BG24" s="102"/>
-      <c r="BH24" s="102"/>
-      <c r="BI24" s="102"/>
-      <c r="BJ24" s="102"/>
-      <c r="BK24" s="102"/>
-      <c r="BL24" s="102"/>
-      <c r="BM24" s="102"/>
-      <c r="BN24" s="102"/>
-      <c r="BO24" s="102"/>
-      <c r="BP24" s="102"/>
-      <c r="BQ24" s="102"/>
-      <c r="BR24" s="102"/>
-      <c r="BS24" s="102"/>
-      <c r="BT24" s="102"/>
-      <c r="BU24" s="102"/>
-      <c r="BV24" s="102"/>
-      <c r="BW24" s="102"/>
-      <c r="BX24" s="102"/>
-      <c r="BY24" s="102"/>
-      <c r="BZ24" s="102"/>
-      <c r="CA24" s="102"/>
-      <c r="CB24" s="102"/>
-      <c r="CC24" s="102"/>
-      <c r="CD24" s="102"/>
-      <c r="CE24" s="102"/>
-      <c r="CF24" s="102"/>
-      <c r="CG24" s="102"/>
-      <c r="CH24" s="102"/>
-      <c r="CI24" s="102"/>
-      <c r="CJ24" s="102"/>
-      <c r="CK24" s="102"/>
-      <c r="CL24" s="102"/>
-      <c r="CM24" s="102"/>
-      <c r="CN24" s="102"/>
-      <c r="CO24" s="102"/>
-      <c r="CP24" s="102"/>
-      <c r="CQ24" s="102"/>
-      <c r="CR24" s="102"/>
-      <c r="CS24" s="102"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="78"/>
+      <c r="E24" s="79"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="70"/>
+      <c r="R24" s="70"/>
+      <c r="S24" s="70"/>
+      <c r="T24" s="70"/>
+      <c r="U24" s="70"/>
+      <c r="V24" s="70"/>
+      <c r="W24" s="70"/>
+      <c r="X24" s="70"/>
+      <c r="Y24" s="70"/>
+      <c r="Z24" s="70"/>
+      <c r="AA24" s="70"/>
+      <c r="AB24" s="70"/>
+      <c r="AC24" s="70"/>
+      <c r="AD24" s="70"/>
+      <c r="AE24" s="70"/>
+      <c r="AF24" s="70"/>
+      <c r="AG24" s="70"/>
+      <c r="AH24" s="70"/>
+      <c r="AI24" s="70"/>
+      <c r="AJ24" s="70"/>
+      <c r="AK24" s="70"/>
+      <c r="AL24" s="70"/>
+      <c r="AM24" s="70"/>
+      <c r="AN24" s="70"/>
+      <c r="AO24" s="70"/>
+      <c r="AP24" s="70"/>
+      <c r="AQ24" s="70"/>
+      <c r="AR24" s="70"/>
+      <c r="AS24" s="70"/>
+      <c r="AT24" s="70"/>
+      <c r="AU24" s="70"/>
+      <c r="AV24" s="70"/>
+      <c r="AW24" s="70"/>
+      <c r="AX24" s="70"/>
+      <c r="AY24" s="70"/>
+      <c r="AZ24" s="70"/>
+      <c r="BA24" s="70"/>
+      <c r="BB24" s="70"/>
+      <c r="BC24" s="70"/>
+      <c r="BD24" s="70"/>
+      <c r="BE24" s="70"/>
+      <c r="BF24" s="70"/>
+      <c r="BG24" s="70"/>
+      <c r="BH24" s="70"/>
+      <c r="BI24" s="70"/>
+      <c r="BJ24" s="70"/>
+      <c r="BK24" s="70"/>
+      <c r="BL24" s="70"/>
+      <c r="BM24" s="70"/>
+      <c r="BN24" s="70"/>
+      <c r="BO24" s="70"/>
+      <c r="BP24" s="70"/>
+      <c r="BQ24" s="70"/>
+      <c r="BR24" s="70"/>
+      <c r="BS24" s="70"/>
+      <c r="BT24" s="70"/>
+      <c r="BU24" s="70"/>
+      <c r="BV24" s="70"/>
+      <c r="BW24" s="70"/>
+      <c r="BX24" s="70"/>
+      <c r="BY24" s="70"/>
+      <c r="BZ24" s="70"/>
+      <c r="CA24" s="70"/>
+      <c r="CB24" s="70"/>
+      <c r="CC24" s="70"/>
+      <c r="CD24" s="70"/>
+      <c r="CE24" s="70"/>
+      <c r="CF24" s="70"/>
+      <c r="CG24" s="70"/>
+      <c r="CH24" s="70"/>
+      <c r="CI24" s="70"/>
+      <c r="CJ24" s="70"/>
+      <c r="CK24" s="70"/>
+      <c r="CL24" s="70"/>
+      <c r="CM24" s="70"/>
+      <c r="CN24" s="70"/>
+      <c r="CO24" s="70"/>
+      <c r="CP24" s="70"/>
+      <c r="CQ24" s="70"/>
+      <c r="CR24" s="70"/>
+      <c r="CS24" s="70"/>
     </row>
     <row r="25" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="107"/>
-      <c r="C25" s="109"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="102"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="102"/>
-      <c r="K25" s="102"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="102"/>
-      <c r="N25" s="102"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="102"/>
-      <c r="Q25" s="102"/>
-      <c r="R25" s="102"/>
-      <c r="S25" s="102"/>
-      <c r="T25" s="102"/>
-      <c r="U25" s="102"/>
-      <c r="V25" s="102"/>
-      <c r="W25" s="102"/>
-      <c r="X25" s="102"/>
-      <c r="Y25" s="102"/>
-      <c r="Z25" s="102"/>
-      <c r="AA25" s="102"/>
-      <c r="AB25" s="102"/>
-      <c r="AC25" s="102"/>
-      <c r="AD25" s="102"/>
-      <c r="AE25" s="102"/>
-      <c r="AF25" s="102"/>
-      <c r="AG25" s="102"/>
-      <c r="AH25" s="102"/>
-      <c r="AI25" s="102"/>
-      <c r="AJ25" s="102"/>
-      <c r="AK25" s="102"/>
-      <c r="AL25" s="102"/>
-      <c r="AM25" s="102"/>
-      <c r="AN25" s="102"/>
-      <c r="AO25" s="102"/>
-      <c r="AP25" s="102"/>
-      <c r="AQ25" s="102"/>
-      <c r="AR25" s="102"/>
-      <c r="AS25" s="102"/>
-      <c r="AT25" s="102"/>
-      <c r="AU25" s="102"/>
-      <c r="AV25" s="102"/>
-      <c r="AW25" s="102"/>
-      <c r="AX25" s="102"/>
-      <c r="AY25" s="102"/>
-      <c r="AZ25" s="102"/>
-      <c r="BA25" s="102"/>
-      <c r="BB25" s="102"/>
-      <c r="BC25" s="102"/>
-      <c r="BD25" s="102"/>
-      <c r="BE25" s="102"/>
-      <c r="BF25" s="102"/>
-      <c r="BG25" s="102"/>
-      <c r="BH25" s="102"/>
-      <c r="BI25" s="102"/>
-      <c r="BJ25" s="102"/>
-      <c r="BK25" s="102"/>
-      <c r="BL25" s="102"/>
-      <c r="BM25" s="102"/>
-      <c r="BN25" s="102"/>
-      <c r="BO25" s="102"/>
-      <c r="BP25" s="102"/>
-      <c r="BQ25" s="102"/>
-      <c r="BR25" s="102"/>
-      <c r="BS25" s="102"/>
-      <c r="BT25" s="102"/>
-      <c r="BU25" s="102"/>
-      <c r="BV25" s="102"/>
-      <c r="BW25" s="102"/>
-      <c r="BX25" s="102"/>
-      <c r="BY25" s="102"/>
-      <c r="BZ25" s="102"/>
-      <c r="CA25" s="102"/>
-      <c r="CB25" s="102"/>
-      <c r="CC25" s="102"/>
-      <c r="CD25" s="102"/>
-      <c r="CE25" s="102"/>
-      <c r="CF25" s="102"/>
-      <c r="CG25" s="102"/>
-      <c r="CH25" s="102"/>
-      <c r="CI25" s="102"/>
-      <c r="CJ25" s="102"/>
-      <c r="CK25" s="102"/>
-      <c r="CL25" s="102"/>
-      <c r="CM25" s="102"/>
-      <c r="CN25" s="102"/>
-      <c r="CO25" s="102"/>
-      <c r="CP25" s="102"/>
-      <c r="CQ25" s="102"/>
-      <c r="CR25" s="102"/>
-      <c r="CS25" s="102"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="70"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="70"/>
+      <c r="Q25" s="70"/>
+      <c r="R25" s="70"/>
+      <c r="S25" s="70"/>
+      <c r="T25" s="70"/>
+      <c r="U25" s="70"/>
+      <c r="V25" s="70"/>
+      <c r="W25" s="70"/>
+      <c r="X25" s="70"/>
+      <c r="Y25" s="70"/>
+      <c r="Z25" s="70"/>
+      <c r="AA25" s="70"/>
+      <c r="AB25" s="70"/>
+      <c r="AC25" s="70"/>
+      <c r="AD25" s="70"/>
+      <c r="AE25" s="70"/>
+      <c r="AF25" s="70"/>
+      <c r="AG25" s="70"/>
+      <c r="AH25" s="70"/>
+      <c r="AI25" s="70"/>
+      <c r="AJ25" s="70"/>
+      <c r="AK25" s="70"/>
+      <c r="AL25" s="70"/>
+      <c r="AM25" s="70"/>
+      <c r="AN25" s="70"/>
+      <c r="AO25" s="70"/>
+      <c r="AP25" s="70"/>
+      <c r="AQ25" s="70"/>
+      <c r="AR25" s="70"/>
+      <c r="AS25" s="70"/>
+      <c r="AT25" s="70"/>
+      <c r="AU25" s="70"/>
+      <c r="AV25" s="70"/>
+      <c r="AW25" s="70"/>
+      <c r="AX25" s="70"/>
+      <c r="AY25" s="70"/>
+      <c r="AZ25" s="70"/>
+      <c r="BA25" s="70"/>
+      <c r="BB25" s="70"/>
+      <c r="BC25" s="70"/>
+      <c r="BD25" s="70"/>
+      <c r="BE25" s="70"/>
+      <c r="BF25" s="70"/>
+      <c r="BG25" s="70"/>
+      <c r="BH25" s="70"/>
+      <c r="BI25" s="70"/>
+      <c r="BJ25" s="70"/>
+      <c r="BK25" s="70"/>
+      <c r="BL25" s="70"/>
+      <c r="BM25" s="70"/>
+      <c r="BN25" s="70"/>
+      <c r="BO25" s="70"/>
+      <c r="BP25" s="70"/>
+      <c r="BQ25" s="70"/>
+      <c r="BR25" s="70"/>
+      <c r="BS25" s="70"/>
+      <c r="BT25" s="70"/>
+      <c r="BU25" s="70"/>
+      <c r="BV25" s="70"/>
+      <c r="BW25" s="70"/>
+      <c r="BX25" s="70"/>
+      <c r="BY25" s="70"/>
+      <c r="BZ25" s="70"/>
+      <c r="CA25" s="70"/>
+      <c r="CB25" s="70"/>
+      <c r="CC25" s="70"/>
+      <c r="CD25" s="70"/>
+      <c r="CE25" s="70"/>
+      <c r="CF25" s="70"/>
+      <c r="CG25" s="70"/>
+      <c r="CH25" s="70"/>
+      <c r="CI25" s="70"/>
+      <c r="CJ25" s="70"/>
+      <c r="CK25" s="70"/>
+      <c r="CL25" s="70"/>
+      <c r="CM25" s="70"/>
+      <c r="CN25" s="70"/>
+      <c r="CO25" s="70"/>
+      <c r="CP25" s="70"/>
+      <c r="CQ25" s="70"/>
+      <c r="CR25" s="70"/>
+      <c r="CS25" s="70"/>
     </row>
     <row r="26" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="107"/>
-      <c r="C26" s="109"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="102"/>
-      <c r="I26" s="102"/>
-      <c r="J26" s="102"/>
-      <c r="K26" s="102"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="102"/>
-      <c r="N26" s="102"/>
-      <c r="O26" s="102"/>
-      <c r="P26" s="102"/>
-      <c r="Q26" s="102"/>
-      <c r="R26" s="102"/>
-      <c r="S26" s="102"/>
-      <c r="T26" s="102"/>
-      <c r="U26" s="102"/>
-      <c r="V26" s="102"/>
-      <c r="W26" s="102"/>
-      <c r="X26" s="102"/>
-      <c r="Y26" s="102"/>
-      <c r="Z26" s="102"/>
-      <c r="AA26" s="102"/>
-      <c r="AB26" s="102"/>
-      <c r="AC26" s="102"/>
-      <c r="AD26" s="102"/>
-      <c r="AE26" s="102"/>
-      <c r="AF26" s="102"/>
-      <c r="AG26" s="102"/>
-      <c r="AH26" s="102"/>
-      <c r="AI26" s="102"/>
-      <c r="AJ26" s="102"/>
-      <c r="AK26" s="102"/>
-      <c r="AL26" s="102"/>
-      <c r="AM26" s="102"/>
-      <c r="AN26" s="102"/>
-      <c r="AO26" s="102"/>
-      <c r="AP26" s="102"/>
-      <c r="AQ26" s="102"/>
-      <c r="AR26" s="102"/>
-      <c r="AS26" s="102"/>
-      <c r="AT26" s="102"/>
-      <c r="AU26" s="102"/>
-      <c r="AV26" s="102"/>
-      <c r="AW26" s="102"/>
-      <c r="AX26" s="102"/>
-      <c r="AY26" s="102"/>
-      <c r="AZ26" s="102"/>
-      <c r="BA26" s="102"/>
-      <c r="BB26" s="102"/>
-      <c r="BC26" s="102"/>
-      <c r="BD26" s="102"/>
-      <c r="BE26" s="102"/>
-      <c r="BF26" s="102"/>
-      <c r="BG26" s="102"/>
-      <c r="BH26" s="102"/>
-      <c r="BI26" s="102"/>
-      <c r="BJ26" s="102"/>
-      <c r="BK26" s="102"/>
-      <c r="BL26" s="102"/>
-      <c r="BM26" s="102"/>
-      <c r="BN26" s="102"/>
-      <c r="BO26" s="102"/>
-      <c r="BP26" s="102"/>
-      <c r="BQ26" s="102"/>
-      <c r="BR26" s="102"/>
-      <c r="BS26" s="102"/>
-      <c r="BT26" s="102"/>
-      <c r="BU26" s="102"/>
-      <c r="BV26" s="102"/>
-      <c r="BW26" s="102"/>
-      <c r="BX26" s="102"/>
-      <c r="BY26" s="102"/>
-      <c r="BZ26" s="102"/>
-      <c r="CA26" s="102"/>
-      <c r="CB26" s="102"/>
-      <c r="CC26" s="102"/>
-      <c r="CD26" s="102"/>
-      <c r="CE26" s="102"/>
-      <c r="CF26" s="102"/>
-      <c r="CG26" s="102"/>
-      <c r="CH26" s="102"/>
-      <c r="CI26" s="102"/>
-      <c r="CJ26" s="102"/>
-      <c r="CK26" s="102"/>
-      <c r="CL26" s="102"/>
-      <c r="CM26" s="102"/>
-      <c r="CN26" s="102"/>
-      <c r="CO26" s="102"/>
-      <c r="CP26" s="102"/>
-      <c r="CQ26" s="102"/>
-      <c r="CR26" s="102"/>
-      <c r="CS26" s="102"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="70"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="70"/>
+      <c r="Q26" s="70"/>
+      <c r="R26" s="70"/>
+      <c r="S26" s="70"/>
+      <c r="T26" s="70"/>
+      <c r="U26" s="70"/>
+      <c r="V26" s="70"/>
+      <c r="W26" s="70"/>
+      <c r="X26" s="70"/>
+      <c r="Y26" s="70"/>
+      <c r="Z26" s="70"/>
+      <c r="AA26" s="70"/>
+      <c r="AB26" s="70"/>
+      <c r="AC26" s="70"/>
+      <c r="AD26" s="70"/>
+      <c r="AE26" s="70"/>
+      <c r="AF26" s="70"/>
+      <c r="AG26" s="70"/>
+      <c r="AH26" s="70"/>
+      <c r="AI26" s="70"/>
+      <c r="AJ26" s="70"/>
+      <c r="AK26" s="70"/>
+      <c r="AL26" s="70"/>
+      <c r="AM26" s="70"/>
+      <c r="AN26" s="70"/>
+      <c r="AO26" s="70"/>
+      <c r="AP26" s="70"/>
+      <c r="AQ26" s="70"/>
+      <c r="AR26" s="70"/>
+      <c r="AS26" s="70"/>
+      <c r="AT26" s="70"/>
+      <c r="AU26" s="70"/>
+      <c r="AV26" s="70"/>
+      <c r="AW26" s="70"/>
+      <c r="AX26" s="70"/>
+      <c r="AY26" s="70"/>
+      <c r="AZ26" s="70"/>
+      <c r="BA26" s="70"/>
+      <c r="BB26" s="70"/>
+      <c r="BC26" s="70"/>
+      <c r="BD26" s="70"/>
+      <c r="BE26" s="70"/>
+      <c r="BF26" s="70"/>
+      <c r="BG26" s="70"/>
+      <c r="BH26" s="70"/>
+      <c r="BI26" s="70"/>
+      <c r="BJ26" s="70"/>
+      <c r="BK26" s="70"/>
+      <c r="BL26" s="70"/>
+      <c r="BM26" s="70"/>
+      <c r="BN26" s="70"/>
+      <c r="BO26" s="70"/>
+      <c r="BP26" s="70"/>
+      <c r="BQ26" s="70"/>
+      <c r="BR26" s="70"/>
+      <c r="BS26" s="70"/>
+      <c r="BT26" s="70"/>
+      <c r="BU26" s="70"/>
+      <c r="BV26" s="70"/>
+      <c r="BW26" s="70"/>
+      <c r="BX26" s="70"/>
+      <c r="BY26" s="70"/>
+      <c r="BZ26" s="70"/>
+      <c r="CA26" s="70"/>
+      <c r="CB26" s="70"/>
+      <c r="CC26" s="70"/>
+      <c r="CD26" s="70"/>
+      <c r="CE26" s="70"/>
+      <c r="CF26" s="70"/>
+      <c r="CG26" s="70"/>
+      <c r="CH26" s="70"/>
+      <c r="CI26" s="70"/>
+      <c r="CJ26" s="70"/>
+      <c r="CK26" s="70"/>
+      <c r="CL26" s="70"/>
+      <c r="CM26" s="70"/>
+      <c r="CN26" s="70"/>
+      <c r="CO26" s="70"/>
+      <c r="CP26" s="70"/>
+      <c r="CQ26" s="70"/>
+      <c r="CR26" s="70"/>
+      <c r="CS26" s="70"/>
     </row>
     <row r="27" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="107"/>
-      <c r="C27" s="109"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="102"/>
-      <c r="H27" s="102"/>
-      <c r="I27" s="102"/>
-      <c r="J27" s="102"/>
-      <c r="K27" s="102"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="102"/>
-      <c r="N27" s="102"/>
-      <c r="O27" s="102"/>
-      <c r="P27" s="102"/>
-      <c r="Q27" s="102"/>
-      <c r="R27" s="102"/>
-      <c r="S27" s="102"/>
-      <c r="T27" s="102"/>
-      <c r="U27" s="102"/>
-      <c r="V27" s="102"/>
-      <c r="W27" s="102"/>
-      <c r="X27" s="102"/>
-      <c r="Y27" s="102"/>
-      <c r="Z27" s="102"/>
-      <c r="AA27" s="102"/>
-      <c r="AB27" s="102"/>
-      <c r="AC27" s="102"/>
-      <c r="AD27" s="102"/>
-      <c r="AE27" s="102"/>
-      <c r="AF27" s="102"/>
-      <c r="AG27" s="102"/>
-      <c r="AH27" s="102"/>
-      <c r="AI27" s="102"/>
-      <c r="AJ27" s="102"/>
-      <c r="AK27" s="102"/>
-      <c r="AL27" s="102"/>
-      <c r="AM27" s="102"/>
-      <c r="AN27" s="102"/>
-      <c r="AO27" s="102"/>
-      <c r="AP27" s="102"/>
-      <c r="AQ27" s="102"/>
-      <c r="AR27" s="102"/>
-      <c r="AS27" s="102"/>
-      <c r="AT27" s="102"/>
-      <c r="AU27" s="102"/>
-      <c r="AV27" s="102"/>
-      <c r="AW27" s="102"/>
-      <c r="AX27" s="102"/>
-      <c r="AY27" s="102"/>
-      <c r="AZ27" s="102"/>
-      <c r="BA27" s="102"/>
-      <c r="BB27" s="102"/>
-      <c r="BC27" s="102"/>
-      <c r="BD27" s="102"/>
-      <c r="BE27" s="102"/>
-      <c r="BF27" s="102"/>
-      <c r="BG27" s="102"/>
-      <c r="BH27" s="102"/>
-      <c r="BI27" s="102"/>
-      <c r="BJ27" s="102"/>
-      <c r="BK27" s="102"/>
-      <c r="BL27" s="102"/>
-      <c r="BM27" s="102"/>
-      <c r="BN27" s="102"/>
-      <c r="BO27" s="102"/>
-      <c r="BP27" s="102"/>
-      <c r="BQ27" s="102"/>
-      <c r="BR27" s="102"/>
-      <c r="BS27" s="102"/>
-      <c r="BT27" s="102"/>
-      <c r="BU27" s="102"/>
-      <c r="BV27" s="102"/>
-      <c r="BW27" s="102"/>
-      <c r="BX27" s="102"/>
-      <c r="BY27" s="102"/>
-      <c r="BZ27" s="102"/>
-      <c r="CA27" s="102"/>
-      <c r="CB27" s="102"/>
-      <c r="CC27" s="102"/>
-      <c r="CD27" s="102"/>
-      <c r="CE27" s="102"/>
-      <c r="CF27" s="102"/>
-      <c r="CG27" s="102"/>
-      <c r="CH27" s="102"/>
-      <c r="CI27" s="102"/>
-      <c r="CJ27" s="102"/>
-      <c r="CK27" s="102"/>
-      <c r="CL27" s="102"/>
-      <c r="CM27" s="102"/>
-      <c r="CN27" s="102"/>
-      <c r="CO27" s="102"/>
-      <c r="CP27" s="102"/>
-      <c r="CQ27" s="102"/>
-      <c r="CR27" s="102"/>
-      <c r="CS27" s="102"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="79"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="70"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="70"/>
+      <c r="Q27" s="70"/>
+      <c r="R27" s="70"/>
+      <c r="S27" s="70"/>
+      <c r="T27" s="70"/>
+      <c r="U27" s="70"/>
+      <c r="V27" s="70"/>
+      <c r="W27" s="70"/>
+      <c r="X27" s="70"/>
+      <c r="Y27" s="70"/>
+      <c r="Z27" s="70"/>
+      <c r="AA27" s="70"/>
+      <c r="AB27" s="70"/>
+      <c r="AC27" s="70"/>
+      <c r="AD27" s="70"/>
+      <c r="AE27" s="70"/>
+      <c r="AF27" s="70"/>
+      <c r="AG27" s="70"/>
+      <c r="AH27" s="70"/>
+      <c r="AI27" s="70"/>
+      <c r="AJ27" s="70"/>
+      <c r="AK27" s="70"/>
+      <c r="AL27" s="70"/>
+      <c r="AM27" s="70"/>
+      <c r="AN27" s="70"/>
+      <c r="AO27" s="70"/>
+      <c r="AP27" s="70"/>
+      <c r="AQ27" s="70"/>
+      <c r="AR27" s="70"/>
+      <c r="AS27" s="70"/>
+      <c r="AT27" s="70"/>
+      <c r="AU27" s="70"/>
+      <c r="AV27" s="70"/>
+      <c r="AW27" s="70"/>
+      <c r="AX27" s="70"/>
+      <c r="AY27" s="70"/>
+      <c r="AZ27" s="70"/>
+      <c r="BA27" s="70"/>
+      <c r="BB27" s="70"/>
+      <c r="BC27" s="70"/>
+      <c r="BD27" s="70"/>
+      <c r="BE27" s="70"/>
+      <c r="BF27" s="70"/>
+      <c r="BG27" s="70"/>
+      <c r="BH27" s="70"/>
+      <c r="BI27" s="70"/>
+      <c r="BJ27" s="70"/>
+      <c r="BK27" s="70"/>
+      <c r="BL27" s="70"/>
+      <c r="BM27" s="70"/>
+      <c r="BN27" s="70"/>
+      <c r="BO27" s="70"/>
+      <c r="BP27" s="70"/>
+      <c r="BQ27" s="70"/>
+      <c r="BR27" s="70"/>
+      <c r="BS27" s="70"/>
+      <c r="BT27" s="70"/>
+      <c r="BU27" s="70"/>
+      <c r="BV27" s="70"/>
+      <c r="BW27" s="70"/>
+      <c r="BX27" s="70"/>
+      <c r="BY27" s="70"/>
+      <c r="BZ27" s="70"/>
+      <c r="CA27" s="70"/>
+      <c r="CB27" s="70"/>
+      <c r="CC27" s="70"/>
+      <c r="CD27" s="70"/>
+      <c r="CE27" s="70"/>
+      <c r="CF27" s="70"/>
+      <c r="CG27" s="70"/>
+      <c r="CH27" s="70"/>
+      <c r="CI27" s="70"/>
+      <c r="CJ27" s="70"/>
+      <c r="CK27" s="70"/>
+      <c r="CL27" s="70"/>
+      <c r="CM27" s="70"/>
+      <c r="CN27" s="70"/>
+      <c r="CO27" s="70"/>
+      <c r="CP27" s="70"/>
+      <c r="CQ27" s="70"/>
+      <c r="CR27" s="70"/>
+      <c r="CS27" s="70"/>
     </row>
     <row r="28" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="107"/>
-      <c r="C28" s="109"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="102"/>
-      <c r="H28" s="102"/>
-      <c r="I28" s="102"/>
-      <c r="J28" s="102"/>
-      <c r="K28" s="102"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="102"/>
-      <c r="N28" s="102"/>
-      <c r="O28" s="102"/>
-      <c r="P28" s="102"/>
-      <c r="Q28" s="102"/>
-      <c r="R28" s="102"/>
-      <c r="S28" s="102"/>
-      <c r="T28" s="102"/>
-      <c r="U28" s="102"/>
-      <c r="V28" s="102"/>
-      <c r="W28" s="102"/>
-      <c r="X28" s="102"/>
-      <c r="Y28" s="102"/>
-      <c r="Z28" s="102"/>
-      <c r="AA28" s="102"/>
-      <c r="AB28" s="102"/>
-      <c r="AC28" s="102"/>
-      <c r="AD28" s="102"/>
-      <c r="AE28" s="102"/>
-      <c r="AF28" s="102"/>
-      <c r="AG28" s="102"/>
-      <c r="AH28" s="102"/>
-      <c r="AI28" s="102"/>
-      <c r="AJ28" s="102"/>
-      <c r="AK28" s="102"/>
-      <c r="AL28" s="102"/>
-      <c r="AM28" s="102"/>
-      <c r="AN28" s="102"/>
-      <c r="AO28" s="102"/>
-      <c r="AP28" s="102"/>
-      <c r="AQ28" s="102"/>
-      <c r="AR28" s="102"/>
-      <c r="AS28" s="102"/>
-      <c r="AT28" s="102"/>
-      <c r="AU28" s="102"/>
-      <c r="AV28" s="102"/>
-      <c r="AW28" s="102"/>
-      <c r="AX28" s="102"/>
-      <c r="AY28" s="102"/>
-      <c r="AZ28" s="102"/>
-      <c r="BA28" s="102"/>
-      <c r="BB28" s="102"/>
-      <c r="BC28" s="102"/>
-      <c r="BD28" s="102"/>
-      <c r="BE28" s="102"/>
-      <c r="BF28" s="102"/>
-      <c r="BG28" s="102"/>
-      <c r="BH28" s="102"/>
-      <c r="BI28" s="102"/>
-      <c r="BJ28" s="102"/>
-      <c r="BK28" s="102"/>
-      <c r="BL28" s="102"/>
-      <c r="BM28" s="102"/>
-      <c r="BN28" s="102"/>
-      <c r="BO28" s="102"/>
-      <c r="BP28" s="102"/>
-      <c r="BQ28" s="102"/>
-      <c r="BR28" s="102"/>
-      <c r="BS28" s="102"/>
-      <c r="BT28" s="102"/>
-      <c r="BU28" s="102"/>
-      <c r="BV28" s="102"/>
-      <c r="BW28" s="102"/>
-      <c r="BX28" s="102"/>
-      <c r="BY28" s="102"/>
-      <c r="BZ28" s="102"/>
-      <c r="CA28" s="102"/>
-      <c r="CB28" s="102"/>
-      <c r="CC28" s="102"/>
-      <c r="CD28" s="102"/>
-      <c r="CE28" s="102"/>
-      <c r="CF28" s="102"/>
-      <c r="CG28" s="102"/>
-      <c r="CH28" s="102"/>
-      <c r="CI28" s="102"/>
-      <c r="CJ28" s="102"/>
-      <c r="CK28" s="102"/>
-      <c r="CL28" s="102"/>
-      <c r="CM28" s="102"/>
-      <c r="CN28" s="102"/>
-      <c r="CO28" s="102"/>
-      <c r="CP28" s="102"/>
-      <c r="CQ28" s="102"/>
-      <c r="CR28" s="102"/>
-      <c r="CS28" s="102"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="70"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="70"/>
+      <c r="Q28" s="70"/>
+      <c r="R28" s="70"/>
+      <c r="S28" s="70"/>
+      <c r="T28" s="70"/>
+      <c r="U28" s="70"/>
+      <c r="V28" s="70"/>
+      <c r="W28" s="70"/>
+      <c r="X28" s="70"/>
+      <c r="Y28" s="70"/>
+      <c r="Z28" s="70"/>
+      <c r="AA28" s="70"/>
+      <c r="AB28" s="70"/>
+      <c r="AC28" s="70"/>
+      <c r="AD28" s="70"/>
+      <c r="AE28" s="70"/>
+      <c r="AF28" s="70"/>
+      <c r="AG28" s="70"/>
+      <c r="AH28" s="70"/>
+      <c r="AI28" s="70"/>
+      <c r="AJ28" s="70"/>
+      <c r="AK28" s="70"/>
+      <c r="AL28" s="70"/>
+      <c r="AM28" s="70"/>
+      <c r="AN28" s="70"/>
+      <c r="AO28" s="70"/>
+      <c r="AP28" s="70"/>
+      <c r="AQ28" s="70"/>
+      <c r="AR28" s="70"/>
+      <c r="AS28" s="70"/>
+      <c r="AT28" s="70"/>
+      <c r="AU28" s="70"/>
+      <c r="AV28" s="70"/>
+      <c r="AW28" s="70"/>
+      <c r="AX28" s="70"/>
+      <c r="AY28" s="70"/>
+      <c r="AZ28" s="70"/>
+      <c r="BA28" s="70"/>
+      <c r="BB28" s="70"/>
+      <c r="BC28" s="70"/>
+      <c r="BD28" s="70"/>
+      <c r="BE28" s="70"/>
+      <c r="BF28" s="70"/>
+      <c r="BG28" s="70"/>
+      <c r="BH28" s="70"/>
+      <c r="BI28" s="70"/>
+      <c r="BJ28" s="70"/>
+      <c r="BK28" s="70"/>
+      <c r="BL28" s="70"/>
+      <c r="BM28" s="70"/>
+      <c r="BN28" s="70"/>
+      <c r="BO28" s="70"/>
+      <c r="BP28" s="70"/>
+      <c r="BQ28" s="70"/>
+      <c r="BR28" s="70"/>
+      <c r="BS28" s="70"/>
+      <c r="BT28" s="70"/>
+      <c r="BU28" s="70"/>
+      <c r="BV28" s="70"/>
+      <c r="BW28" s="70"/>
+      <c r="BX28" s="70"/>
+      <c r="BY28" s="70"/>
+      <c r="BZ28" s="70"/>
+      <c r="CA28" s="70"/>
+      <c r="CB28" s="70"/>
+      <c r="CC28" s="70"/>
+      <c r="CD28" s="70"/>
+      <c r="CE28" s="70"/>
+      <c r="CF28" s="70"/>
+      <c r="CG28" s="70"/>
+      <c r="CH28" s="70"/>
+      <c r="CI28" s="70"/>
+      <c r="CJ28" s="70"/>
+      <c r="CK28" s="70"/>
+      <c r="CL28" s="70"/>
+      <c r="CM28" s="70"/>
+      <c r="CN28" s="70"/>
+      <c r="CO28" s="70"/>
+      <c r="CP28" s="70"/>
+      <c r="CQ28" s="70"/>
+      <c r="CR28" s="70"/>
+      <c r="CS28" s="70"/>
     </row>
     <row r="29" spans="2:97" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="107"/>
-      <c r="C29" s="109"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="102"/>
-      <c r="H29" s="102"/>
-      <c r="I29" s="102"/>
-      <c r="J29" s="102"/>
-      <c r="K29" s="102"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="102"/>
-      <c r="N29" s="102"/>
-      <c r="O29" s="102"/>
-      <c r="P29" s="102"/>
-      <c r="Q29" s="102"/>
-      <c r="R29" s="102"/>
-      <c r="S29" s="102"/>
-      <c r="T29" s="102"/>
-      <c r="U29" s="102"/>
-      <c r="V29" s="102"/>
-      <c r="W29" s="102"/>
-      <c r="X29" s="102"/>
-      <c r="Y29" s="102"/>
-      <c r="Z29" s="102"/>
-      <c r="AA29" s="102"/>
-      <c r="AB29" s="102"/>
-      <c r="AC29" s="102"/>
-      <c r="AD29" s="102"/>
-      <c r="AE29" s="102"/>
-      <c r="AF29" s="102"/>
-      <c r="AG29" s="102"/>
-      <c r="AH29" s="102"/>
-      <c r="AI29" s="102"/>
-      <c r="AJ29" s="102"/>
-      <c r="AK29" s="102"/>
-      <c r="AL29" s="102"/>
-      <c r="AM29" s="102"/>
-      <c r="AN29" s="102"/>
-      <c r="AO29" s="102"/>
-      <c r="AP29" s="102"/>
-      <c r="AQ29" s="102"/>
-      <c r="AR29" s="102"/>
-      <c r="AS29" s="102"/>
-      <c r="AT29" s="102"/>
-      <c r="AU29" s="102"/>
-      <c r="AV29" s="102"/>
-      <c r="AW29" s="102"/>
-      <c r="AX29" s="102"/>
-      <c r="AY29" s="102"/>
-      <c r="AZ29" s="102"/>
-      <c r="BA29" s="102"/>
-      <c r="BB29" s="102"/>
-      <c r="BC29" s="102"/>
-      <c r="BD29" s="102"/>
-      <c r="BE29" s="102"/>
-      <c r="BF29" s="102"/>
-      <c r="BG29" s="102"/>
-      <c r="BH29" s="102"/>
-      <c r="BI29" s="102"/>
-      <c r="BJ29" s="102"/>
-      <c r="BK29" s="102"/>
-      <c r="BL29" s="102"/>
-      <c r="BM29" s="102"/>
-      <c r="BN29" s="102"/>
-      <c r="BO29" s="102"/>
-      <c r="BP29" s="102"/>
-      <c r="BQ29" s="102"/>
-      <c r="BR29" s="102"/>
-      <c r="BS29" s="102"/>
-      <c r="BT29" s="102"/>
-      <c r="BU29" s="102"/>
-      <c r="BV29" s="102"/>
-      <c r="BW29" s="102"/>
-      <c r="BX29" s="102"/>
-      <c r="BY29" s="102"/>
-      <c r="BZ29" s="102"/>
-      <c r="CA29" s="102"/>
-      <c r="CB29" s="102"/>
-      <c r="CC29" s="102"/>
-      <c r="CD29" s="102"/>
-      <c r="CE29" s="102"/>
-      <c r="CF29" s="102"/>
-      <c r="CG29" s="102"/>
-      <c r="CH29" s="102"/>
-      <c r="CI29" s="102"/>
-      <c r="CJ29" s="102"/>
-      <c r="CK29" s="102"/>
-      <c r="CL29" s="102"/>
-      <c r="CM29" s="102"/>
-      <c r="CN29" s="102"/>
-      <c r="CO29" s="102"/>
-      <c r="CP29" s="102"/>
-      <c r="CQ29" s="102"/>
-      <c r="CR29" s="102"/>
-      <c r="CS29" s="102"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="70"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="70"/>
+      <c r="R29" s="70"/>
+      <c r="S29" s="70"/>
+      <c r="T29" s="70"/>
+      <c r="U29" s="70"/>
+      <c r="V29" s="70"/>
+      <c r="W29" s="70"/>
+      <c r="X29" s="70"/>
+      <c r="Y29" s="70"/>
+      <c r="Z29" s="70"/>
+      <c r="AA29" s="70"/>
+      <c r="AB29" s="70"/>
+      <c r="AC29" s="70"/>
+      <c r="AD29" s="70"/>
+      <c r="AE29" s="70"/>
+      <c r="AF29" s="70"/>
+      <c r="AG29" s="70"/>
+      <c r="AH29" s="70"/>
+      <c r="AI29" s="70"/>
+      <c r="AJ29" s="70"/>
+      <c r="AK29" s="70"/>
+      <c r="AL29" s="70"/>
+      <c r="AM29" s="70"/>
+      <c r="AN29" s="70"/>
+      <c r="AO29" s="70"/>
+      <c r="AP29" s="70"/>
+      <c r="AQ29" s="70"/>
+      <c r="AR29" s="70"/>
+      <c r="AS29" s="70"/>
+      <c r="AT29" s="70"/>
+      <c r="AU29" s="70"/>
+      <c r="AV29" s="70"/>
+      <c r="AW29" s="70"/>
+      <c r="AX29" s="70"/>
+      <c r="AY29" s="70"/>
+      <c r="AZ29" s="70"/>
+      <c r="BA29" s="70"/>
+      <c r="BB29" s="70"/>
+      <c r="BC29" s="70"/>
+      <c r="BD29" s="70"/>
+      <c r="BE29" s="70"/>
+      <c r="BF29" s="70"/>
+      <c r="BG29" s="70"/>
+      <c r="BH29" s="70"/>
+      <c r="BI29" s="70"/>
+      <c r="BJ29" s="70"/>
+      <c r="BK29" s="70"/>
+      <c r="BL29" s="70"/>
+      <c r="BM29" s="70"/>
+      <c r="BN29" s="70"/>
+      <c r="BO29" s="70"/>
+      <c r="BP29" s="70"/>
+      <c r="BQ29" s="70"/>
+      <c r="BR29" s="70"/>
+      <c r="BS29" s="70"/>
+      <c r="BT29" s="70"/>
+      <c r="BU29" s="70"/>
+      <c r="BV29" s="70"/>
+      <c r="BW29" s="70"/>
+      <c r="BX29" s="70"/>
+      <c r="BY29" s="70"/>
+      <c r="BZ29" s="70"/>
+      <c r="CA29" s="70"/>
+      <c r="CB29" s="70"/>
+      <c r="CC29" s="70"/>
+      <c r="CD29" s="70"/>
+      <c r="CE29" s="70"/>
+      <c r="CF29" s="70"/>
+      <c r="CG29" s="70"/>
+      <c r="CH29" s="70"/>
+      <c r="CI29" s="70"/>
+      <c r="CJ29" s="70"/>
+      <c r="CK29" s="70"/>
+      <c r="CL29" s="70"/>
+      <c r="CM29" s="70"/>
+      <c r="CN29" s="70"/>
+      <c r="CO29" s="70"/>
+      <c r="CP29" s="70"/>
+      <c r="CQ29" s="70"/>
+      <c r="CR29" s="70"/>
+      <c r="CS29" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AP4:AV4"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:M4"/>
+    <mergeCell ref="N4:T4"/>
+    <mergeCell ref="U4:AA4"/>
+    <mergeCell ref="AB4:AH4"/>
+    <mergeCell ref="AI4:AO4"/>
     <mergeCell ref="CM4:CS4"/>
     <mergeCell ref="AW4:BC4"/>
     <mergeCell ref="BD4:BJ4"/>
@@ -7336,26 +9555,9 @@
     <mergeCell ref="BR4:BX4"/>
     <mergeCell ref="BY4:CE4"/>
     <mergeCell ref="CF4:CL4"/>
-    <mergeCell ref="G4:M4"/>
-    <mergeCell ref="N4:T4"/>
-    <mergeCell ref="U4:AA4"/>
-    <mergeCell ref="AB4:AH4"/>
-    <mergeCell ref="AI4:AO4"/>
-    <mergeCell ref="AP4:AV4"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="G7:CS41">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND($E7&lt;=G$5,$F7&gt;=G$5,$F7&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:CS6">
+  <conditionalFormatting sqref="G6:CS41">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($E6&lt;=G$5,$F6&gt;=G$5,$F6&lt;&gt;"")</formula>
     </cfRule>
@@ -7368,265 +9570,265 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DC256FA-0328-4FE7-B957-7159BD224610}">
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="52.4140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10" style="78" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10" style="58" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="57" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="79">
+      <c r="B2" s="59">
         <v>46236</v>
       </c>
-      <c r="C2" s="79">
+      <c r="C2" s="59">
         <v>46332</v>
       </c>
-      <c r="D2" s="80">
+      <c r="D2" s="60">
         <v>95.75</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="79">
+      <c r="B3" s="59">
         <v>46236</v>
       </c>
-      <c r="C3" s="79">
+      <c r="C3" s="59">
         <v>46240</v>
       </c>
-      <c r="D3" s="80">
+      <c r="D3" s="60">
         <v>3.5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="79">
+      <c r="B4" s="59">
         <v>46236</v>
       </c>
-      <c r="C4" s="79">
+      <c r="C4" s="59">
         <v>46236</v>
       </c>
-      <c r="D4" s="80">
+      <c r="D4" s="60">
         <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="79">
+      <c r="B5" s="59">
         <v>46237</v>
       </c>
-      <c r="C5" s="79">
+      <c r="C5" s="59">
         <v>46237</v>
       </c>
-      <c r="D5" s="80">
+      <c r="D5" s="60">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="79">
+      <c r="B6" s="59">
         <v>46238</v>
       </c>
-      <c r="C6" s="79">
+      <c r="C6" s="59">
         <v>46238</v>
       </c>
-      <c r="D6" s="80">
+      <c r="D6" s="60">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="79">
+      <c r="B7" s="59">
         <v>46239</v>
       </c>
-      <c r="C7" s="79">
+      <c r="C7" s="59">
         <v>46239</v>
       </c>
-      <c r="D7" s="80">
+      <c r="D7" s="60">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="79">
+      <c r="B8" s="59">
         <v>46240</v>
       </c>
-      <c r="C8" s="79">
+      <c r="C8" s="59">
         <v>46240</v>
       </c>
-      <c r="D8" s="80">
+      <c r="D8" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="79">
+      <c r="B9" s="59">
         <v>46241</v>
       </c>
-      <c r="C9" s="79">
+      <c r="C9" s="59">
         <v>46260</v>
       </c>
-      <c r="D9" s="80">
+      <c r="D9" s="60">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="79">
+      <c r="B10" s="59">
         <v>46241</v>
       </c>
-      <c r="C10" s="79">
+      <c r="C10" s="59">
         <v>46245</v>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="60">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="81" t="s">
+      <c r="A11" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="79">
+      <c r="B11" s="59">
         <v>46246</v>
       </c>
-      <c r="C11" s="79">
+      <c r="C11" s="59">
         <v>46252</v>
       </c>
-      <c r="D11" s="80">
+      <c r="D11" s="60">
         <v>7.5</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="79">
+      <c r="B12" s="59">
         <v>46253</v>
       </c>
-      <c r="C12" s="79">
+      <c r="C12" s="59">
         <v>46253</v>
       </c>
-      <c r="D12" s="80">
+      <c r="D12" s="60">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="79">
+      <c r="B13" s="59">
         <v>46254</v>
       </c>
-      <c r="C13" s="79">
+      <c r="C13" s="59">
         <v>46257</v>
       </c>
-      <c r="D13" s="80">
+      <c r="D13" s="60">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="79">
+      <c r="B14" s="59">
         <v>46258</v>
       </c>
-      <c r="C14" s="79">
+      <c r="C14" s="59">
         <v>46258</v>
       </c>
-      <c r="D14" s="80">
+      <c r="D14" s="60">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="81" t="s">
+      <c r="A15" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="79">
+      <c r="B15" s="59">
         <v>46259</v>
       </c>
-      <c r="C15" s="79">
+      <c r="C15" s="59">
         <v>46259</v>
       </c>
-      <c r="D15" s="80">
+      <c r="D15" s="60">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="81" t="s">
+      <c r="A16" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="79">
+      <c r="B16" s="59">
         <v>46260</v>
       </c>
-      <c r="C16" s="79">
+      <c r="C16" s="59">
         <v>46260</v>
       </c>
-      <c r="D16" s="80">
+      <c r="D16" s="60">
         <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="79">
+      <c r="B17" s="59">
         <v>46260</v>
       </c>
-      <c r="C17" s="79">
+      <c r="C17" s="59">
         <v>46260</v>
       </c>
-      <c r="D17" s="80">
+      <c r="D17" s="60">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="81" t="s">
+      <c r="A18" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="79">
+      <c r="B18" s="59">
         <v>46260</v>
       </c>
-      <c r="C18" s="79">
+      <c r="C18" s="59">
         <v>46260</v>
       </c>
-      <c r="D18" s="80">
+      <c r="D18" s="60">
         <v>0</v>
       </c>
     </row>

--- a/高橋さん用フォルダ/図解.xlsx
+++ b/高橋さん用フォルダ/図解.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\iret_pm\高橋さん用フォルダ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136F4520-C606-4DB8-B640-0E0DDC0BF441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5121DF95-6A1F-44B7-A9BD-1FAA8B80E009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{048F0377-5F86-481C-B78B-CC2C2E2E164F}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="11380" windowHeight="13370" xr2:uid="{048F0377-5F86-481C-B78B-CC2C2E2E164F}"/>
   </bookViews>
   <sheets>
     <sheet name="8_図解" sheetId="6" r:id="rId1"/>
@@ -368,58 +368,6 @@
     <t>(Revenue)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Projet Start Day</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>：202X/XX/XX</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Projet End Day</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>：202X/XX/XX</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>(Key Partners)</t>
   </si>
   <si>
@@ -438,6 +386,58 @@
   <si>
     <t>(Key Resources)</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Projet Start Day</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：202X/XX/XX</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Projet End Day</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：202X/XX/XX</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -448,7 +448,7 @@
     <numFmt numFmtId="177" formatCode="d"/>
     <numFmt numFmtId="178" formatCode="0\ &quot;日&quot;"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,15 +494,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
@@ -1499,7 +1490,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1551,368 +1542,371 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="5" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="5" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="55" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="56" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="61" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="5" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="55" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="56" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="5" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="5" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="5" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="61" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2016,7 +2010,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200"/>
-            <a:t>外部に委託 される活動 や、外部か ら調達され るリソース</a:t>
+            <a:t>外部に委託 される活動 や、外部から調達されるリソース</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
         </a:p>
@@ -2083,7 +2077,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200"/>
-            <a:t>ビジネスモデ ルが機能する よう組織が取 組まなければ ならない活動</a:t>
+            <a:t>ビジネスモデ ルが機能するよう組織が取 組まなければならない活動</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
         </a:p>
@@ -2150,7 +2144,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200"/>
-            <a:t>ここにあげた要 素を提供するの に必要となる資 源</a:t>
+            <a:t>ここにあげた要素を提供するのに必要となる資源</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
         </a:p>
@@ -2217,7 +2211,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200"/>
-            <a:t>顧客の抱え る問題を解 決し、ニー ズを満たす もの </a:t>
+            <a:t>顧客の抱える問題を解決し、ニーズを満たすもの </a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
         </a:p>
@@ -2284,7 +2278,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200"/>
-            <a:t>顧客との関係性 を構築、維持、展 開するための 様々な仕組み</a:t>
+            <a:t>顧客との関係性を構築、維持、展開するための様々な仕組み</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
         </a:p>
@@ -2351,7 +2345,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200"/>
-            <a:t>顧客の求める価値を 提供していることを告 知する方法、その価 値を届ける様々な ルート </a:t>
+            <a:t>顧客の求める価値を 提供していることを告知する方法、その価値を届ける様々な ルート </a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
         </a:p>
@@ -2418,7 +2412,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200"/>
-            <a:t>組織が作り出 す価値を届け る相手：人、 他の組織 </a:t>
+            <a:t>組織が作り出す価値を届ける相手：人、 他の組織 </a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
         </a:p>
@@ -2552,7 +2546,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200"/>
-            <a:t>顧客に、与える価値が届けら れる際、支払われるお金 </a:t>
+            <a:t>顧客に、与える価値が届けられる際、支払われるお金 </a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
         </a:p>
@@ -2705,14 +2699,14 @@
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200"/>
-            <a:t>・教材のコンテ ンツ作成 </a:t>
+            <a:t>・教材のコンテンツ作成 </a:t>
           </a:r>
           <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200"/>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200"/>
-            <a:t>・施設・備品・ インストラクターの調達 </a:t>
+            <a:t>・施設・備品・インストラクターの調達 </a:t>
           </a:r>
           <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200"/>
         </a:p>
@@ -2861,7 +2855,7 @@
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200"/>
-            <a:t>理科に関心を持ってくれる子供（特に 女子学生）を育てることで、 社会に貢献</a:t>
+            <a:t>理科に関心を持ってくれる子供（特に女子学生）を育てることで、社会に貢献</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
         </a:p>
@@ -5104,96 +5098,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="132" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="133" t="s">
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="132" t="s">
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="T1" s="133"/>
-      <c r="U1" s="133"/>
-      <c r="V1" s="133"/>
-      <c r="W1" s="133"/>
-      <c r="X1" s="134"/>
-      <c r="Y1" s="133" t="s">
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="Z1" s="133"/>
-      <c r="AA1" s="133"/>
-      <c r="AB1" s="133"/>
-      <c r="AC1" s="133"/>
-      <c r="AD1" s="134"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="64"/>
     </row>
     <row r="2" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="135" t="s">
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="79" t="s">
-        <v>78</v>
-      </c>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="135" t="s">
-        <v>79</v>
-      </c>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
-      <c r="V2" s="79"/>
-      <c r="W2" s="79"/>
-      <c r="X2" s="136"/>
-      <c r="Y2" s="79" t="s">
+      <c r="T2" s="18"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="66"/>
+      <c r="Y2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="79"/>
-      <c r="AB2" s="79"/>
-      <c r="AC2" s="79"/>
-      <c r="AD2" s="136"/>
+      <c r="Z2" s="18"/>
+      <c r="AA2" s="18"/>
+      <c r="AB2" s="18"/>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="66"/>
     </row>
     <row r="3" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="12"/>
       <c r="G3" s="12"/>
       <c r="L3" s="13"/>
       <c r="S3" s="12"/>
-      <c r="T3" s="137" t="s">
-        <v>80</v>
+      <c r="T3" s="67" t="s">
+        <v>78</v>
       </c>
       <c r="X3" s="13"/>
       <c r="AD3" s="13"/>
@@ -5248,53 +5242,53 @@
     </row>
     <row r="10" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="12"/>
-      <c r="G10" s="132" t="s">
+      <c r="G10" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
-      <c r="J10" s="133"/>
-      <c r="K10" s="133"/>
-      <c r="L10" s="134"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="79"/>
-      <c r="P10" s="79"/>
-      <c r="Q10" s="79"/>
-      <c r="R10" s="79"/>
-      <c r="S10" s="132" t="s">
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="T10" s="133"/>
-      <c r="U10" s="133"/>
-      <c r="V10" s="133"/>
-      <c r="W10" s="133"/>
+      <c r="T10" s="63"/>
+      <c r="U10" s="63"/>
+      <c r="V10" s="63"/>
+      <c r="W10" s="63"/>
       <c r="X10" s="11"/>
       <c r="AD10" s="13"/>
     </row>
     <row r="11" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="12"/>
-      <c r="G11" s="135" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="136"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="79"/>
-      <c r="P11" s="79"/>
-      <c r="Q11" s="79"/>
-      <c r="R11" s="79"/>
-      <c r="S11" s="135" t="s">
+      <c r="G11" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="T11" s="79"/>
-      <c r="U11" s="79"/>
-      <c r="V11" s="79"/>
-      <c r="W11" s="79"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="18"/>
       <c r="X11" s="13"/>
       <c r="AD11" s="13"/>
     </row>
@@ -5363,30 +5357,30 @@
       <c r="AD18" s="13"/>
     </row>
     <row r="19" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="132" t="s">
+      <c r="A19" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="133"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="133"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="133"/>
-      <c r="L19" s="133"/>
-      <c r="M19" s="133"/>
-      <c r="N19" s="133"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="132" t="s">
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="Q19" s="133"/>
-      <c r="R19" s="133"/>
-      <c r="S19" s="133"/>
-      <c r="T19" s="133"/>
+      <c r="Q19" s="63"/>
+      <c r="R19" s="63"/>
+      <c r="S19" s="63"/>
+      <c r="T19" s="63"/>
       <c r="U19" s="10"/>
       <c r="V19" s="10"/>
       <c r="W19" s="10"/>
@@ -5399,30 +5393,30 @@
       <c r="AD19" s="11"/>
     </row>
     <row r="20" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="135" t="s">
+      <c r="A20" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="79"/>
-      <c r="O20" s="136"/>
-      <c r="P20" s="135" t="s">
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="66"/>
+      <c r="P20" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="Q20" s="79"/>
-      <c r="R20" s="79"/>
-      <c r="S20" s="79"/>
-      <c r="T20" s="79"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="18"/>
       <c r="AD20" s="13"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.55000000000000004">
@@ -5495,88 +5489,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="132" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="133" t="s">
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="132" t="s">
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="T1" s="133"/>
-      <c r="U1" s="133"/>
-      <c r="V1" s="133"/>
-      <c r="W1" s="133"/>
-      <c r="X1" s="134"/>
-      <c r="Y1" s="133" t="s">
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="Z1" s="133"/>
-      <c r="AA1" s="133"/>
-      <c r="AB1" s="133"/>
-      <c r="AC1" s="133"/>
-      <c r="AD1" s="134"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="64"/>
     </row>
     <row r="2" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="135" t="s">
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="79" t="s">
-        <v>78</v>
-      </c>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="135" t="s">
-        <v>79</v>
-      </c>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
-      <c r="V2" s="79"/>
-      <c r="W2" s="79"/>
-      <c r="X2" s="136"/>
-      <c r="Y2" s="79" t="s">
+      <c r="T2" s="18"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="66"/>
+      <c r="Y2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="79"/>
-      <c r="AB2" s="79"/>
-      <c r="AC2" s="79"/>
-      <c r="AD2" s="136"/>
+      <c r="Z2" s="18"/>
+      <c r="AA2" s="18"/>
+      <c r="AB2" s="18"/>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="66"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="12"/>
@@ -5636,24 +5630,24 @@
     </row>
     <row r="10" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="12"/>
-      <c r="G10" s="132" t="s">
+      <c r="G10" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
-      <c r="J10" s="133"/>
-      <c r="K10" s="133"/>
-      <c r="L10" s="134"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="79"/>
-      <c r="P10" s="79"/>
-      <c r="Q10" s="79"/>
-      <c r="R10" s="79"/>
-      <c r="S10" s="132" t="s">
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="T10" s="133"/>
+      <c r="T10" s="63"/>
       <c r="U10" s="10"/>
       <c r="V10" s="10"/>
       <c r="W10" s="10"/>
@@ -5662,24 +5656,24 @@
     </row>
     <row r="11" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="12"/>
-      <c r="G11" s="135" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="136"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="79"/>
-      <c r="P11" s="79"/>
-      <c r="Q11" s="79"/>
-      <c r="R11" s="79"/>
-      <c r="S11" s="135" t="s">
+      <c r="G11" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="T11" s="79"/>
+      <c r="T11" s="18"/>
       <c r="X11" s="13"/>
       <c r="AD11" s="13"/>
     </row>
@@ -5748,28 +5742,28 @@
       <c r="AD18" s="13"/>
     </row>
     <row r="19" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="132" t="s">
+      <c r="A19" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="133"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="133"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="133"/>
-      <c r="L19" s="133"/>
-      <c r="M19" s="133"/>
-      <c r="N19" s="133"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="132" t="s">
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="Q19" s="133"/>
-      <c r="R19" s="133"/>
+      <c r="Q19" s="63"/>
+      <c r="R19" s="63"/>
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
       <c r="U19" s="10"/>
@@ -5784,28 +5778,28 @@
       <c r="AD19" s="11"/>
     </row>
     <row r="20" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="135" t="s">
+      <c r="A20" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="79"/>
-      <c r="O20" s="136"/>
-      <c r="P20" s="135" t="s">
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="66"/>
+      <c r="P20" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="Q20" s="79"/>
-      <c r="R20" s="79"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
       <c r="AD20" s="13"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.55000000000000004">
@@ -5874,494 +5868,494 @@
   <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.9140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.58203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="74" t="s">
+    <row r="1" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="78"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="78" t="s">
+      <c r="F1" s="83"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="78"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="76"/>
-    </row>
-    <row r="2" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22" t="s">
+      <c r="J1" s="83"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="81"/>
+    </row>
+    <row r="2" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="84" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="23"/>
-      <c r="G2" s="20" t="s">
+      <c r="F2" s="138"/>
+      <c r="G2" s="136" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="20"/>
-      <c r="I2" s="23" t="s">
+      <c r="H2" s="136"/>
+      <c r="I2" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="23"/>
-      <c r="K2" s="24">
+      <c r="J2" s="87"/>
+      <c r="K2" s="23">
         <v>62.3</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="21"/>
-    </row>
-    <row r="3" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="21"/>
-    </row>
-    <row r="4" spans="1:13" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="26" t="s">
+      <c r="M2" s="86"/>
+    </row>
+    <row r="3" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="84" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="86"/>
+    </row>
+    <row r="4" spans="1:13" ht="23" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="28"/>
-    </row>
-    <row r="5" spans="1:13" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="30" t="s">
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="91"/>
+    </row>
+    <row r="5" spans="1:13" ht="23" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="32" t="s">
+      <c r="I5" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="34" t="s">
+      <c r="K5" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="35"/>
-      <c r="M5" s="36"/>
-    </row>
-    <row r="6" spans="1:13" ht="20.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="37" t="s">
+      <c r="L5" s="98"/>
+      <c r="M5" s="99"/>
+    </row>
+    <row r="6" spans="1:13" ht="23" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="103">
         <v>1</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="42"/>
-    </row>
-    <row r="7" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="44"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="48"/>
-    </row>
-    <row r="8" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="50" t="s">
+      <c r="E6" s="102"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="105"/>
+    </row>
+    <row r="7" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="107"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="111"/>
+    </row>
+    <row r="8" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="116">
         <v>1</v>
       </c>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="54"/>
-    </row>
-    <row r="9" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="44"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="48"/>
-    </row>
-    <row r="10" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="57" t="s">
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="115"/>
+      <c r="J8" s="117"/>
+      <c r="K8" s="118"/>
+      <c r="L8" s="115"/>
+      <c r="M8" s="117"/>
+    </row>
+    <row r="9" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="107"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="109"/>
+      <c r="D9" s="109"/>
+      <c r="E9" s="109"/>
+      <c r="F9" s="109"/>
+      <c r="G9" s="109"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="109"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="109"/>
+      <c r="M9" s="111"/>
+    </row>
+    <row r="10" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="120" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="116">
         <v>1</v>
       </c>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="54"/>
-    </row>
-    <row r="11" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="58"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="48"/>
-    </row>
-    <row r="12" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="57" t="s">
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="117"/>
+      <c r="K10" s="118"/>
+      <c r="L10" s="115"/>
+      <c r="M10" s="117"/>
+    </row>
+    <row r="11" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="121"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="109"/>
+      <c r="D11" s="109"/>
+      <c r="E11" s="109"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="109"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="109"/>
+      <c r="M11" s="111"/>
+    </row>
+    <row r="12" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="116">
         <v>0.8</v>
       </c>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="54"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="54"/>
-    </row>
-    <row r="13" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="58"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="48"/>
-    </row>
-    <row r="14" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="57" t="s">
+      <c r="E12" s="115"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="115"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="117"/>
+      <c r="K12" s="118"/>
+      <c r="L12" s="115"/>
+      <c r="M12" s="117"/>
+    </row>
+    <row r="13" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="121"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="109"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="109"/>
+      <c r="M13" s="111"/>
+    </row>
+    <row r="14" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="116">
         <v>0.4</v>
       </c>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="54"/>
-    </row>
-    <row r="15" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="58"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="48"/>
-    </row>
-    <row r="16" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="57" t="s">
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="115"/>
+      <c r="M14" s="117"/>
+    </row>
+    <row r="15" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="121"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="109"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="109"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="109"/>
+      <c r="M15" s="111"/>
+    </row>
+    <row r="16" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="54"/>
-    </row>
-    <row r="17" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="58"/>
-      <c r="B17" s="56"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="48"/>
-    </row>
-    <row r="18" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="57" t="s">
+      <c r="B16" s="114"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="115"/>
+      <c r="M16" s="117"/>
+    </row>
+    <row r="17" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="121"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="109"/>
+      <c r="E17" s="109"/>
+      <c r="F17" s="109"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="109"/>
+      <c r="M17" s="111"/>
+    </row>
+    <row r="18" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="54"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="54"/>
-    </row>
-    <row r="19" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="58"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="48"/>
-    </row>
-    <row r="20" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="57" t="s">
+      <c r="B18" s="114"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="118"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="117"/>
+    </row>
+    <row r="19" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="121"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="109"/>
+      <c r="D19" s="109"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="109"/>
+      <c r="G19" s="109"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="109"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="109"/>
+      <c r="M19" s="111"/>
+    </row>
+    <row r="20" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="52"/>
-      <c r="M20" s="54"/>
-    </row>
-    <row r="21" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="58"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="48"/>
-    </row>
-    <row r="22" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="57" t="s">
+      <c r="B20" s="114"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="115"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="118"/>
+      <c r="L20" s="115"/>
+      <c r="M20" s="117"/>
+    </row>
+    <row r="21" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="121"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="109"/>
+      <c r="D21" s="109"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="109"/>
+      <c r="G21" s="109"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="112"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="111"/>
+    </row>
+    <row r="22" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="51"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="55"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="54"/>
-    </row>
-    <row r="23" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="37"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="41"/>
-      <c r="M23" s="59"/>
-    </row>
-    <row r="24" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="61" t="s">
+      <c r="B22" s="114"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="118"/>
+      <c r="L22" s="115"/>
+      <c r="M22" s="117"/>
+    </row>
+    <row r="23" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="100"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="122"/>
+      <c r="K23" s="123"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="122"/>
+    </row>
+    <row r="24" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="62"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="65"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="64"/>
-      <c r="M24" s="66"/>
-    </row>
-    <row r="25" spans="1:13" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="67"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="69"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="72"/>
+      <c r="B24" s="125"/>
+      <c r="C24" s="126"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="126"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="126"/>
+      <c r="H24" s="127"/>
+      <c r="I24" s="126"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="126"/>
+      <c r="L24" s="127"/>
+      <c r="M24" s="129"/>
+    </row>
+    <row r="25" spans="1:13" ht="23" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="130"/>
+      <c r="B25" s="131"/>
+      <c r="C25" s="132"/>
+      <c r="D25" s="133"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="133"/>
+      <c r="I25" s="132"/>
+      <c r="J25" s="134"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="135"/>
     </row>
     <row r="26" spans="1:13" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="73"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="73"/>
-      <c r="K26" s="73"/>
-      <c r="L26" s="73"/>
-      <c r="M26" s="73"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -6395,412 +6389,412 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="79"/>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
+      <c r="A1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
     </row>
     <row r="2" spans="1:13" ht="23" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
     </row>
     <row r="3" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82" t="s">
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="79"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="18"/>
     </row>
     <row r="4" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="79"/>
-      <c r="B4" s="84">
+      <c r="A4" s="18"/>
+      <c r="B4" s="21">
         <v>0.9</v>
       </c>
-      <c r="C4" s="85">
+      <c r="C4" s="22">
         <v>0.05</v>
       </c>
-      <c r="D4" s="86">
+      <c r="D4" s="23">
         <v>0.09</v>
       </c>
-      <c r="E4" s="87">
+      <c r="E4" s="24">
         <v>0.18</v>
       </c>
-      <c r="F4" s="87">
+      <c r="F4" s="24">
         <v>0.36</v>
       </c>
-      <c r="G4" s="87">
+      <c r="G4" s="24">
         <v>0.72</v>
       </c>
-      <c r="H4" s="87">
+      <c r="H4" s="24">
         <v>0.72</v>
       </c>
-      <c r="I4" s="87">
+      <c r="I4" s="24">
         <v>0.36</v>
       </c>
-      <c r="J4" s="87">
+      <c r="J4" s="24">
         <v>0.18</v>
       </c>
-      <c r="K4" s="86">
+      <c r="K4" s="23">
         <v>0.09</v>
       </c>
-      <c r="L4" s="88">
+      <c r="L4" s="25">
         <v>0.05</v>
       </c>
-      <c r="M4" s="79"/>
+      <c r="M4" s="18"/>
     </row>
     <row r="5" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="79"/>
-      <c r="B5" s="84">
+      <c r="A5" s="18"/>
+      <c r="B5" s="21">
         <v>0.7</v>
       </c>
-      <c r="C5" s="85">
+      <c r="C5" s="22">
         <v>0.04</v>
       </c>
-      <c r="D5" s="86">
+      <c r="D5" s="23">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E5" s="86">
+      <c r="E5" s="23">
         <v>0.14000000000000001</v>
       </c>
-      <c r="F5" s="87">
+      <c r="F5" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="G5" s="87">
+      <c r="G5" s="24">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H5" s="87">
+      <c r="H5" s="24">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I5" s="87">
+      <c r="I5" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J5" s="86">
+      <c r="J5" s="23">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K5" s="86">
+      <c r="K5" s="23">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L5" s="88">
+      <c r="L5" s="25">
         <v>0.04</v>
       </c>
-      <c r="M5" s="79"/>
+      <c r="M5" s="18"/>
     </row>
     <row r="6" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="79"/>
-      <c r="B6" s="84">
+      <c r="A6" s="18"/>
+      <c r="B6" s="21">
         <v>0.5</v>
       </c>
-      <c r="C6" s="85">
+      <c r="C6" s="22">
         <v>0.03</v>
       </c>
-      <c r="D6" s="85">
+      <c r="D6" s="22">
         <v>0.05</v>
       </c>
-      <c r="E6" s="89">
+      <c r="E6" s="26">
         <v>0.1</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="27">
         <v>0.2</v>
       </c>
-      <c r="G6" s="90">
+      <c r="G6" s="27">
         <v>0.4</v>
       </c>
-      <c r="H6" s="90">
+      <c r="H6" s="27">
         <v>0.4</v>
       </c>
-      <c r="I6" s="90">
+      <c r="I6" s="27">
         <v>0.2</v>
       </c>
-      <c r="J6" s="89">
+      <c r="J6" s="26">
         <v>0.1</v>
       </c>
-      <c r="K6" s="85">
+      <c r="K6" s="22">
         <v>0.05</v>
       </c>
-      <c r="L6" s="88">
+      <c r="L6" s="25">
         <v>0.03</v>
       </c>
-      <c r="M6" s="79"/>
+      <c r="M6" s="18"/>
     </row>
     <row r="7" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="79"/>
-      <c r="B7" s="84">
+      <c r="A7" s="18"/>
+      <c r="B7" s="21">
         <v>0.3</v>
       </c>
-      <c r="C7" s="85">
+      <c r="C7" s="22">
         <v>0.02</v>
       </c>
-      <c r="D7" s="85">
+      <c r="D7" s="22">
         <v>0.03</v>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="23">
         <v>0.06</v>
       </c>
-      <c r="F7" s="86">
+      <c r="F7" s="23">
         <v>0.12</v>
       </c>
-      <c r="G7" s="87">
+      <c r="G7" s="24">
         <v>0.24</v>
       </c>
-      <c r="H7" s="87">
+      <c r="H7" s="24">
         <v>0.24</v>
       </c>
-      <c r="I7" s="86">
+      <c r="I7" s="23">
         <v>0.12</v>
       </c>
-      <c r="J7" s="86">
+      <c r="J7" s="23">
         <v>0.06</v>
       </c>
-      <c r="K7" s="85">
+      <c r="K7" s="22">
         <v>0.03</v>
       </c>
-      <c r="L7" s="88">
+      <c r="L7" s="25">
         <v>0.02</v>
       </c>
-      <c r="M7" s="79"/>
+      <c r="M7" s="18"/>
     </row>
     <row r="8" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="79"/>
-      <c r="B8" s="84">
+      <c r="A8" s="18"/>
+      <c r="B8" s="21">
         <v>0.1</v>
       </c>
-      <c r="C8" s="85">
+      <c r="C8" s="22">
         <v>0.01</v>
       </c>
-      <c r="D8" s="85">
+      <c r="D8" s="22">
         <v>0.01</v>
       </c>
-      <c r="E8" s="85">
+      <c r="E8" s="22">
         <v>0.02</v>
       </c>
-      <c r="F8" s="85">
+      <c r="F8" s="22">
         <v>0.04</v>
       </c>
-      <c r="G8" s="86">
+      <c r="G8" s="23">
         <v>0.08</v>
       </c>
-      <c r="H8" s="86">
+      <c r="H8" s="23">
         <v>0.08</v>
       </c>
-      <c r="I8" s="85">
+      <c r="I8" s="22">
         <v>0.04</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="22">
         <v>0.02</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="22">
         <v>0.01</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="25">
         <v>0.01</v>
       </c>
-      <c r="M8" s="79"/>
+      <c r="M8" s="18"/>
     </row>
     <row r="9" spans="1:13" ht="23" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="79"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="92">
+      <c r="A9" s="18"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29">
         <v>0.05</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="30">
         <v>0.1</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="30">
         <v>0.2</v>
       </c>
-      <c r="F9" s="93">
+      <c r="F9" s="30">
         <v>0.4</v>
       </c>
-      <c r="G9" s="93">
+      <c r="G9" s="30">
         <v>0.8</v>
       </c>
-      <c r="H9" s="93">
+      <c r="H9" s="30">
         <v>0.8</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="30">
         <v>0.4</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="30">
         <v>0.2</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="30">
         <v>0.1</v>
       </c>
-      <c r="L9" s="94">
+      <c r="L9" s="31">
         <v>0.05</v>
       </c>
-      <c r="M9" s="79"/>
+      <c r="M9" s="18"/>
     </row>
     <row r="10" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="79"/>
-      <c r="B10" s="95"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
     </row>
     <row r="11" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="79"/>
-      <c r="B11" s="95"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
     </row>
     <row r="12" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="79"/>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
     </row>
     <row r="13" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="79"/>
-      <c r="B13" s="79"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="79"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
     </row>
     <row r="14" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="79"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
     </row>
     <row r="15" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="79"/>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="79"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
     </row>
     <row r="16" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="79"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
     </row>
     <row r="17" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="79"/>
-      <c r="B17" s="79"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
     </row>
     <row r="18" spans="1:13" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="79"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="79"/>
-      <c r="K18" s="79"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="79"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6838,26 +6832,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:98" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="128" t="s">
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="129">
+      <c r="F1" s="59">
         <v>46236</v>
       </c>
     </row>
     <row r="2" spans="2:98" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="130" t="s">
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="131">
+      <c r="F2" s="61">
         <v>46332</v>
       </c>
     </row>
@@ -6865,3436 +6859,3429 @@
       <c r="B3" s="7"/>
     </row>
     <row r="4" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="96" t="s">
+      <c r="C4" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="97" t="s">
+      <c r="D4" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="96" t="s">
+      <c r="E4" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="98" t="s">
+      <c r="F4" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="99">
+      <c r="G4" s="70">
         <f>G5</f>
         <v>46236</v>
       </c>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="101"/>
-      <c r="N4" s="99">
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="78"/>
+      <c r="N4" s="70">
         <f t="shared" ref="N4" si="0">N5</f>
         <v>46243</v>
       </c>
-      <c r="O4" s="100"/>
-      <c r="P4" s="100"/>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="101"/>
-      <c r="U4" s="99">
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="70">
         <f t="shared" ref="U4" si="1">U5</f>
         <v>46250</v>
       </c>
-      <c r="V4" s="100"/>
-      <c r="W4" s="100"/>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="101"/>
-      <c r="AB4" s="99">
+      <c r="V4" s="71"/>
+      <c r="W4" s="71"/>
+      <c r="X4" s="71"/>
+      <c r="Y4" s="71"/>
+      <c r="Z4" s="71"/>
+      <c r="AA4" s="78"/>
+      <c r="AB4" s="70">
         <f t="shared" ref="AB4" si="2">AB5</f>
         <v>46257</v>
       </c>
-      <c r="AC4" s="100"/>
-      <c r="AD4" s="100"/>
-      <c r="AE4" s="100"/>
-      <c r="AF4" s="100"/>
-      <c r="AG4" s="100"/>
-      <c r="AH4" s="100"/>
-      <c r="AI4" s="99">
+      <c r="AC4" s="71"/>
+      <c r="AD4" s="71"/>
+      <c r="AE4" s="71"/>
+      <c r="AF4" s="71"/>
+      <c r="AG4" s="71"/>
+      <c r="AH4" s="71"/>
+      <c r="AI4" s="70">
         <f t="shared" ref="AI4" si="3">AI5</f>
         <v>46264</v>
       </c>
-      <c r="AJ4" s="100"/>
-      <c r="AK4" s="100"/>
-      <c r="AL4" s="100"/>
-      <c r="AM4" s="100"/>
-      <c r="AN4" s="100"/>
-      <c r="AO4" s="100"/>
-      <c r="AP4" s="99">
+      <c r="AJ4" s="71"/>
+      <c r="AK4" s="71"/>
+      <c r="AL4" s="71"/>
+      <c r="AM4" s="71"/>
+      <c r="AN4" s="71"/>
+      <c r="AO4" s="71"/>
+      <c r="AP4" s="70">
         <f t="shared" ref="AP4" si="4">AP5</f>
         <v>46271</v>
       </c>
-      <c r="AQ4" s="100"/>
-      <c r="AR4" s="100"/>
-      <c r="AS4" s="100"/>
-      <c r="AT4" s="100"/>
-      <c r="AU4" s="100"/>
-      <c r="AV4" s="100"/>
-      <c r="AW4" s="99">
+      <c r="AQ4" s="71"/>
+      <c r="AR4" s="71"/>
+      <c r="AS4" s="71"/>
+      <c r="AT4" s="71"/>
+      <c r="AU4" s="71"/>
+      <c r="AV4" s="71"/>
+      <c r="AW4" s="70">
         <f t="shared" ref="AW4" si="5">AW5</f>
         <v>46278</v>
       </c>
-      <c r="AX4" s="100"/>
-      <c r="AY4" s="100"/>
-      <c r="AZ4" s="100"/>
-      <c r="BA4" s="100"/>
-      <c r="BB4" s="100"/>
-      <c r="BC4" s="100"/>
-      <c r="BD4" s="99">
+      <c r="AX4" s="71"/>
+      <c r="AY4" s="71"/>
+      <c r="AZ4" s="71"/>
+      <c r="BA4" s="71"/>
+      <c r="BB4" s="71"/>
+      <c r="BC4" s="71"/>
+      <c r="BD4" s="70">
         <f t="shared" ref="BD4" si="6">BD5</f>
         <v>46285</v>
       </c>
-      <c r="BE4" s="100"/>
-      <c r="BF4" s="100"/>
-      <c r="BG4" s="100"/>
-      <c r="BH4" s="100"/>
-      <c r="BI4" s="100"/>
-      <c r="BJ4" s="100"/>
-      <c r="BK4" s="99">
+      <c r="BE4" s="71"/>
+      <c r="BF4" s="71"/>
+      <c r="BG4" s="71"/>
+      <c r="BH4" s="71"/>
+      <c r="BI4" s="71"/>
+      <c r="BJ4" s="71"/>
+      <c r="BK4" s="70">
         <f t="shared" ref="BK4" si="7">BK5</f>
         <v>46292</v>
       </c>
-      <c r="BL4" s="100"/>
-      <c r="BM4" s="100"/>
-      <c r="BN4" s="100"/>
-      <c r="BO4" s="100"/>
-      <c r="BP4" s="100"/>
-      <c r="BQ4" s="100"/>
-      <c r="BR4" s="99">
+      <c r="BL4" s="71"/>
+      <c r="BM4" s="71"/>
+      <c r="BN4" s="71"/>
+      <c r="BO4" s="71"/>
+      <c r="BP4" s="71"/>
+      <c r="BQ4" s="71"/>
+      <c r="BR4" s="70">
         <f t="shared" ref="BR4" si="8">BR5</f>
         <v>46299</v>
       </c>
-      <c r="BS4" s="100"/>
-      <c r="BT4" s="100"/>
-      <c r="BU4" s="100"/>
-      <c r="BV4" s="100"/>
-      <c r="BW4" s="100"/>
-      <c r="BX4" s="100"/>
-      <c r="BY4" s="99">
+      <c r="BS4" s="71"/>
+      <c r="BT4" s="71"/>
+      <c r="BU4" s="71"/>
+      <c r="BV4" s="71"/>
+      <c r="BW4" s="71"/>
+      <c r="BX4" s="71"/>
+      <c r="BY4" s="70">
         <f t="shared" ref="BY4" si="9">BY5</f>
         <v>46306</v>
       </c>
-      <c r="BZ4" s="100"/>
-      <c r="CA4" s="100"/>
-      <c r="CB4" s="100"/>
-      <c r="CC4" s="100"/>
-      <c r="CD4" s="100"/>
-      <c r="CE4" s="100"/>
-      <c r="CF4" s="99">
+      <c r="BZ4" s="71"/>
+      <c r="CA4" s="71"/>
+      <c r="CB4" s="71"/>
+      <c r="CC4" s="71"/>
+      <c r="CD4" s="71"/>
+      <c r="CE4" s="71"/>
+      <c r="CF4" s="70">
         <f t="shared" ref="CF4" si="10">CF5</f>
         <v>46313</v>
       </c>
-      <c r="CG4" s="100"/>
-      <c r="CH4" s="100"/>
-      <c r="CI4" s="100"/>
-      <c r="CJ4" s="100"/>
-      <c r="CK4" s="100"/>
-      <c r="CL4" s="100"/>
-      <c r="CM4" s="99">
+      <c r="CG4" s="71"/>
+      <c r="CH4" s="71"/>
+      <c r="CI4" s="71"/>
+      <c r="CJ4" s="71"/>
+      <c r="CK4" s="71"/>
+      <c r="CL4" s="71"/>
+      <c r="CM4" s="70">
         <f t="shared" ref="CM4" si="11">CM5</f>
         <v>46320</v>
       </c>
-      <c r="CN4" s="100"/>
-      <c r="CO4" s="100"/>
-      <c r="CP4" s="100"/>
-      <c r="CQ4" s="100"/>
-      <c r="CR4" s="100"/>
-      <c r="CS4" s="100"/>
-      <c r="CT4" s="102"/>
+      <c r="CN4" s="71"/>
+      <c r="CO4" s="71"/>
+      <c r="CP4" s="71"/>
+      <c r="CQ4" s="71"/>
+      <c r="CR4" s="71"/>
+      <c r="CS4" s="71"/>
+      <c r="CT4" s="33"/>
     </row>
     <row r="5" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="104">
+      <c r="B5" s="74"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="34">
         <f>F1</f>
         <v>46236</v>
       </c>
-      <c r="H5" s="104">
+      <c r="H5" s="34">
         <f>G5+1</f>
         <v>46237</v>
       </c>
-      <c r="I5" s="104">
+      <c r="I5" s="34">
         <f t="shared" ref="I5:BT5" si="12">H5+1</f>
         <v>46238</v>
       </c>
-      <c r="J5" s="104">
+      <c r="J5" s="34">
         <f t="shared" si="12"/>
         <v>46239</v>
       </c>
-      <c r="K5" s="104">
+      <c r="K5" s="34">
         <f t="shared" si="12"/>
         <v>46240</v>
       </c>
-      <c r="L5" s="104">
+      <c r="L5" s="34">
         <f t="shared" si="12"/>
         <v>46241</v>
       </c>
-      <c r="M5" s="104">
+      <c r="M5" s="34">
         <f t="shared" si="12"/>
         <v>46242</v>
       </c>
-      <c r="N5" s="104">
+      <c r="N5" s="34">
         <f t="shared" si="12"/>
         <v>46243</v>
       </c>
-      <c r="O5" s="104">
+      <c r="O5" s="34">
         <f t="shared" si="12"/>
         <v>46244</v>
       </c>
-      <c r="P5" s="104">
+      <c r="P5" s="34">
         <f t="shared" si="12"/>
         <v>46245</v>
       </c>
-      <c r="Q5" s="104">
+      <c r="Q5" s="34">
         <f t="shared" si="12"/>
         <v>46246</v>
       </c>
-      <c r="R5" s="104">
+      <c r="R5" s="34">
         <f t="shared" si="12"/>
         <v>46247</v>
       </c>
-      <c r="S5" s="104">
+      <c r="S5" s="34">
         <f t="shared" si="12"/>
         <v>46248</v>
       </c>
-      <c r="T5" s="104">
+      <c r="T5" s="34">
         <f t="shared" si="12"/>
         <v>46249</v>
       </c>
-      <c r="U5" s="104">
+      <c r="U5" s="34">
         <f t="shared" si="12"/>
         <v>46250</v>
       </c>
-      <c r="V5" s="104">
+      <c r="V5" s="34">
         <f t="shared" si="12"/>
         <v>46251</v>
       </c>
-      <c r="W5" s="104">
+      <c r="W5" s="34">
         <f t="shared" si="12"/>
         <v>46252</v>
       </c>
-      <c r="X5" s="104">
+      <c r="X5" s="34">
         <f t="shared" si="12"/>
         <v>46253</v>
       </c>
-      <c r="Y5" s="104">
+      <c r="Y5" s="34">
         <f t="shared" si="12"/>
         <v>46254</v>
       </c>
-      <c r="Z5" s="104">
+      <c r="Z5" s="34">
         <f t="shared" si="12"/>
         <v>46255</v>
       </c>
-      <c r="AA5" s="104">
+      <c r="AA5" s="34">
         <f t="shared" si="12"/>
         <v>46256</v>
       </c>
-      <c r="AB5" s="104">
+      <c r="AB5" s="34">
         <f t="shared" si="12"/>
         <v>46257</v>
       </c>
-      <c r="AC5" s="104">
+      <c r="AC5" s="34">
         <f t="shared" si="12"/>
         <v>46258</v>
       </c>
-      <c r="AD5" s="104">
+      <c r="AD5" s="34">
         <f t="shared" si="12"/>
         <v>46259</v>
       </c>
-      <c r="AE5" s="104">
+      <c r="AE5" s="34">
         <f t="shared" si="12"/>
         <v>46260</v>
       </c>
-      <c r="AF5" s="104">
+      <c r="AF5" s="34">
         <f t="shared" si="12"/>
         <v>46261</v>
       </c>
-      <c r="AG5" s="104">
+      <c r="AG5" s="34">
         <f t="shared" si="12"/>
         <v>46262</v>
       </c>
-      <c r="AH5" s="104">
+      <c r="AH5" s="34">
         <f t="shared" si="12"/>
         <v>46263</v>
       </c>
-      <c r="AI5" s="104">
+      <c r="AI5" s="34">
         <f t="shared" si="12"/>
         <v>46264</v>
       </c>
-      <c r="AJ5" s="104">
+      <c r="AJ5" s="34">
         <f t="shared" si="12"/>
         <v>46265</v>
       </c>
-      <c r="AK5" s="104">
+      <c r="AK5" s="34">
         <f t="shared" si="12"/>
         <v>46266</v>
       </c>
-      <c r="AL5" s="104">
+      <c r="AL5" s="34">
         <f t="shared" si="12"/>
         <v>46267</v>
       </c>
-      <c r="AM5" s="104">
+      <c r="AM5" s="34">
         <f t="shared" si="12"/>
         <v>46268</v>
       </c>
-      <c r="AN5" s="104">
+      <c r="AN5" s="34">
         <f t="shared" si="12"/>
         <v>46269</v>
       </c>
-      <c r="AO5" s="104">
+      <c r="AO5" s="34">
         <f t="shared" si="12"/>
         <v>46270</v>
       </c>
-      <c r="AP5" s="104">
+      <c r="AP5" s="34">
         <f t="shared" si="12"/>
         <v>46271</v>
       </c>
-      <c r="AQ5" s="104">
+      <c r="AQ5" s="34">
         <f t="shared" si="12"/>
         <v>46272</v>
       </c>
-      <c r="AR5" s="104">
+      <c r="AR5" s="34">
         <f t="shared" si="12"/>
         <v>46273</v>
       </c>
-      <c r="AS5" s="104">
+      <c r="AS5" s="34">
         <f t="shared" si="12"/>
         <v>46274</v>
       </c>
-      <c r="AT5" s="104">
+      <c r="AT5" s="34">
         <f t="shared" si="12"/>
         <v>46275</v>
       </c>
-      <c r="AU5" s="104">
+      <c r="AU5" s="34">
         <f t="shared" si="12"/>
         <v>46276</v>
       </c>
-      <c r="AV5" s="104">
+      <c r="AV5" s="34">
         <f t="shared" si="12"/>
         <v>46277</v>
       </c>
-      <c r="AW5" s="104">
+      <c r="AW5" s="34">
         <f t="shared" si="12"/>
         <v>46278</v>
       </c>
-      <c r="AX5" s="104">
+      <c r="AX5" s="34">
         <f t="shared" si="12"/>
         <v>46279</v>
       </c>
-      <c r="AY5" s="104">
+      <c r="AY5" s="34">
         <f t="shared" si="12"/>
         <v>46280</v>
       </c>
-      <c r="AZ5" s="104">
+      <c r="AZ5" s="34">
         <f t="shared" si="12"/>
         <v>46281</v>
       </c>
-      <c r="BA5" s="104">
+      <c r="BA5" s="34">
         <f t="shared" si="12"/>
         <v>46282</v>
       </c>
-      <c r="BB5" s="104">
+      <c r="BB5" s="34">
         <f t="shared" si="12"/>
         <v>46283</v>
       </c>
-      <c r="BC5" s="104">
+      <c r="BC5" s="34">
         <f t="shared" si="12"/>
         <v>46284</v>
       </c>
-      <c r="BD5" s="104">
+      <c r="BD5" s="34">
         <f t="shared" si="12"/>
         <v>46285</v>
       </c>
-      <c r="BE5" s="104">
+      <c r="BE5" s="34">
         <f t="shared" si="12"/>
         <v>46286</v>
       </c>
-      <c r="BF5" s="104">
+      <c r="BF5" s="34">
         <f t="shared" si="12"/>
         <v>46287</v>
       </c>
-      <c r="BG5" s="104">
+      <c r="BG5" s="34">
         <f t="shared" si="12"/>
         <v>46288</v>
       </c>
-      <c r="BH5" s="104">
+      <c r="BH5" s="34">
         <f t="shared" si="12"/>
         <v>46289</v>
       </c>
-      <c r="BI5" s="104">
+      <c r="BI5" s="34">
         <f t="shared" si="12"/>
         <v>46290</v>
       </c>
-      <c r="BJ5" s="104">
+      <c r="BJ5" s="34">
         <f t="shared" si="12"/>
         <v>46291</v>
       </c>
-      <c r="BK5" s="104">
+      <c r="BK5" s="34">
         <f t="shared" si="12"/>
         <v>46292</v>
       </c>
-      <c r="BL5" s="104">
+      <c r="BL5" s="34">
         <f t="shared" si="12"/>
         <v>46293</v>
       </c>
-      <c r="BM5" s="104">
+      <c r="BM5" s="34">
         <f t="shared" si="12"/>
         <v>46294</v>
       </c>
-      <c r="BN5" s="104">
+      <c r="BN5" s="34">
         <f t="shared" si="12"/>
         <v>46295</v>
       </c>
-      <c r="BO5" s="104">
+      <c r="BO5" s="34">
         <f t="shared" si="12"/>
         <v>46296</v>
       </c>
-      <c r="BP5" s="104">
+      <c r="BP5" s="34">
         <f t="shared" si="12"/>
         <v>46297</v>
       </c>
-      <c r="BQ5" s="104">
+      <c r="BQ5" s="34">
         <f t="shared" si="12"/>
         <v>46298</v>
       </c>
-      <c r="BR5" s="104">
+      <c r="BR5" s="34">
         <f t="shared" si="12"/>
         <v>46299</v>
       </c>
-      <c r="BS5" s="104">
+      <c r="BS5" s="34">
         <f t="shared" si="12"/>
         <v>46300</v>
       </c>
-      <c r="BT5" s="104">
+      <c r="BT5" s="34">
         <f t="shared" si="12"/>
         <v>46301</v>
       </c>
-      <c r="BU5" s="104">
+      <c r="BU5" s="34">
         <f t="shared" ref="BU5:CS5" si="13">BT5+1</f>
         <v>46302</v>
       </c>
-      <c r="BV5" s="104">
+      <c r="BV5" s="34">
         <f t="shared" si="13"/>
         <v>46303</v>
       </c>
-      <c r="BW5" s="104">
+      <c r="BW5" s="34">
         <f t="shared" si="13"/>
         <v>46304</v>
       </c>
-      <c r="BX5" s="104">
+      <c r="BX5" s="34">
         <f t="shared" si="13"/>
         <v>46305</v>
       </c>
-      <c r="BY5" s="104">
+      <c r="BY5" s="34">
         <f t="shared" si="13"/>
         <v>46306</v>
       </c>
-      <c r="BZ5" s="104">
+      <c r="BZ5" s="34">
         <f t="shared" si="13"/>
         <v>46307</v>
       </c>
-      <c r="CA5" s="104">
+      <c r="CA5" s="34">
         <f t="shared" si="13"/>
         <v>46308</v>
       </c>
-      <c r="CB5" s="104">
+      <c r="CB5" s="34">
         <f t="shared" si="13"/>
         <v>46309</v>
       </c>
-      <c r="CC5" s="104">
+      <c r="CC5" s="34">
         <f t="shared" si="13"/>
         <v>46310</v>
       </c>
-      <c r="CD5" s="104">
+      <c r="CD5" s="34">
         <f t="shared" si="13"/>
         <v>46311</v>
       </c>
-      <c r="CE5" s="104">
+      <c r="CE5" s="34">
         <f t="shared" si="13"/>
         <v>46312</v>
       </c>
-      <c r="CF5" s="104">
+      <c r="CF5" s="34">
         <f t="shared" si="13"/>
         <v>46313</v>
       </c>
-      <c r="CG5" s="104">
+      <c r="CG5" s="34">
         <f t="shared" si="13"/>
         <v>46314</v>
       </c>
-      <c r="CH5" s="104">
+      <c r="CH5" s="34">
         <f t="shared" si="13"/>
         <v>46315</v>
       </c>
-      <c r="CI5" s="104">
+      <c r="CI5" s="34">
         <f t="shared" si="13"/>
         <v>46316</v>
       </c>
-      <c r="CJ5" s="104">
+      <c r="CJ5" s="34">
         <f t="shared" si="13"/>
         <v>46317</v>
       </c>
-      <c r="CK5" s="104">
+      <c r="CK5" s="34">
         <f t="shared" si="13"/>
         <v>46318</v>
       </c>
-      <c r="CL5" s="104">
+      <c r="CL5" s="34">
         <f t="shared" si="13"/>
         <v>46319</v>
       </c>
-      <c r="CM5" s="104">
+      <c r="CM5" s="34">
         <f t="shared" si="13"/>
         <v>46320</v>
       </c>
-      <c r="CN5" s="104">
+      <c r="CN5" s="34">
         <f t="shared" si="13"/>
         <v>46321</v>
       </c>
-      <c r="CO5" s="104">
+      <c r="CO5" s="34">
         <f t="shared" si="13"/>
         <v>46322</v>
       </c>
-      <c r="CP5" s="104">
+      <c r="CP5" s="34">
         <f t="shared" si="13"/>
         <v>46323</v>
       </c>
-      <c r="CQ5" s="104">
+      <c r="CQ5" s="34">
         <f t="shared" si="13"/>
         <v>46324</v>
       </c>
-      <c r="CR5" s="104">
+      <c r="CR5" s="34">
         <f t="shared" si="13"/>
         <v>46325</v>
       </c>
-      <c r="CS5" s="104">
+      <c r="CS5" s="34">
         <f t="shared" si="13"/>
         <v>46326</v>
       </c>
-      <c r="CT5" s="102"/>
+      <c r="CT5" s="33"/>
     </row>
     <row r="6" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="105" t="s">
+      <c r="B6" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="106"/>
-      <c r="D6" s="107">
+      <c r="C6" s="36"/>
+      <c r="D6" s="37">
         <f>SUM(D7:D12)</f>
         <v>3.5</v>
       </c>
-      <c r="E6" s="108">
+      <c r="E6" s="38">
         <v>46236</v>
       </c>
-      <c r="F6" s="108">
+      <c r="F6" s="38">
         <v>46240</v>
       </c>
-      <c r="G6" s="109"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="110"/>
-      <c r="M6" s="110"/>
-      <c r="N6" s="110"/>
-      <c r="O6" s="110"/>
-      <c r="P6" s="110"/>
-      <c r="Q6" s="110"/>
-      <c r="R6" s="110"/>
-      <c r="S6" s="110"/>
-      <c r="T6" s="110"/>
-      <c r="U6" s="110"/>
-      <c r="V6" s="110"/>
-      <c r="W6" s="110"/>
-      <c r="X6" s="110"/>
-      <c r="Y6" s="110"/>
-      <c r="Z6" s="110"/>
-      <c r="AA6" s="110"/>
-      <c r="AB6" s="110"/>
-      <c r="AC6" s="110"/>
-      <c r="AD6" s="110"/>
-      <c r="AE6" s="110"/>
-      <c r="AF6" s="110"/>
-      <c r="AG6" s="110"/>
-      <c r="AH6" s="110"/>
-      <c r="AI6" s="110"/>
-      <c r="AJ6" s="110"/>
-      <c r="AK6" s="110"/>
-      <c r="AL6" s="110"/>
-      <c r="AM6" s="110"/>
-      <c r="AN6" s="110"/>
-      <c r="AO6" s="110"/>
-      <c r="AP6" s="110"/>
-      <c r="AQ6" s="110"/>
-      <c r="AR6" s="110"/>
-      <c r="AS6" s="110"/>
-      <c r="AT6" s="110"/>
-      <c r="AU6" s="110"/>
-      <c r="AV6" s="110"/>
-      <c r="AW6" s="110"/>
-      <c r="AX6" s="110"/>
-      <c r="AY6" s="110"/>
-      <c r="AZ6" s="110"/>
-      <c r="BA6" s="110"/>
-      <c r="BB6" s="110"/>
-      <c r="BC6" s="110"/>
-      <c r="BD6" s="110"/>
-      <c r="BE6" s="110"/>
-      <c r="BF6" s="110"/>
-      <c r="BG6" s="110"/>
-      <c r="BH6" s="110"/>
-      <c r="BI6" s="110"/>
-      <c r="BJ6" s="110"/>
-      <c r="BK6" s="110"/>
-      <c r="BL6" s="110"/>
-      <c r="BM6" s="110"/>
-      <c r="BN6" s="110"/>
-      <c r="BO6" s="110"/>
-      <c r="BP6" s="110"/>
-      <c r="BQ6" s="110"/>
-      <c r="BR6" s="110"/>
-      <c r="BS6" s="110"/>
-      <c r="BT6" s="110"/>
-      <c r="BU6" s="110"/>
-      <c r="BV6" s="110"/>
-      <c r="BW6" s="110"/>
-      <c r="BX6" s="110"/>
-      <c r="BY6" s="110"/>
-      <c r="BZ6" s="110"/>
-      <c r="CA6" s="110"/>
-      <c r="CB6" s="110"/>
-      <c r="CC6" s="110"/>
-      <c r="CD6" s="110"/>
-      <c r="CE6" s="110"/>
-      <c r="CF6" s="110"/>
-      <c r="CG6" s="110"/>
-      <c r="CH6" s="110"/>
-      <c r="CI6" s="110"/>
-      <c r="CJ6" s="110"/>
-      <c r="CK6" s="110"/>
-      <c r="CL6" s="110"/>
-      <c r="CM6" s="110"/>
-      <c r="CN6" s="110"/>
-      <c r="CO6" s="110"/>
-      <c r="CP6" s="110"/>
-      <c r="CQ6" s="110"/>
-      <c r="CR6" s="110"/>
-      <c r="CS6" s="110"/>
-      <c r="CT6" s="102"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="40"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="40"/>
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="40"/>
+      <c r="AA6" s="40"/>
+      <c r="AB6" s="40"/>
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="40"/>
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="40"/>
+      <c r="AG6" s="40"/>
+      <c r="AH6" s="40"/>
+      <c r="AI6" s="40"/>
+      <c r="AJ6" s="40"/>
+      <c r="AK6" s="40"/>
+      <c r="AL6" s="40"/>
+      <c r="AM6" s="40"/>
+      <c r="AN6" s="40"/>
+      <c r="AO6" s="40"/>
+      <c r="AP6" s="40"/>
+      <c r="AQ6" s="40"/>
+      <c r="AR6" s="40"/>
+      <c r="AS6" s="40"/>
+      <c r="AT6" s="40"/>
+      <c r="AU6" s="40"/>
+      <c r="AV6" s="40"/>
+      <c r="AW6" s="40"/>
+      <c r="AX6" s="40"/>
+      <c r="AY6" s="40"/>
+      <c r="AZ6" s="40"/>
+      <c r="BA6" s="40"/>
+      <c r="BB6" s="40"/>
+      <c r="BC6" s="40"/>
+      <c r="BD6" s="40"/>
+      <c r="BE6" s="40"/>
+      <c r="BF6" s="40"/>
+      <c r="BG6" s="40"/>
+      <c r="BH6" s="40"/>
+      <c r="BI6" s="40"/>
+      <c r="BJ6" s="40"/>
+      <c r="BK6" s="40"/>
+      <c r="BL6" s="40"/>
+      <c r="BM6" s="40"/>
+      <c r="BN6" s="40"/>
+      <c r="BO6" s="40"/>
+      <c r="BP6" s="40"/>
+      <c r="BQ6" s="40"/>
+      <c r="BR6" s="40"/>
+      <c r="BS6" s="40"/>
+      <c r="BT6" s="40"/>
+      <c r="BU6" s="40"/>
+      <c r="BV6" s="40"/>
+      <c r="BW6" s="40"/>
+      <c r="BX6" s="40"/>
+      <c r="BY6" s="40"/>
+      <c r="BZ6" s="40"/>
+      <c r="CA6" s="40"/>
+      <c r="CB6" s="40"/>
+      <c r="CC6" s="40"/>
+      <c r="CD6" s="40"/>
+      <c r="CE6" s="40"/>
+      <c r="CF6" s="40"/>
+      <c r="CG6" s="40"/>
+      <c r="CH6" s="40"/>
+      <c r="CI6" s="40"/>
+      <c r="CJ6" s="40"/>
+      <c r="CK6" s="40"/>
+      <c r="CL6" s="40"/>
+      <c r="CM6" s="40"/>
+      <c r="CN6" s="40"/>
+      <c r="CO6" s="40"/>
+      <c r="CP6" s="40"/>
+      <c r="CQ6" s="40"/>
+      <c r="CR6" s="40"/>
+      <c r="CS6" s="40"/>
+      <c r="CT6" s="33"/>
     </row>
     <row r="7" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="111" t="s">
+      <c r="B7" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="112"/>
-      <c r="D7" s="113">
+      <c r="C7" s="42"/>
+      <c r="D7" s="43">
         <v>0.5</v>
       </c>
-      <c r="E7" s="114">
+      <c r="E7" s="44">
         <v>46236</v>
       </c>
-      <c r="F7" s="114">
+      <c r="F7" s="44">
         <v>46236</v>
       </c>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110"/>
-      <c r="M7" s="110"/>
-      <c r="N7" s="110"/>
-      <c r="O7" s="110"/>
-      <c r="P7" s="110"/>
-      <c r="Q7" s="110"/>
-      <c r="R7" s="110"/>
-      <c r="S7" s="110"/>
-      <c r="T7" s="110"/>
-      <c r="U7" s="110"/>
-      <c r="V7" s="110"/>
-      <c r="W7" s="110"/>
-      <c r="X7" s="110"/>
-      <c r="Y7" s="110"/>
-      <c r="Z7" s="110"/>
-      <c r="AA7" s="110"/>
-      <c r="AB7" s="110"/>
-      <c r="AC7" s="110"/>
-      <c r="AD7" s="110"/>
-      <c r="AE7" s="110"/>
-      <c r="AF7" s="110"/>
-      <c r="AG7" s="110"/>
-      <c r="AH7" s="110"/>
-      <c r="AI7" s="110"/>
-      <c r="AJ7" s="110"/>
-      <c r="AK7" s="110"/>
-      <c r="AL7" s="110"/>
-      <c r="AM7" s="110"/>
-      <c r="AN7" s="110"/>
-      <c r="AO7" s="110"/>
-      <c r="AP7" s="110"/>
-      <c r="AQ7" s="110"/>
-      <c r="AR7" s="110"/>
-      <c r="AS7" s="110"/>
-      <c r="AT7" s="110"/>
-      <c r="AU7" s="110"/>
-      <c r="AV7" s="110"/>
-      <c r="AW7" s="110"/>
-      <c r="AX7" s="110"/>
-      <c r="AY7" s="110"/>
-      <c r="AZ7" s="110"/>
-      <c r="BA7" s="110"/>
-      <c r="BB7" s="110"/>
-      <c r="BC7" s="110"/>
-      <c r="BD7" s="110"/>
-      <c r="BE7" s="110"/>
-      <c r="BF7" s="110"/>
-      <c r="BG7" s="110"/>
-      <c r="BH7" s="110"/>
-      <c r="BI7" s="110"/>
-      <c r="BJ7" s="110"/>
-      <c r="BK7" s="110"/>
-      <c r="BL7" s="110"/>
-      <c r="BM7" s="110"/>
-      <c r="BN7" s="110"/>
-      <c r="BO7" s="110"/>
-      <c r="BP7" s="110"/>
-      <c r="BQ7" s="110"/>
-      <c r="BR7" s="110"/>
-      <c r="BS7" s="110"/>
-      <c r="BT7" s="110"/>
-      <c r="BU7" s="110"/>
-      <c r="BV7" s="110"/>
-      <c r="BW7" s="110"/>
-      <c r="BX7" s="110"/>
-      <c r="BY7" s="110"/>
-      <c r="BZ7" s="110"/>
-      <c r="CA7" s="110"/>
-      <c r="CB7" s="110"/>
-      <c r="CC7" s="110"/>
-      <c r="CD7" s="110"/>
-      <c r="CE7" s="110"/>
-      <c r="CF7" s="110"/>
-      <c r="CG7" s="110"/>
-      <c r="CH7" s="110"/>
-      <c r="CI7" s="110"/>
-      <c r="CJ7" s="110"/>
-      <c r="CK7" s="110"/>
-      <c r="CL7" s="110"/>
-      <c r="CM7" s="110"/>
-      <c r="CN7" s="110"/>
-      <c r="CO7" s="110"/>
-      <c r="CP7" s="110"/>
-      <c r="CQ7" s="110"/>
-      <c r="CR7" s="110"/>
-      <c r="CS7" s="110"/>
-      <c r="CT7" s="102"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="40"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="40"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="40"/>
+      <c r="AA7" s="40"/>
+      <c r="AB7" s="40"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="40"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="40"/>
+      <c r="AG7" s="40"/>
+      <c r="AH7" s="40"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="AL7" s="40"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="40"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="40"/>
+      <c r="AR7" s="40"/>
+      <c r="AS7" s="40"/>
+      <c r="AT7" s="40"/>
+      <c r="AU7" s="40"/>
+      <c r="AV7" s="40"/>
+      <c r="AW7" s="40"/>
+      <c r="AX7" s="40"/>
+      <c r="AY7" s="40"/>
+      <c r="AZ7" s="40"/>
+      <c r="BA7" s="40"/>
+      <c r="BB7" s="40"/>
+      <c r="BC7" s="40"/>
+      <c r="BD7" s="40"/>
+      <c r="BE7" s="40"/>
+      <c r="BF7" s="40"/>
+      <c r="BG7" s="40"/>
+      <c r="BH7" s="40"/>
+      <c r="BI7" s="40"/>
+      <c r="BJ7" s="40"/>
+      <c r="BK7" s="40"/>
+      <c r="BL7" s="40"/>
+      <c r="BM7" s="40"/>
+      <c r="BN7" s="40"/>
+      <c r="BO7" s="40"/>
+      <c r="BP7" s="40"/>
+      <c r="BQ7" s="40"/>
+      <c r="BR7" s="40"/>
+      <c r="BS7" s="40"/>
+      <c r="BT7" s="40"/>
+      <c r="BU7" s="40"/>
+      <c r="BV7" s="40"/>
+      <c r="BW7" s="40"/>
+      <c r="BX7" s="40"/>
+      <c r="BY7" s="40"/>
+      <c r="BZ7" s="40"/>
+      <c r="CA7" s="40"/>
+      <c r="CB7" s="40"/>
+      <c r="CC7" s="40"/>
+      <c r="CD7" s="40"/>
+      <c r="CE7" s="40"/>
+      <c r="CF7" s="40"/>
+      <c r="CG7" s="40"/>
+      <c r="CH7" s="40"/>
+      <c r="CI7" s="40"/>
+      <c r="CJ7" s="40"/>
+      <c r="CK7" s="40"/>
+      <c r="CL7" s="40"/>
+      <c r="CM7" s="40"/>
+      <c r="CN7" s="40"/>
+      <c r="CO7" s="40"/>
+      <c r="CP7" s="40"/>
+      <c r="CQ7" s="40"/>
+      <c r="CR7" s="40"/>
+      <c r="CS7" s="40"/>
+      <c r="CT7" s="33"/>
     </row>
     <row r="8" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="111" t="s">
+      <c r="B8" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="115"/>
-      <c r="D8" s="116">
+      <c r="C8" s="45"/>
+      <c r="D8" s="46">
         <v>1</v>
       </c>
-      <c r="E8" s="117">
+      <c r="E8" s="47">
         <v>46237</v>
       </c>
-      <c r="F8" s="117">
+      <c r="F8" s="47">
         <v>46237</v>
       </c>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110"/>
-      <c r="L8" s="110"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="110"/>
-      <c r="O8" s="110"/>
-      <c r="P8" s="110"/>
-      <c r="Q8" s="110"/>
-      <c r="R8" s="110"/>
-      <c r="S8" s="110"/>
-      <c r="T8" s="110"/>
-      <c r="U8" s="110"/>
-      <c r="V8" s="110"/>
-      <c r="W8" s="110"/>
-      <c r="X8" s="110"/>
-      <c r="Y8" s="110"/>
-      <c r="Z8" s="110"/>
-      <c r="AA8" s="110"/>
-      <c r="AB8" s="110"/>
-      <c r="AC8" s="110"/>
-      <c r="AD8" s="110"/>
-      <c r="AE8" s="110"/>
-      <c r="AF8" s="110"/>
-      <c r="AG8" s="110"/>
-      <c r="AH8" s="110"/>
-      <c r="AI8" s="110"/>
-      <c r="AJ8" s="110"/>
-      <c r="AK8" s="110"/>
-      <c r="AL8" s="110"/>
-      <c r="AM8" s="110"/>
-      <c r="AN8" s="110"/>
-      <c r="AO8" s="110"/>
-      <c r="AP8" s="110"/>
-      <c r="AQ8" s="110"/>
-      <c r="AR8" s="110"/>
-      <c r="AS8" s="110"/>
-      <c r="AT8" s="110"/>
-      <c r="AU8" s="110"/>
-      <c r="AV8" s="110"/>
-      <c r="AW8" s="110"/>
-      <c r="AX8" s="110"/>
-      <c r="AY8" s="110"/>
-      <c r="AZ8" s="110"/>
-      <c r="BA8" s="110"/>
-      <c r="BB8" s="110"/>
-      <c r="BC8" s="110"/>
-      <c r="BD8" s="110"/>
-      <c r="BE8" s="110"/>
-      <c r="BF8" s="110"/>
-      <c r="BG8" s="110"/>
-      <c r="BH8" s="110"/>
-      <c r="BI8" s="110"/>
-      <c r="BJ8" s="110"/>
-      <c r="BK8" s="110"/>
-      <c r="BL8" s="110"/>
-      <c r="BM8" s="110"/>
-      <c r="BN8" s="110"/>
-      <c r="BO8" s="110"/>
-      <c r="BP8" s="110"/>
-      <c r="BQ8" s="110"/>
-      <c r="BR8" s="110"/>
-      <c r="BS8" s="110"/>
-      <c r="BT8" s="110"/>
-      <c r="BU8" s="110"/>
-      <c r="BV8" s="110"/>
-      <c r="BW8" s="110"/>
-      <c r="BX8" s="110"/>
-      <c r="BY8" s="110"/>
-      <c r="BZ8" s="110"/>
-      <c r="CA8" s="110"/>
-      <c r="CB8" s="110"/>
-      <c r="CC8" s="110"/>
-      <c r="CD8" s="110"/>
-      <c r="CE8" s="110"/>
-      <c r="CF8" s="110"/>
-      <c r="CG8" s="110"/>
-      <c r="CH8" s="110"/>
-      <c r="CI8" s="110"/>
-      <c r="CJ8" s="110"/>
-      <c r="CK8" s="110"/>
-      <c r="CL8" s="110"/>
-      <c r="CM8" s="110"/>
-      <c r="CN8" s="110"/>
-      <c r="CO8" s="110"/>
-      <c r="CP8" s="110"/>
-      <c r="CQ8" s="110"/>
-      <c r="CR8" s="110"/>
-      <c r="CS8" s="110"/>
-      <c r="CT8" s="102"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="40"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="40"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="40"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="40"/>
+      <c r="AA8" s="40"/>
+      <c r="AB8" s="40"/>
+      <c r="AC8" s="40"/>
+      <c r="AD8" s="40"/>
+      <c r="AE8" s="40"/>
+      <c r="AF8" s="40"/>
+      <c r="AG8" s="40"/>
+      <c r="AH8" s="40"/>
+      <c r="AI8" s="40"/>
+      <c r="AJ8" s="40"/>
+      <c r="AK8" s="40"/>
+      <c r="AL8" s="40"/>
+      <c r="AM8" s="40"/>
+      <c r="AN8" s="40"/>
+      <c r="AO8" s="40"/>
+      <c r="AP8" s="40"/>
+      <c r="AQ8" s="40"/>
+      <c r="AR8" s="40"/>
+      <c r="AS8" s="40"/>
+      <c r="AT8" s="40"/>
+      <c r="AU8" s="40"/>
+      <c r="AV8" s="40"/>
+      <c r="AW8" s="40"/>
+      <c r="AX8" s="40"/>
+      <c r="AY8" s="40"/>
+      <c r="AZ8" s="40"/>
+      <c r="BA8" s="40"/>
+      <c r="BB8" s="40"/>
+      <c r="BC8" s="40"/>
+      <c r="BD8" s="40"/>
+      <c r="BE8" s="40"/>
+      <c r="BF8" s="40"/>
+      <c r="BG8" s="40"/>
+      <c r="BH8" s="40"/>
+      <c r="BI8" s="40"/>
+      <c r="BJ8" s="40"/>
+      <c r="BK8" s="40"/>
+      <c r="BL8" s="40"/>
+      <c r="BM8" s="40"/>
+      <c r="BN8" s="40"/>
+      <c r="BO8" s="40"/>
+      <c r="BP8" s="40"/>
+      <c r="BQ8" s="40"/>
+      <c r="BR8" s="40"/>
+      <c r="BS8" s="40"/>
+      <c r="BT8" s="40"/>
+      <c r="BU8" s="40"/>
+      <c r="BV8" s="40"/>
+      <c r="BW8" s="40"/>
+      <c r="BX8" s="40"/>
+      <c r="BY8" s="40"/>
+      <c r="BZ8" s="40"/>
+      <c r="CA8" s="40"/>
+      <c r="CB8" s="40"/>
+      <c r="CC8" s="40"/>
+      <c r="CD8" s="40"/>
+      <c r="CE8" s="40"/>
+      <c r="CF8" s="40"/>
+      <c r="CG8" s="40"/>
+      <c r="CH8" s="40"/>
+      <c r="CI8" s="40"/>
+      <c r="CJ8" s="40"/>
+      <c r="CK8" s="40"/>
+      <c r="CL8" s="40"/>
+      <c r="CM8" s="40"/>
+      <c r="CN8" s="40"/>
+      <c r="CO8" s="40"/>
+      <c r="CP8" s="40"/>
+      <c r="CQ8" s="40"/>
+      <c r="CR8" s="40"/>
+      <c r="CS8" s="40"/>
+      <c r="CT8" s="33"/>
     </row>
     <row r="9" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="111" t="s">
+      <c r="B9" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="115"/>
-      <c r="D9" s="116">
+      <c r="C9" s="45"/>
+      <c r="D9" s="46">
         <v>1</v>
       </c>
-      <c r="E9" s="117">
+      <c r="E9" s="47">
         <v>46238</v>
       </c>
-      <c r="F9" s="117">
+      <c r="F9" s="47">
         <v>46238</v>
       </c>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="110"/>
-      <c r="M9" s="110"/>
-      <c r="N9" s="110"/>
-      <c r="O9" s="110"/>
-      <c r="P9" s="110"/>
-      <c r="Q9" s="110"/>
-      <c r="R9" s="110"/>
-      <c r="S9" s="110"/>
-      <c r="T9" s="110"/>
-      <c r="U9" s="110"/>
-      <c r="V9" s="110"/>
-      <c r="W9" s="110"/>
-      <c r="X9" s="110"/>
-      <c r="Y9" s="110"/>
-      <c r="Z9" s="110"/>
-      <c r="AA9" s="110"/>
-      <c r="AB9" s="110"/>
-      <c r="AC9" s="110"/>
-      <c r="AD9" s="110"/>
-      <c r="AE9" s="110"/>
-      <c r="AF9" s="110"/>
-      <c r="AG9" s="110"/>
-      <c r="AH9" s="110"/>
-      <c r="AI9" s="110"/>
-      <c r="AJ9" s="110"/>
-      <c r="AK9" s="110"/>
-      <c r="AL9" s="110"/>
-      <c r="AM9" s="110"/>
-      <c r="AN9" s="110"/>
-      <c r="AO9" s="110"/>
-      <c r="AP9" s="110"/>
-      <c r="AQ9" s="110"/>
-      <c r="AR9" s="110"/>
-      <c r="AS9" s="110"/>
-      <c r="AT9" s="110"/>
-      <c r="AU9" s="110"/>
-      <c r="AV9" s="110"/>
-      <c r="AW9" s="110"/>
-      <c r="AX9" s="110"/>
-      <c r="AY9" s="110"/>
-      <c r="AZ9" s="110"/>
-      <c r="BA9" s="110"/>
-      <c r="BB9" s="110"/>
-      <c r="BC9" s="110"/>
-      <c r="BD9" s="110"/>
-      <c r="BE9" s="110"/>
-      <c r="BF9" s="110"/>
-      <c r="BG9" s="110"/>
-      <c r="BH9" s="110"/>
-      <c r="BI9" s="110"/>
-      <c r="BJ9" s="110"/>
-      <c r="BK9" s="110"/>
-      <c r="BL9" s="110"/>
-      <c r="BM9" s="110"/>
-      <c r="BN9" s="110"/>
-      <c r="BO9" s="110"/>
-      <c r="BP9" s="110"/>
-      <c r="BQ9" s="110"/>
-      <c r="BR9" s="110"/>
-      <c r="BS9" s="110"/>
-      <c r="BT9" s="110"/>
-      <c r="BU9" s="110"/>
-      <c r="BV9" s="110"/>
-      <c r="BW9" s="110"/>
-      <c r="BX9" s="110"/>
-      <c r="BY9" s="110"/>
-      <c r="BZ9" s="110"/>
-      <c r="CA9" s="110"/>
-      <c r="CB9" s="110"/>
-      <c r="CC9" s="110"/>
-      <c r="CD9" s="110"/>
-      <c r="CE9" s="110"/>
-      <c r="CF9" s="110"/>
-      <c r="CG9" s="110"/>
-      <c r="CH9" s="110"/>
-      <c r="CI9" s="110"/>
-      <c r="CJ9" s="110"/>
-      <c r="CK9" s="110"/>
-      <c r="CL9" s="110"/>
-      <c r="CM9" s="110"/>
-      <c r="CN9" s="110"/>
-      <c r="CO9" s="110"/>
-      <c r="CP9" s="110"/>
-      <c r="CQ9" s="110"/>
-      <c r="CR9" s="110"/>
-      <c r="CS9" s="110"/>
-      <c r="CT9" s="102"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="40"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="40"/>
+      <c r="AA9" s="40"/>
+      <c r="AB9" s="40"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="40"/>
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="40"/>
+      <c r="AG9" s="40"/>
+      <c r="AH9" s="40"/>
+      <c r="AI9" s="40"/>
+      <c r="AJ9" s="40"/>
+      <c r="AK9" s="40"/>
+      <c r="AL9" s="40"/>
+      <c r="AM9" s="40"/>
+      <c r="AN9" s="40"/>
+      <c r="AO9" s="40"/>
+      <c r="AP9" s="40"/>
+      <c r="AQ9" s="40"/>
+      <c r="AR9" s="40"/>
+      <c r="AS9" s="40"/>
+      <c r="AT9" s="40"/>
+      <c r="AU9" s="40"/>
+      <c r="AV9" s="40"/>
+      <c r="AW9" s="40"/>
+      <c r="AX9" s="40"/>
+      <c r="AY9" s="40"/>
+      <c r="AZ9" s="40"/>
+      <c r="BA9" s="40"/>
+      <c r="BB9" s="40"/>
+      <c r="BC9" s="40"/>
+      <c r="BD9" s="40"/>
+      <c r="BE9" s="40"/>
+      <c r="BF9" s="40"/>
+      <c r="BG9" s="40"/>
+      <c r="BH9" s="40"/>
+      <c r="BI9" s="40"/>
+      <c r="BJ9" s="40"/>
+      <c r="BK9" s="40"/>
+      <c r="BL9" s="40"/>
+      <c r="BM9" s="40"/>
+      <c r="BN9" s="40"/>
+      <c r="BO9" s="40"/>
+      <c r="BP9" s="40"/>
+      <c r="BQ9" s="40"/>
+      <c r="BR9" s="40"/>
+      <c r="BS9" s="40"/>
+      <c r="BT9" s="40"/>
+      <c r="BU9" s="40"/>
+      <c r="BV9" s="40"/>
+      <c r="BW9" s="40"/>
+      <c r="BX9" s="40"/>
+      <c r="BY9" s="40"/>
+      <c r="BZ9" s="40"/>
+      <c r="CA9" s="40"/>
+      <c r="CB9" s="40"/>
+      <c r="CC9" s="40"/>
+      <c r="CD9" s="40"/>
+      <c r="CE9" s="40"/>
+      <c r="CF9" s="40"/>
+      <c r="CG9" s="40"/>
+      <c r="CH9" s="40"/>
+      <c r="CI9" s="40"/>
+      <c r="CJ9" s="40"/>
+      <c r="CK9" s="40"/>
+      <c r="CL9" s="40"/>
+      <c r="CM9" s="40"/>
+      <c r="CN9" s="40"/>
+      <c r="CO9" s="40"/>
+      <c r="CP9" s="40"/>
+      <c r="CQ9" s="40"/>
+      <c r="CR9" s="40"/>
+      <c r="CS9" s="40"/>
+      <c r="CT9" s="33"/>
     </row>
     <row r="10" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="111" t="s">
+      <c r="B10" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="116">
+      <c r="C10" s="45"/>
+      <c r="D10" s="46">
         <v>1</v>
       </c>
-      <c r="E10" s="117">
+      <c r="E10" s="47">
         <v>46239</v>
       </c>
-      <c r="F10" s="117">
+      <c r="F10" s="47">
         <v>46239</v>
       </c>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="110"/>
-      <c r="O10" s="110"/>
-      <c r="P10" s="110"/>
-      <c r="Q10" s="110"/>
-      <c r="R10" s="110"/>
-      <c r="S10" s="110"/>
-      <c r="T10" s="110"/>
-      <c r="U10" s="110"/>
-      <c r="V10" s="110"/>
-      <c r="W10" s="110"/>
-      <c r="X10" s="110"/>
-      <c r="Y10" s="110"/>
-      <c r="Z10" s="110"/>
-      <c r="AA10" s="110"/>
-      <c r="AB10" s="110"/>
-      <c r="AC10" s="110"/>
-      <c r="AD10" s="110"/>
-      <c r="AE10" s="110"/>
-      <c r="AF10" s="110"/>
-      <c r="AG10" s="110"/>
-      <c r="AH10" s="110"/>
-      <c r="AI10" s="110"/>
-      <c r="AJ10" s="110"/>
-      <c r="AK10" s="110"/>
-      <c r="AL10" s="110"/>
-      <c r="AM10" s="110"/>
-      <c r="AN10" s="110"/>
-      <c r="AO10" s="110"/>
-      <c r="AP10" s="110"/>
-      <c r="AQ10" s="110"/>
-      <c r="AR10" s="110"/>
-      <c r="AS10" s="110"/>
-      <c r="AT10" s="110"/>
-      <c r="AU10" s="110"/>
-      <c r="AV10" s="110"/>
-      <c r="AW10" s="110"/>
-      <c r="AX10" s="110"/>
-      <c r="AY10" s="110"/>
-      <c r="AZ10" s="110"/>
-      <c r="BA10" s="110"/>
-      <c r="BB10" s="110"/>
-      <c r="BC10" s="110"/>
-      <c r="BD10" s="110"/>
-      <c r="BE10" s="110"/>
-      <c r="BF10" s="110"/>
-      <c r="BG10" s="110"/>
-      <c r="BH10" s="110"/>
-      <c r="BI10" s="110"/>
-      <c r="BJ10" s="110"/>
-      <c r="BK10" s="110"/>
-      <c r="BL10" s="110"/>
-      <c r="BM10" s="110"/>
-      <c r="BN10" s="110"/>
-      <c r="BO10" s="110"/>
-      <c r="BP10" s="110"/>
-      <c r="BQ10" s="110"/>
-      <c r="BR10" s="110"/>
-      <c r="BS10" s="110"/>
-      <c r="BT10" s="110"/>
-      <c r="BU10" s="110"/>
-      <c r="BV10" s="110"/>
-      <c r="BW10" s="110"/>
-      <c r="BX10" s="110"/>
-      <c r="BY10" s="110"/>
-      <c r="BZ10" s="110"/>
-      <c r="CA10" s="110"/>
-      <c r="CB10" s="110"/>
-      <c r="CC10" s="110"/>
-      <c r="CD10" s="110"/>
-      <c r="CE10" s="110"/>
-      <c r="CF10" s="110"/>
-      <c r="CG10" s="110"/>
-      <c r="CH10" s="110"/>
-      <c r="CI10" s="110"/>
-      <c r="CJ10" s="110"/>
-      <c r="CK10" s="110"/>
-      <c r="CL10" s="110"/>
-      <c r="CM10" s="110"/>
-      <c r="CN10" s="110"/>
-      <c r="CO10" s="110"/>
-      <c r="CP10" s="110"/>
-      <c r="CQ10" s="110"/>
-      <c r="CR10" s="110"/>
-      <c r="CS10" s="110"/>
-      <c r="CT10" s="102"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="40"/>
+      <c r="S10" s="40"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="40"/>
+      <c r="V10" s="40"/>
+      <c r="W10" s="40"/>
+      <c r="X10" s="40"/>
+      <c r="Y10" s="40"/>
+      <c r="Z10" s="40"/>
+      <c r="AA10" s="40"/>
+      <c r="AB10" s="40"/>
+      <c r="AC10" s="40"/>
+      <c r="AD10" s="40"/>
+      <c r="AE10" s="40"/>
+      <c r="AF10" s="40"/>
+      <c r="AG10" s="40"/>
+      <c r="AH10" s="40"/>
+      <c r="AI10" s="40"/>
+      <c r="AJ10" s="40"/>
+      <c r="AK10" s="40"/>
+      <c r="AL10" s="40"/>
+      <c r="AM10" s="40"/>
+      <c r="AN10" s="40"/>
+      <c r="AO10" s="40"/>
+      <c r="AP10" s="40"/>
+      <c r="AQ10" s="40"/>
+      <c r="AR10" s="40"/>
+      <c r="AS10" s="40"/>
+      <c r="AT10" s="40"/>
+      <c r="AU10" s="40"/>
+      <c r="AV10" s="40"/>
+      <c r="AW10" s="40"/>
+      <c r="AX10" s="40"/>
+      <c r="AY10" s="40"/>
+      <c r="AZ10" s="40"/>
+      <c r="BA10" s="40"/>
+      <c r="BB10" s="40"/>
+      <c r="BC10" s="40"/>
+      <c r="BD10" s="40"/>
+      <c r="BE10" s="40"/>
+      <c r="BF10" s="40"/>
+      <c r="BG10" s="40"/>
+      <c r="BH10" s="40"/>
+      <c r="BI10" s="40"/>
+      <c r="BJ10" s="40"/>
+      <c r="BK10" s="40"/>
+      <c r="BL10" s="40"/>
+      <c r="BM10" s="40"/>
+      <c r="BN10" s="40"/>
+      <c r="BO10" s="40"/>
+      <c r="BP10" s="40"/>
+      <c r="BQ10" s="40"/>
+      <c r="BR10" s="40"/>
+      <c r="BS10" s="40"/>
+      <c r="BT10" s="40"/>
+      <c r="BU10" s="40"/>
+      <c r="BV10" s="40"/>
+      <c r="BW10" s="40"/>
+      <c r="BX10" s="40"/>
+      <c r="BY10" s="40"/>
+      <c r="BZ10" s="40"/>
+      <c r="CA10" s="40"/>
+      <c r="CB10" s="40"/>
+      <c r="CC10" s="40"/>
+      <c r="CD10" s="40"/>
+      <c r="CE10" s="40"/>
+      <c r="CF10" s="40"/>
+      <c r="CG10" s="40"/>
+      <c r="CH10" s="40"/>
+      <c r="CI10" s="40"/>
+      <c r="CJ10" s="40"/>
+      <c r="CK10" s="40"/>
+      <c r="CL10" s="40"/>
+      <c r="CM10" s="40"/>
+      <c r="CN10" s="40"/>
+      <c r="CO10" s="40"/>
+      <c r="CP10" s="40"/>
+      <c r="CQ10" s="40"/>
+      <c r="CR10" s="40"/>
+      <c r="CS10" s="40"/>
+      <c r="CT10" s="33"/>
     </row>
     <row r="11" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="111" t="s">
+      <c r="B11" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="115"/>
-      <c r="D11" s="116">
+      <c r="C11" s="45"/>
+      <c r="D11" s="46">
         <v>0</v>
       </c>
-      <c r="E11" s="117">
+      <c r="E11" s="47">
         <v>46240</v>
       </c>
-      <c r="F11" s="117">
+      <c r="F11" s="47">
         <v>46240</v>
       </c>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="110"/>
-      <c r="M11" s="110"/>
-      <c r="N11" s="110"/>
-      <c r="O11" s="110"/>
-      <c r="P11" s="110"/>
-      <c r="Q11" s="110"/>
-      <c r="R11" s="110"/>
-      <c r="S11" s="110"/>
-      <c r="T11" s="110"/>
-      <c r="U11" s="110"/>
-      <c r="V11" s="110"/>
-      <c r="W11" s="110"/>
-      <c r="X11" s="110"/>
-      <c r="Y11" s="110"/>
-      <c r="Z11" s="110"/>
-      <c r="AA11" s="110"/>
-      <c r="AB11" s="110"/>
-      <c r="AC11" s="110"/>
-      <c r="AD11" s="110"/>
-      <c r="AE11" s="110"/>
-      <c r="AF11" s="110"/>
-      <c r="AG11" s="110"/>
-      <c r="AH11" s="110"/>
-      <c r="AI11" s="110"/>
-      <c r="AJ11" s="110"/>
-      <c r="AK11" s="110"/>
-      <c r="AL11" s="110"/>
-      <c r="AM11" s="110"/>
-      <c r="AN11" s="110"/>
-      <c r="AO11" s="110"/>
-      <c r="AP11" s="110"/>
-      <c r="AQ11" s="110"/>
-      <c r="AR11" s="110"/>
-      <c r="AS11" s="110"/>
-      <c r="AT11" s="110"/>
-      <c r="AU11" s="110"/>
-      <c r="AV11" s="110"/>
-      <c r="AW11" s="110"/>
-      <c r="AX11" s="110"/>
-      <c r="AY11" s="110"/>
-      <c r="AZ11" s="110"/>
-      <c r="BA11" s="110"/>
-      <c r="BB11" s="110"/>
-      <c r="BC11" s="110"/>
-      <c r="BD11" s="110"/>
-      <c r="BE11" s="110"/>
-      <c r="BF11" s="110"/>
-      <c r="BG11" s="110"/>
-      <c r="BH11" s="110"/>
-      <c r="BI11" s="110"/>
-      <c r="BJ11" s="110"/>
-      <c r="BK11" s="110"/>
-      <c r="BL11" s="110"/>
-      <c r="BM11" s="110"/>
-      <c r="BN11" s="110"/>
-      <c r="BO11" s="110"/>
-      <c r="BP11" s="110"/>
-      <c r="BQ11" s="110"/>
-      <c r="BR11" s="110"/>
-      <c r="BS11" s="110"/>
-      <c r="BT11" s="110"/>
-      <c r="BU11" s="110"/>
-      <c r="BV11" s="110"/>
-      <c r="BW11" s="110"/>
-      <c r="BX11" s="110"/>
-      <c r="BY11" s="110"/>
-      <c r="BZ11" s="110"/>
-      <c r="CA11" s="110"/>
-      <c r="CB11" s="110"/>
-      <c r="CC11" s="110"/>
-      <c r="CD11" s="110"/>
-      <c r="CE11" s="110"/>
-      <c r="CF11" s="110"/>
-      <c r="CG11" s="110"/>
-      <c r="CH11" s="110"/>
-      <c r="CI11" s="110"/>
-      <c r="CJ11" s="110"/>
-      <c r="CK11" s="110"/>
-      <c r="CL11" s="110"/>
-      <c r="CM11" s="110"/>
-      <c r="CN11" s="110"/>
-      <c r="CO11" s="110"/>
-      <c r="CP11" s="110"/>
-      <c r="CQ11" s="110"/>
-      <c r="CR11" s="110"/>
-      <c r="CS11" s="110"/>
-      <c r="CT11" s="102"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="40"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="40"/>
+      <c r="W11" s="40"/>
+      <c r="X11" s="40"/>
+      <c r="Y11" s="40"/>
+      <c r="Z11" s="40"/>
+      <c r="AA11" s="40"/>
+      <c r="AB11" s="40"/>
+      <c r="AC11" s="40"/>
+      <c r="AD11" s="40"/>
+      <c r="AE11" s="40"/>
+      <c r="AF11" s="40"/>
+      <c r="AG11" s="40"/>
+      <c r="AH11" s="40"/>
+      <c r="AI11" s="40"/>
+      <c r="AJ11" s="40"/>
+      <c r="AK11" s="40"/>
+      <c r="AL11" s="40"/>
+      <c r="AM11" s="40"/>
+      <c r="AN11" s="40"/>
+      <c r="AO11" s="40"/>
+      <c r="AP11" s="40"/>
+      <c r="AQ11" s="40"/>
+      <c r="AR11" s="40"/>
+      <c r="AS11" s="40"/>
+      <c r="AT11" s="40"/>
+      <c r="AU11" s="40"/>
+      <c r="AV11" s="40"/>
+      <c r="AW11" s="40"/>
+      <c r="AX11" s="40"/>
+      <c r="AY11" s="40"/>
+      <c r="AZ11" s="40"/>
+      <c r="BA11" s="40"/>
+      <c r="BB11" s="40"/>
+      <c r="BC11" s="40"/>
+      <c r="BD11" s="40"/>
+      <c r="BE11" s="40"/>
+      <c r="BF11" s="40"/>
+      <c r="BG11" s="40"/>
+      <c r="BH11" s="40"/>
+      <c r="BI11" s="40"/>
+      <c r="BJ11" s="40"/>
+      <c r="BK11" s="40"/>
+      <c r="BL11" s="40"/>
+      <c r="BM11" s="40"/>
+      <c r="BN11" s="40"/>
+      <c r="BO11" s="40"/>
+      <c r="BP11" s="40"/>
+      <c r="BQ11" s="40"/>
+      <c r="BR11" s="40"/>
+      <c r="BS11" s="40"/>
+      <c r="BT11" s="40"/>
+      <c r="BU11" s="40"/>
+      <c r="BV11" s="40"/>
+      <c r="BW11" s="40"/>
+      <c r="BX11" s="40"/>
+      <c r="BY11" s="40"/>
+      <c r="BZ11" s="40"/>
+      <c r="CA11" s="40"/>
+      <c r="CB11" s="40"/>
+      <c r="CC11" s="40"/>
+      <c r="CD11" s="40"/>
+      <c r="CE11" s="40"/>
+      <c r="CF11" s="40"/>
+      <c r="CG11" s="40"/>
+      <c r="CH11" s="40"/>
+      <c r="CI11" s="40"/>
+      <c r="CJ11" s="40"/>
+      <c r="CK11" s="40"/>
+      <c r="CL11" s="40"/>
+      <c r="CM11" s="40"/>
+      <c r="CN11" s="40"/>
+      <c r="CO11" s="40"/>
+      <c r="CP11" s="40"/>
+      <c r="CQ11" s="40"/>
+      <c r="CR11" s="40"/>
+      <c r="CS11" s="40"/>
+      <c r="CT11" s="33"/>
     </row>
     <row r="12" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="111"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="120"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="110"/>
-      <c r="L12" s="110"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="110"/>
-      <c r="P12" s="110"/>
-      <c r="Q12" s="110"/>
-      <c r="R12" s="110"/>
-      <c r="S12" s="110"/>
-      <c r="T12" s="110"/>
-      <c r="U12" s="110"/>
-      <c r="V12" s="110"/>
-      <c r="W12" s="110"/>
-      <c r="X12" s="110"/>
-      <c r="Y12" s="110"/>
-      <c r="Z12" s="110"/>
-      <c r="AA12" s="110"/>
-      <c r="AB12" s="110"/>
-      <c r="AC12" s="110"/>
-      <c r="AD12" s="110"/>
-      <c r="AE12" s="110"/>
-      <c r="AF12" s="110"/>
-      <c r="AG12" s="110"/>
-      <c r="AH12" s="110"/>
-      <c r="AI12" s="110"/>
-      <c r="AJ12" s="110"/>
-      <c r="AK12" s="110"/>
-      <c r="AL12" s="110"/>
-      <c r="AM12" s="110"/>
-      <c r="AN12" s="110"/>
-      <c r="AO12" s="110"/>
-      <c r="AP12" s="110"/>
-      <c r="AQ12" s="110"/>
-      <c r="AR12" s="110"/>
-      <c r="AS12" s="110"/>
-      <c r="AT12" s="110"/>
-      <c r="AU12" s="110"/>
-      <c r="AV12" s="110"/>
-      <c r="AW12" s="110"/>
-      <c r="AX12" s="110"/>
-      <c r="AY12" s="110"/>
-      <c r="AZ12" s="110"/>
-      <c r="BA12" s="110"/>
-      <c r="BB12" s="110"/>
-      <c r="BC12" s="110"/>
-      <c r="BD12" s="110"/>
-      <c r="BE12" s="110"/>
-      <c r="BF12" s="110"/>
-      <c r="BG12" s="110"/>
-      <c r="BH12" s="110"/>
-      <c r="BI12" s="110"/>
-      <c r="BJ12" s="110"/>
-      <c r="BK12" s="110"/>
-      <c r="BL12" s="110"/>
-      <c r="BM12" s="110"/>
-      <c r="BN12" s="110"/>
-      <c r="BO12" s="110"/>
-      <c r="BP12" s="110"/>
-      <c r="BQ12" s="110"/>
-      <c r="BR12" s="110"/>
-      <c r="BS12" s="110"/>
-      <c r="BT12" s="110"/>
-      <c r="BU12" s="110"/>
-      <c r="BV12" s="110"/>
-      <c r="BW12" s="110"/>
-      <c r="BX12" s="110"/>
-      <c r="BY12" s="110"/>
-      <c r="BZ12" s="110"/>
-      <c r="CA12" s="110"/>
-      <c r="CB12" s="110"/>
-      <c r="CC12" s="110"/>
-      <c r="CD12" s="110"/>
-      <c r="CE12" s="110"/>
-      <c r="CF12" s="110"/>
-      <c r="CG12" s="110"/>
-      <c r="CH12" s="110"/>
-      <c r="CI12" s="110"/>
-      <c r="CJ12" s="110"/>
-      <c r="CK12" s="110"/>
-      <c r="CL12" s="110"/>
-      <c r="CM12" s="110"/>
-      <c r="CN12" s="110"/>
-      <c r="CO12" s="110"/>
-      <c r="CP12" s="110"/>
-      <c r="CQ12" s="110"/>
-      <c r="CR12" s="110"/>
-      <c r="CS12" s="110"/>
-      <c r="CT12" s="102"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
+      <c r="V12" s="40"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="40"/>
+      <c r="Y12" s="40"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="40"/>
+      <c r="AB12" s="40"/>
+      <c r="AC12" s="40"/>
+      <c r="AD12" s="40"/>
+      <c r="AE12" s="40"/>
+      <c r="AF12" s="40"/>
+      <c r="AG12" s="40"/>
+      <c r="AH12" s="40"/>
+      <c r="AI12" s="40"/>
+      <c r="AJ12" s="40"/>
+      <c r="AK12" s="40"/>
+      <c r="AL12" s="40"/>
+      <c r="AM12" s="40"/>
+      <c r="AN12" s="40"/>
+      <c r="AO12" s="40"/>
+      <c r="AP12" s="40"/>
+      <c r="AQ12" s="40"/>
+      <c r="AR12" s="40"/>
+      <c r="AS12" s="40"/>
+      <c r="AT12" s="40"/>
+      <c r="AU12" s="40"/>
+      <c r="AV12" s="40"/>
+      <c r="AW12" s="40"/>
+      <c r="AX12" s="40"/>
+      <c r="AY12" s="40"/>
+      <c r="AZ12" s="40"/>
+      <c r="BA12" s="40"/>
+      <c r="BB12" s="40"/>
+      <c r="BC12" s="40"/>
+      <c r="BD12" s="40"/>
+      <c r="BE12" s="40"/>
+      <c r="BF12" s="40"/>
+      <c r="BG12" s="40"/>
+      <c r="BH12" s="40"/>
+      <c r="BI12" s="40"/>
+      <c r="BJ12" s="40"/>
+      <c r="BK12" s="40"/>
+      <c r="BL12" s="40"/>
+      <c r="BM12" s="40"/>
+      <c r="BN12" s="40"/>
+      <c r="BO12" s="40"/>
+      <c r="BP12" s="40"/>
+      <c r="BQ12" s="40"/>
+      <c r="BR12" s="40"/>
+      <c r="BS12" s="40"/>
+      <c r="BT12" s="40"/>
+      <c r="BU12" s="40"/>
+      <c r="BV12" s="40"/>
+      <c r="BW12" s="40"/>
+      <c r="BX12" s="40"/>
+      <c r="BY12" s="40"/>
+      <c r="BZ12" s="40"/>
+      <c r="CA12" s="40"/>
+      <c r="CB12" s="40"/>
+      <c r="CC12" s="40"/>
+      <c r="CD12" s="40"/>
+      <c r="CE12" s="40"/>
+      <c r="CF12" s="40"/>
+      <c r="CG12" s="40"/>
+      <c r="CH12" s="40"/>
+      <c r="CI12" s="40"/>
+      <c r="CJ12" s="40"/>
+      <c r="CK12" s="40"/>
+      <c r="CL12" s="40"/>
+      <c r="CM12" s="40"/>
+      <c r="CN12" s="40"/>
+      <c r="CO12" s="40"/>
+      <c r="CP12" s="40"/>
+      <c r="CQ12" s="40"/>
+      <c r="CR12" s="40"/>
+      <c r="CS12" s="40"/>
+      <c r="CT12" s="33"/>
     </row>
     <row r="13" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="105" t="s">
+      <c r="B13" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="106"/>
-      <c r="D13" s="107">
+      <c r="C13" s="36"/>
+      <c r="D13" s="37">
         <f>SUM(D14:D22)</f>
         <v>21</v>
       </c>
-      <c r="E13" s="108">
+      <c r="E13" s="38">
         <v>46241</v>
       </c>
-      <c r="F13" s="108">
+      <c r="F13" s="38">
         <v>46260</v>
       </c>
-      <c r="G13" s="109"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="110"/>
-      <c r="L13" s="110"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="110"/>
-      <c r="P13" s="110"/>
-      <c r="Q13" s="110"/>
-      <c r="R13" s="110"/>
-      <c r="S13" s="110"/>
-      <c r="T13" s="110"/>
-      <c r="U13" s="110"/>
-      <c r="V13" s="110"/>
-      <c r="W13" s="110"/>
-      <c r="X13" s="110"/>
-      <c r="Y13" s="110"/>
-      <c r="Z13" s="110"/>
-      <c r="AA13" s="110"/>
-      <c r="AB13" s="110"/>
-      <c r="AC13" s="110"/>
-      <c r="AD13" s="110"/>
-      <c r="AE13" s="110"/>
-      <c r="AF13" s="110"/>
-      <c r="AG13" s="110"/>
-      <c r="AH13" s="110"/>
-      <c r="AI13" s="110"/>
-      <c r="AJ13" s="110"/>
-      <c r="AK13" s="110"/>
-      <c r="AL13" s="110"/>
-      <c r="AM13" s="110"/>
-      <c r="AN13" s="110"/>
-      <c r="AO13" s="110"/>
-      <c r="AP13" s="110"/>
-      <c r="AQ13" s="110"/>
-      <c r="AR13" s="110"/>
-      <c r="AS13" s="110"/>
-      <c r="AT13" s="110"/>
-      <c r="AU13" s="110"/>
-      <c r="AV13" s="110"/>
-      <c r="AW13" s="110"/>
-      <c r="AX13" s="110"/>
-      <c r="AY13" s="110"/>
-      <c r="AZ13" s="110"/>
-      <c r="BA13" s="110"/>
-      <c r="BB13" s="110"/>
-      <c r="BC13" s="110"/>
-      <c r="BD13" s="110"/>
-      <c r="BE13" s="110"/>
-      <c r="BF13" s="110"/>
-      <c r="BG13" s="110"/>
-      <c r="BH13" s="110"/>
-      <c r="BI13" s="110"/>
-      <c r="BJ13" s="110"/>
-      <c r="BK13" s="110"/>
-      <c r="BL13" s="110"/>
-      <c r="BM13" s="110"/>
-      <c r="BN13" s="110"/>
-      <c r="BO13" s="110"/>
-      <c r="BP13" s="110"/>
-      <c r="BQ13" s="110"/>
-      <c r="BR13" s="110"/>
-      <c r="BS13" s="110"/>
-      <c r="BT13" s="110"/>
-      <c r="BU13" s="110"/>
-      <c r="BV13" s="110"/>
-      <c r="BW13" s="110"/>
-      <c r="BX13" s="110"/>
-      <c r="BY13" s="110"/>
-      <c r="BZ13" s="110"/>
-      <c r="CA13" s="110"/>
-      <c r="CB13" s="110"/>
-      <c r="CC13" s="110"/>
-      <c r="CD13" s="110"/>
-      <c r="CE13" s="110"/>
-      <c r="CF13" s="110"/>
-      <c r="CG13" s="110"/>
-      <c r="CH13" s="110"/>
-      <c r="CI13" s="110"/>
-      <c r="CJ13" s="110"/>
-      <c r="CK13" s="110"/>
-      <c r="CL13" s="110"/>
-      <c r="CM13" s="110"/>
-      <c r="CN13" s="110"/>
-      <c r="CO13" s="110"/>
-      <c r="CP13" s="110"/>
-      <c r="CQ13" s="110"/>
-      <c r="CR13" s="110"/>
-      <c r="CS13" s="110"/>
-      <c r="CT13" s="102"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="40"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="40"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="40"/>
+      <c r="AC13" s="40"/>
+      <c r="AD13" s="40"/>
+      <c r="AE13" s="40"/>
+      <c r="AF13" s="40"/>
+      <c r="AG13" s="40"/>
+      <c r="AH13" s="40"/>
+      <c r="AI13" s="40"/>
+      <c r="AJ13" s="40"/>
+      <c r="AK13" s="40"/>
+      <c r="AL13" s="40"/>
+      <c r="AM13" s="40"/>
+      <c r="AN13" s="40"/>
+      <c r="AO13" s="40"/>
+      <c r="AP13" s="40"/>
+      <c r="AQ13" s="40"/>
+      <c r="AR13" s="40"/>
+      <c r="AS13" s="40"/>
+      <c r="AT13" s="40"/>
+      <c r="AU13" s="40"/>
+      <c r="AV13" s="40"/>
+      <c r="AW13" s="40"/>
+      <c r="AX13" s="40"/>
+      <c r="AY13" s="40"/>
+      <c r="AZ13" s="40"/>
+      <c r="BA13" s="40"/>
+      <c r="BB13" s="40"/>
+      <c r="BC13" s="40"/>
+      <c r="BD13" s="40"/>
+      <c r="BE13" s="40"/>
+      <c r="BF13" s="40"/>
+      <c r="BG13" s="40"/>
+      <c r="BH13" s="40"/>
+      <c r="BI13" s="40"/>
+      <c r="BJ13" s="40"/>
+      <c r="BK13" s="40"/>
+      <c r="BL13" s="40"/>
+      <c r="BM13" s="40"/>
+      <c r="BN13" s="40"/>
+      <c r="BO13" s="40"/>
+      <c r="BP13" s="40"/>
+      <c r="BQ13" s="40"/>
+      <c r="BR13" s="40"/>
+      <c r="BS13" s="40"/>
+      <c r="BT13" s="40"/>
+      <c r="BU13" s="40"/>
+      <c r="BV13" s="40"/>
+      <c r="BW13" s="40"/>
+      <c r="BX13" s="40"/>
+      <c r="BY13" s="40"/>
+      <c r="BZ13" s="40"/>
+      <c r="CA13" s="40"/>
+      <c r="CB13" s="40"/>
+      <c r="CC13" s="40"/>
+      <c r="CD13" s="40"/>
+      <c r="CE13" s="40"/>
+      <c r="CF13" s="40"/>
+      <c r="CG13" s="40"/>
+      <c r="CH13" s="40"/>
+      <c r="CI13" s="40"/>
+      <c r="CJ13" s="40"/>
+      <c r="CK13" s="40"/>
+      <c r="CL13" s="40"/>
+      <c r="CM13" s="40"/>
+      <c r="CN13" s="40"/>
+      <c r="CO13" s="40"/>
+      <c r="CP13" s="40"/>
+      <c r="CQ13" s="40"/>
+      <c r="CR13" s="40"/>
+      <c r="CS13" s="40"/>
+      <c r="CT13" s="33"/>
     </row>
     <row r="14" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="121" t="s">
+      <c r="B14" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="112"/>
-      <c r="D14" s="113">
+      <c r="C14" s="42"/>
+      <c r="D14" s="43">
         <v>5</v>
       </c>
-      <c r="E14" s="114">
+      <c r="E14" s="44">
         <v>46241</v>
       </c>
-      <c r="F14" s="114">
+      <c r="F14" s="44">
         <v>46245</v>
       </c>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="122"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="110"/>
-      <c r="P14" s="110"/>
-      <c r="Q14" s="110"/>
-      <c r="R14" s="110"/>
-      <c r="S14" s="110"/>
-      <c r="T14" s="110"/>
-      <c r="U14" s="110"/>
-      <c r="V14" s="110"/>
-      <c r="W14" s="110"/>
-      <c r="X14" s="110"/>
-      <c r="Y14" s="110"/>
-      <c r="Z14" s="110"/>
-      <c r="AA14" s="110"/>
-      <c r="AB14" s="110"/>
-      <c r="AC14" s="110"/>
-      <c r="AD14" s="110"/>
-      <c r="AE14" s="110"/>
-      <c r="AF14" s="110"/>
-      <c r="AG14" s="110"/>
-      <c r="AH14" s="110"/>
-      <c r="AI14" s="110"/>
-      <c r="AJ14" s="110"/>
-      <c r="AK14" s="110"/>
-      <c r="AL14" s="110"/>
-      <c r="AM14" s="110"/>
-      <c r="AN14" s="110"/>
-      <c r="AO14" s="110"/>
-      <c r="AP14" s="110"/>
-      <c r="AQ14" s="110"/>
-      <c r="AR14" s="110"/>
-      <c r="AS14" s="110"/>
-      <c r="AT14" s="110"/>
-      <c r="AU14" s="110"/>
-      <c r="AV14" s="110"/>
-      <c r="AW14" s="110"/>
-      <c r="AX14" s="110"/>
-      <c r="AY14" s="110"/>
-      <c r="AZ14" s="110"/>
-      <c r="BA14" s="110"/>
-      <c r="BB14" s="110"/>
-      <c r="BC14" s="110"/>
-      <c r="BD14" s="110"/>
-      <c r="BE14" s="110"/>
-      <c r="BF14" s="110"/>
-      <c r="BG14" s="110"/>
-      <c r="BH14" s="110"/>
-      <c r="BI14" s="110"/>
-      <c r="BJ14" s="110"/>
-      <c r="BK14" s="110"/>
-      <c r="BL14" s="110"/>
-      <c r="BM14" s="110"/>
-      <c r="BN14" s="110"/>
-      <c r="BO14" s="110"/>
-      <c r="BP14" s="110"/>
-      <c r="BQ14" s="110"/>
-      <c r="BR14" s="110"/>
-      <c r="BS14" s="110"/>
-      <c r="BT14" s="110"/>
-      <c r="BU14" s="110"/>
-      <c r="BV14" s="110"/>
-      <c r="BW14" s="110"/>
-      <c r="BX14" s="110"/>
-      <c r="BY14" s="110"/>
-      <c r="BZ14" s="110"/>
-      <c r="CA14" s="110"/>
-      <c r="CB14" s="110"/>
-      <c r="CC14" s="110"/>
-      <c r="CD14" s="110"/>
-      <c r="CE14" s="110"/>
-      <c r="CF14" s="110"/>
-      <c r="CG14" s="110"/>
-      <c r="CH14" s="110"/>
-      <c r="CI14" s="110"/>
-      <c r="CJ14" s="110"/>
-      <c r="CK14" s="110"/>
-      <c r="CL14" s="110"/>
-      <c r="CM14" s="110"/>
-      <c r="CN14" s="110"/>
-      <c r="CO14" s="110"/>
-      <c r="CP14" s="110"/>
-      <c r="CQ14" s="110"/>
-      <c r="CR14" s="110"/>
-      <c r="CS14" s="110"/>
-      <c r="CT14" s="102"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="40"/>
+      <c r="S14" s="40"/>
+      <c r="T14" s="40"/>
+      <c r="U14" s="40"/>
+      <c r="V14" s="40"/>
+      <c r="W14" s="40"/>
+      <c r="X14" s="40"/>
+      <c r="Y14" s="40"/>
+      <c r="Z14" s="40"/>
+      <c r="AA14" s="40"/>
+      <c r="AB14" s="40"/>
+      <c r="AC14" s="40"/>
+      <c r="AD14" s="40"/>
+      <c r="AE14" s="40"/>
+      <c r="AF14" s="40"/>
+      <c r="AG14" s="40"/>
+      <c r="AH14" s="40"/>
+      <c r="AI14" s="40"/>
+      <c r="AJ14" s="40"/>
+      <c r="AK14" s="40"/>
+      <c r="AL14" s="40"/>
+      <c r="AM14" s="40"/>
+      <c r="AN14" s="40"/>
+      <c r="AO14" s="40"/>
+      <c r="AP14" s="40"/>
+      <c r="AQ14" s="40"/>
+      <c r="AR14" s="40"/>
+      <c r="AS14" s="40"/>
+      <c r="AT14" s="40"/>
+      <c r="AU14" s="40"/>
+      <c r="AV14" s="40"/>
+      <c r="AW14" s="40"/>
+      <c r="AX14" s="40"/>
+      <c r="AY14" s="40"/>
+      <c r="AZ14" s="40"/>
+      <c r="BA14" s="40"/>
+      <c r="BB14" s="40"/>
+      <c r="BC14" s="40"/>
+      <c r="BD14" s="40"/>
+      <c r="BE14" s="40"/>
+      <c r="BF14" s="40"/>
+      <c r="BG14" s="40"/>
+      <c r="BH14" s="40"/>
+      <c r="BI14" s="40"/>
+      <c r="BJ14" s="40"/>
+      <c r="BK14" s="40"/>
+      <c r="BL14" s="40"/>
+      <c r="BM14" s="40"/>
+      <c r="BN14" s="40"/>
+      <c r="BO14" s="40"/>
+      <c r="BP14" s="40"/>
+      <c r="BQ14" s="40"/>
+      <c r="BR14" s="40"/>
+      <c r="BS14" s="40"/>
+      <c r="BT14" s="40"/>
+      <c r="BU14" s="40"/>
+      <c r="BV14" s="40"/>
+      <c r="BW14" s="40"/>
+      <c r="BX14" s="40"/>
+      <c r="BY14" s="40"/>
+      <c r="BZ14" s="40"/>
+      <c r="CA14" s="40"/>
+      <c r="CB14" s="40"/>
+      <c r="CC14" s="40"/>
+      <c r="CD14" s="40"/>
+      <c r="CE14" s="40"/>
+      <c r="CF14" s="40"/>
+      <c r="CG14" s="40"/>
+      <c r="CH14" s="40"/>
+      <c r="CI14" s="40"/>
+      <c r="CJ14" s="40"/>
+      <c r="CK14" s="40"/>
+      <c r="CL14" s="40"/>
+      <c r="CM14" s="40"/>
+      <c r="CN14" s="40"/>
+      <c r="CO14" s="40"/>
+      <c r="CP14" s="40"/>
+      <c r="CQ14" s="40"/>
+      <c r="CR14" s="40"/>
+      <c r="CS14" s="40"/>
+      <c r="CT14" s="33"/>
     </row>
     <row r="15" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="121" t="s">
+      <c r="B15" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="123"/>
-      <c r="D15" s="124">
+      <c r="C15" s="53"/>
+      <c r="D15" s="54">
         <v>7.5</v>
       </c>
-      <c r="E15" s="125">
+      <c r="E15" s="55">
         <v>46246</v>
       </c>
-      <c r="F15" s="117">
+      <c r="F15" s="47">
         <v>46252</v>
       </c>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="110"/>
-      <c r="N15" s="110"/>
-      <c r="O15" s="110"/>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="110"/>
-      <c r="R15" s="110"/>
-      <c r="S15" s="110"/>
-      <c r="T15" s="110"/>
-      <c r="U15" s="110"/>
-      <c r="V15" s="110"/>
-      <c r="W15" s="110"/>
-      <c r="X15" s="110"/>
-      <c r="Y15" s="110"/>
-      <c r="Z15" s="110"/>
-      <c r="AA15" s="110"/>
-      <c r="AB15" s="110"/>
-      <c r="AC15" s="110"/>
-      <c r="AD15" s="110"/>
-      <c r="AE15" s="110"/>
-      <c r="AF15" s="110"/>
-      <c r="AG15" s="110"/>
-      <c r="AH15" s="110"/>
-      <c r="AI15" s="110"/>
-      <c r="AJ15" s="110"/>
-      <c r="AK15" s="110"/>
-      <c r="AL15" s="110"/>
-      <c r="AM15" s="110"/>
-      <c r="AN15" s="110"/>
-      <c r="AO15" s="110"/>
-      <c r="AP15" s="110"/>
-      <c r="AQ15" s="110"/>
-      <c r="AR15" s="110"/>
-      <c r="AS15" s="110"/>
-      <c r="AT15" s="110"/>
-      <c r="AU15" s="110"/>
-      <c r="AV15" s="110"/>
-      <c r="AW15" s="110"/>
-      <c r="AX15" s="110"/>
-      <c r="AY15" s="110"/>
-      <c r="AZ15" s="110"/>
-      <c r="BA15" s="110"/>
-      <c r="BB15" s="110"/>
-      <c r="BC15" s="110"/>
-      <c r="BD15" s="110"/>
-      <c r="BE15" s="110"/>
-      <c r="BF15" s="110"/>
-      <c r="BG15" s="110"/>
-      <c r="BH15" s="110"/>
-      <c r="BI15" s="110"/>
-      <c r="BJ15" s="110"/>
-      <c r="BK15" s="110"/>
-      <c r="BL15" s="110"/>
-      <c r="BM15" s="110"/>
-      <c r="BN15" s="110"/>
-      <c r="BO15" s="110"/>
-      <c r="BP15" s="110"/>
-      <c r="BQ15" s="110"/>
-      <c r="BR15" s="110"/>
-      <c r="BS15" s="110"/>
-      <c r="BT15" s="110"/>
-      <c r="BU15" s="110"/>
-      <c r="BV15" s="110"/>
-      <c r="BW15" s="110"/>
-      <c r="BX15" s="110"/>
-      <c r="BY15" s="110"/>
-      <c r="BZ15" s="110"/>
-      <c r="CA15" s="110"/>
-      <c r="CB15" s="110"/>
-      <c r="CC15" s="110"/>
-      <c r="CD15" s="110"/>
-      <c r="CE15" s="110"/>
-      <c r="CF15" s="110"/>
-      <c r="CG15" s="110"/>
-      <c r="CH15" s="110"/>
-      <c r="CI15" s="110"/>
-      <c r="CJ15" s="110"/>
-      <c r="CK15" s="110"/>
-      <c r="CL15" s="110"/>
-      <c r="CM15" s="110"/>
-      <c r="CN15" s="110"/>
-      <c r="CO15" s="110"/>
-      <c r="CP15" s="110"/>
-      <c r="CQ15" s="110"/>
-      <c r="CR15" s="110"/>
-      <c r="CS15" s="110"/>
-      <c r="CT15" s="102"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="40"/>
+      <c r="AB15" s="40"/>
+      <c r="AC15" s="40"/>
+      <c r="AD15" s="40"/>
+      <c r="AE15" s="40"/>
+      <c r="AF15" s="40"/>
+      <c r="AG15" s="40"/>
+      <c r="AH15" s="40"/>
+      <c r="AI15" s="40"/>
+      <c r="AJ15" s="40"/>
+      <c r="AK15" s="40"/>
+      <c r="AL15" s="40"/>
+      <c r="AM15" s="40"/>
+      <c r="AN15" s="40"/>
+      <c r="AO15" s="40"/>
+      <c r="AP15" s="40"/>
+      <c r="AQ15" s="40"/>
+      <c r="AR15" s="40"/>
+      <c r="AS15" s="40"/>
+      <c r="AT15" s="40"/>
+      <c r="AU15" s="40"/>
+      <c r="AV15" s="40"/>
+      <c r="AW15" s="40"/>
+      <c r="AX15" s="40"/>
+      <c r="AY15" s="40"/>
+      <c r="AZ15" s="40"/>
+      <c r="BA15" s="40"/>
+      <c r="BB15" s="40"/>
+      <c r="BC15" s="40"/>
+      <c r="BD15" s="40"/>
+      <c r="BE15" s="40"/>
+      <c r="BF15" s="40"/>
+      <c r="BG15" s="40"/>
+      <c r="BH15" s="40"/>
+      <c r="BI15" s="40"/>
+      <c r="BJ15" s="40"/>
+      <c r="BK15" s="40"/>
+      <c r="BL15" s="40"/>
+      <c r="BM15" s="40"/>
+      <c r="BN15" s="40"/>
+      <c r="BO15" s="40"/>
+      <c r="BP15" s="40"/>
+      <c r="BQ15" s="40"/>
+      <c r="BR15" s="40"/>
+      <c r="BS15" s="40"/>
+      <c r="BT15" s="40"/>
+      <c r="BU15" s="40"/>
+      <c r="BV15" s="40"/>
+      <c r="BW15" s="40"/>
+      <c r="BX15" s="40"/>
+      <c r="BY15" s="40"/>
+      <c r="BZ15" s="40"/>
+      <c r="CA15" s="40"/>
+      <c r="CB15" s="40"/>
+      <c r="CC15" s="40"/>
+      <c r="CD15" s="40"/>
+      <c r="CE15" s="40"/>
+      <c r="CF15" s="40"/>
+      <c r="CG15" s="40"/>
+      <c r="CH15" s="40"/>
+      <c r="CI15" s="40"/>
+      <c r="CJ15" s="40"/>
+      <c r="CK15" s="40"/>
+      <c r="CL15" s="40"/>
+      <c r="CM15" s="40"/>
+      <c r="CN15" s="40"/>
+      <c r="CO15" s="40"/>
+      <c r="CP15" s="40"/>
+      <c r="CQ15" s="40"/>
+      <c r="CR15" s="40"/>
+      <c r="CS15" s="40"/>
+      <c r="CT15" s="33"/>
     </row>
     <row r="16" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="121" t="s">
+      <c r="B16" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="123"/>
-      <c r="D16" s="124">
+      <c r="C16" s="53"/>
+      <c r="D16" s="54">
         <v>1</v>
       </c>
-      <c r="E16" s="125">
+      <c r="E16" s="55">
         <v>46253</v>
       </c>
-      <c r="F16" s="117">
+      <c r="F16" s="47">
         <v>46253</v>
       </c>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="110"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110"/>
-      <c r="M16" s="110"/>
-      <c r="N16" s="110"/>
-      <c r="O16" s="110"/>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="110"/>
-      <c r="R16" s="110"/>
-      <c r="S16" s="110"/>
-      <c r="T16" s="110"/>
-      <c r="U16" s="110"/>
-      <c r="V16" s="110"/>
-      <c r="W16" s="110"/>
-      <c r="X16" s="110"/>
-      <c r="Y16" s="110"/>
-      <c r="Z16" s="110"/>
-      <c r="AA16" s="110"/>
-      <c r="AB16" s="110"/>
-      <c r="AC16" s="110"/>
-      <c r="AD16" s="110"/>
-      <c r="AE16" s="110"/>
-      <c r="AF16" s="110"/>
-      <c r="AG16" s="110"/>
-      <c r="AH16" s="110"/>
-      <c r="AI16" s="110"/>
-      <c r="AJ16" s="110"/>
-      <c r="AK16" s="110"/>
-      <c r="AL16" s="110"/>
-      <c r="AM16" s="110"/>
-      <c r="AN16" s="110"/>
-      <c r="AO16" s="110"/>
-      <c r="AP16" s="110"/>
-      <c r="AQ16" s="110"/>
-      <c r="AR16" s="110"/>
-      <c r="AS16" s="110"/>
-      <c r="AT16" s="110"/>
-      <c r="AU16" s="110"/>
-      <c r="AV16" s="110"/>
-      <c r="AW16" s="110"/>
-      <c r="AX16" s="110"/>
-      <c r="AY16" s="110"/>
-      <c r="AZ16" s="110"/>
-      <c r="BA16" s="110"/>
-      <c r="BB16" s="110"/>
-      <c r="BC16" s="110"/>
-      <c r="BD16" s="110"/>
-      <c r="BE16" s="110"/>
-      <c r="BF16" s="110"/>
-      <c r="BG16" s="110"/>
-      <c r="BH16" s="110"/>
-      <c r="BI16" s="110"/>
-      <c r="BJ16" s="110"/>
-      <c r="BK16" s="110"/>
-      <c r="BL16" s="110"/>
-      <c r="BM16" s="110"/>
-      <c r="BN16" s="110"/>
-      <c r="BO16" s="110"/>
-      <c r="BP16" s="110"/>
-      <c r="BQ16" s="110"/>
-      <c r="BR16" s="110"/>
-      <c r="BS16" s="110"/>
-      <c r="BT16" s="110"/>
-      <c r="BU16" s="110"/>
-      <c r="BV16" s="110"/>
-      <c r="BW16" s="110"/>
-      <c r="BX16" s="110"/>
-      <c r="BY16" s="110"/>
-      <c r="BZ16" s="110"/>
-      <c r="CA16" s="110"/>
-      <c r="CB16" s="110"/>
-      <c r="CC16" s="110"/>
-      <c r="CD16" s="110"/>
-      <c r="CE16" s="110"/>
-      <c r="CF16" s="110"/>
-      <c r="CG16" s="110"/>
-      <c r="CH16" s="110"/>
-      <c r="CI16" s="110"/>
-      <c r="CJ16" s="110"/>
-      <c r="CK16" s="110"/>
-      <c r="CL16" s="110"/>
-      <c r="CM16" s="110"/>
-      <c r="CN16" s="110"/>
-      <c r="CO16" s="110"/>
-      <c r="CP16" s="110"/>
-      <c r="CQ16" s="110"/>
-      <c r="CR16" s="110"/>
-      <c r="CS16" s="110"/>
-      <c r="CT16" s="102"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="40"/>
+      <c r="W16" s="40"/>
+      <c r="X16" s="40"/>
+      <c r="Y16" s="40"/>
+      <c r="Z16" s="40"/>
+      <c r="AA16" s="40"/>
+      <c r="AB16" s="40"/>
+      <c r="AC16" s="40"/>
+      <c r="AD16" s="40"/>
+      <c r="AE16" s="40"/>
+      <c r="AF16" s="40"/>
+      <c r="AG16" s="40"/>
+      <c r="AH16" s="40"/>
+      <c r="AI16" s="40"/>
+      <c r="AJ16" s="40"/>
+      <c r="AK16" s="40"/>
+      <c r="AL16" s="40"/>
+      <c r="AM16" s="40"/>
+      <c r="AN16" s="40"/>
+      <c r="AO16" s="40"/>
+      <c r="AP16" s="40"/>
+      <c r="AQ16" s="40"/>
+      <c r="AR16" s="40"/>
+      <c r="AS16" s="40"/>
+      <c r="AT16" s="40"/>
+      <c r="AU16" s="40"/>
+      <c r="AV16" s="40"/>
+      <c r="AW16" s="40"/>
+      <c r="AX16" s="40"/>
+      <c r="AY16" s="40"/>
+      <c r="AZ16" s="40"/>
+      <c r="BA16" s="40"/>
+      <c r="BB16" s="40"/>
+      <c r="BC16" s="40"/>
+      <c r="BD16" s="40"/>
+      <c r="BE16" s="40"/>
+      <c r="BF16" s="40"/>
+      <c r="BG16" s="40"/>
+      <c r="BH16" s="40"/>
+      <c r="BI16" s="40"/>
+      <c r="BJ16" s="40"/>
+      <c r="BK16" s="40"/>
+      <c r="BL16" s="40"/>
+      <c r="BM16" s="40"/>
+      <c r="BN16" s="40"/>
+      <c r="BO16" s="40"/>
+      <c r="BP16" s="40"/>
+      <c r="BQ16" s="40"/>
+      <c r="BR16" s="40"/>
+      <c r="BS16" s="40"/>
+      <c r="BT16" s="40"/>
+      <c r="BU16" s="40"/>
+      <c r="BV16" s="40"/>
+      <c r="BW16" s="40"/>
+      <c r="BX16" s="40"/>
+      <c r="BY16" s="40"/>
+      <c r="BZ16" s="40"/>
+      <c r="CA16" s="40"/>
+      <c r="CB16" s="40"/>
+      <c r="CC16" s="40"/>
+      <c r="CD16" s="40"/>
+      <c r="CE16" s="40"/>
+      <c r="CF16" s="40"/>
+      <c r="CG16" s="40"/>
+      <c r="CH16" s="40"/>
+      <c r="CI16" s="40"/>
+      <c r="CJ16" s="40"/>
+      <c r="CK16" s="40"/>
+      <c r="CL16" s="40"/>
+      <c r="CM16" s="40"/>
+      <c r="CN16" s="40"/>
+      <c r="CO16" s="40"/>
+      <c r="CP16" s="40"/>
+      <c r="CQ16" s="40"/>
+      <c r="CR16" s="40"/>
+      <c r="CS16" s="40"/>
+      <c r="CT16" s="33"/>
     </row>
     <row r="17" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="121" t="s">
+      <c r="B17" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="123"/>
-      <c r="D17" s="124">
+      <c r="C17" s="53"/>
+      <c r="D17" s="54">
         <v>4</v>
       </c>
-      <c r="E17" s="125">
+      <c r="E17" s="55">
         <v>46254</v>
       </c>
-      <c r="F17" s="117">
+      <c r="F17" s="47">
         <v>46257</v>
       </c>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="110"/>
-      <c r="M17" s="110"/>
-      <c r="N17" s="110"/>
-      <c r="O17" s="110"/>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="110"/>
-      <c r="R17" s="110"/>
-      <c r="S17" s="110"/>
-      <c r="T17" s="110"/>
-      <c r="U17" s="110"/>
-      <c r="V17" s="110"/>
-      <c r="W17" s="110"/>
-      <c r="X17" s="110"/>
-      <c r="Y17" s="110"/>
-      <c r="Z17" s="110"/>
-      <c r="AA17" s="110"/>
-      <c r="AB17" s="110"/>
-      <c r="AC17" s="110"/>
-      <c r="AD17" s="110"/>
-      <c r="AE17" s="110"/>
-      <c r="AF17" s="110"/>
-      <c r="AG17" s="110"/>
-      <c r="AH17" s="110"/>
-      <c r="AI17" s="110"/>
-      <c r="AJ17" s="110"/>
-      <c r="AK17" s="110"/>
-      <c r="AL17" s="110"/>
-      <c r="AM17" s="110"/>
-      <c r="AN17" s="110"/>
-      <c r="AO17" s="110"/>
-      <c r="AP17" s="110"/>
-      <c r="AQ17" s="110"/>
-      <c r="AR17" s="110"/>
-      <c r="AS17" s="110"/>
-      <c r="AT17" s="110"/>
-      <c r="AU17" s="110"/>
-      <c r="AV17" s="110"/>
-      <c r="AW17" s="110"/>
-      <c r="AX17" s="110"/>
-      <c r="AY17" s="110"/>
-      <c r="AZ17" s="110"/>
-      <c r="BA17" s="110"/>
-      <c r="BB17" s="110"/>
-      <c r="BC17" s="110"/>
-      <c r="BD17" s="110"/>
-      <c r="BE17" s="110"/>
-      <c r="BF17" s="110"/>
-      <c r="BG17" s="110"/>
-      <c r="BH17" s="110"/>
-      <c r="BI17" s="110"/>
-      <c r="BJ17" s="110"/>
-      <c r="BK17" s="110"/>
-      <c r="BL17" s="110"/>
-      <c r="BM17" s="110"/>
-      <c r="BN17" s="110"/>
-      <c r="BO17" s="110"/>
-      <c r="BP17" s="110"/>
-      <c r="BQ17" s="110"/>
-      <c r="BR17" s="110"/>
-      <c r="BS17" s="110"/>
-      <c r="BT17" s="110"/>
-      <c r="BU17" s="110"/>
-      <c r="BV17" s="110"/>
-      <c r="BW17" s="110"/>
-      <c r="BX17" s="110"/>
-      <c r="BY17" s="110"/>
-      <c r="BZ17" s="110"/>
-      <c r="CA17" s="110"/>
-      <c r="CB17" s="110"/>
-      <c r="CC17" s="110"/>
-      <c r="CD17" s="110"/>
-      <c r="CE17" s="110"/>
-      <c r="CF17" s="110"/>
-      <c r="CG17" s="110"/>
-      <c r="CH17" s="110"/>
-      <c r="CI17" s="110"/>
-      <c r="CJ17" s="110"/>
-      <c r="CK17" s="110"/>
-      <c r="CL17" s="110"/>
-      <c r="CM17" s="110"/>
-      <c r="CN17" s="110"/>
-      <c r="CO17" s="110"/>
-      <c r="CP17" s="110"/>
-      <c r="CQ17" s="110"/>
-      <c r="CR17" s="110"/>
-      <c r="CS17" s="110"/>
-      <c r="CT17" s="102"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="40"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="40"/>
+      <c r="Y17" s="40"/>
+      <c r="Z17" s="40"/>
+      <c r="AA17" s="40"/>
+      <c r="AB17" s="40"/>
+      <c r="AC17" s="40"/>
+      <c r="AD17" s="40"/>
+      <c r="AE17" s="40"/>
+      <c r="AF17" s="40"/>
+      <c r="AG17" s="40"/>
+      <c r="AH17" s="40"/>
+      <c r="AI17" s="40"/>
+      <c r="AJ17" s="40"/>
+      <c r="AK17" s="40"/>
+      <c r="AL17" s="40"/>
+      <c r="AM17" s="40"/>
+      <c r="AN17" s="40"/>
+      <c r="AO17" s="40"/>
+      <c r="AP17" s="40"/>
+      <c r="AQ17" s="40"/>
+      <c r="AR17" s="40"/>
+      <c r="AS17" s="40"/>
+      <c r="AT17" s="40"/>
+      <c r="AU17" s="40"/>
+      <c r="AV17" s="40"/>
+      <c r="AW17" s="40"/>
+      <c r="AX17" s="40"/>
+      <c r="AY17" s="40"/>
+      <c r="AZ17" s="40"/>
+      <c r="BA17" s="40"/>
+      <c r="BB17" s="40"/>
+      <c r="BC17" s="40"/>
+      <c r="BD17" s="40"/>
+      <c r="BE17" s="40"/>
+      <c r="BF17" s="40"/>
+      <c r="BG17" s="40"/>
+      <c r="BH17" s="40"/>
+      <c r="BI17" s="40"/>
+      <c r="BJ17" s="40"/>
+      <c r="BK17" s="40"/>
+      <c r="BL17" s="40"/>
+      <c r="BM17" s="40"/>
+      <c r="BN17" s="40"/>
+      <c r="BO17" s="40"/>
+      <c r="BP17" s="40"/>
+      <c r="BQ17" s="40"/>
+      <c r="BR17" s="40"/>
+      <c r="BS17" s="40"/>
+      <c r="BT17" s="40"/>
+      <c r="BU17" s="40"/>
+      <c r="BV17" s="40"/>
+      <c r="BW17" s="40"/>
+      <c r="BX17" s="40"/>
+      <c r="BY17" s="40"/>
+      <c r="BZ17" s="40"/>
+      <c r="CA17" s="40"/>
+      <c r="CB17" s="40"/>
+      <c r="CC17" s="40"/>
+      <c r="CD17" s="40"/>
+      <c r="CE17" s="40"/>
+      <c r="CF17" s="40"/>
+      <c r="CG17" s="40"/>
+      <c r="CH17" s="40"/>
+      <c r="CI17" s="40"/>
+      <c r="CJ17" s="40"/>
+      <c r="CK17" s="40"/>
+      <c r="CL17" s="40"/>
+      <c r="CM17" s="40"/>
+      <c r="CN17" s="40"/>
+      <c r="CO17" s="40"/>
+      <c r="CP17" s="40"/>
+      <c r="CQ17" s="40"/>
+      <c r="CR17" s="40"/>
+      <c r="CS17" s="40"/>
+      <c r="CT17" s="33"/>
     </row>
     <row r="18" spans="2:98" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="121" t="s">
+      <c r="B18" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="123"/>
-      <c r="D18" s="124">
+      <c r="C18" s="53"/>
+      <c r="D18" s="54">
         <v>1</v>
       </c>
-      <c r="E18" s="125">
+      <c r="E18" s="55">
         <v>46258</v>
       </c>
-      <c r="F18" s="117">
+      <c r="F18" s="47">
         <v>46258</v>
       </c>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="110"/>
-      <c r="M18" s="110"/>
-      <c r="N18" s="110"/>
-      <c r="O18" s="110"/>
-      <c r="P18" s="110"/>
-      <c r="Q18" s="110"/>
-      <c r="R18" s="110"/>
-      <c r="S18" s="110"/>
-      <c r="T18" s="110"/>
-      <c r="U18" s="110"/>
-      <c r="V18" s="110"/>
-      <c r="W18" s="110"/>
-      <c r="X18" s="110"/>
-      <c r="Y18" s="110"/>
-      <c r="Z18" s="110"/>
-      <c r="AA18" s="110"/>
-      <c r="AB18" s="110"/>
-      <c r="AC18" s="110"/>
-      <c r="AD18" s="110"/>
-      <c r="AE18" s="110"/>
-      <c r="AF18" s="110"/>
-      <c r="AG18" s="110"/>
-      <c r="AH18" s="110"/>
-      <c r="AI18" s="110"/>
-      <c r="AJ18" s="110"/>
-      <c r="AK18" s="110"/>
-      <c r="AL18" s="110"/>
-      <c r="AM18" s="110"/>
-      <c r="AN18" s="110"/>
-      <c r="AO18" s="110"/>
-      <c r="AP18" s="110"/>
-      <c r="AQ18" s="110"/>
-      <c r="AR18" s="110"/>
-      <c r="AS18" s="110"/>
-      <c r="AT18" s="110"/>
-      <c r="AU18" s="110"/>
-      <c r="AV18" s="110"/>
-      <c r="AW18" s="110"/>
-      <c r="AX18" s="110"/>
-      <c r="AY18" s="110"/>
-      <c r="AZ18" s="110"/>
-      <c r="BA18" s="110"/>
-      <c r="BB18" s="110"/>
-      <c r="BC18" s="110"/>
-      <c r="BD18" s="110"/>
-      <c r="BE18" s="110"/>
-      <c r="BF18" s="110"/>
-      <c r="BG18" s="110"/>
-      <c r="BH18" s="110"/>
-      <c r="BI18" s="110"/>
-      <c r="BJ18" s="110"/>
-      <c r="BK18" s="110"/>
-      <c r="BL18" s="110"/>
-      <c r="BM18" s="110"/>
-      <c r="BN18" s="110"/>
-      <c r="BO18" s="110"/>
-      <c r="BP18" s="110"/>
-      <c r="BQ18" s="110"/>
-      <c r="BR18" s="110"/>
-      <c r="BS18" s="110"/>
-      <c r="BT18" s="110"/>
-      <c r="BU18" s="110"/>
-      <c r="BV18" s="110"/>
-      <c r="BW18" s="110"/>
-      <c r="BX18" s="110"/>
-      <c r="BY18" s="110"/>
-      <c r="BZ18" s="110"/>
-      <c r="CA18" s="110"/>
-      <c r="CB18" s="110"/>
-      <c r="CC18" s="110"/>
-      <c r="CD18" s="110"/>
-      <c r="CE18" s="110"/>
-      <c r="CF18" s="110"/>
-      <c r="CG18" s="110"/>
-      <c r="CH18" s="110"/>
-      <c r="CI18" s="110"/>
-      <c r="CJ18" s="110"/>
-      <c r="CK18" s="110"/>
-      <c r="CL18" s="110"/>
-      <c r="CM18" s="110"/>
-      <c r="CN18" s="110"/>
-      <c r="CO18" s="110"/>
-      <c r="CP18" s="110"/>
-      <c r="CQ18" s="110"/>
-      <c r="CR18" s="110"/>
-      <c r="CS18" s="110"/>
-      <c r="CT18" s="102"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="40"/>
+      <c r="S18" s="40"/>
+      <c r="T18" s="40"/>
+      <c r="U18" s="40"/>
+      <c r="V18" s="40"/>
+      <c r="W18" s="40"/>
+      <c r="X18" s="40"/>
+      <c r="Y18" s="40"/>
+      <c r="Z18" s="40"/>
+      <c r="AA18" s="40"/>
+      <c r="AB18" s="40"/>
+      <c r="AC18" s="40"/>
+      <c r="AD18" s="40"/>
+      <c r="AE18" s="40"/>
+      <c r="AF18" s="40"/>
+      <c r="AG18" s="40"/>
+      <c r="AH18" s="40"/>
+      <c r="AI18" s="40"/>
+      <c r="AJ18" s="40"/>
+      <c r="AK18" s="40"/>
+      <c r="AL18" s="40"/>
+      <c r="AM18" s="40"/>
+      <c r="AN18" s="40"/>
+      <c r="AO18" s="40"/>
+      <c r="AP18" s="40"/>
+      <c r="AQ18" s="40"/>
+      <c r="AR18" s="40"/>
+      <c r="AS18" s="40"/>
+      <c r="AT18" s="40"/>
+      <c r="AU18" s="40"/>
+      <c r="AV18" s="40"/>
+      <c r="AW18" s="40"/>
+      <c r="AX18" s="40"/>
+      <c r="AY18" s="40"/>
+      <c r="AZ18" s="40"/>
+      <c r="BA18" s="40"/>
+      <c r="BB18" s="40"/>
+      <c r="BC18" s="40"/>
+      <c r="BD18" s="40"/>
+      <c r="BE18" s="40"/>
+      <c r="BF18" s="40"/>
+      <c r="BG18" s="40"/>
+      <c r="BH18" s="40"/>
+      <c r="BI18" s="40"/>
+      <c r="BJ18" s="40"/>
+      <c r="BK18" s="40"/>
+      <c r="BL18" s="40"/>
+      <c r="BM18" s="40"/>
+      <c r="BN18" s="40"/>
+      <c r="BO18" s="40"/>
+      <c r="BP18" s="40"/>
+      <c r="BQ18" s="40"/>
+      <c r="BR18" s="40"/>
+      <c r="BS18" s="40"/>
+      <c r="BT18" s="40"/>
+      <c r="BU18" s="40"/>
+      <c r="BV18" s="40"/>
+      <c r="BW18" s="40"/>
+      <c r="BX18" s="40"/>
+      <c r="BY18" s="40"/>
+      <c r="BZ18" s="40"/>
+      <c r="CA18" s="40"/>
+      <c r="CB18" s="40"/>
+      <c r="CC18" s="40"/>
+      <c r="CD18" s="40"/>
+      <c r="CE18" s="40"/>
+      <c r="CF18" s="40"/>
+      <c r="CG18" s="40"/>
+      <c r="CH18" s="40"/>
+      <c r="CI18" s="40"/>
+      <c r="CJ18" s="40"/>
+      <c r="CK18" s="40"/>
+      <c r="CL18" s="40"/>
+      <c r="CM18" s="40"/>
+      <c r="CN18" s="40"/>
+      <c r="CO18" s="40"/>
+      <c r="CP18" s="40"/>
+      <c r="CQ18" s="40"/>
+      <c r="CR18" s="40"/>
+      <c r="CS18" s="40"/>
+      <c r="CT18" s="33"/>
     </row>
     <row r="19" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="121" t="s">
+      <c r="B19" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="123"/>
-      <c r="D19" s="124">
+      <c r="C19" s="53"/>
+      <c r="D19" s="54">
         <v>1</v>
       </c>
-      <c r="E19" s="125">
+      <c r="E19" s="55">
         <v>46259</v>
       </c>
-      <c r="F19" s="117">
+      <c r="F19" s="47">
         <v>46259</v>
       </c>
-      <c r="G19" s="110"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="110"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="110"/>
-      <c r="U19" s="110"/>
-      <c r="V19" s="110"/>
-      <c r="W19" s="110"/>
-      <c r="X19" s="110"/>
-      <c r="Y19" s="110"/>
-      <c r="Z19" s="110"/>
-      <c r="AA19" s="110"/>
-      <c r="AB19" s="110"/>
-      <c r="AC19" s="110"/>
-      <c r="AD19" s="110"/>
-      <c r="AE19" s="110"/>
-      <c r="AF19" s="110"/>
-      <c r="AG19" s="110"/>
-      <c r="AH19" s="110"/>
-      <c r="AI19" s="110"/>
-      <c r="AJ19" s="110"/>
-      <c r="AK19" s="110"/>
-      <c r="AL19" s="110"/>
-      <c r="AM19" s="110"/>
-      <c r="AN19" s="110"/>
-      <c r="AO19" s="110"/>
-      <c r="AP19" s="110"/>
-      <c r="AQ19" s="110"/>
-      <c r="AR19" s="110"/>
-      <c r="AS19" s="110"/>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
-      <c r="BA19" s="110"/>
-      <c r="BB19" s="110"/>
-      <c r="BC19" s="110"/>
-      <c r="BD19" s="110"/>
-      <c r="BE19" s="110"/>
-      <c r="BF19" s="110"/>
-      <c r="BG19" s="110"/>
-      <c r="BH19" s="110"/>
-      <c r="BI19" s="110"/>
-      <c r="BJ19" s="110"/>
-      <c r="BK19" s="110"/>
-      <c r="BL19" s="110"/>
-      <c r="BM19" s="110"/>
-      <c r="BN19" s="110"/>
-      <c r="BO19" s="110"/>
-      <c r="BP19" s="110"/>
-      <c r="BQ19" s="110"/>
-      <c r="BR19" s="110"/>
-      <c r="BS19" s="110"/>
-      <c r="BT19" s="110"/>
-      <c r="BU19" s="110"/>
-      <c r="BV19" s="110"/>
-      <c r="BW19" s="110"/>
-      <c r="BX19" s="110"/>
-      <c r="BY19" s="110"/>
-      <c r="BZ19" s="110"/>
-      <c r="CA19" s="110"/>
-      <c r="CB19" s="110"/>
-      <c r="CC19" s="110"/>
-      <c r="CD19" s="110"/>
-      <c r="CE19" s="110"/>
-      <c r="CF19" s="110"/>
-      <c r="CG19" s="110"/>
-      <c r="CH19" s="110"/>
-      <c r="CI19" s="110"/>
-      <c r="CJ19" s="110"/>
-      <c r="CK19" s="110"/>
-      <c r="CL19" s="110"/>
-      <c r="CM19" s="110"/>
-      <c r="CN19" s="110"/>
-      <c r="CO19" s="110"/>
-      <c r="CP19" s="110"/>
-      <c r="CQ19" s="110"/>
-      <c r="CR19" s="110"/>
-      <c r="CS19" s="110"/>
-      <c r="CT19" s="102"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="40"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="40"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="40"/>
+      <c r="W19" s="40"/>
+      <c r="X19" s="40"/>
+      <c r="Y19" s="40"/>
+      <c r="Z19" s="40"/>
+      <c r="AA19" s="40"/>
+      <c r="AB19" s="40"/>
+      <c r="AC19" s="40"/>
+      <c r="AD19" s="40"/>
+      <c r="AE19" s="40"/>
+      <c r="AF19" s="40"/>
+      <c r="AG19" s="40"/>
+      <c r="AH19" s="40"/>
+      <c r="AI19" s="40"/>
+      <c r="AJ19" s="40"/>
+      <c r="AK19" s="40"/>
+      <c r="AL19" s="40"/>
+      <c r="AM19" s="40"/>
+      <c r="AN19" s="40"/>
+      <c r="AO19" s="40"/>
+      <c r="AP19" s="40"/>
+      <c r="AQ19" s="40"/>
+      <c r="AR19" s="40"/>
+      <c r="AS19" s="40"/>
+      <c r="AT19" s="40"/>
+      <c r="AU19" s="40"/>
+      <c r="AV19" s="40"/>
+      <c r="AW19" s="40"/>
+      <c r="AX19" s="40"/>
+      <c r="AY19" s="40"/>
+      <c r="AZ19" s="40"/>
+      <c r="BA19" s="40"/>
+      <c r="BB19" s="40"/>
+      <c r="BC19" s="40"/>
+      <c r="BD19" s="40"/>
+      <c r="BE19" s="40"/>
+      <c r="BF19" s="40"/>
+      <c r="BG19" s="40"/>
+      <c r="BH19" s="40"/>
+      <c r="BI19" s="40"/>
+      <c r="BJ19" s="40"/>
+      <c r="BK19" s="40"/>
+      <c r="BL19" s="40"/>
+      <c r="BM19" s="40"/>
+      <c r="BN19" s="40"/>
+      <c r="BO19" s="40"/>
+      <c r="BP19" s="40"/>
+      <c r="BQ19" s="40"/>
+      <c r="BR19" s="40"/>
+      <c r="BS19" s="40"/>
+      <c r="BT19" s="40"/>
+      <c r="BU19" s="40"/>
+      <c r="BV19" s="40"/>
+      <c r="BW19" s="40"/>
+      <c r="BX19" s="40"/>
+      <c r="BY19" s="40"/>
+      <c r="BZ19" s="40"/>
+      <c r="CA19" s="40"/>
+      <c r="CB19" s="40"/>
+      <c r="CC19" s="40"/>
+      <c r="CD19" s="40"/>
+      <c r="CE19" s="40"/>
+      <c r="CF19" s="40"/>
+      <c r="CG19" s="40"/>
+      <c r="CH19" s="40"/>
+      <c r="CI19" s="40"/>
+      <c r="CJ19" s="40"/>
+      <c r="CK19" s="40"/>
+      <c r="CL19" s="40"/>
+      <c r="CM19" s="40"/>
+      <c r="CN19" s="40"/>
+      <c r="CO19" s="40"/>
+      <c r="CP19" s="40"/>
+      <c r="CQ19" s="40"/>
+      <c r="CR19" s="40"/>
+      <c r="CS19" s="40"/>
+      <c r="CT19" s="33"/>
     </row>
     <row r="20" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="121" t="s">
+      <c r="B20" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="123"/>
-      <c r="D20" s="124">
+      <c r="C20" s="53"/>
+      <c r="D20" s="54">
         <v>0.5</v>
       </c>
-      <c r="E20" s="125">
+      <c r="E20" s="55">
         <v>46260</v>
       </c>
-      <c r="F20" s="117">
+      <c r="F20" s="47">
         <v>46260</v>
       </c>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="110"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
-      <c r="U20" s="110"/>
-      <c r="V20" s="110"/>
-      <c r="W20" s="110"/>
-      <c r="X20" s="110"/>
-      <c r="Y20" s="110"/>
-      <c r="Z20" s="110"/>
-      <c r="AA20" s="110"/>
-      <c r="AB20" s="110"/>
-      <c r="AC20" s="110"/>
-      <c r="AD20" s="110"/>
-      <c r="AE20" s="110"/>
-      <c r="AF20" s="110"/>
-      <c r="AG20" s="110"/>
-      <c r="AH20" s="110"/>
-      <c r="AI20" s="110"/>
-      <c r="AJ20" s="110"/>
-      <c r="AK20" s="110"/>
-      <c r="AL20" s="110"/>
-      <c r="AM20" s="110"/>
-      <c r="AN20" s="110"/>
-      <c r="AO20" s="110"/>
-      <c r="AP20" s="110"/>
-      <c r="AQ20" s="110"/>
-      <c r="AR20" s="110"/>
-      <c r="AS20" s="110"/>
-      <c r="AT20" s="110"/>
-      <c r="AU20" s="110"/>
-      <c r="AV20" s="110"/>
-      <c r="AW20" s="110"/>
-      <c r="AX20" s="110"/>
-      <c r="AY20" s="110"/>
-      <c r="AZ20" s="110"/>
-      <c r="BA20" s="110"/>
-      <c r="BB20" s="110"/>
-      <c r="BC20" s="110"/>
-      <c r="BD20" s="110"/>
-      <c r="BE20" s="110"/>
-      <c r="BF20" s="110"/>
-      <c r="BG20" s="110"/>
-      <c r="BH20" s="110"/>
-      <c r="BI20" s="110"/>
-      <c r="BJ20" s="110"/>
-      <c r="BK20" s="110"/>
-      <c r="BL20" s="110"/>
-      <c r="BM20" s="110"/>
-      <c r="BN20" s="110"/>
-      <c r="BO20" s="110"/>
-      <c r="BP20" s="110"/>
-      <c r="BQ20" s="110"/>
-      <c r="BR20" s="110"/>
-      <c r="BS20" s="110"/>
-      <c r="BT20" s="110"/>
-      <c r="BU20" s="110"/>
-      <c r="BV20" s="110"/>
-      <c r="BW20" s="110"/>
-      <c r="BX20" s="110"/>
-      <c r="BY20" s="110"/>
-      <c r="BZ20" s="110"/>
-      <c r="CA20" s="110"/>
-      <c r="CB20" s="110"/>
-      <c r="CC20" s="110"/>
-      <c r="CD20" s="110"/>
-      <c r="CE20" s="110"/>
-      <c r="CF20" s="110"/>
-      <c r="CG20" s="110"/>
-      <c r="CH20" s="110"/>
-      <c r="CI20" s="110"/>
-      <c r="CJ20" s="110"/>
-      <c r="CK20" s="110"/>
-      <c r="CL20" s="110"/>
-      <c r="CM20" s="110"/>
-      <c r="CN20" s="110"/>
-      <c r="CO20" s="110"/>
-      <c r="CP20" s="110"/>
-      <c r="CQ20" s="110"/>
-      <c r="CR20" s="110"/>
-      <c r="CS20" s="110"/>
-      <c r="CT20" s="102"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="40"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="40"/>
+      <c r="R20" s="40"/>
+      <c r="S20" s="40"/>
+      <c r="T20" s="40"/>
+      <c r="U20" s="40"/>
+      <c r="V20" s="40"/>
+      <c r="W20" s="40"/>
+      <c r="X20" s="40"/>
+      <c r="Y20" s="40"/>
+      <c r="Z20" s="40"/>
+      <c r="AA20" s="40"/>
+      <c r="AB20" s="40"/>
+      <c r="AC20" s="40"/>
+      <c r="AD20" s="40"/>
+      <c r="AE20" s="40"/>
+      <c r="AF20" s="40"/>
+      <c r="AG20" s="40"/>
+      <c r="AH20" s="40"/>
+      <c r="AI20" s="40"/>
+      <c r="AJ20" s="40"/>
+      <c r="AK20" s="40"/>
+      <c r="AL20" s="40"/>
+      <c r="AM20" s="40"/>
+      <c r="AN20" s="40"/>
+      <c r="AO20" s="40"/>
+      <c r="AP20" s="40"/>
+      <c r="AQ20" s="40"/>
+      <c r="AR20" s="40"/>
+      <c r="AS20" s="40"/>
+      <c r="AT20" s="40"/>
+      <c r="AU20" s="40"/>
+      <c r="AV20" s="40"/>
+      <c r="AW20" s="40"/>
+      <c r="AX20" s="40"/>
+      <c r="AY20" s="40"/>
+      <c r="AZ20" s="40"/>
+      <c r="BA20" s="40"/>
+      <c r="BB20" s="40"/>
+      <c r="BC20" s="40"/>
+      <c r="BD20" s="40"/>
+      <c r="BE20" s="40"/>
+      <c r="BF20" s="40"/>
+      <c r="BG20" s="40"/>
+      <c r="BH20" s="40"/>
+      <c r="BI20" s="40"/>
+      <c r="BJ20" s="40"/>
+      <c r="BK20" s="40"/>
+      <c r="BL20" s="40"/>
+      <c r="BM20" s="40"/>
+      <c r="BN20" s="40"/>
+      <c r="BO20" s="40"/>
+      <c r="BP20" s="40"/>
+      <c r="BQ20" s="40"/>
+      <c r="BR20" s="40"/>
+      <c r="BS20" s="40"/>
+      <c r="BT20" s="40"/>
+      <c r="BU20" s="40"/>
+      <c r="BV20" s="40"/>
+      <c r="BW20" s="40"/>
+      <c r="BX20" s="40"/>
+      <c r="BY20" s="40"/>
+      <c r="BZ20" s="40"/>
+      <c r="CA20" s="40"/>
+      <c r="CB20" s="40"/>
+      <c r="CC20" s="40"/>
+      <c r="CD20" s="40"/>
+      <c r="CE20" s="40"/>
+      <c r="CF20" s="40"/>
+      <c r="CG20" s="40"/>
+      <c r="CH20" s="40"/>
+      <c r="CI20" s="40"/>
+      <c r="CJ20" s="40"/>
+      <c r="CK20" s="40"/>
+      <c r="CL20" s="40"/>
+      <c r="CM20" s="40"/>
+      <c r="CN20" s="40"/>
+      <c r="CO20" s="40"/>
+      <c r="CP20" s="40"/>
+      <c r="CQ20" s="40"/>
+      <c r="CR20" s="40"/>
+      <c r="CS20" s="40"/>
+      <c r="CT20" s="33"/>
     </row>
     <row r="21" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="121" t="s">
+      <c r="B21" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="123"/>
-      <c r="D21" s="124">
+      <c r="C21" s="53"/>
+      <c r="D21" s="54">
         <v>1</v>
       </c>
-      <c r="E21" s="125">
+      <c r="E21" s="55">
         <v>46260</v>
       </c>
-      <c r="F21" s="117">
+      <c r="F21" s="47">
         <v>46260</v>
       </c>
-      <c r="G21" s="110"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="110"/>
-      <c r="J21" s="110"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="110"/>
-      <c r="M21" s="110"/>
-      <c r="N21" s="110"/>
-      <c r="O21" s="110"/>
-      <c r="P21" s="110"/>
-      <c r="Q21" s="110"/>
-      <c r="R21" s="110"/>
-      <c r="S21" s="110"/>
-      <c r="T21" s="110"/>
-      <c r="U21" s="110"/>
-      <c r="V21" s="110"/>
-      <c r="W21" s="110"/>
-      <c r="X21" s="110"/>
-      <c r="Y21" s="110"/>
-      <c r="Z21" s="110"/>
-      <c r="AA21" s="110"/>
-      <c r="AB21" s="110"/>
-      <c r="AC21" s="110"/>
-      <c r="AD21" s="110"/>
-      <c r="AE21" s="110"/>
-      <c r="AF21" s="110"/>
-      <c r="AG21" s="110"/>
-      <c r="AH21" s="110"/>
-      <c r="AI21" s="110"/>
-      <c r="AJ21" s="110"/>
-      <c r="AK21" s="110"/>
-      <c r="AL21" s="110"/>
-      <c r="AM21" s="110"/>
-      <c r="AN21" s="110"/>
-      <c r="AO21" s="110"/>
-      <c r="AP21" s="110"/>
-      <c r="AQ21" s="110"/>
-      <c r="AR21" s="110"/>
-      <c r="AS21" s="110"/>
-      <c r="AT21" s="110"/>
-      <c r="AU21" s="110"/>
-      <c r="AV21" s="110"/>
-      <c r="AW21" s="110"/>
-      <c r="AX21" s="110"/>
-      <c r="AY21" s="110"/>
-      <c r="AZ21" s="110"/>
-      <c r="BA21" s="110"/>
-      <c r="BB21" s="110"/>
-      <c r="BC21" s="110"/>
-      <c r="BD21" s="110"/>
-      <c r="BE21" s="110"/>
-      <c r="BF21" s="110"/>
-      <c r="BG21" s="110"/>
-      <c r="BH21" s="110"/>
-      <c r="BI21" s="110"/>
-      <c r="BJ21" s="110"/>
-      <c r="BK21" s="110"/>
-      <c r="BL21" s="110"/>
-      <c r="BM21" s="110"/>
-      <c r="BN21" s="110"/>
-      <c r="BO21" s="110"/>
-      <c r="BP21" s="110"/>
-      <c r="BQ21" s="110"/>
-      <c r="BR21" s="110"/>
-      <c r="BS21" s="110"/>
-      <c r="BT21" s="110"/>
-      <c r="BU21" s="110"/>
-      <c r="BV21" s="110"/>
-      <c r="BW21" s="110"/>
-      <c r="BX21" s="110"/>
-      <c r="BY21" s="110"/>
-      <c r="BZ21" s="110"/>
-      <c r="CA21" s="110"/>
-      <c r="CB21" s="110"/>
-      <c r="CC21" s="110"/>
-      <c r="CD21" s="110"/>
-      <c r="CE21" s="110"/>
-      <c r="CF21" s="110"/>
-      <c r="CG21" s="110"/>
-      <c r="CH21" s="110"/>
-      <c r="CI21" s="110"/>
-      <c r="CJ21" s="110"/>
-      <c r="CK21" s="110"/>
-      <c r="CL21" s="110"/>
-      <c r="CM21" s="110"/>
-      <c r="CN21" s="110"/>
-      <c r="CO21" s="110"/>
-      <c r="CP21" s="110"/>
-      <c r="CQ21" s="110"/>
-      <c r="CR21" s="110"/>
-      <c r="CS21" s="110"/>
-      <c r="CT21" s="102"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="40"/>
+      <c r="S21" s="40"/>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="40"/>
+      <c r="X21" s="40"/>
+      <c r="Y21" s="40"/>
+      <c r="Z21" s="40"/>
+      <c r="AA21" s="40"/>
+      <c r="AB21" s="40"/>
+      <c r="AC21" s="40"/>
+      <c r="AD21" s="40"/>
+      <c r="AE21" s="40"/>
+      <c r="AF21" s="40"/>
+      <c r="AG21" s="40"/>
+      <c r="AH21" s="40"/>
+      <c r="AI21" s="40"/>
+      <c r="AJ21" s="40"/>
+      <c r="AK21" s="40"/>
+      <c r="AL21" s="40"/>
+      <c r="AM21" s="40"/>
+      <c r="AN21" s="40"/>
+      <c r="AO21" s="40"/>
+      <c r="AP21" s="40"/>
+      <c r="AQ21" s="40"/>
+      <c r="AR21" s="40"/>
+      <c r="AS21" s="40"/>
+      <c r="AT21" s="40"/>
+      <c r="AU21" s="40"/>
+      <c r="AV21" s="40"/>
+      <c r="AW21" s="40"/>
+      <c r="AX21" s="40"/>
+      <c r="AY21" s="40"/>
+      <c r="AZ21" s="40"/>
+      <c r="BA21" s="40"/>
+      <c r="BB21" s="40"/>
+      <c r="BC21" s="40"/>
+      <c r="BD21" s="40"/>
+      <c r="BE21" s="40"/>
+      <c r="BF21" s="40"/>
+      <c r="BG21" s="40"/>
+      <c r="BH21" s="40"/>
+      <c r="BI21" s="40"/>
+      <c r="BJ21" s="40"/>
+      <c r="BK21" s="40"/>
+      <c r="BL21" s="40"/>
+      <c r="BM21" s="40"/>
+      <c r="BN21" s="40"/>
+      <c r="BO21" s="40"/>
+      <c r="BP21" s="40"/>
+      <c r="BQ21" s="40"/>
+      <c r="BR21" s="40"/>
+      <c r="BS21" s="40"/>
+      <c r="BT21" s="40"/>
+      <c r="BU21" s="40"/>
+      <c r="BV21" s="40"/>
+      <c r="BW21" s="40"/>
+      <c r="BX21" s="40"/>
+      <c r="BY21" s="40"/>
+      <c r="BZ21" s="40"/>
+      <c r="CA21" s="40"/>
+      <c r="CB21" s="40"/>
+      <c r="CC21" s="40"/>
+      <c r="CD21" s="40"/>
+      <c r="CE21" s="40"/>
+      <c r="CF21" s="40"/>
+      <c r="CG21" s="40"/>
+      <c r="CH21" s="40"/>
+      <c r="CI21" s="40"/>
+      <c r="CJ21" s="40"/>
+      <c r="CK21" s="40"/>
+      <c r="CL21" s="40"/>
+      <c r="CM21" s="40"/>
+      <c r="CN21" s="40"/>
+      <c r="CO21" s="40"/>
+      <c r="CP21" s="40"/>
+      <c r="CQ21" s="40"/>
+      <c r="CR21" s="40"/>
+      <c r="CS21" s="40"/>
+      <c r="CT21" s="33"/>
     </row>
     <row r="22" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="121" t="s">
+      <c r="B22" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="123"/>
-      <c r="D22" s="124">
+      <c r="C22" s="53"/>
+      <c r="D22" s="54">
         <v>0</v>
       </c>
-      <c r="E22" s="125">
+      <c r="E22" s="55">
         <v>46260</v>
       </c>
-      <c r="F22" s="117">
+      <c r="F22" s="47">
         <v>46260</v>
       </c>
-      <c r="G22" s="110"/>
-      <c r="H22" s="110"/>
-      <c r="I22" s="110"/>
-      <c r="J22" s="110"/>
-      <c r="K22" s="110"/>
-      <c r="L22" s="110"/>
-      <c r="M22" s="110"/>
-      <c r="N22" s="110"/>
-      <c r="O22" s="110"/>
-      <c r="P22" s="110"/>
-      <c r="Q22" s="110"/>
-      <c r="R22" s="110"/>
-      <c r="S22" s="110"/>
-      <c r="T22" s="110"/>
-      <c r="U22" s="110"/>
-      <c r="V22" s="110"/>
-      <c r="W22" s="110"/>
-      <c r="X22" s="110"/>
-      <c r="Y22" s="110"/>
-      <c r="Z22" s="110"/>
-      <c r="AA22" s="110"/>
-      <c r="AB22" s="110"/>
-      <c r="AC22" s="110"/>
-      <c r="AD22" s="110"/>
-      <c r="AE22" s="110"/>
-      <c r="AF22" s="110"/>
-      <c r="AG22" s="110"/>
-      <c r="AH22" s="110"/>
-      <c r="AI22" s="110"/>
-      <c r="AJ22" s="110"/>
-      <c r="AK22" s="110"/>
-      <c r="AL22" s="110"/>
-      <c r="AM22" s="110"/>
-      <c r="AN22" s="110"/>
-      <c r="AO22" s="110"/>
-      <c r="AP22" s="110"/>
-      <c r="AQ22" s="110"/>
-      <c r="AR22" s="110"/>
-      <c r="AS22" s="110"/>
-      <c r="AT22" s="110"/>
-      <c r="AU22" s="110"/>
-      <c r="AV22" s="110"/>
-      <c r="AW22" s="110"/>
-      <c r="AX22" s="110"/>
-      <c r="AY22" s="110"/>
-      <c r="AZ22" s="110"/>
-      <c r="BA22" s="110"/>
-      <c r="BB22" s="110"/>
-      <c r="BC22" s="110"/>
-      <c r="BD22" s="110"/>
-      <c r="BE22" s="110"/>
-      <c r="BF22" s="110"/>
-      <c r="BG22" s="110"/>
-      <c r="BH22" s="110"/>
-      <c r="BI22" s="110"/>
-      <c r="BJ22" s="110"/>
-      <c r="BK22" s="110"/>
-      <c r="BL22" s="110"/>
-      <c r="BM22" s="110"/>
-      <c r="BN22" s="110"/>
-      <c r="BO22" s="110"/>
-      <c r="BP22" s="110"/>
-      <c r="BQ22" s="110"/>
-      <c r="BR22" s="110"/>
-      <c r="BS22" s="110"/>
-      <c r="BT22" s="110"/>
-      <c r="BU22" s="110"/>
-      <c r="BV22" s="110"/>
-      <c r="BW22" s="110"/>
-      <c r="BX22" s="110"/>
-      <c r="BY22" s="110"/>
-      <c r="BZ22" s="110"/>
-      <c r="CA22" s="110"/>
-      <c r="CB22" s="110"/>
-      <c r="CC22" s="110"/>
-      <c r="CD22" s="110"/>
-      <c r="CE22" s="110"/>
-      <c r="CF22" s="110"/>
-      <c r="CG22" s="110"/>
-      <c r="CH22" s="110"/>
-      <c r="CI22" s="110"/>
-      <c r="CJ22" s="110"/>
-      <c r="CK22" s="110"/>
-      <c r="CL22" s="110"/>
-      <c r="CM22" s="110"/>
-      <c r="CN22" s="110"/>
-      <c r="CO22" s="110"/>
-      <c r="CP22" s="110"/>
-      <c r="CQ22" s="110"/>
-      <c r="CR22" s="110"/>
-      <c r="CS22" s="110"/>
-      <c r="CT22" s="102"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="40"/>
+      <c r="P22" s="40"/>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="40"/>
+      <c r="S22" s="40"/>
+      <c r="T22" s="40"/>
+      <c r="U22" s="40"/>
+      <c r="V22" s="40"/>
+      <c r="W22" s="40"/>
+      <c r="X22" s="40"/>
+      <c r="Y22" s="40"/>
+      <c r="Z22" s="40"/>
+      <c r="AA22" s="40"/>
+      <c r="AB22" s="40"/>
+      <c r="AC22" s="40"/>
+      <c r="AD22" s="40"/>
+      <c r="AE22" s="40"/>
+      <c r="AF22" s="40"/>
+      <c r="AG22" s="40"/>
+      <c r="AH22" s="40"/>
+      <c r="AI22" s="40"/>
+      <c r="AJ22" s="40"/>
+      <c r="AK22" s="40"/>
+      <c r="AL22" s="40"/>
+      <c r="AM22" s="40"/>
+      <c r="AN22" s="40"/>
+      <c r="AO22" s="40"/>
+      <c r="AP22" s="40"/>
+      <c r="AQ22" s="40"/>
+      <c r="AR22" s="40"/>
+      <c r="AS22" s="40"/>
+      <c r="AT22" s="40"/>
+      <c r="AU22" s="40"/>
+      <c r="AV22" s="40"/>
+      <c r="AW22" s="40"/>
+      <c r="AX22" s="40"/>
+      <c r="AY22" s="40"/>
+      <c r="AZ22" s="40"/>
+      <c r="BA22" s="40"/>
+      <c r="BB22" s="40"/>
+      <c r="BC22" s="40"/>
+      <c r="BD22" s="40"/>
+      <c r="BE22" s="40"/>
+      <c r="BF22" s="40"/>
+      <c r="BG22" s="40"/>
+      <c r="BH22" s="40"/>
+      <c r="BI22" s="40"/>
+      <c r="BJ22" s="40"/>
+      <c r="BK22" s="40"/>
+      <c r="BL22" s="40"/>
+      <c r="BM22" s="40"/>
+      <c r="BN22" s="40"/>
+      <c r="BO22" s="40"/>
+      <c r="BP22" s="40"/>
+      <c r="BQ22" s="40"/>
+      <c r="BR22" s="40"/>
+      <c r="BS22" s="40"/>
+      <c r="BT22" s="40"/>
+      <c r="BU22" s="40"/>
+      <c r="BV22" s="40"/>
+      <c r="BW22" s="40"/>
+      <c r="BX22" s="40"/>
+      <c r="BY22" s="40"/>
+      <c r="BZ22" s="40"/>
+      <c r="CA22" s="40"/>
+      <c r="CB22" s="40"/>
+      <c r="CC22" s="40"/>
+      <c r="CD22" s="40"/>
+      <c r="CE22" s="40"/>
+      <c r="CF22" s="40"/>
+      <c r="CG22" s="40"/>
+      <c r="CH22" s="40"/>
+      <c r="CI22" s="40"/>
+      <c r="CJ22" s="40"/>
+      <c r="CK22" s="40"/>
+      <c r="CL22" s="40"/>
+      <c r="CM22" s="40"/>
+      <c r="CN22" s="40"/>
+      <c r="CO22" s="40"/>
+      <c r="CP22" s="40"/>
+      <c r="CQ22" s="40"/>
+      <c r="CR22" s="40"/>
+      <c r="CS22" s="40"/>
+      <c r="CT22" s="33"/>
     </row>
     <row r="23" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="121"/>
-      <c r="C23" s="123"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="110"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="110"/>
-      <c r="L23" s="110"/>
-      <c r="M23" s="110"/>
-      <c r="N23" s="110"/>
-      <c r="O23" s="110"/>
-      <c r="P23" s="110"/>
-      <c r="Q23" s="110"/>
-      <c r="R23" s="110"/>
-      <c r="S23" s="110"/>
-      <c r="T23" s="110"/>
-      <c r="U23" s="110"/>
-      <c r="V23" s="110"/>
-      <c r="W23" s="110"/>
-      <c r="X23" s="110"/>
-      <c r="Y23" s="110"/>
-      <c r="Z23" s="110"/>
-      <c r="AA23" s="110"/>
-      <c r="AB23" s="110"/>
-      <c r="AC23" s="110"/>
-      <c r="AD23" s="110"/>
-      <c r="AE23" s="110"/>
-      <c r="AF23" s="110"/>
-      <c r="AG23" s="110"/>
-      <c r="AH23" s="110"/>
-      <c r="AI23" s="110"/>
-      <c r="AJ23" s="110"/>
-      <c r="AK23" s="110"/>
-      <c r="AL23" s="110"/>
-      <c r="AM23" s="110"/>
-      <c r="AN23" s="110"/>
-      <c r="AO23" s="110"/>
-      <c r="AP23" s="110"/>
-      <c r="AQ23" s="110"/>
-      <c r="AR23" s="110"/>
-      <c r="AS23" s="110"/>
-      <c r="AT23" s="110"/>
-      <c r="AU23" s="110"/>
-      <c r="AV23" s="110"/>
-      <c r="AW23" s="110"/>
-      <c r="AX23" s="110"/>
-      <c r="AY23" s="110"/>
-      <c r="AZ23" s="110"/>
-      <c r="BA23" s="110"/>
-      <c r="BB23" s="110"/>
-      <c r="BC23" s="110"/>
-      <c r="BD23" s="110"/>
-      <c r="BE23" s="110"/>
-      <c r="BF23" s="110"/>
-      <c r="BG23" s="110"/>
-      <c r="BH23" s="110"/>
-      <c r="BI23" s="110"/>
-      <c r="BJ23" s="110"/>
-      <c r="BK23" s="110"/>
-      <c r="BL23" s="110"/>
-      <c r="BM23" s="110"/>
-      <c r="BN23" s="110"/>
-      <c r="BO23" s="110"/>
-      <c r="BP23" s="110"/>
-      <c r="BQ23" s="110"/>
-      <c r="BR23" s="110"/>
-      <c r="BS23" s="110"/>
-      <c r="BT23" s="110"/>
-      <c r="BU23" s="110"/>
-      <c r="BV23" s="110"/>
-      <c r="BW23" s="110"/>
-      <c r="BX23" s="110"/>
-      <c r="BY23" s="110"/>
-      <c r="BZ23" s="110"/>
-      <c r="CA23" s="110"/>
-      <c r="CB23" s="110"/>
-      <c r="CC23" s="110"/>
-      <c r="CD23" s="110"/>
-      <c r="CE23" s="110"/>
-      <c r="CF23" s="110"/>
-      <c r="CG23" s="110"/>
-      <c r="CH23" s="110"/>
-      <c r="CI23" s="110"/>
-      <c r="CJ23" s="110"/>
-      <c r="CK23" s="110"/>
-      <c r="CL23" s="110"/>
-      <c r="CM23" s="110"/>
-      <c r="CN23" s="110"/>
-      <c r="CO23" s="110"/>
-      <c r="CP23" s="110"/>
-      <c r="CQ23" s="110"/>
-      <c r="CR23" s="110"/>
-      <c r="CS23" s="110"/>
-      <c r="CT23" s="102"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="40"/>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="40"/>
+      <c r="S23" s="40"/>
+      <c r="T23" s="40"/>
+      <c r="U23" s="40"/>
+      <c r="V23" s="40"/>
+      <c r="W23" s="40"/>
+      <c r="X23" s="40"/>
+      <c r="Y23" s="40"/>
+      <c r="Z23" s="40"/>
+      <c r="AA23" s="40"/>
+      <c r="AB23" s="40"/>
+      <c r="AC23" s="40"/>
+      <c r="AD23" s="40"/>
+      <c r="AE23" s="40"/>
+      <c r="AF23" s="40"/>
+      <c r="AG23" s="40"/>
+      <c r="AH23" s="40"/>
+      <c r="AI23" s="40"/>
+      <c r="AJ23" s="40"/>
+      <c r="AK23" s="40"/>
+      <c r="AL23" s="40"/>
+      <c r="AM23" s="40"/>
+      <c r="AN23" s="40"/>
+      <c r="AO23" s="40"/>
+      <c r="AP23" s="40"/>
+      <c r="AQ23" s="40"/>
+      <c r="AR23" s="40"/>
+      <c r="AS23" s="40"/>
+      <c r="AT23" s="40"/>
+      <c r="AU23" s="40"/>
+      <c r="AV23" s="40"/>
+      <c r="AW23" s="40"/>
+      <c r="AX23" s="40"/>
+      <c r="AY23" s="40"/>
+      <c r="AZ23" s="40"/>
+      <c r="BA23" s="40"/>
+      <c r="BB23" s="40"/>
+      <c r="BC23" s="40"/>
+      <c r="BD23" s="40"/>
+      <c r="BE23" s="40"/>
+      <c r="BF23" s="40"/>
+      <c r="BG23" s="40"/>
+      <c r="BH23" s="40"/>
+      <c r="BI23" s="40"/>
+      <c r="BJ23" s="40"/>
+      <c r="BK23" s="40"/>
+      <c r="BL23" s="40"/>
+      <c r="BM23" s="40"/>
+      <c r="BN23" s="40"/>
+      <c r="BO23" s="40"/>
+      <c r="BP23" s="40"/>
+      <c r="BQ23" s="40"/>
+      <c r="BR23" s="40"/>
+      <c r="BS23" s="40"/>
+      <c r="BT23" s="40"/>
+      <c r="BU23" s="40"/>
+      <c r="BV23" s="40"/>
+      <c r="BW23" s="40"/>
+      <c r="BX23" s="40"/>
+      <c r="BY23" s="40"/>
+      <c r="BZ23" s="40"/>
+      <c r="CA23" s="40"/>
+      <c r="CB23" s="40"/>
+      <c r="CC23" s="40"/>
+      <c r="CD23" s="40"/>
+      <c r="CE23" s="40"/>
+      <c r="CF23" s="40"/>
+      <c r="CG23" s="40"/>
+      <c r="CH23" s="40"/>
+      <c r="CI23" s="40"/>
+      <c r="CJ23" s="40"/>
+      <c r="CK23" s="40"/>
+      <c r="CL23" s="40"/>
+      <c r="CM23" s="40"/>
+      <c r="CN23" s="40"/>
+      <c r="CO23" s="40"/>
+      <c r="CP23" s="40"/>
+      <c r="CQ23" s="40"/>
+      <c r="CR23" s="40"/>
+      <c r="CS23" s="40"/>
+      <c r="CT23" s="33"/>
     </row>
     <row r="24" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="121"/>
-      <c r="C24" s="123"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="110"/>
-      <c r="I24" s="110"/>
-      <c r="J24" s="110"/>
-      <c r="K24" s="110"/>
-      <c r="L24" s="110"/>
-      <c r="M24" s="110"/>
-      <c r="N24" s="110"/>
-      <c r="O24" s="110"/>
-      <c r="P24" s="110"/>
-      <c r="Q24" s="110"/>
-      <c r="R24" s="110"/>
-      <c r="S24" s="110"/>
-      <c r="T24" s="110"/>
-      <c r="U24" s="110"/>
-      <c r="V24" s="110"/>
-      <c r="W24" s="110"/>
-      <c r="X24" s="110"/>
-      <c r="Y24" s="110"/>
-      <c r="Z24" s="110"/>
-      <c r="AA24" s="110"/>
-      <c r="AB24" s="110"/>
-      <c r="AC24" s="110"/>
-      <c r="AD24" s="110"/>
-      <c r="AE24" s="110"/>
-      <c r="AF24" s="110"/>
-      <c r="AG24" s="110"/>
-      <c r="AH24" s="110"/>
-      <c r="AI24" s="110"/>
-      <c r="AJ24" s="110"/>
-      <c r="AK24" s="110"/>
-      <c r="AL24" s="110"/>
-      <c r="AM24" s="110"/>
-      <c r="AN24" s="110"/>
-      <c r="AO24" s="110"/>
-      <c r="AP24" s="110"/>
-      <c r="AQ24" s="110"/>
-      <c r="AR24" s="110"/>
-      <c r="AS24" s="110"/>
-      <c r="AT24" s="110"/>
-      <c r="AU24" s="110"/>
-      <c r="AV24" s="110"/>
-      <c r="AW24" s="110"/>
-      <c r="AX24" s="110"/>
-      <c r="AY24" s="110"/>
-      <c r="AZ24" s="110"/>
-      <c r="BA24" s="110"/>
-      <c r="BB24" s="110"/>
-      <c r="BC24" s="110"/>
-      <c r="BD24" s="110"/>
-      <c r="BE24" s="110"/>
-      <c r="BF24" s="110"/>
-      <c r="BG24" s="110"/>
-      <c r="BH24" s="110"/>
-      <c r="BI24" s="110"/>
-      <c r="BJ24" s="110"/>
-      <c r="BK24" s="110"/>
-      <c r="BL24" s="110"/>
-      <c r="BM24" s="110"/>
-      <c r="BN24" s="110"/>
-      <c r="BO24" s="110"/>
-      <c r="BP24" s="110"/>
-      <c r="BQ24" s="110"/>
-      <c r="BR24" s="110"/>
-      <c r="BS24" s="110"/>
-      <c r="BT24" s="110"/>
-      <c r="BU24" s="110"/>
-      <c r="BV24" s="110"/>
-      <c r="BW24" s="110"/>
-      <c r="BX24" s="110"/>
-      <c r="BY24" s="110"/>
-      <c r="BZ24" s="110"/>
-      <c r="CA24" s="110"/>
-      <c r="CB24" s="110"/>
-      <c r="CC24" s="110"/>
-      <c r="CD24" s="110"/>
-      <c r="CE24" s="110"/>
-      <c r="CF24" s="110"/>
-      <c r="CG24" s="110"/>
-      <c r="CH24" s="110"/>
-      <c r="CI24" s="110"/>
-      <c r="CJ24" s="110"/>
-      <c r="CK24" s="110"/>
-      <c r="CL24" s="110"/>
-      <c r="CM24" s="110"/>
-      <c r="CN24" s="110"/>
-      <c r="CO24" s="110"/>
-      <c r="CP24" s="110"/>
-      <c r="CQ24" s="110"/>
-      <c r="CR24" s="110"/>
-      <c r="CS24" s="110"/>
-      <c r="CT24" s="102"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
+      <c r="S24" s="40"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+      <c r="V24" s="40"/>
+      <c r="W24" s="40"/>
+      <c r="X24" s="40"/>
+      <c r="Y24" s="40"/>
+      <c r="Z24" s="40"/>
+      <c r="AA24" s="40"/>
+      <c r="AB24" s="40"/>
+      <c r="AC24" s="40"/>
+      <c r="AD24" s="40"/>
+      <c r="AE24" s="40"/>
+      <c r="AF24" s="40"/>
+      <c r="AG24" s="40"/>
+      <c r="AH24" s="40"/>
+      <c r="AI24" s="40"/>
+      <c r="AJ24" s="40"/>
+      <c r="AK24" s="40"/>
+      <c r="AL24" s="40"/>
+      <c r="AM24" s="40"/>
+      <c r="AN24" s="40"/>
+      <c r="AO24" s="40"/>
+      <c r="AP24" s="40"/>
+      <c r="AQ24" s="40"/>
+      <c r="AR24" s="40"/>
+      <c r="AS24" s="40"/>
+      <c r="AT24" s="40"/>
+      <c r="AU24" s="40"/>
+      <c r="AV24" s="40"/>
+      <c r="AW24" s="40"/>
+      <c r="AX24" s="40"/>
+      <c r="AY24" s="40"/>
+      <c r="AZ24" s="40"/>
+      <c r="BA24" s="40"/>
+      <c r="BB24" s="40"/>
+      <c r="BC24" s="40"/>
+      <c r="BD24" s="40"/>
+      <c r="BE24" s="40"/>
+      <c r="BF24" s="40"/>
+      <c r="BG24" s="40"/>
+      <c r="BH24" s="40"/>
+      <c r="BI24" s="40"/>
+      <c r="BJ24" s="40"/>
+      <c r="BK24" s="40"/>
+      <c r="BL24" s="40"/>
+      <c r="BM24" s="40"/>
+      <c r="BN24" s="40"/>
+      <c r="BO24" s="40"/>
+      <c r="BP24" s="40"/>
+      <c r="BQ24" s="40"/>
+      <c r="BR24" s="40"/>
+      <c r="BS24" s="40"/>
+      <c r="BT24" s="40"/>
+      <c r="BU24" s="40"/>
+      <c r="BV24" s="40"/>
+      <c r="BW24" s="40"/>
+      <c r="BX24" s="40"/>
+      <c r="BY24" s="40"/>
+      <c r="BZ24" s="40"/>
+      <c r="CA24" s="40"/>
+      <c r="CB24" s="40"/>
+      <c r="CC24" s="40"/>
+      <c r="CD24" s="40"/>
+      <c r="CE24" s="40"/>
+      <c r="CF24" s="40"/>
+      <c r="CG24" s="40"/>
+      <c r="CH24" s="40"/>
+      <c r="CI24" s="40"/>
+      <c r="CJ24" s="40"/>
+      <c r="CK24" s="40"/>
+      <c r="CL24" s="40"/>
+      <c r="CM24" s="40"/>
+      <c r="CN24" s="40"/>
+      <c r="CO24" s="40"/>
+      <c r="CP24" s="40"/>
+      <c r="CQ24" s="40"/>
+      <c r="CR24" s="40"/>
+      <c r="CS24" s="40"/>
+      <c r="CT24" s="33"/>
     </row>
     <row r="25" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="121"/>
-      <c r="C25" s="123"/>
-      <c r="D25" s="124"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="110"/>
-      <c r="L25" s="110"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="110"/>
-      <c r="O25" s="110"/>
-      <c r="P25" s="110"/>
-      <c r="Q25" s="110"/>
-      <c r="R25" s="110"/>
-      <c r="S25" s="110"/>
-      <c r="T25" s="110"/>
-      <c r="U25" s="110"/>
-      <c r="V25" s="110"/>
-      <c r="W25" s="110"/>
-      <c r="X25" s="110"/>
-      <c r="Y25" s="110"/>
-      <c r="Z25" s="110"/>
-      <c r="AA25" s="110"/>
-      <c r="AB25" s="110"/>
-      <c r="AC25" s="110"/>
-      <c r="AD25" s="110"/>
-      <c r="AE25" s="110"/>
-      <c r="AF25" s="110"/>
-      <c r="AG25" s="110"/>
-      <c r="AH25" s="110"/>
-      <c r="AI25" s="110"/>
-      <c r="AJ25" s="110"/>
-      <c r="AK25" s="110"/>
-      <c r="AL25" s="110"/>
-      <c r="AM25" s="110"/>
-      <c r="AN25" s="110"/>
-      <c r="AO25" s="110"/>
-      <c r="AP25" s="110"/>
-      <c r="AQ25" s="110"/>
-      <c r="AR25" s="110"/>
-      <c r="AS25" s="110"/>
-      <c r="AT25" s="110"/>
-      <c r="AU25" s="110"/>
-      <c r="AV25" s="110"/>
-      <c r="AW25" s="110"/>
-      <c r="AX25" s="110"/>
-      <c r="AY25" s="110"/>
-      <c r="AZ25" s="110"/>
-      <c r="BA25" s="110"/>
-      <c r="BB25" s="110"/>
-      <c r="BC25" s="110"/>
-      <c r="BD25" s="110"/>
-      <c r="BE25" s="110"/>
-      <c r="BF25" s="110"/>
-      <c r="BG25" s="110"/>
-      <c r="BH25" s="110"/>
-      <c r="BI25" s="110"/>
-      <c r="BJ25" s="110"/>
-      <c r="BK25" s="110"/>
-      <c r="BL25" s="110"/>
-      <c r="BM25" s="110"/>
-      <c r="BN25" s="110"/>
-      <c r="BO25" s="110"/>
-      <c r="BP25" s="110"/>
-      <c r="BQ25" s="110"/>
-      <c r="BR25" s="110"/>
-      <c r="BS25" s="110"/>
-      <c r="BT25" s="110"/>
-      <c r="BU25" s="110"/>
-      <c r="BV25" s="110"/>
-      <c r="BW25" s="110"/>
-      <c r="BX25" s="110"/>
-      <c r="BY25" s="110"/>
-      <c r="BZ25" s="110"/>
-      <c r="CA25" s="110"/>
-      <c r="CB25" s="110"/>
-      <c r="CC25" s="110"/>
-      <c r="CD25" s="110"/>
-      <c r="CE25" s="110"/>
-      <c r="CF25" s="110"/>
-      <c r="CG25" s="110"/>
-      <c r="CH25" s="110"/>
-      <c r="CI25" s="110"/>
-      <c r="CJ25" s="110"/>
-      <c r="CK25" s="110"/>
-      <c r="CL25" s="110"/>
-      <c r="CM25" s="110"/>
-      <c r="CN25" s="110"/>
-      <c r="CO25" s="110"/>
-      <c r="CP25" s="110"/>
-      <c r="CQ25" s="110"/>
-      <c r="CR25" s="110"/>
-      <c r="CS25" s="110"/>
-      <c r="CT25" s="102"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="40"/>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="40"/>
+      <c r="S25" s="40"/>
+      <c r="T25" s="40"/>
+      <c r="U25" s="40"/>
+      <c r="V25" s="40"/>
+      <c r="W25" s="40"/>
+      <c r="X25" s="40"/>
+      <c r="Y25" s="40"/>
+      <c r="Z25" s="40"/>
+      <c r="AA25" s="40"/>
+      <c r="AB25" s="40"/>
+      <c r="AC25" s="40"/>
+      <c r="AD25" s="40"/>
+      <c r="AE25" s="40"/>
+      <c r="AF25" s="40"/>
+      <c r="AG25" s="40"/>
+      <c r="AH25" s="40"/>
+      <c r="AI25" s="40"/>
+      <c r="AJ25" s="40"/>
+      <c r="AK25" s="40"/>
+      <c r="AL25" s="40"/>
+      <c r="AM25" s="40"/>
+      <c r="AN25" s="40"/>
+      <c r="AO25" s="40"/>
+      <c r="AP25" s="40"/>
+      <c r="AQ25" s="40"/>
+      <c r="AR25" s="40"/>
+      <c r="AS25" s="40"/>
+      <c r="AT25" s="40"/>
+      <c r="AU25" s="40"/>
+      <c r="AV25" s="40"/>
+      <c r="AW25" s="40"/>
+      <c r="AX25" s="40"/>
+      <c r="AY25" s="40"/>
+      <c r="AZ25" s="40"/>
+      <c r="BA25" s="40"/>
+      <c r="BB25" s="40"/>
+      <c r="BC25" s="40"/>
+      <c r="BD25" s="40"/>
+      <c r="BE25" s="40"/>
+      <c r="BF25" s="40"/>
+      <c r="BG25" s="40"/>
+      <c r="BH25" s="40"/>
+      <c r="BI25" s="40"/>
+      <c r="BJ25" s="40"/>
+      <c r="BK25" s="40"/>
+      <c r="BL25" s="40"/>
+      <c r="BM25" s="40"/>
+      <c r="BN25" s="40"/>
+      <c r="BO25" s="40"/>
+      <c r="BP25" s="40"/>
+      <c r="BQ25" s="40"/>
+      <c r="BR25" s="40"/>
+      <c r="BS25" s="40"/>
+      <c r="BT25" s="40"/>
+      <c r="BU25" s="40"/>
+      <c r="BV25" s="40"/>
+      <c r="BW25" s="40"/>
+      <c r="BX25" s="40"/>
+      <c r="BY25" s="40"/>
+      <c r="BZ25" s="40"/>
+      <c r="CA25" s="40"/>
+      <c r="CB25" s="40"/>
+      <c r="CC25" s="40"/>
+      <c r="CD25" s="40"/>
+      <c r="CE25" s="40"/>
+      <c r="CF25" s="40"/>
+      <c r="CG25" s="40"/>
+      <c r="CH25" s="40"/>
+      <c r="CI25" s="40"/>
+      <c r="CJ25" s="40"/>
+      <c r="CK25" s="40"/>
+      <c r="CL25" s="40"/>
+      <c r="CM25" s="40"/>
+      <c r="CN25" s="40"/>
+      <c r="CO25" s="40"/>
+      <c r="CP25" s="40"/>
+      <c r="CQ25" s="40"/>
+      <c r="CR25" s="40"/>
+      <c r="CS25" s="40"/>
+      <c r="CT25" s="33"/>
     </row>
     <row r="26" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="121"/>
-      <c r="C26" s="123"/>
-      <c r="D26" s="124"/>
-      <c r="E26" s="125"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="110"/>
-      <c r="L26" s="110"/>
-      <c r="M26" s="110"/>
-      <c r="N26" s="110"/>
-      <c r="O26" s="110"/>
-      <c r="P26" s="110"/>
-      <c r="Q26" s="110"/>
-      <c r="R26" s="110"/>
-      <c r="S26" s="110"/>
-      <c r="T26" s="110"/>
-      <c r="U26" s="110"/>
-      <c r="V26" s="110"/>
-      <c r="W26" s="110"/>
-      <c r="X26" s="110"/>
-      <c r="Y26" s="110"/>
-      <c r="Z26" s="110"/>
-      <c r="AA26" s="110"/>
-      <c r="AB26" s="110"/>
-      <c r="AC26" s="110"/>
-      <c r="AD26" s="110"/>
-      <c r="AE26" s="110"/>
-      <c r="AF26" s="110"/>
-      <c r="AG26" s="110"/>
-      <c r="AH26" s="110"/>
-      <c r="AI26" s="110"/>
-      <c r="AJ26" s="110"/>
-      <c r="AK26" s="110"/>
-      <c r="AL26" s="110"/>
-      <c r="AM26" s="110"/>
-      <c r="AN26" s="110"/>
-      <c r="AO26" s="110"/>
-      <c r="AP26" s="110"/>
-      <c r="AQ26" s="110"/>
-      <c r="AR26" s="110"/>
-      <c r="AS26" s="110"/>
-      <c r="AT26" s="110"/>
-      <c r="AU26" s="110"/>
-      <c r="AV26" s="110"/>
-      <c r="AW26" s="110"/>
-      <c r="AX26" s="110"/>
-      <c r="AY26" s="110"/>
-      <c r="AZ26" s="110"/>
-      <c r="BA26" s="110"/>
-      <c r="BB26" s="110"/>
-      <c r="BC26" s="110"/>
-      <c r="BD26" s="110"/>
-      <c r="BE26" s="110"/>
-      <c r="BF26" s="110"/>
-      <c r="BG26" s="110"/>
-      <c r="BH26" s="110"/>
-      <c r="BI26" s="110"/>
-      <c r="BJ26" s="110"/>
-      <c r="BK26" s="110"/>
-      <c r="BL26" s="110"/>
-      <c r="BM26" s="110"/>
-      <c r="BN26" s="110"/>
-      <c r="BO26" s="110"/>
-      <c r="BP26" s="110"/>
-      <c r="BQ26" s="110"/>
-      <c r="BR26" s="110"/>
-      <c r="BS26" s="110"/>
-      <c r="BT26" s="110"/>
-      <c r="BU26" s="110"/>
-      <c r="BV26" s="110"/>
-      <c r="BW26" s="110"/>
-      <c r="BX26" s="110"/>
-      <c r="BY26" s="110"/>
-      <c r="BZ26" s="110"/>
-      <c r="CA26" s="110"/>
-      <c r="CB26" s="110"/>
-      <c r="CC26" s="110"/>
-      <c r="CD26" s="110"/>
-      <c r="CE26" s="110"/>
-      <c r="CF26" s="110"/>
-      <c r="CG26" s="110"/>
-      <c r="CH26" s="110"/>
-      <c r="CI26" s="110"/>
-      <c r="CJ26" s="110"/>
-      <c r="CK26" s="110"/>
-      <c r="CL26" s="110"/>
-      <c r="CM26" s="110"/>
-      <c r="CN26" s="110"/>
-      <c r="CO26" s="110"/>
-      <c r="CP26" s="110"/>
-      <c r="CQ26" s="110"/>
-      <c r="CR26" s="110"/>
-      <c r="CS26" s="110"/>
-      <c r="CT26" s="102"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="40"/>
+      <c r="P26" s="40"/>
+      <c r="Q26" s="40"/>
+      <c r="R26" s="40"/>
+      <c r="S26" s="40"/>
+      <c r="T26" s="40"/>
+      <c r="U26" s="40"/>
+      <c r="V26" s="40"/>
+      <c r="W26" s="40"/>
+      <c r="X26" s="40"/>
+      <c r="Y26" s="40"/>
+      <c r="Z26" s="40"/>
+      <c r="AA26" s="40"/>
+      <c r="AB26" s="40"/>
+      <c r="AC26" s="40"/>
+      <c r="AD26" s="40"/>
+      <c r="AE26" s="40"/>
+      <c r="AF26" s="40"/>
+      <c r="AG26" s="40"/>
+      <c r="AH26" s="40"/>
+      <c r="AI26" s="40"/>
+      <c r="AJ26" s="40"/>
+      <c r="AK26" s="40"/>
+      <c r="AL26" s="40"/>
+      <c r="AM26" s="40"/>
+      <c r="AN26" s="40"/>
+      <c r="AO26" s="40"/>
+      <c r="AP26" s="40"/>
+      <c r="AQ26" s="40"/>
+      <c r="AR26" s="40"/>
+      <c r="AS26" s="40"/>
+      <c r="AT26" s="40"/>
+      <c r="AU26" s="40"/>
+      <c r="AV26" s="40"/>
+      <c r="AW26" s="40"/>
+      <c r="AX26" s="40"/>
+      <c r="AY26" s="40"/>
+      <c r="AZ26" s="40"/>
+      <c r="BA26" s="40"/>
+      <c r="BB26" s="40"/>
+      <c r="BC26" s="40"/>
+      <c r="BD26" s="40"/>
+      <c r="BE26" s="40"/>
+      <c r="BF26" s="40"/>
+      <c r="BG26" s="40"/>
+      <c r="BH26" s="40"/>
+      <c r="BI26" s="40"/>
+      <c r="BJ26" s="40"/>
+      <c r="BK26" s="40"/>
+      <c r="BL26" s="40"/>
+      <c r="BM26" s="40"/>
+      <c r="BN26" s="40"/>
+      <c r="BO26" s="40"/>
+      <c r="BP26" s="40"/>
+      <c r="BQ26" s="40"/>
+      <c r="BR26" s="40"/>
+      <c r="BS26" s="40"/>
+      <c r="BT26" s="40"/>
+      <c r="BU26" s="40"/>
+      <c r="BV26" s="40"/>
+      <c r="BW26" s="40"/>
+      <c r="BX26" s="40"/>
+      <c r="BY26" s="40"/>
+      <c r="BZ26" s="40"/>
+      <c r="CA26" s="40"/>
+      <c r="CB26" s="40"/>
+      <c r="CC26" s="40"/>
+      <c r="CD26" s="40"/>
+      <c r="CE26" s="40"/>
+      <c r="CF26" s="40"/>
+      <c r="CG26" s="40"/>
+      <c r="CH26" s="40"/>
+      <c r="CI26" s="40"/>
+      <c r="CJ26" s="40"/>
+      <c r="CK26" s="40"/>
+      <c r="CL26" s="40"/>
+      <c r="CM26" s="40"/>
+      <c r="CN26" s="40"/>
+      <c r="CO26" s="40"/>
+      <c r="CP26" s="40"/>
+      <c r="CQ26" s="40"/>
+      <c r="CR26" s="40"/>
+      <c r="CS26" s="40"/>
+      <c r="CT26" s="33"/>
     </row>
     <row r="27" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="121"/>
-      <c r="C27" s="123"/>
-      <c r="D27" s="124"/>
-      <c r="E27" s="125"/>
-      <c r="F27" s="117"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="110"/>
-      <c r="L27" s="110"/>
-      <c r="M27" s="110"/>
-      <c r="N27" s="110"/>
-      <c r="O27" s="110"/>
-      <c r="P27" s="110"/>
-      <c r="Q27" s="110"/>
-      <c r="R27" s="110"/>
-      <c r="S27" s="110"/>
-      <c r="T27" s="110"/>
-      <c r="U27" s="110"/>
-      <c r="V27" s="110"/>
-      <c r="W27" s="110"/>
-      <c r="X27" s="110"/>
-      <c r="Y27" s="110"/>
-      <c r="Z27" s="110"/>
-      <c r="AA27" s="110"/>
-      <c r="AB27" s="110"/>
-      <c r="AC27" s="110"/>
-      <c r="AD27" s="110"/>
-      <c r="AE27" s="110"/>
-      <c r="AF27" s="110"/>
-      <c r="AG27" s="110"/>
-      <c r="AH27" s="110"/>
-      <c r="AI27" s="110"/>
-      <c r="AJ27" s="110"/>
-      <c r="AK27" s="110"/>
-      <c r="AL27" s="110"/>
-      <c r="AM27" s="110"/>
-      <c r="AN27" s="110"/>
-      <c r="AO27" s="110"/>
-      <c r="AP27" s="110"/>
-      <c r="AQ27" s="110"/>
-      <c r="AR27" s="110"/>
-      <c r="AS27" s="110"/>
-      <c r="AT27" s="110"/>
-      <c r="AU27" s="110"/>
-      <c r="AV27" s="110"/>
-      <c r="AW27" s="110"/>
-      <c r="AX27" s="110"/>
-      <c r="AY27" s="110"/>
-      <c r="AZ27" s="110"/>
-      <c r="BA27" s="110"/>
-      <c r="BB27" s="110"/>
-      <c r="BC27" s="110"/>
-      <c r="BD27" s="110"/>
-      <c r="BE27" s="110"/>
-      <c r="BF27" s="110"/>
-      <c r="BG27" s="110"/>
-      <c r="BH27" s="110"/>
-      <c r="BI27" s="110"/>
-      <c r="BJ27" s="110"/>
-      <c r="BK27" s="110"/>
-      <c r="BL27" s="110"/>
-      <c r="BM27" s="110"/>
-      <c r="BN27" s="110"/>
-      <c r="BO27" s="110"/>
-      <c r="BP27" s="110"/>
-      <c r="BQ27" s="110"/>
-      <c r="BR27" s="110"/>
-      <c r="BS27" s="110"/>
-      <c r="BT27" s="110"/>
-      <c r="BU27" s="110"/>
-      <c r="BV27" s="110"/>
-      <c r="BW27" s="110"/>
-      <c r="BX27" s="110"/>
-      <c r="BY27" s="110"/>
-      <c r="BZ27" s="110"/>
-      <c r="CA27" s="110"/>
-      <c r="CB27" s="110"/>
-      <c r="CC27" s="110"/>
-      <c r="CD27" s="110"/>
-      <c r="CE27" s="110"/>
-      <c r="CF27" s="110"/>
-      <c r="CG27" s="110"/>
-      <c r="CH27" s="110"/>
-      <c r="CI27" s="110"/>
-      <c r="CJ27" s="110"/>
-      <c r="CK27" s="110"/>
-      <c r="CL27" s="110"/>
-      <c r="CM27" s="110"/>
-      <c r="CN27" s="110"/>
-      <c r="CO27" s="110"/>
-      <c r="CP27" s="110"/>
-      <c r="CQ27" s="110"/>
-      <c r="CR27" s="110"/>
-      <c r="CS27" s="110"/>
-      <c r="CT27" s="102"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="40"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="40"/>
+      <c r="S27" s="40"/>
+      <c r="T27" s="40"/>
+      <c r="U27" s="40"/>
+      <c r="V27" s="40"/>
+      <c r="W27" s="40"/>
+      <c r="X27" s="40"/>
+      <c r="Y27" s="40"/>
+      <c r="Z27" s="40"/>
+      <c r="AA27" s="40"/>
+      <c r="AB27" s="40"/>
+      <c r="AC27" s="40"/>
+      <c r="AD27" s="40"/>
+      <c r="AE27" s="40"/>
+      <c r="AF27" s="40"/>
+      <c r="AG27" s="40"/>
+      <c r="AH27" s="40"/>
+      <c r="AI27" s="40"/>
+      <c r="AJ27" s="40"/>
+      <c r="AK27" s="40"/>
+      <c r="AL27" s="40"/>
+      <c r="AM27" s="40"/>
+      <c r="AN27" s="40"/>
+      <c r="AO27" s="40"/>
+      <c r="AP27" s="40"/>
+      <c r="AQ27" s="40"/>
+      <c r="AR27" s="40"/>
+      <c r="AS27" s="40"/>
+      <c r="AT27" s="40"/>
+      <c r="AU27" s="40"/>
+      <c r="AV27" s="40"/>
+      <c r="AW27" s="40"/>
+      <c r="AX27" s="40"/>
+      <c r="AY27" s="40"/>
+      <c r="AZ27" s="40"/>
+      <c r="BA27" s="40"/>
+      <c r="BB27" s="40"/>
+      <c r="BC27" s="40"/>
+      <c r="BD27" s="40"/>
+      <c r="BE27" s="40"/>
+      <c r="BF27" s="40"/>
+      <c r="BG27" s="40"/>
+      <c r="BH27" s="40"/>
+      <c r="BI27" s="40"/>
+      <c r="BJ27" s="40"/>
+      <c r="BK27" s="40"/>
+      <c r="BL27" s="40"/>
+      <c r="BM27" s="40"/>
+      <c r="BN27" s="40"/>
+      <c r="BO27" s="40"/>
+      <c r="BP27" s="40"/>
+      <c r="BQ27" s="40"/>
+      <c r="BR27" s="40"/>
+      <c r="BS27" s="40"/>
+      <c r="BT27" s="40"/>
+      <c r="BU27" s="40"/>
+      <c r="BV27" s="40"/>
+      <c r="BW27" s="40"/>
+      <c r="BX27" s="40"/>
+      <c r="BY27" s="40"/>
+      <c r="BZ27" s="40"/>
+      <c r="CA27" s="40"/>
+      <c r="CB27" s="40"/>
+      <c r="CC27" s="40"/>
+      <c r="CD27" s="40"/>
+      <c r="CE27" s="40"/>
+      <c r="CF27" s="40"/>
+      <c r="CG27" s="40"/>
+      <c r="CH27" s="40"/>
+      <c r="CI27" s="40"/>
+      <c r="CJ27" s="40"/>
+      <c r="CK27" s="40"/>
+      <c r="CL27" s="40"/>
+      <c r="CM27" s="40"/>
+      <c r="CN27" s="40"/>
+      <c r="CO27" s="40"/>
+      <c r="CP27" s="40"/>
+      <c r="CQ27" s="40"/>
+      <c r="CR27" s="40"/>
+      <c r="CS27" s="40"/>
+      <c r="CT27" s="33"/>
     </row>
     <row r="28" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="121"/>
-      <c r="C28" s="123"/>
-      <c r="D28" s="124"/>
-      <c r="E28" s="125"/>
-      <c r="F28" s="117"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="110"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="110"/>
-      <c r="N28" s="110"/>
-      <c r="O28" s="110"/>
-      <c r="P28" s="110"/>
-      <c r="Q28" s="110"/>
-      <c r="R28" s="110"/>
-      <c r="S28" s="110"/>
-      <c r="T28" s="110"/>
-      <c r="U28" s="110"/>
-      <c r="V28" s="110"/>
-      <c r="W28" s="110"/>
-      <c r="X28" s="110"/>
-      <c r="Y28" s="110"/>
-      <c r="Z28" s="110"/>
-      <c r="AA28" s="110"/>
-      <c r="AB28" s="110"/>
-      <c r="AC28" s="110"/>
-      <c r="AD28" s="110"/>
-      <c r="AE28" s="110"/>
-      <c r="AF28" s="110"/>
-      <c r="AG28" s="110"/>
-      <c r="AH28" s="110"/>
-      <c r="AI28" s="110"/>
-      <c r="AJ28" s="110"/>
-      <c r="AK28" s="110"/>
-      <c r="AL28" s="110"/>
-      <c r="AM28" s="110"/>
-      <c r="AN28" s="110"/>
-      <c r="AO28" s="110"/>
-      <c r="AP28" s="110"/>
-      <c r="AQ28" s="110"/>
-      <c r="AR28" s="110"/>
-      <c r="AS28" s="110"/>
-      <c r="AT28" s="110"/>
-      <c r="AU28" s="110"/>
-      <c r="AV28" s="110"/>
-      <c r="AW28" s="110"/>
-      <c r="AX28" s="110"/>
-      <c r="AY28" s="110"/>
-      <c r="AZ28" s="110"/>
-      <c r="BA28" s="110"/>
-      <c r="BB28" s="110"/>
-      <c r="BC28" s="110"/>
-      <c r="BD28" s="110"/>
-      <c r="BE28" s="110"/>
-      <c r="BF28" s="110"/>
-      <c r="BG28" s="110"/>
-      <c r="BH28" s="110"/>
-      <c r="BI28" s="110"/>
-      <c r="BJ28" s="110"/>
-      <c r="BK28" s="110"/>
-      <c r="BL28" s="110"/>
-      <c r="BM28" s="110"/>
-      <c r="BN28" s="110"/>
-      <c r="BO28" s="110"/>
-      <c r="BP28" s="110"/>
-      <c r="BQ28" s="110"/>
-      <c r="BR28" s="110"/>
-      <c r="BS28" s="110"/>
-      <c r="BT28" s="110"/>
-      <c r="BU28" s="110"/>
-      <c r="BV28" s="110"/>
-      <c r="BW28" s="110"/>
-      <c r="BX28" s="110"/>
-      <c r="BY28" s="110"/>
-      <c r="BZ28" s="110"/>
-      <c r="CA28" s="110"/>
-      <c r="CB28" s="110"/>
-      <c r="CC28" s="110"/>
-      <c r="CD28" s="110"/>
-      <c r="CE28" s="110"/>
-      <c r="CF28" s="110"/>
-      <c r="CG28" s="110"/>
-      <c r="CH28" s="110"/>
-      <c r="CI28" s="110"/>
-      <c r="CJ28" s="110"/>
-      <c r="CK28" s="110"/>
-      <c r="CL28" s="110"/>
-      <c r="CM28" s="110"/>
-      <c r="CN28" s="110"/>
-      <c r="CO28" s="110"/>
-      <c r="CP28" s="110"/>
-      <c r="CQ28" s="110"/>
-      <c r="CR28" s="110"/>
-      <c r="CS28" s="110"/>
-      <c r="CT28" s="102"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="40"/>
+      <c r="S28" s="40"/>
+      <c r="T28" s="40"/>
+      <c r="U28" s="40"/>
+      <c r="V28" s="40"/>
+      <c r="W28" s="40"/>
+      <c r="X28" s="40"/>
+      <c r="Y28" s="40"/>
+      <c r="Z28" s="40"/>
+      <c r="AA28" s="40"/>
+      <c r="AB28" s="40"/>
+      <c r="AC28" s="40"/>
+      <c r="AD28" s="40"/>
+      <c r="AE28" s="40"/>
+      <c r="AF28" s="40"/>
+      <c r="AG28" s="40"/>
+      <c r="AH28" s="40"/>
+      <c r="AI28" s="40"/>
+      <c r="AJ28" s="40"/>
+      <c r="AK28" s="40"/>
+      <c r="AL28" s="40"/>
+      <c r="AM28" s="40"/>
+      <c r="AN28" s="40"/>
+      <c r="AO28" s="40"/>
+      <c r="AP28" s="40"/>
+      <c r="AQ28" s="40"/>
+      <c r="AR28" s="40"/>
+      <c r="AS28" s="40"/>
+      <c r="AT28" s="40"/>
+      <c r="AU28" s="40"/>
+      <c r="AV28" s="40"/>
+      <c r="AW28" s="40"/>
+      <c r="AX28" s="40"/>
+      <c r="AY28" s="40"/>
+      <c r="AZ28" s="40"/>
+      <c r="BA28" s="40"/>
+      <c r="BB28" s="40"/>
+      <c r="BC28" s="40"/>
+      <c r="BD28" s="40"/>
+      <c r="BE28" s="40"/>
+      <c r="BF28" s="40"/>
+      <c r="BG28" s="40"/>
+      <c r="BH28" s="40"/>
+      <c r="BI28" s="40"/>
+      <c r="BJ28" s="40"/>
+      <c r="BK28" s="40"/>
+      <c r="BL28" s="40"/>
+      <c r="BM28" s="40"/>
+      <c r="BN28" s="40"/>
+      <c r="BO28" s="40"/>
+      <c r="BP28" s="40"/>
+      <c r="BQ28" s="40"/>
+      <c r="BR28" s="40"/>
+      <c r="BS28" s="40"/>
+      <c r="BT28" s="40"/>
+      <c r="BU28" s="40"/>
+      <c r="BV28" s="40"/>
+      <c r="BW28" s="40"/>
+      <c r="BX28" s="40"/>
+      <c r="BY28" s="40"/>
+      <c r="BZ28" s="40"/>
+      <c r="CA28" s="40"/>
+      <c r="CB28" s="40"/>
+      <c r="CC28" s="40"/>
+      <c r="CD28" s="40"/>
+      <c r="CE28" s="40"/>
+      <c r="CF28" s="40"/>
+      <c r="CG28" s="40"/>
+      <c r="CH28" s="40"/>
+      <c r="CI28" s="40"/>
+      <c r="CJ28" s="40"/>
+      <c r="CK28" s="40"/>
+      <c r="CL28" s="40"/>
+      <c r="CM28" s="40"/>
+      <c r="CN28" s="40"/>
+      <c r="CO28" s="40"/>
+      <c r="CP28" s="40"/>
+      <c r="CQ28" s="40"/>
+      <c r="CR28" s="40"/>
+      <c r="CS28" s="40"/>
+      <c r="CT28" s="33"/>
     </row>
     <row r="29" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="121"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="124"/>
-      <c r="E29" s="125"/>
-      <c r="F29" s="117"/>
-      <c r="G29" s="110"/>
-      <c r="H29" s="110"/>
-      <c r="I29" s="110"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="110"/>
-      <c r="L29" s="110"/>
-      <c r="M29" s="110"/>
-      <c r="N29" s="110"/>
-      <c r="O29" s="110"/>
-      <c r="P29" s="110"/>
-      <c r="Q29" s="110"/>
-      <c r="R29" s="110"/>
-      <c r="S29" s="110"/>
-      <c r="T29" s="110"/>
-      <c r="U29" s="110"/>
-      <c r="V29" s="110"/>
-      <c r="W29" s="110"/>
-      <c r="X29" s="110"/>
-      <c r="Y29" s="110"/>
-      <c r="Z29" s="110"/>
-      <c r="AA29" s="110"/>
-      <c r="AB29" s="110"/>
-      <c r="AC29" s="110"/>
-      <c r="AD29" s="110"/>
-      <c r="AE29" s="110"/>
-      <c r="AF29" s="110"/>
-      <c r="AG29" s="110"/>
-      <c r="AH29" s="110"/>
-      <c r="AI29" s="110"/>
-      <c r="AJ29" s="110"/>
-      <c r="AK29" s="110"/>
-      <c r="AL29" s="110"/>
-      <c r="AM29" s="110"/>
-      <c r="AN29" s="110"/>
-      <c r="AO29" s="110"/>
-      <c r="AP29" s="110"/>
-      <c r="AQ29" s="110"/>
-      <c r="AR29" s="110"/>
-      <c r="AS29" s="110"/>
-      <c r="AT29" s="110"/>
-      <c r="AU29" s="110"/>
-      <c r="AV29" s="110"/>
-      <c r="AW29" s="110"/>
-      <c r="AX29" s="110"/>
-      <c r="AY29" s="110"/>
-      <c r="AZ29" s="110"/>
-      <c r="BA29" s="110"/>
-      <c r="BB29" s="110"/>
-      <c r="BC29" s="110"/>
-      <c r="BD29" s="110"/>
-      <c r="BE29" s="110"/>
-      <c r="BF29" s="110"/>
-      <c r="BG29" s="110"/>
-      <c r="BH29" s="110"/>
-      <c r="BI29" s="110"/>
-      <c r="BJ29" s="110"/>
-      <c r="BK29" s="110"/>
-      <c r="BL29" s="110"/>
-      <c r="BM29" s="110"/>
-      <c r="BN29" s="110"/>
-      <c r="BO29" s="110"/>
-      <c r="BP29" s="110"/>
-      <c r="BQ29" s="110"/>
-      <c r="BR29" s="110"/>
-      <c r="BS29" s="110"/>
-      <c r="BT29" s="110"/>
-      <c r="BU29" s="110"/>
-      <c r="BV29" s="110"/>
-      <c r="BW29" s="110"/>
-      <c r="BX29" s="110"/>
-      <c r="BY29" s="110"/>
-      <c r="BZ29" s="110"/>
-      <c r="CA29" s="110"/>
-      <c r="CB29" s="110"/>
-      <c r="CC29" s="110"/>
-      <c r="CD29" s="110"/>
-      <c r="CE29" s="110"/>
-      <c r="CF29" s="110"/>
-      <c r="CG29" s="110"/>
-      <c r="CH29" s="110"/>
-      <c r="CI29" s="110"/>
-      <c r="CJ29" s="110"/>
-      <c r="CK29" s="110"/>
-      <c r="CL29" s="110"/>
-      <c r="CM29" s="110"/>
-      <c r="CN29" s="110"/>
-      <c r="CO29" s="110"/>
-      <c r="CP29" s="110"/>
-      <c r="CQ29" s="110"/>
-      <c r="CR29" s="110"/>
-      <c r="CS29" s="110"/>
-      <c r="CT29" s="102"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="40"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="40"/>
+      <c r="V29" s="40"/>
+      <c r="W29" s="40"/>
+      <c r="X29" s="40"/>
+      <c r="Y29" s="40"/>
+      <c r="Z29" s="40"/>
+      <c r="AA29" s="40"/>
+      <c r="AB29" s="40"/>
+      <c r="AC29" s="40"/>
+      <c r="AD29" s="40"/>
+      <c r="AE29" s="40"/>
+      <c r="AF29" s="40"/>
+      <c r="AG29" s="40"/>
+      <c r="AH29" s="40"/>
+      <c r="AI29" s="40"/>
+      <c r="AJ29" s="40"/>
+      <c r="AK29" s="40"/>
+      <c r="AL29" s="40"/>
+      <c r="AM29" s="40"/>
+      <c r="AN29" s="40"/>
+      <c r="AO29" s="40"/>
+      <c r="AP29" s="40"/>
+      <c r="AQ29" s="40"/>
+      <c r="AR29" s="40"/>
+      <c r="AS29" s="40"/>
+      <c r="AT29" s="40"/>
+      <c r="AU29" s="40"/>
+      <c r="AV29" s="40"/>
+      <c r="AW29" s="40"/>
+      <c r="AX29" s="40"/>
+      <c r="AY29" s="40"/>
+      <c r="AZ29" s="40"/>
+      <c r="BA29" s="40"/>
+      <c r="BB29" s="40"/>
+      <c r="BC29" s="40"/>
+      <c r="BD29" s="40"/>
+      <c r="BE29" s="40"/>
+      <c r="BF29" s="40"/>
+      <c r="BG29" s="40"/>
+      <c r="BH29" s="40"/>
+      <c r="BI29" s="40"/>
+      <c r="BJ29" s="40"/>
+      <c r="BK29" s="40"/>
+      <c r="BL29" s="40"/>
+      <c r="BM29" s="40"/>
+      <c r="BN29" s="40"/>
+      <c r="BO29" s="40"/>
+      <c r="BP29" s="40"/>
+      <c r="BQ29" s="40"/>
+      <c r="BR29" s="40"/>
+      <c r="BS29" s="40"/>
+      <c r="BT29" s="40"/>
+      <c r="BU29" s="40"/>
+      <c r="BV29" s="40"/>
+      <c r="BW29" s="40"/>
+      <c r="BX29" s="40"/>
+      <c r="BY29" s="40"/>
+      <c r="BZ29" s="40"/>
+      <c r="CA29" s="40"/>
+      <c r="CB29" s="40"/>
+      <c r="CC29" s="40"/>
+      <c r="CD29" s="40"/>
+      <c r="CE29" s="40"/>
+      <c r="CF29" s="40"/>
+      <c r="CG29" s="40"/>
+      <c r="CH29" s="40"/>
+      <c r="CI29" s="40"/>
+      <c r="CJ29" s="40"/>
+      <c r="CK29" s="40"/>
+      <c r="CL29" s="40"/>
+      <c r="CM29" s="40"/>
+      <c r="CN29" s="40"/>
+      <c r="CO29" s="40"/>
+      <c r="CP29" s="40"/>
+      <c r="CQ29" s="40"/>
+      <c r="CR29" s="40"/>
+      <c r="CS29" s="40"/>
+      <c r="CT29" s="33"/>
     </row>
     <row r="30" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="126"/>
-      <c r="C30" s="102"/>
-      <c r="D30" s="102"/>
-      <c r="E30" s="102"/>
-      <c r="F30" s="102"/>
-      <c r="G30" s="127"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="127"/>
-      <c r="J30" s="127"/>
-      <c r="K30" s="127"/>
-      <c r="L30" s="127"/>
-      <c r="M30" s="127"/>
-      <c r="N30" s="127"/>
-      <c r="O30" s="127"/>
-      <c r="P30" s="127"/>
-      <c r="Q30" s="127"/>
-      <c r="R30" s="127"/>
-      <c r="S30" s="127"/>
-      <c r="T30" s="127"/>
-      <c r="U30" s="127"/>
-      <c r="V30" s="127"/>
-      <c r="W30" s="127"/>
-      <c r="X30" s="127"/>
-      <c r="Y30" s="127"/>
-      <c r="Z30" s="127"/>
-      <c r="AA30" s="127"/>
-      <c r="AB30" s="127"/>
-      <c r="AC30" s="127"/>
-      <c r="AD30" s="127"/>
-      <c r="AE30" s="127"/>
-      <c r="AF30" s="127"/>
-      <c r="AG30" s="127"/>
-      <c r="AH30" s="127"/>
-      <c r="AI30" s="127"/>
-      <c r="AJ30" s="127"/>
-      <c r="AK30" s="127"/>
-      <c r="AL30" s="102"/>
-      <c r="AM30" s="102"/>
-      <c r="AN30" s="102"/>
-      <c r="AO30" s="102"/>
-      <c r="AP30" s="102"/>
-      <c r="AQ30" s="102"/>
-      <c r="AR30" s="102"/>
-      <c r="AS30" s="102"/>
-      <c r="AT30" s="102"/>
-      <c r="AU30" s="102"/>
-      <c r="AV30" s="102"/>
-      <c r="AW30" s="102"/>
-      <c r="AX30" s="102"/>
-      <c r="AY30" s="102"/>
-      <c r="AZ30" s="102"/>
-      <c r="BA30" s="102"/>
-      <c r="BB30" s="102"/>
-      <c r="BC30" s="102"/>
-      <c r="BD30" s="102"/>
-      <c r="BE30" s="102"/>
-      <c r="BF30" s="102"/>
-      <c r="BG30" s="102"/>
-      <c r="BH30" s="102"/>
-      <c r="BI30" s="102"/>
-      <c r="BJ30" s="102"/>
-      <c r="BK30" s="102"/>
-      <c r="BL30" s="102"/>
-      <c r="BM30" s="102"/>
-      <c r="BN30" s="102"/>
-      <c r="BO30" s="102"/>
-      <c r="BP30" s="102"/>
-      <c r="BQ30" s="102"/>
-      <c r="BR30" s="102"/>
-      <c r="BS30" s="102"/>
-      <c r="BT30" s="102"/>
-      <c r="BU30" s="102"/>
-      <c r="BV30" s="102"/>
-      <c r="BW30" s="102"/>
-      <c r="BX30" s="102"/>
-      <c r="BY30" s="102"/>
-      <c r="BZ30" s="102"/>
-      <c r="CA30" s="102"/>
-      <c r="CB30" s="102"/>
-      <c r="CC30" s="102"/>
-      <c r="CD30" s="102"/>
-      <c r="CE30" s="102"/>
-      <c r="CF30" s="102"/>
-      <c r="CG30" s="102"/>
-      <c r="CH30" s="102"/>
-      <c r="CI30" s="102"/>
-      <c r="CJ30" s="102"/>
-      <c r="CK30" s="102"/>
-      <c r="CL30" s="102"/>
-      <c r="CM30" s="102"/>
-      <c r="CN30" s="102"/>
-      <c r="CO30" s="102"/>
-      <c r="CP30" s="102"/>
-      <c r="CQ30" s="102"/>
-      <c r="CR30" s="102"/>
-      <c r="CS30" s="102"/>
-      <c r="CT30" s="102"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="57"/>
+      <c r="V30" s="57"/>
+      <c r="W30" s="57"/>
+      <c r="X30" s="57"/>
+      <c r="Y30" s="57"/>
+      <c r="Z30" s="57"/>
+      <c r="AA30" s="57"/>
+      <c r="AB30" s="57"/>
+      <c r="AC30" s="57"/>
+      <c r="AD30" s="57"/>
+      <c r="AE30" s="57"/>
+      <c r="AF30" s="57"/>
+      <c r="AG30" s="57"/>
+      <c r="AH30" s="57"/>
+      <c r="AI30" s="57"/>
+      <c r="AJ30" s="57"/>
+      <c r="AK30" s="57"/>
+      <c r="AL30" s="33"/>
+      <c r="AM30" s="33"/>
+      <c r="AN30" s="33"/>
+      <c r="AO30" s="33"/>
+      <c r="AP30" s="33"/>
+      <c r="AQ30" s="33"/>
+      <c r="AR30" s="33"/>
+      <c r="AS30" s="33"/>
+      <c r="AT30" s="33"/>
+      <c r="AU30" s="33"/>
+      <c r="AV30" s="33"/>
+      <c r="AW30" s="33"/>
+      <c r="AX30" s="33"/>
+      <c r="AY30" s="33"/>
+      <c r="AZ30" s="33"/>
+      <c r="BA30" s="33"/>
+      <c r="BB30" s="33"/>
+      <c r="BC30" s="33"/>
+      <c r="BD30" s="33"/>
+      <c r="BE30" s="33"/>
+      <c r="BF30" s="33"/>
+      <c r="BG30" s="33"/>
+      <c r="BH30" s="33"/>
+      <c r="BI30" s="33"/>
+      <c r="BJ30" s="33"/>
+      <c r="BK30" s="33"/>
+      <c r="BL30" s="33"/>
+      <c r="BM30" s="33"/>
+      <c r="BN30" s="33"/>
+      <c r="BO30" s="33"/>
+      <c r="BP30" s="33"/>
+      <c r="BQ30" s="33"/>
+      <c r="BR30" s="33"/>
+      <c r="BS30" s="33"/>
+      <c r="BT30" s="33"/>
+      <c r="BU30" s="33"/>
+      <c r="BV30" s="33"/>
+      <c r="BW30" s="33"/>
+      <c r="BX30" s="33"/>
+      <c r="BY30" s="33"/>
+      <c r="BZ30" s="33"/>
+      <c r="CA30" s="33"/>
+      <c r="CB30" s="33"/>
+      <c r="CC30" s="33"/>
+      <c r="CD30" s="33"/>
+      <c r="CE30" s="33"/>
+      <c r="CF30" s="33"/>
+      <c r="CG30" s="33"/>
+      <c r="CH30" s="33"/>
+      <c r="CI30" s="33"/>
+      <c r="CJ30" s="33"/>
+      <c r="CK30" s="33"/>
+      <c r="CL30" s="33"/>
+      <c r="CM30" s="33"/>
+      <c r="CN30" s="33"/>
+      <c r="CO30" s="33"/>
+      <c r="CP30" s="33"/>
+      <c r="CQ30" s="33"/>
+      <c r="CR30" s="33"/>
+      <c r="CS30" s="33"/>
+      <c r="CT30" s="33"/>
     </row>
     <row r="31" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="126"/>
-      <c r="C31" s="102"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="102"/>
-      <c r="F31" s="102"/>
-      <c r="G31" s="127"/>
-      <c r="H31" s="127"/>
-      <c r="I31" s="127"/>
-      <c r="J31" s="127"/>
-      <c r="K31" s="127"/>
-      <c r="L31" s="127"/>
-      <c r="M31" s="127"/>
-      <c r="N31" s="127"/>
-      <c r="O31" s="127"/>
-      <c r="P31" s="127"/>
-      <c r="Q31" s="127"/>
-      <c r="R31" s="127"/>
-      <c r="S31" s="127"/>
-      <c r="T31" s="127"/>
-      <c r="U31" s="127"/>
-      <c r="V31" s="127"/>
-      <c r="W31" s="127"/>
-      <c r="X31" s="127"/>
-      <c r="Y31" s="127"/>
-      <c r="Z31" s="127"/>
-      <c r="AA31" s="127"/>
-      <c r="AB31" s="127"/>
-      <c r="AC31" s="127"/>
-      <c r="AD31" s="127"/>
-      <c r="AE31" s="127"/>
-      <c r="AF31" s="127"/>
-      <c r="AG31" s="127"/>
-      <c r="AH31" s="127"/>
-      <c r="AI31" s="127"/>
-      <c r="AJ31" s="127"/>
-      <c r="AK31" s="127"/>
-      <c r="AL31" s="102"/>
-      <c r="AM31" s="102"/>
-      <c r="AN31" s="102"/>
-      <c r="AO31" s="102"/>
-      <c r="AP31" s="102"/>
-      <c r="AQ31" s="102"/>
-      <c r="AR31" s="102"/>
-      <c r="AS31" s="102"/>
-      <c r="AT31" s="102"/>
-      <c r="AU31" s="102"/>
-      <c r="AV31" s="102"/>
-      <c r="AW31" s="102"/>
-      <c r="AX31" s="102"/>
-      <c r="AY31" s="102"/>
-      <c r="AZ31" s="102"/>
-      <c r="BA31" s="102"/>
-      <c r="BB31" s="102"/>
-      <c r="BC31" s="102"/>
-      <c r="BD31" s="102"/>
-      <c r="BE31" s="102"/>
-      <c r="BF31" s="102"/>
-      <c r="BG31" s="102"/>
-      <c r="BH31" s="102"/>
-      <c r="BI31" s="102"/>
-      <c r="BJ31" s="102"/>
-      <c r="BK31" s="102"/>
-      <c r="BL31" s="102"/>
-      <c r="BM31" s="102"/>
-      <c r="BN31" s="102"/>
-      <c r="BO31" s="102"/>
-      <c r="BP31" s="102"/>
-      <c r="BQ31" s="102"/>
-      <c r="BR31" s="102"/>
-      <c r="BS31" s="102"/>
-      <c r="BT31" s="102"/>
-      <c r="BU31" s="102"/>
-      <c r="BV31" s="102"/>
-      <c r="BW31" s="102"/>
-      <c r="BX31" s="102"/>
-      <c r="BY31" s="102"/>
-      <c r="BZ31" s="102"/>
-      <c r="CA31" s="102"/>
-      <c r="CB31" s="102"/>
-      <c r="CC31" s="102"/>
-      <c r="CD31" s="102"/>
-      <c r="CE31" s="102"/>
-      <c r="CF31" s="102"/>
-      <c r="CG31" s="102"/>
-      <c r="CH31" s="102"/>
-      <c r="CI31" s="102"/>
-      <c r="CJ31" s="102"/>
-      <c r="CK31" s="102"/>
-      <c r="CL31" s="102"/>
-      <c r="CM31" s="102"/>
-      <c r="CN31" s="102"/>
-      <c r="CO31" s="102"/>
-      <c r="CP31" s="102"/>
-      <c r="CQ31" s="102"/>
-      <c r="CR31" s="102"/>
-      <c r="CS31" s="102"/>
-      <c r="CT31" s="102"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="57"/>
+      <c r="P31" s="57"/>
+      <c r="Q31" s="57"/>
+      <c r="R31" s="57"/>
+      <c r="S31" s="57"/>
+      <c r="T31" s="57"/>
+      <c r="U31" s="57"/>
+      <c r="V31" s="57"/>
+      <c r="W31" s="57"/>
+      <c r="X31" s="57"/>
+      <c r="Y31" s="57"/>
+      <c r="Z31" s="57"/>
+      <c r="AA31" s="57"/>
+      <c r="AB31" s="57"/>
+      <c r="AC31" s="57"/>
+      <c r="AD31" s="57"/>
+      <c r="AE31" s="57"/>
+      <c r="AF31" s="57"/>
+      <c r="AG31" s="57"/>
+      <c r="AH31" s="57"/>
+      <c r="AI31" s="57"/>
+      <c r="AJ31" s="57"/>
+      <c r="AK31" s="57"/>
+      <c r="AL31" s="33"/>
+      <c r="AM31" s="33"/>
+      <c r="AN31" s="33"/>
+      <c r="AO31" s="33"/>
+      <c r="AP31" s="33"/>
+      <c r="AQ31" s="33"/>
+      <c r="AR31" s="33"/>
+      <c r="AS31" s="33"/>
+      <c r="AT31" s="33"/>
+      <c r="AU31" s="33"/>
+      <c r="AV31" s="33"/>
+      <c r="AW31" s="33"/>
+      <c r="AX31" s="33"/>
+      <c r="AY31" s="33"/>
+      <c r="AZ31" s="33"/>
+      <c r="BA31" s="33"/>
+      <c r="BB31" s="33"/>
+      <c r="BC31" s="33"/>
+      <c r="BD31" s="33"/>
+      <c r="BE31" s="33"/>
+      <c r="BF31" s="33"/>
+      <c r="BG31" s="33"/>
+      <c r="BH31" s="33"/>
+      <c r="BI31" s="33"/>
+      <c r="BJ31" s="33"/>
+      <c r="BK31" s="33"/>
+      <c r="BL31" s="33"/>
+      <c r="BM31" s="33"/>
+      <c r="BN31" s="33"/>
+      <c r="BO31" s="33"/>
+      <c r="BP31" s="33"/>
+      <c r="BQ31" s="33"/>
+      <c r="BR31" s="33"/>
+      <c r="BS31" s="33"/>
+      <c r="BT31" s="33"/>
+      <c r="BU31" s="33"/>
+      <c r="BV31" s="33"/>
+      <c r="BW31" s="33"/>
+      <c r="BX31" s="33"/>
+      <c r="BY31" s="33"/>
+      <c r="BZ31" s="33"/>
+      <c r="CA31" s="33"/>
+      <c r="CB31" s="33"/>
+      <c r="CC31" s="33"/>
+      <c r="CD31" s="33"/>
+      <c r="CE31" s="33"/>
+      <c r="CF31" s="33"/>
+      <c r="CG31" s="33"/>
+      <c r="CH31" s="33"/>
+      <c r="CI31" s="33"/>
+      <c r="CJ31" s="33"/>
+      <c r="CK31" s="33"/>
+      <c r="CL31" s="33"/>
+      <c r="CM31" s="33"/>
+      <c r="CN31" s="33"/>
+      <c r="CO31" s="33"/>
+      <c r="CP31" s="33"/>
+      <c r="CQ31" s="33"/>
+      <c r="CR31" s="33"/>
+      <c r="CS31" s="33"/>
+      <c r="CT31" s="33"/>
     </row>
     <row r="32" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="126"/>
-      <c r="C32" s="102"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="102"/>
-      <c r="G32" s="127"/>
-      <c r="H32" s="127"/>
-      <c r="I32" s="127"/>
-      <c r="J32" s="127"/>
-      <c r="K32" s="127"/>
-      <c r="L32" s="127"/>
-      <c r="M32" s="127"/>
-      <c r="N32" s="127"/>
-      <c r="O32" s="127"/>
-      <c r="P32" s="127"/>
-      <c r="Q32" s="127"/>
-      <c r="R32" s="127"/>
-      <c r="S32" s="127"/>
-      <c r="T32" s="127"/>
-      <c r="U32" s="127"/>
-      <c r="V32" s="127"/>
-      <c r="W32" s="127"/>
-      <c r="X32" s="127"/>
-      <c r="Y32" s="127"/>
-      <c r="Z32" s="127"/>
-      <c r="AA32" s="127"/>
-      <c r="AB32" s="127"/>
-      <c r="AC32" s="127"/>
-      <c r="AD32" s="127"/>
-      <c r="AE32" s="127"/>
-      <c r="AF32" s="127"/>
-      <c r="AG32" s="127"/>
-      <c r="AH32" s="127"/>
-      <c r="AI32" s="127"/>
-      <c r="AJ32" s="127"/>
-      <c r="AK32" s="127"/>
-      <c r="AL32" s="102"/>
-      <c r="AM32" s="102"/>
-      <c r="AN32" s="102"/>
-      <c r="AO32" s="102"/>
-      <c r="AP32" s="102"/>
-      <c r="AQ32" s="102"/>
-      <c r="AR32" s="102"/>
-      <c r="AS32" s="102"/>
-      <c r="AT32" s="102"/>
-      <c r="AU32" s="102"/>
-      <c r="AV32" s="102"/>
-      <c r="AW32" s="102"/>
-      <c r="AX32" s="102"/>
-      <c r="AY32" s="102"/>
-      <c r="AZ32" s="102"/>
-      <c r="BA32" s="102"/>
-      <c r="BB32" s="102"/>
-      <c r="BC32" s="102"/>
-      <c r="BD32" s="102"/>
-      <c r="BE32" s="102"/>
-      <c r="BF32" s="102"/>
-      <c r="BG32" s="102"/>
-      <c r="BH32" s="102"/>
-      <c r="BI32" s="102"/>
-      <c r="BJ32" s="102"/>
-      <c r="BK32" s="102"/>
-      <c r="BL32" s="102"/>
-      <c r="BM32" s="102"/>
-      <c r="BN32" s="102"/>
-      <c r="BO32" s="102"/>
-      <c r="BP32" s="102"/>
-      <c r="BQ32" s="102"/>
-      <c r="BR32" s="102"/>
-      <c r="BS32" s="102"/>
-      <c r="BT32" s="102"/>
-      <c r="BU32" s="102"/>
-      <c r="BV32" s="102"/>
-      <c r="BW32" s="102"/>
-      <c r="BX32" s="102"/>
-      <c r="BY32" s="102"/>
-      <c r="BZ32" s="102"/>
-      <c r="CA32" s="102"/>
-      <c r="CB32" s="102"/>
-      <c r="CC32" s="102"/>
-      <c r="CD32" s="102"/>
-      <c r="CE32" s="102"/>
-      <c r="CF32" s="102"/>
-      <c r="CG32" s="102"/>
-      <c r="CH32" s="102"/>
-      <c r="CI32" s="102"/>
-      <c r="CJ32" s="102"/>
-      <c r="CK32" s="102"/>
-      <c r="CL32" s="102"/>
-      <c r="CM32" s="102"/>
-      <c r="CN32" s="102"/>
-      <c r="CO32" s="102"/>
-      <c r="CP32" s="102"/>
-      <c r="CQ32" s="102"/>
-      <c r="CR32" s="102"/>
-      <c r="CS32" s="102"/>
-      <c r="CT32" s="102"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="57"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="57"/>
+      <c r="O32" s="57"/>
+      <c r="P32" s="57"/>
+      <c r="Q32" s="57"/>
+      <c r="R32" s="57"/>
+      <c r="S32" s="57"/>
+      <c r="T32" s="57"/>
+      <c r="U32" s="57"/>
+      <c r="V32" s="57"/>
+      <c r="W32" s="57"/>
+      <c r="X32" s="57"/>
+      <c r="Y32" s="57"/>
+      <c r="Z32" s="57"/>
+      <c r="AA32" s="57"/>
+      <c r="AB32" s="57"/>
+      <c r="AC32" s="57"/>
+      <c r="AD32" s="57"/>
+      <c r="AE32" s="57"/>
+      <c r="AF32" s="57"/>
+      <c r="AG32" s="57"/>
+      <c r="AH32" s="57"/>
+      <c r="AI32" s="57"/>
+      <c r="AJ32" s="57"/>
+      <c r="AK32" s="57"/>
+      <c r="AL32" s="33"/>
+      <c r="AM32" s="33"/>
+      <c r="AN32" s="33"/>
+      <c r="AO32" s="33"/>
+      <c r="AP32" s="33"/>
+      <c r="AQ32" s="33"/>
+      <c r="AR32" s="33"/>
+      <c r="AS32" s="33"/>
+      <c r="AT32" s="33"/>
+      <c r="AU32" s="33"/>
+      <c r="AV32" s="33"/>
+      <c r="AW32" s="33"/>
+      <c r="AX32" s="33"/>
+      <c r="AY32" s="33"/>
+      <c r="AZ32" s="33"/>
+      <c r="BA32" s="33"/>
+      <c r="BB32" s="33"/>
+      <c r="BC32" s="33"/>
+      <c r="BD32" s="33"/>
+      <c r="BE32" s="33"/>
+      <c r="BF32" s="33"/>
+      <c r="BG32" s="33"/>
+      <c r="BH32" s="33"/>
+      <c r="BI32" s="33"/>
+      <c r="BJ32" s="33"/>
+      <c r="BK32" s="33"/>
+      <c r="BL32" s="33"/>
+      <c r="BM32" s="33"/>
+      <c r="BN32" s="33"/>
+      <c r="BO32" s="33"/>
+      <c r="BP32" s="33"/>
+      <c r="BQ32" s="33"/>
+      <c r="BR32" s="33"/>
+      <c r="BS32" s="33"/>
+      <c r="BT32" s="33"/>
+      <c r="BU32" s="33"/>
+      <c r="BV32" s="33"/>
+      <c r="BW32" s="33"/>
+      <c r="BX32" s="33"/>
+      <c r="BY32" s="33"/>
+      <c r="BZ32" s="33"/>
+      <c r="CA32" s="33"/>
+      <c r="CB32" s="33"/>
+      <c r="CC32" s="33"/>
+      <c r="CD32" s="33"/>
+      <c r="CE32" s="33"/>
+      <c r="CF32" s="33"/>
+      <c r="CG32" s="33"/>
+      <c r="CH32" s="33"/>
+      <c r="CI32" s="33"/>
+      <c r="CJ32" s="33"/>
+      <c r="CK32" s="33"/>
+      <c r="CL32" s="33"/>
+      <c r="CM32" s="33"/>
+      <c r="CN32" s="33"/>
+      <c r="CO32" s="33"/>
+      <c r="CP32" s="33"/>
+      <c r="CQ32" s="33"/>
+      <c r="CR32" s="33"/>
+      <c r="CS32" s="33"/>
+      <c r="CT32" s="33"/>
     </row>
     <row r="33" spans="2:98" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="126"/>
-      <c r="C33" s="102"/>
-      <c r="D33" s="102"/>
-      <c r="E33" s="102"/>
-      <c r="F33" s="102"/>
-      <c r="G33" s="127"/>
-      <c r="H33" s="127"/>
-      <c r="I33" s="127"/>
-      <c r="J33" s="127"/>
-      <c r="K33" s="127"/>
-      <c r="L33" s="127"/>
-      <c r="M33" s="127"/>
-      <c r="N33" s="127"/>
-      <c r="O33" s="127"/>
-      <c r="P33" s="127"/>
-      <c r="Q33" s="127"/>
-      <c r="R33" s="127"/>
-      <c r="S33" s="127"/>
-      <c r="T33" s="127"/>
-      <c r="U33" s="127"/>
-      <c r="V33" s="127"/>
-      <c r="W33" s="127"/>
-      <c r="X33" s="127"/>
-      <c r="Y33" s="127"/>
-      <c r="Z33" s="127"/>
-      <c r="AA33" s="127"/>
-      <c r="AB33" s="127"/>
-      <c r="AC33" s="127"/>
-      <c r="AD33" s="127"/>
-      <c r="AE33" s="127"/>
-      <c r="AF33" s="127"/>
-      <c r="AG33" s="127"/>
-      <c r="AH33" s="127"/>
-      <c r="AI33" s="127"/>
-      <c r="AJ33" s="127"/>
-      <c r="AK33" s="127"/>
-      <c r="AL33" s="102"/>
-      <c r="AM33" s="102"/>
-      <c r="AN33" s="102"/>
-      <c r="AO33" s="102"/>
-      <c r="AP33" s="102"/>
-      <c r="AQ33" s="102"/>
-      <c r="AR33" s="102"/>
-      <c r="AS33" s="102"/>
-      <c r="AT33" s="102"/>
-      <c r="AU33" s="102"/>
-      <c r="AV33" s="102"/>
-      <c r="AW33" s="102"/>
-      <c r="AX33" s="102"/>
-      <c r="AY33" s="102"/>
-      <c r="AZ33" s="102"/>
-      <c r="BA33" s="102"/>
-      <c r="BB33" s="102"/>
-      <c r="BC33" s="102"/>
-      <c r="BD33" s="102"/>
-      <c r="BE33" s="102"/>
-      <c r="BF33" s="102"/>
-      <c r="BG33" s="102"/>
-      <c r="BH33" s="102"/>
-      <c r="BI33" s="102"/>
-      <c r="BJ33" s="102"/>
-      <c r="BK33" s="102"/>
-      <c r="BL33" s="102"/>
-      <c r="BM33" s="102"/>
-      <c r="BN33" s="102"/>
-      <c r="BO33" s="102"/>
-      <c r="BP33" s="102"/>
-      <c r="BQ33" s="102"/>
-      <c r="BR33" s="102"/>
-      <c r="BS33" s="102"/>
-      <c r="BT33" s="102"/>
-      <c r="BU33" s="102"/>
-      <c r="BV33" s="102"/>
-      <c r="BW33" s="102"/>
-      <c r="BX33" s="102"/>
-      <c r="BY33" s="102"/>
-      <c r="BZ33" s="102"/>
-      <c r="CA33" s="102"/>
-      <c r="CB33" s="102"/>
-      <c r="CC33" s="102"/>
-      <c r="CD33" s="102"/>
-      <c r="CE33" s="102"/>
-      <c r="CF33" s="102"/>
-      <c r="CG33" s="102"/>
-      <c r="CH33" s="102"/>
-      <c r="CI33" s="102"/>
-      <c r="CJ33" s="102"/>
-      <c r="CK33" s="102"/>
-      <c r="CL33" s="102"/>
-      <c r="CM33" s="102"/>
-      <c r="CN33" s="102"/>
-      <c r="CO33" s="102"/>
-      <c r="CP33" s="102"/>
-      <c r="CQ33" s="102"/>
-      <c r="CR33" s="102"/>
-      <c r="CS33" s="102"/>
-      <c r="CT33" s="102"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="57"/>
+      <c r="P33" s="57"/>
+      <c r="Q33" s="57"/>
+      <c r="R33" s="57"/>
+      <c r="S33" s="57"/>
+      <c r="T33" s="57"/>
+      <c r="U33" s="57"/>
+      <c r="V33" s="57"/>
+      <c r="W33" s="57"/>
+      <c r="X33" s="57"/>
+      <c r="Y33" s="57"/>
+      <c r="Z33" s="57"/>
+      <c r="AA33" s="57"/>
+      <c r="AB33" s="57"/>
+      <c r="AC33" s="57"/>
+      <c r="AD33" s="57"/>
+      <c r="AE33" s="57"/>
+      <c r="AF33" s="57"/>
+      <c r="AG33" s="57"/>
+      <c r="AH33" s="57"/>
+      <c r="AI33" s="57"/>
+      <c r="AJ33" s="57"/>
+      <c r="AK33" s="57"/>
+      <c r="AL33" s="33"/>
+      <c r="AM33" s="33"/>
+      <c r="AN33" s="33"/>
+      <c r="AO33" s="33"/>
+      <c r="AP33" s="33"/>
+      <c r="AQ33" s="33"/>
+      <c r="AR33" s="33"/>
+      <c r="AS33" s="33"/>
+      <c r="AT33" s="33"/>
+      <c r="AU33" s="33"/>
+      <c r="AV33" s="33"/>
+      <c r="AW33" s="33"/>
+      <c r="AX33" s="33"/>
+      <c r="AY33" s="33"/>
+      <c r="AZ33" s="33"/>
+      <c r="BA33" s="33"/>
+      <c r="BB33" s="33"/>
+      <c r="BC33" s="33"/>
+      <c r="BD33" s="33"/>
+      <c r="BE33" s="33"/>
+      <c r="BF33" s="33"/>
+      <c r="BG33" s="33"/>
+      <c r="BH33" s="33"/>
+      <c r="BI33" s="33"/>
+      <c r="BJ33" s="33"/>
+      <c r="BK33" s="33"/>
+      <c r="BL33" s="33"/>
+      <c r="BM33" s="33"/>
+      <c r="BN33" s="33"/>
+      <c r="BO33" s="33"/>
+      <c r="BP33" s="33"/>
+      <c r="BQ33" s="33"/>
+      <c r="BR33" s="33"/>
+      <c r="BS33" s="33"/>
+      <c r="BT33" s="33"/>
+      <c r="BU33" s="33"/>
+      <c r="BV33" s="33"/>
+      <c r="BW33" s="33"/>
+      <c r="BX33" s="33"/>
+      <c r="BY33" s="33"/>
+      <c r="BZ33" s="33"/>
+      <c r="CA33" s="33"/>
+      <c r="CB33" s="33"/>
+      <c r="CC33" s="33"/>
+      <c r="CD33" s="33"/>
+      <c r="CE33" s="33"/>
+      <c r="CF33" s="33"/>
+      <c r="CG33" s="33"/>
+      <c r="CH33" s="33"/>
+      <c r="CI33" s="33"/>
+      <c r="CJ33" s="33"/>
+      <c r="CK33" s="33"/>
+      <c r="CL33" s="33"/>
+      <c r="CM33" s="33"/>
+      <c r="CN33" s="33"/>
+      <c r="CO33" s="33"/>
+      <c r="CP33" s="33"/>
+      <c r="CQ33" s="33"/>
+      <c r="CR33" s="33"/>
+      <c r="CS33" s="33"/>
+      <c r="CT33" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="CM4:CS4"/>
-    <mergeCell ref="AW4:BC4"/>
-    <mergeCell ref="BD4:BJ4"/>
-    <mergeCell ref="BK4:BQ4"/>
-    <mergeCell ref="BR4:BX4"/>
-    <mergeCell ref="BY4:CE4"/>
-    <mergeCell ref="CF4:CL4"/>
     <mergeCell ref="AP4:AV4"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="B4:B5"/>
@@ -10307,6 +10294,13 @@
     <mergeCell ref="U4:AA4"/>
     <mergeCell ref="AB4:AH4"/>
     <mergeCell ref="AI4:AO4"/>
+    <mergeCell ref="CM4:CS4"/>
+    <mergeCell ref="AW4:BC4"/>
+    <mergeCell ref="BD4:BJ4"/>
+    <mergeCell ref="BK4:BQ4"/>
+    <mergeCell ref="BR4:BX4"/>
+    <mergeCell ref="BY4:CE4"/>
+    <mergeCell ref="CF4:CL4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="G6:CS41">
